--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_8_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{05BEAEA2-6A2F-4741-AE99-4729EDC813A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A107595E-E8AE-4385-A26A-F5427270776A}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{5F8D299F-6166-4DE7-B783-485A6DC645C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E10300C-18F5-4B5E-8A02-51F9225CA8AD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-20955" yWindow="2355" windowWidth="19185" windowHeight="11265" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="1380">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -1898,9 +1898,6 @@
     <t>A01 - Crop and animal production, hunting and related service activities</t>
   </si>
   <si>
-    <t>Afforestation</t>
-  </si>
-  <si>
     <t>American Carbon Registry (ACR)</t>
   </si>
   <si>
@@ -1931,9 +1928,6 @@
     <t>A02 - Forestry and logging</t>
   </si>
   <si>
-    <t>Avoided Conversion</t>
-  </si>
-  <si>
     <t>ART Registry</t>
   </si>
   <si>
@@ -1967,9 +1961,6 @@
     <t>A03 - Fishing and aquaculture</t>
   </si>
   <si>
-    <t>Change of Fuel or Raw Materials</t>
-  </si>
-  <si>
     <t>Biocarbon Registry (BCR)</t>
   </si>
   <si>
@@ -2000,9 +1991,6 @@
     <t>B05 - Mining of coal and lignite</t>
   </si>
   <si>
-    <t>Coal Mine Methane</t>
-  </si>
-  <si>
     <t>Carbon Assets Trading System (CATS)</t>
   </si>
   <si>
@@ -2030,9 +2018,6 @@
     <t>B06 - Extraction of crude petroleum and natural gas</t>
   </si>
   <si>
-    <t>Conservation</t>
-  </si>
-  <si>
     <t>CDM Registry</t>
   </si>
   <si>
@@ -2057,9 +2042,6 @@
     <t>B07 - Mining of metal ores</t>
   </si>
   <si>
-    <t>Energy Demand</t>
-  </si>
-  <si>
     <t>Chile National Registry</t>
   </si>
   <si>
@@ -2078,9 +2060,6 @@
     <t>B08 - Other mining and quarrying</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>Climate Action Reserve (CAR)</t>
   </si>
   <si>
@@ -2102,9 +2081,6 @@
     <t>B09 - Mining support service activities</t>
   </si>
   <si>
-    <t>GHG Management</t>
-  </si>
-  <si>
     <t>Costa Rica National Registry</t>
   </si>
   <si>
@@ -2126,9 +2102,6 @@
     <t>C10 - Manufacture of food products</t>
   </si>
   <si>
-    <t>Improved Forest Management</t>
-  </si>
-  <si>
     <t>Covalent Registry</t>
   </si>
   <si>
@@ -2150,9 +2123,6 @@
     <t>C11 - Manufacture of beverages</t>
   </si>
   <si>
-    <t>Landfill Gas Capture/Combustion</t>
-  </si>
-  <si>
     <t>Cultivo</t>
   </si>
   <si>
@@ -2165,15 +2135,9 @@
     <t>GIS Advisory</t>
   </si>
   <si>
-    <t>Pre-registry</t>
-  </si>
-  <si>
     <t>C12 - Manufacture of tobacco products</t>
   </si>
   <si>
-    <t>Livestock</t>
-  </si>
-  <si>
     <t>EcoRegistry</t>
   </si>
   <si>
@@ -2192,9 +2156,6 @@
     <t>C13 - Manufacture of textiles</t>
   </si>
   <si>
-    <t>Nitrogen Management</t>
-  </si>
-  <si>
     <t>Equitable Earth</t>
   </si>
   <si>
@@ -2213,9 +2174,6 @@
     <t>C14 - Manufacture of wearing apparel</t>
   </si>
   <si>
-    <t>Organic Waste Composting</t>
-  </si>
-  <si>
     <t>Global Carbon Council (GCC)</t>
   </si>
   <si>
@@ -2231,9 +2189,6 @@
     <t>C15 - Manufacture of leather and related products</t>
   </si>
   <si>
-    <t>Organic Waste Digestion</t>
-  </si>
-  <si>
     <t>Global Carbon Market Utility (GCMU)</t>
   </si>
   <si>
@@ -2249,9 +2204,6 @@
     <t>C16 - Manufacture of wood and of products of wood and cork, except furniture; manufacture of articles of straw and plaiting materials</t>
   </si>
   <si>
-    <t>Ozone Depleting Substances</t>
-  </si>
-  <si>
     <t>Gold Standard</t>
   </si>
   <si>
@@ -2270,9 +2222,6 @@
     <t>C17 - Manufacture of paper and paper products</t>
   </si>
   <si>
-    <t>Plastic Waste Collection</t>
-  </si>
-  <si>
     <t>Isometric</t>
   </si>
   <si>
@@ -2291,9 +2240,6 @@
     <t>C18 - Printing and reproduction of recorded media</t>
   </si>
   <si>
-    <t>Plastic Waste Recycling</t>
-  </si>
-  <si>
     <t>Joint Crediting Mechanism</t>
   </si>
   <si>
@@ -2309,9 +2255,6 @@
     <t>C19 - Manufacture of coke and refined petroleum products</t>
   </si>
   <si>
-    <t>REDD+: Reduced Emissions from Deforestation and Degradation</t>
-  </si>
-  <si>
     <t>Mexico National Registry</t>
   </si>
   <si>
@@ -2327,9 +2270,6 @@
     <t>C20 - Manufacture of chemicals and chemical products</t>
   </si>
   <si>
-    <t>Reforestation and Revegetation</t>
-  </si>
-  <si>
     <t>MoorFutures</t>
   </si>
   <si>
@@ -2342,1769 +2282,1907 @@
     <t>C21 - Manufacture of basic pharmaceutical products and pharmaceutical preparations</t>
   </si>
   <si>
+    <t>Natural Forest Standard (NFS) Registry</t>
+  </si>
+  <si>
+    <t>Ecosystem Restoration Standard</t>
+  </si>
+  <si>
+    <t>BCR0003_Quantification of GHG emission Reductions. Activities that prevent land use change in high mountain ecosystems</t>
+  </si>
+  <si>
+    <t>C22 - Manufacture of rubber and plastic products</t>
+  </si>
+  <si>
+    <t>Open Carbon Protocol</t>
+  </si>
+  <si>
+    <t>Global Carbon Council</t>
+  </si>
+  <si>
+    <t>BCR0004_Quantification of GHG emission reductions. Activities that avoid Land Use change in continental wetlands</t>
+  </si>
+  <si>
+    <t>C23 - Manufacture of other non-metallic mineral products</t>
+  </si>
+  <si>
+    <t>Open Earth Foundation</t>
+  </si>
+  <si>
+    <t>BCR0005_Quantification of GHG Emissions Reduction. Activities that prevent Land Use Change in Natural Savannas</t>
+  </si>
+  <si>
+    <t>C24 - Manufacture of basic metals</t>
+  </si>
+  <si>
+    <t>PACM Registry</t>
+  </si>
+  <si>
+    <t>Inclusive Carbon Standard</t>
+  </si>
+  <si>
+    <t>BCR0006_Quantification of GHG Emission Reductions by converting gasoline vehicles to natural gas</t>
+  </si>
+  <si>
+    <t>C25 - Manufacture of fabricated metal products, except machinery and equipment</t>
+  </si>
+  <si>
+    <t>Pakistan National Registry</t>
+  </si>
+  <si>
+    <t>International Carbon Registry</t>
+  </si>
+  <si>
+    <t>CAR - Adipic Acid Production</t>
+  </si>
+  <si>
+    <t>C26 - Manufacture of computer, electronic and optical products</t>
+  </si>
+  <si>
+    <t>Plan Vivo</t>
+  </si>
+  <si>
+    <t>CAR - Biochar</t>
+  </si>
+  <si>
+    <t>C27 - Manufacture of electrical equipment</t>
+  </si>
+  <si>
+    <t>Puro Standard and Registry</t>
+  </si>
+  <si>
+    <t>IUCN UK Peatland Programme</t>
+  </si>
+  <si>
+    <t>CAR - Canada Grassland</t>
+  </si>
+  <si>
+    <t>C28 - Manufacture of machinery and equipment n.e.c.</t>
+  </si>
+  <si>
+    <t>Registry of China Certified Emission Reduction Trading System</t>
+  </si>
+  <si>
+    <t>CAR - Coal Mine Methane</t>
+  </si>
+  <si>
+    <t>C29 - Manufacture of motor vehicles, trailers and semi-trailers</t>
+  </si>
+  <si>
+    <t>Riverse</t>
+  </si>
+  <si>
+    <t>CAR - Forest</t>
+  </si>
+  <si>
+    <t>C30 - Manufacture of other transport equipment</t>
+  </si>
+  <si>
+    <t>Royal Kingdom of Bhutan</t>
+  </si>
+  <si>
+    <t>CAR - Grassland</t>
+  </si>
+  <si>
+    <t>C31 - Manufacture of furniture</t>
+  </si>
+  <si>
+    <t>Singapore National Registry</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Boiler Efficiency</t>
+  </si>
+  <si>
+    <t>C32 - Other manufacturing</t>
+  </si>
+  <si>
+    <t>Sweden National Registry</t>
+  </si>
+  <si>
+    <t>PACM</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Forest</t>
+  </si>
+  <si>
+    <t>C33 - Repair, maintenance and installation of machinery and equipment</t>
+  </si>
+  <si>
+    <t>Switzerland National Registry</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Halocarbon</t>
+  </si>
+  <si>
+    <t>D35 - Electricity, gas, steam and air conditioning supply</t>
+  </si>
+  <si>
+    <t>UK Land Carbon Registry</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Landfill</t>
+  </si>
+  <si>
+    <t>E36 - Water collection, treatment and supply</t>
+  </si>
+  <si>
+    <t>UNFCCC International Registry</t>
+  </si>
+  <si>
+    <t>Puro.earth</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Livestock</t>
+  </si>
+  <si>
+    <t>E37 - Sewerage</t>
+  </si>
+  <si>
+    <t>Verra</t>
+  </si>
+  <si>
+    <t>CAR - Mexico Ozone Depleting Substances</t>
+  </si>
+  <si>
+    <t>E38 - Waste collection, treatment and disposal, and recovery activities</t>
+  </si>
+  <si>
+    <t>CAR - Nitric Acid Production</t>
+  </si>
+  <si>
+    <t>E39 - Remediation and other waste management service activities</t>
+  </si>
+  <si>
+    <t>RUN Carbon Crediting Program</t>
+  </si>
+  <si>
+    <t>CAR - Nitrogen Management</t>
+  </si>
+  <si>
+    <t>F41 - Construction of residential and non-residential buildings</t>
+  </si>
+  <si>
+    <t>CAR - Organic Waste Composting</t>
+  </si>
+  <si>
+    <t>F42 - Civil engineering</t>
+  </si>
+  <si>
+    <t>SOCIAL CARBON Registry</t>
+  </si>
+  <si>
+    <t>CAR - Organic Waste Digestion</t>
+  </si>
+  <si>
+    <t>F43 - Specialized construction activities</t>
+  </si>
+  <si>
+    <t>CAR - Ozone Depleting Substances</t>
+  </si>
+  <si>
+    <t>G46 - Wholesale trade</t>
+  </si>
+  <si>
+    <t>CAR - Rice Cultivation</t>
+  </si>
+  <si>
+    <t>G47 - Retail trade</t>
+  </si>
+  <si>
+    <t>Trusted Carbon</t>
+  </si>
+  <si>
+    <t>CAR - Soil Enrichment</t>
+  </si>
+  <si>
+    <t>H49 - Land transport and transport via pipelines</t>
+  </si>
+  <si>
+    <t>CAR - U.S. Landfill</t>
+  </si>
+  <si>
+    <t>H50 - Water transport</t>
+  </si>
+  <si>
+    <t>CAR - U.S. Livestock</t>
+  </si>
+  <si>
+    <t>H51 - Air transport</t>
+  </si>
+  <si>
+    <t>CAR - Urban Forest Management</t>
+  </si>
+  <si>
+    <t>H52 - Warehousing and support activities for transportation</t>
+  </si>
+  <si>
+    <t>CAR - Urban Tree Planting</t>
+  </si>
+  <si>
+    <t>H53 - Postal and courier activities</t>
+  </si>
+  <si>
+    <t>CCB - M/E-ER01</t>
+  </si>
+  <si>
+    <t>I55 - Accommodation</t>
+  </si>
+  <si>
+    <t>CCB - M/LU-REDD+</t>
+  </si>
+  <si>
+    <t>I56 - Food and beverage service activities</t>
+  </si>
+  <si>
+    <t>CCB - M/UT/B-H01</t>
+  </si>
+  <si>
+    <t>J58 - Publishing activities</t>
+  </si>
+  <si>
+    <t>CCB - M/UT/F-A01</t>
+  </si>
+  <si>
+    <t>J59 - Motion picture, video and television programme production, sound recording and music publishing activities</t>
+  </si>
+  <si>
+    <t>CCER - Energy-Saving Highway Tunnel Lighting System (CCER-07-001)</t>
+  </si>
+  <si>
+    <t>J60 - Programming, broadcasting, news agency and other content distribution activities</t>
+  </si>
+  <si>
+    <t>CCER - Forestation Carbon Sequestration (CCER-14-001)</t>
+  </si>
+  <si>
+    <t>K61 - Telecommunications</t>
+  </si>
+  <si>
+    <t>CCER - Grid-Connected Offshore Wind Power Generation (CCER-01-0022)</t>
+  </si>
+  <si>
+    <t>K62 - Computer programming, consultancy and related activities</t>
+  </si>
+  <si>
+    <t>CCER - Grid-Connected Solar Thermal Power Generation (CCER-01-001)</t>
+  </si>
+  <si>
+    <t>K63 - Computing infrastructure, data processing, hosting, and other information service activities</t>
+  </si>
+  <si>
+    <t>CCER - Mangrove Afforestation (CCER-14-002)</t>
+  </si>
+  <si>
+    <t>L64 - Financial service activities, except insurance and pension funding</t>
+  </si>
+  <si>
+    <t>CCER - Utilization of Low-Concentration Coal Mine Methane and Ventilation Air Methane (CCER-10-001)</t>
+  </si>
+  <si>
+    <t>L65 - Insurance, reinsurance and pension funding, except compulsory social security</t>
+  </si>
+  <si>
+    <t>CDM - ACM0001</t>
+  </si>
+  <si>
+    <t>L66 - Activities auxiliary to financial service and insurance activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0002</t>
+  </si>
+  <si>
+    <t>M68 - Real estate activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0003</t>
+  </si>
+  <si>
+    <t>N69 - Legal and accounting activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0004</t>
+  </si>
+  <si>
+    <t>N70 - Activities of head offices; management consultancy activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0005</t>
+  </si>
+  <si>
+    <t>N71 - Architectural and engineering activities; technical testing and analysis</t>
+  </si>
+  <si>
+    <t>CDM - ACM0006</t>
+  </si>
+  <si>
+    <t>N72 - Scientific research and development </t>
+  </si>
+  <si>
+    <t>CDM - ACM0007</t>
+  </si>
+  <si>
+    <t>N73 - Activities of advertising, market research and public relations</t>
+  </si>
+  <si>
+    <t>CDM - ACM0008</t>
+  </si>
+  <si>
+    <t>N74 - Other professional, scientific and technical activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0009</t>
+  </si>
+  <si>
+    <t>N75 - Veterinary activities </t>
+  </si>
+  <si>
+    <t>CDM - ACM0010</t>
+  </si>
+  <si>
+    <t>O77 - Rental and leasing activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0011</t>
+  </si>
+  <si>
+    <t>O78 - Employment activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0012</t>
+  </si>
+  <si>
+    <t>O79 - Travel agency, tour operator, and other travel related activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0013</t>
+  </si>
+  <si>
+    <t>O80 - Investigation and security activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0014</t>
+  </si>
+  <si>
+    <t>O81 - Services to buildings and landscape activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0015</t>
+  </si>
+  <si>
+    <t>O82 - Office administrative, office support and other business support activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0016</t>
+  </si>
+  <si>
+    <t>P84 - Public administration and defence; compulsory social security</t>
+  </si>
+  <si>
+    <t>CDM - ACM0017</t>
+  </si>
+  <si>
+    <t>Q85 - Education</t>
+  </si>
+  <si>
+    <t>CDM - ACM0018</t>
+  </si>
+  <si>
+    <t>R86 - Human health activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0019</t>
+  </si>
+  <si>
+    <t>R87 - Residential care activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0020</t>
+  </si>
+  <si>
+    <t>R88 - Social work activities without accommodation </t>
+  </si>
+  <si>
+    <t>CDM - ACM0021</t>
+  </si>
+  <si>
+    <t>S90 - Arts creation and performing arts activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0022</t>
+  </si>
+  <si>
+    <t>S91 - Library, archives, museum and other cultural activities </t>
+  </si>
+  <si>
+    <t>CDM - ACM0023</t>
+  </si>
+  <si>
+    <t>S92 - Gambling and betting activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0024</t>
+  </si>
+  <si>
+    <t>S93 - Sports activities and amusement and recreation activities</t>
+  </si>
+  <si>
+    <t>CDM - ACM0025</t>
+  </si>
+  <si>
+    <t>T94 - Activities of membership organizations</t>
+  </si>
+  <si>
+    <t>CDM - ACM0026</t>
+  </si>
+  <si>
+    <t>T95 - Repair and maintenance of computers, personal and household goods, and motor vehicles and motorcycles</t>
+  </si>
+  <si>
+    <t>CDM - AM0001</t>
+  </si>
+  <si>
+    <t>T96 - Personal service activities</t>
+  </si>
+  <si>
+    <t>CDM - AM0007</t>
+  </si>
+  <si>
+    <t>U97 - Activities of households as employers of domestic personnel</t>
+  </si>
+  <si>
+    <t>CDM - AM0009</t>
+  </si>
+  <si>
+    <t>U98 - Undifferentiated goods- and services-producing activities of private households for own use</t>
+  </si>
+  <si>
+    <t>CDM - AM0017</t>
+  </si>
+  <si>
+    <t>V99 - Activities of extraterritorial organizations and bodies </t>
+  </si>
+  <si>
+    <t>CDM - AM0018</t>
+  </si>
+  <si>
+    <t>CDM - AM0019</t>
+  </si>
+  <si>
+    <t>CDM - AM0020</t>
+  </si>
+  <si>
+    <t>CDM - AM0021</t>
+  </si>
+  <si>
+    <t>CDM - AM0023</t>
+  </si>
+  <si>
+    <t>CDM - AM0026</t>
+  </si>
+  <si>
+    <t>CDM - AM0027</t>
+  </si>
+  <si>
+    <t>CDM - AM0028</t>
+  </si>
+  <si>
+    <t>CDM - AM0030</t>
+  </si>
+  <si>
+    <t>CDM - AM0031</t>
+  </si>
+  <si>
+    <t>CDM - AM0035</t>
+  </si>
+  <si>
+    <t>CDM - AM0036</t>
+  </si>
+  <si>
+    <t>CDM - AM0037</t>
+  </si>
+  <si>
+    <t>CDM - AM0038</t>
+  </si>
+  <si>
+    <t>CDM - AM0043</t>
+  </si>
+  <si>
+    <t>CDM - AM0044</t>
+  </si>
+  <si>
+    <t>CDM - AM0045</t>
+  </si>
+  <si>
+    <t>CDM - AM0046</t>
+  </si>
+  <si>
+    <t>CDM - AM0048</t>
+  </si>
+  <si>
+    <t>CDM - AM0049</t>
+  </si>
+  <si>
+    <t>CDM - AM0050</t>
+  </si>
+  <si>
+    <t>CDM - AM0052</t>
+  </si>
+  <si>
+    <t>CDM - AM0053</t>
+  </si>
+  <si>
+    <t>CDM - AM0055</t>
+  </si>
+  <si>
+    <t>CDM - AM0056</t>
+  </si>
+  <si>
+    <t>CDM - AM0057</t>
+  </si>
+  <si>
+    <t>CDM - AM0058</t>
+  </si>
+  <si>
+    <t>CDM - AM0059</t>
+  </si>
+  <si>
+    <t>CDM - AM0060</t>
+  </si>
+  <si>
+    <t>CDM - AM0061</t>
+  </si>
+  <si>
+    <t>CDM - AM0062</t>
+  </si>
+  <si>
+    <t>CDM - AM0063</t>
+  </si>
+  <si>
+    <t>CDM - AM0064</t>
+  </si>
+  <si>
+    <t>CDM - AM0065</t>
+  </si>
+  <si>
+    <t>CDM - AM0066</t>
+  </si>
+  <si>
+    <t>CDM - AM0067</t>
+  </si>
+  <si>
+    <t>CDM - AM0068</t>
+  </si>
+  <si>
+    <t>CDM - AM0069</t>
+  </si>
+  <si>
+    <t>CDM - AM0070</t>
+  </si>
+  <si>
+    <t>CDM - AM0071</t>
+  </si>
+  <si>
+    <t>CDM - AM0072</t>
+  </si>
+  <si>
+    <t>CDM - AM0073</t>
+  </si>
+  <si>
+    <t>CDM - AM0074</t>
+  </si>
+  <si>
+    <t>CDM - AM0075</t>
+  </si>
+  <si>
+    <t>CDM - AM0076</t>
+  </si>
+  <si>
+    <t>CDM - AM0077</t>
+  </si>
+  <si>
+    <t>CDM - AM0078</t>
+  </si>
+  <si>
+    <t>CDM - AM0079</t>
+  </si>
+  <si>
+    <t>CDM - AM0080</t>
+  </si>
+  <si>
+    <t>CDM - AM0081</t>
+  </si>
+  <si>
+    <t>CDM - AM0082</t>
+  </si>
+  <si>
+    <t>CDM - AM0083</t>
+  </si>
+  <si>
+    <t>CDM - AM0084</t>
+  </si>
+  <si>
+    <t>CDM - AM0086</t>
+  </si>
+  <si>
+    <t>CDM - AM0088</t>
+  </si>
+  <si>
+    <t>CDM - AM0089</t>
+  </si>
+  <si>
+    <t>CDM - AM0090</t>
+  </si>
+  <si>
+    <t>CDM - AM0091</t>
+  </si>
+  <si>
+    <t>CDM - AM0092</t>
+  </si>
+  <si>
+    <t>CDM - AM0093</t>
+  </si>
+  <si>
+    <t>CDM - AM0094</t>
+  </si>
+  <si>
+    <t>CDM - AM0095</t>
+  </si>
+  <si>
+    <t>CDM - AM0096</t>
+  </si>
+  <si>
+    <t>CDM - AM0097</t>
+  </si>
+  <si>
+    <t>CDM - AM0098</t>
+  </si>
+  <si>
+    <t>CDM - AM0099</t>
+  </si>
+  <si>
+    <t>CDM - AM0100</t>
+  </si>
+  <si>
+    <t>CDM - AM0101</t>
+  </si>
+  <si>
+    <t>CDM - AM0103</t>
+  </si>
+  <si>
+    <t>CDM - AM0104</t>
+  </si>
+  <si>
+    <t>CDM - AM0105</t>
+  </si>
+  <si>
+    <t>CDM - AM0106</t>
+  </si>
+  <si>
+    <t>CDM - AM0107</t>
+  </si>
+  <si>
+    <t>CDM - AM0108</t>
+  </si>
+  <si>
+    <t>CDM - AM0109</t>
+  </si>
+  <si>
+    <t>CDM - AM0110</t>
+  </si>
+  <si>
+    <t>CDM - AM0111</t>
+  </si>
+  <si>
+    <t>CDM - AM0112</t>
+  </si>
+  <si>
+    <t>CDM - AM0113</t>
+  </si>
+  <si>
+    <t>CDM - AM0114</t>
+  </si>
+  <si>
+    <t>CDM - AM0115</t>
+  </si>
+  <si>
+    <t>CDM - AM0116</t>
+  </si>
+  <si>
+    <t>CDM - AM0117</t>
+  </si>
+  <si>
+    <t>CDM - AM0118</t>
+  </si>
+  <si>
+    <t>CDM - AM0119</t>
+  </si>
+  <si>
+    <t>CDM - AM0120</t>
+  </si>
+  <si>
+    <t>CDM - AM0121</t>
+  </si>
+  <si>
+    <t>CDM - AM0122</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.A.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.B.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.C.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.D.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.E.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.F.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.G.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.H.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.I.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.J.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.K.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.L.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-I.M.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.A.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.B.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.C.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.D.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.E.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.F.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.G.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.H.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.I.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.J.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.K.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.L.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.M.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.N.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.O.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.P.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.Q.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.R.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.S.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-II.T.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.A.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AA.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AB.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AC.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AD.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AE.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AF.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AG.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AH.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AI.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AJ.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AK.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AL.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AM.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AN.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AO.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AP.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AQ.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AR.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AS.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AT.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AU.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AV.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AW.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AX.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.AY.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.B.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BA.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BB.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BC.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BD.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BE.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BF.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BG.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BH.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BI.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BJ.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BK.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BL.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BM.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BN.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BO.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BP.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.BQ.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.C.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.D.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.E.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.F.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.G.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.H.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.I.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.J.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.K.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.L.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.M.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.N.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.O.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.P.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.Q.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.R.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.S.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.T.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.U.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.V.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.W.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.X.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.Y.</t>
+  </si>
+  <si>
+    <t>CDM - AMS-III.Z.</t>
+  </si>
+  <si>
+    <t>CDM - AR-ACM0003</t>
+  </si>
+  <si>
+    <t>CDM - AR-AM0014</t>
+  </si>
+  <si>
+    <t>CDM - AR-AMS0003</t>
+  </si>
+  <si>
+    <t>CDM - AR-AMS0007</t>
+  </si>
+  <si>
+    <t>GS - AFFORESTATION/REFORESTATION GHG EMISSIONS REDUCTION &amp; SEQUESTRATION</t>
+  </si>
+  <si>
+    <t>GS - CARBON MINERALISATION USING REACTIVE MINERAL WASTE</t>
+  </si>
+  <si>
+    <t>GS - CARBON SEQUESTRATION THROUGH ACCELERATED CARBONATION OF CONCRETE AGGREGATE </t>
+  </si>
+  <si>
+    <t>GS - EMISSIONS REDUCTIONS FROM SAFE DRINKING WATER SUPPLY</t>
+  </si>
+  <si>
+    <t>GS - METHANE EMISSIONS REDUCTION BY ADJUSTED WATER MANAGEMENT PRACTICE IN RICE CULTIVATION</t>
+  </si>
+  <si>
+    <t>GS - METHANE EMISSIONS REDUCTION FROM ENTERIC FERMENTATION IN BEEF CATTLE THROUGH APPLICATION OF FEED SUPPLEMENTS</t>
+  </si>
+  <si>
+    <t>GS - METHODOLOGY FOR ANIMAL MANURE MANAGEMENT AND BIOGAS USE FOR THERMAL ENERGY GENERATION</t>
+  </si>
+  <si>
+    <t>GS - METHODOLOGY FOR BIOMASS FERMENTATION WITH CARBON CAPTURE AND GEOLOGIC STORAGE</t>
+  </si>
+  <si>
+    <t>GS - METHODOLOGY FOR COLLECTION OF MACROALGAE TO AVOID EMISSIONS FROM DECOMPOSITION</t>
+  </si>
+  <si>
+    <t>GS - METHODOLOGY FOR METERED &amp; MEASURED ENERGY COOKING DEVICES</t>
+  </si>
+  <si>
+    <t>GS - METHODOLOGY FOR RETROFIT ENERGY EFFICIENCY MEASURES IN SHIPPING </t>
+  </si>
+  <si>
+    <t>GS - REDUCED EMISSIONS FROM COOKING AND HEATING – TECHNOLOGIES AND PRACTICES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION (TPDDTEC)</t>
+  </si>
+  <si>
+    <t>GS - SOIL ORGANIC CARBON ACTIVITY MODULE FOR APPLICATION OF ORGANIC SOIL IMPROVERS FROM PULP AND PAPER MILL SLUDGES</t>
+  </si>
+  <si>
+    <t>GS - SOIL ORGANIC CARBON FRAMEWORK METHODOLOGY</t>
+  </si>
+  <si>
+    <t>GS - SUSTAINABLE MANAGEMENT OF MANGROVES</t>
+  </si>
+  <si>
+    <t>GS - THE GOLD STANDARD SIMPLIFIED METHODOLOGY FOR CLEAN AND EFFICIENT COOKSTOVES</t>
+  </si>
+  <si>
+    <t>GS - TPDDTEC - TECHNOLOGIES AND PRACTICES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION</t>
+  </si>
+  <si>
+    <t>GS - TPDDTEC - TECHNOLOGIES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION</t>
+  </si>
+  <si>
+    <t>ISO - Biochar Production and Storage</t>
+  </si>
+  <si>
+    <t>ISO - Biogenic Carbon Capture and Storage</t>
+  </si>
+  <si>
+    <t>ISO - Biomass Geological Storage</t>
+  </si>
+  <si>
+    <t>ISO - Bio-oil Geological Storage</t>
+  </si>
+  <si>
+    <t>ISO - Direct Air Capture</t>
+  </si>
+  <si>
+    <t>ISO - Direct Ocean Capture and Storage</t>
+  </si>
+  <si>
+    <t>ISO - Electrolytic Seawater Mineralization</t>
+  </si>
+  <si>
+    <t>ISO - Enhanced Weathering</t>
+  </si>
+  <si>
+    <t>ISO - Enhanced Weathering in Agriculture</t>
+  </si>
+  <si>
+    <t>ISO - Mineralization</t>
+  </si>
+  <si>
+    <t>ISO - Ocean Alkalinity Enhancement from Coastal Outfalls</t>
+  </si>
+  <si>
+    <t>ISO - Open System Ex-Situ Mineralization</t>
+  </si>
+  <si>
+    <t>ISO - Reforestation</t>
+  </si>
+  <si>
+    <t>ISO - River Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>ISO - Subsurface Biomass Carbon Removal and Storage</t>
+  </si>
+  <si>
+    <t>ISO - Wastewater Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>JCM - BD_AM001</t>
+  </si>
+  <si>
+    <t>JCM - BD_AM002</t>
+  </si>
+  <si>
+    <t>JCM - BD_AM003</t>
+  </si>
+  <si>
+    <t>JCM - CL_AM001</t>
+  </si>
+  <si>
+    <t>JCM - CL_AM002</t>
+  </si>
+  <si>
+    <t>JCM - CR_AM001</t>
+  </si>
+  <si>
+    <t>JCM - CR_AM002</t>
+  </si>
+  <si>
+    <t>JCM - CR_AM003</t>
+  </si>
+  <si>
+    <t>JCM - ET_AM001</t>
+  </si>
+  <si>
+    <t>JCM - ET_AM002</t>
+  </si>
+  <si>
+    <t>JCM - ET_AM003</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM001</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM002</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM003</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM004</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM005</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM006</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM007</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM008</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM009</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM010</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM011</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM012</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM013</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM014</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM015</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM016</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM017</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM018</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM019</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM020</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM021</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM022</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM023</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM024</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM025</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM026</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM027</t>
+  </si>
+  <si>
+    <t>JCM - ID_AM028</t>
+  </si>
+  <si>
+    <t>JCM - KE_AM001</t>
+  </si>
+  <si>
+    <t>JCM - KE_AM002</t>
+  </si>
+  <si>
+    <t>JCM - KE_AM003</t>
+  </si>
+  <si>
+    <t>JCM - KH_AM001</t>
+  </si>
+  <si>
+    <t>JCM - KH_AM002</t>
+  </si>
+  <si>
+    <t>JCM - KH_AM003</t>
+  </si>
+  <si>
+    <t>JCM - KH_AM004</t>
+  </si>
+  <si>
+    <t>JCM - KH_AM005</t>
+  </si>
+  <si>
+    <t>JCM - LA_AM001</t>
+  </si>
+  <si>
+    <t>JCM - LA_AM002</t>
+  </si>
+  <si>
+    <t>JCM - LA_AM003</t>
+  </si>
+  <si>
+    <t>JCM - LA_AM004</t>
+  </si>
+  <si>
+    <t>JCM - MM_AM001</t>
+  </si>
+  <si>
+    <t>JCM - MM_AM002</t>
+  </si>
+  <si>
+    <t>JCM - MM_AM003</t>
+  </si>
+  <si>
+    <t>JCM - MM_AM004</t>
+  </si>
+  <si>
+    <t>JCM - MM_AM005</t>
+  </si>
+  <si>
+    <t>JCM - MN_AM001</t>
+  </si>
+  <si>
+    <t>JCM - MN_AM002</t>
+  </si>
+  <si>
+    <t>JCM - MN_AM003</t>
+  </si>
+  <si>
+    <t>JCM - MV_AM001</t>
+  </si>
+  <si>
+    <t>JCM - MV_AM002</t>
+  </si>
+  <si>
+    <t>JCM - MX_AM001</t>
+  </si>
+  <si>
+    <t>JCM - PH_AM001</t>
+  </si>
+  <si>
+    <t>JCM - PH_AM002</t>
+  </si>
+  <si>
+    <t>JCM - PW_AM001</t>
+  </si>
+  <si>
+    <t>JCM - SA_AM001</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM001</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM002</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM003</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM004</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM005</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM006</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM007</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM008</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM009</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM010</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM011</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM012</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM013</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM014</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM015</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM016</t>
+  </si>
+  <si>
+    <t>JCM - TH_AM017</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM001</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM002</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM003</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM004</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM005</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM006</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM007</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM008</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM009</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM010</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM011</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM012</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM013</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM014</t>
+  </si>
+  <si>
+    <t>JCM - VN_AM015</t>
+  </si>
+  <si>
+    <t>NTC 6208</t>
+  </si>
+  <si>
+    <t>PURO - Biochar</t>
+  </si>
+  <si>
+    <t>PURO - Carbonated Materials</t>
+  </si>
+  <si>
+    <t>PURO - Enhanced Rock Weathering</t>
+  </si>
+  <si>
+    <t>PURO - Geologically Stored Carbon</t>
+  </si>
+  <si>
+    <t>PURO - Marine Anoxic Carbon Storage</t>
+  </si>
+  <si>
+    <t>PURO - Terrestrial Storage of Biomass</t>
+  </si>
+  <si>
+    <t>PV - PM001</t>
+  </si>
+  <si>
+    <t>PV - PT001</t>
+  </si>
+  <si>
+    <t>PV - PT002</t>
+  </si>
+  <si>
+    <t>PV - PT003</t>
+  </si>
+  <si>
+    <t>PV - PT004</t>
+  </si>
+  <si>
+    <t>PV - PU001</t>
+  </si>
+  <si>
+    <t>PV - PU002</t>
+  </si>
+  <si>
+    <t>PV - PU003</t>
+  </si>
+  <si>
+    <t>PV - PU004</t>
+  </si>
+  <si>
+    <t>PV - PU005</t>
+  </si>
+  <si>
+    <t>TERO.001</t>
+  </si>
+  <si>
+    <t>TERO.002</t>
+  </si>
+  <si>
+    <t>TERO.003</t>
+  </si>
+  <si>
+    <t>TERO.004</t>
+  </si>
+  <si>
+    <t>TERO.005</t>
+  </si>
+  <si>
+    <t>VCS - VM0001</t>
+  </si>
+  <si>
+    <t>VCS - VM0002</t>
+  </si>
+  <si>
+    <t>VCS - VM0003</t>
+  </si>
+  <si>
+    <t>VCS - VM0004</t>
+  </si>
+  <si>
+    <t>VCS - VM0005</t>
+  </si>
+  <si>
+    <t>VCS - VM0006</t>
+  </si>
+  <si>
+    <t>VCS - VM0007</t>
+  </si>
+  <si>
+    <t>VCS - VM0008</t>
+  </si>
+  <si>
+    <t>VCS - VM0009</t>
+  </si>
+  <si>
+    <t>VCS - VM0010</t>
+  </si>
+  <si>
+    <t>VCS - VM0011</t>
+  </si>
+  <si>
+    <t>VCS - VM0012</t>
+  </si>
+  <si>
+    <t>VCS - VM0013</t>
+  </si>
+  <si>
+    <t>VCS - VM0014</t>
+  </si>
+  <si>
+    <t>VCS - VM0015</t>
+  </si>
+  <si>
+    <t>VCS - VM0016</t>
+  </si>
+  <si>
+    <t>VCS - VM0017</t>
+  </si>
+  <si>
+    <t>VCS - VM0018</t>
+  </si>
+  <si>
+    <t>VCS - VM0019</t>
+  </si>
+  <si>
+    <t>VCS - VM0020</t>
+  </si>
+  <si>
+    <t>VCS - VM0021</t>
+  </si>
+  <si>
+    <t>VCS - VM0022</t>
+  </si>
+  <si>
+    <t>VCS - VM0023</t>
+  </si>
+  <si>
+    <t>VCS - VM0024</t>
+  </si>
+  <si>
+    <t>VCS - VM0025</t>
+  </si>
+  <si>
+    <t>VCS - VM0026</t>
+  </si>
+  <si>
+    <t>VCS - VM0027</t>
+  </si>
+  <si>
+    <t>VCS - VM0028</t>
+  </si>
+  <si>
+    <t>VCS - VM0029</t>
+  </si>
+  <si>
+    <t>VCS - VM0030</t>
+  </si>
+  <si>
+    <t>VCS - VM0031</t>
+  </si>
+  <si>
+    <t>VCS - VM0032</t>
+  </si>
+  <si>
+    <t>VCS - VM0033</t>
+  </si>
+  <si>
+    <t>VCS - VM0034</t>
+  </si>
+  <si>
+    <t>VCS - VM0035</t>
+  </si>
+  <si>
+    <t>VCS - VM0036</t>
+  </si>
+  <si>
+    <t>VCS - VM0037</t>
+  </si>
+  <si>
+    <t>VCS - VM0038</t>
+  </si>
+  <si>
+    <t>VCS - VM0039</t>
+  </si>
+  <si>
+    <t>VCS - VM0040</t>
+  </si>
+  <si>
+    <t>VCS - VM0041</t>
+  </si>
+  <si>
+    <t>VCS - VM0042</t>
+  </si>
+  <si>
+    <t>VCS - VM0043</t>
+  </si>
+  <si>
+    <t>VCS - VM0044</t>
+  </si>
+  <si>
+    <t>VCS - VM0045</t>
+  </si>
+  <si>
+    <t>VCS - VM0046</t>
+  </si>
+  <si>
+    <t>VCS - VM0047</t>
+  </si>
+  <si>
+    <t>VCS - VM0048</t>
+  </si>
+  <si>
+    <t>VCS - VM0049</t>
+  </si>
+  <si>
+    <t>VCS - VM0050</t>
+  </si>
+  <si>
+    <t>VCS - VM0051</t>
+  </si>
+  <si>
+    <t>VCS - VM0052</t>
+  </si>
+  <si>
+    <t>VCS - VMR000</t>
+  </si>
+  <si>
+    <t>VCS - VMR004</t>
+  </si>
+  <si>
+    <t>VCS - VMR005</t>
+  </si>
+  <si>
+    <t>VCS - VMR006</t>
+  </si>
+  <si>
+    <t>VCS - VMR007</t>
+  </si>
+  <si>
+    <t>VCS - VMR008</t>
+  </si>
+  <si>
+    <t>VCS - VMR009</t>
+  </si>
+  <si>
+    <t>VCS - VMR010</t>
+  </si>
+  <si>
+    <t>VCS - VMR012</t>
+  </si>
+  <si>
+    <t>VCS - VMR013</t>
+  </si>
+  <si>
+    <t>VCS - VMR014</t>
+  </si>
+  <si>
+    <t>attestations</t>
+  </si>
+  <si>
+    <t>organization role</t>
+  </si>
+  <si>
+    <t>child labor attestation</t>
+  </si>
+  <si>
+    <t>labor worker attestation</t>
+  </si>
+  <si>
+    <t>legal land ownership attestation</t>
+  </si>
+  <si>
+    <t>human rights attestation</t>
+  </si>
+  <si>
+    <t>issuance status</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Pending Issuance</t>
+  </si>
+  <si>
+    <t>Issuing</t>
+  </si>
+  <si>
+    <t>Pre-issuance</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Validation Type</t>
+  </si>
+  <si>
+    <t>Validation of Project Design Document</t>
+  </si>
+  <si>
+    <t>Validation of Renewal of Credit Period</t>
+  </si>
+  <si>
+    <t>Validation of Post Registration Change</t>
+  </si>
+  <si>
+    <t>Estimation Type</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Estimation Status</t>
+  </si>
+  <si>
+    <t>Unvalidated</t>
+  </si>
+  <si>
+    <t>Superseded</t>
+  </si>
+  <si>
+    <t>Project Crediting Period Type</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Renewable</t>
+  </si>
+  <si>
+    <t>UNFCCC Article 6.2 common nomenclatures (Activity Type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomass Energy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Efficiency own generation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Efficiency supply side </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy distribution </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2 usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal bed/mine methane </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFCs and SF6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afforestation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biogas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waste </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any combination of the above </t>
+  </si>
+  <si>
+    <t>Energy Efficiency households</t>
+  </si>
+  <si>
+    <t>Energy Efficiency Industry</t>
+  </si>
+  <si>
+    <t>Energy Efficiency service</t>
+  </si>
+  <si>
+    <t>Fossil fuel switch</t>
+  </si>
+  <si>
+    <t>Fugitive</t>
+  </si>
+  <si>
+    <t>Geothermal</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Landfill gas</t>
+  </si>
+  <si>
+    <t>Methane avoidance</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
+  <si>
     <t>Reforestation</t>
   </si>
   <si>
-    <t>Natural Forest Standard (NFS) Registry</t>
-  </si>
-  <si>
-    <t>Ecosystem Restoration Standard</t>
-  </si>
-  <si>
-    <t>BCR0003_Quantification of GHG emission Reductions. Activities that prevent land use change in high mountain ecosystems</t>
-  </si>
-  <si>
-    <t>C22 - Manufacture of rubber and plastic products</t>
-  </si>
-  <si>
-    <t>Soil Enrichment</t>
-  </si>
-  <si>
-    <t>Open Carbon Protocol</t>
-  </si>
-  <si>
-    <t>Global Carbon Council</t>
-  </si>
-  <si>
-    <t>BCR0004_Quantification of GHG emission reductions. Activities that avoid Land Use change in continental wetlands</t>
-  </si>
-  <si>
-    <t>C23 - Manufacture of other non-metallic mineral products</t>
-  </si>
-  <si>
-    <t>Technical Removal</t>
-  </si>
-  <si>
-    <t>Open Earth Foundation</t>
-  </si>
-  <si>
-    <t>BCR0005_Quantification of GHG Emissions Reduction. Activities that prevent Land Use Change in Natural Savannas</t>
-  </si>
-  <si>
-    <t>C24 - Manufacture of basic metals</t>
-  </si>
-  <si>
-    <t>PACM Registry</t>
-  </si>
-  <si>
-    <t>Inclusive Carbon Standard</t>
-  </si>
-  <si>
-    <t>BCR0006_Quantification of GHG Emission Reductions by converting gasoline vehicles to natural gas</t>
-  </si>
-  <si>
-    <t>C25 - Manufacture of fabricated metal products, except machinery and equipment</t>
-  </si>
-  <si>
-    <t>Pakistan National Registry</t>
-  </si>
-  <si>
-    <t>International Carbon Registry</t>
-  </si>
-  <si>
-    <t>CAR - Adipic Acid Production</t>
-  </si>
-  <si>
-    <t>C26 - Manufacture of computer, electronic and optical products</t>
-  </si>
-  <si>
-    <t>Plan Vivo</t>
-  </si>
-  <si>
-    <t>CAR - Biochar</t>
-  </si>
-  <si>
-    <t>C27 - Manufacture of electrical equipment</t>
-  </si>
-  <si>
-    <t>Puro Standard and Registry</t>
-  </si>
-  <si>
-    <t>IUCN UK Peatland Programme</t>
-  </si>
-  <si>
-    <t>CAR - Canada Grassland</t>
-  </si>
-  <si>
-    <t>C28 - Manufacture of machinery and equipment n.e.c.</t>
-  </si>
-  <si>
-    <t>Registry of China Certified Emission Reduction Trading System</t>
-  </si>
-  <si>
-    <t>CAR - Coal Mine Methane</t>
-  </si>
-  <si>
-    <t>C29 - Manufacture of motor vehicles, trailers and semi-trailers</t>
-  </si>
-  <si>
-    <t>Riverse</t>
-  </si>
-  <si>
-    <t>CAR - Forest</t>
-  </si>
-  <si>
-    <t>C30 - Manufacture of other transport equipment</t>
-  </si>
-  <si>
-    <t>Royal Kingdom of Bhutan</t>
-  </si>
-  <si>
-    <t>CAR - Grassland</t>
-  </si>
-  <si>
-    <t>C31 - Manufacture of furniture</t>
-  </si>
-  <si>
-    <t>Singapore National Registry</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Boiler Efficiency</t>
-  </si>
-  <si>
-    <t>C32 - Other manufacturing</t>
-  </si>
-  <si>
-    <t>Sweden National Registry</t>
-  </si>
-  <si>
-    <t>PACM</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Forest</t>
-  </si>
-  <si>
-    <t>C33 - Repair, maintenance and installation of machinery and equipment</t>
-  </si>
-  <si>
-    <t>Switzerland National Registry</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Halocarbon</t>
-  </si>
-  <si>
-    <t>D35 - Electricity, gas, steam and air conditioning supply</t>
-  </si>
-  <si>
-    <t>UK Land Carbon Registry</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Landfill</t>
-  </si>
-  <si>
-    <t>E36 - Water collection, treatment and supply</t>
-  </si>
-  <si>
-    <t>UNFCCC International Registry</t>
-  </si>
-  <si>
-    <t>Puro.earth</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Livestock</t>
-  </si>
-  <si>
-    <t>E37 - Sewerage</t>
-  </si>
-  <si>
-    <t>Verra</t>
-  </si>
-  <si>
-    <t>CAR - Mexico Ozone Depleting Substances</t>
-  </si>
-  <si>
-    <t>E38 - Waste collection, treatment and disposal, and recovery activities</t>
-  </si>
-  <si>
-    <t>CAR - Nitric Acid Production</t>
-  </si>
-  <si>
-    <t>E39 - Remediation and other waste management service activities</t>
-  </si>
-  <si>
-    <t>RUN Carbon Crediting Program</t>
-  </si>
-  <si>
-    <t>CAR - Nitrogen Management</t>
-  </si>
-  <si>
-    <t>F41 - Construction of residential and non-residential buildings</t>
-  </si>
-  <si>
-    <t>CAR - Organic Waste Composting</t>
-  </si>
-  <si>
-    <t>F42 - Civil engineering</t>
-  </si>
-  <si>
-    <t>SOCIAL CARBON Registry</t>
-  </si>
-  <si>
-    <t>CAR - Organic Waste Digestion</t>
-  </si>
-  <si>
-    <t>F43 - Specialized construction activities</t>
-  </si>
-  <si>
-    <t>CAR - Ozone Depleting Substances</t>
-  </si>
-  <si>
-    <t>G46 - Wholesale trade</t>
-  </si>
-  <si>
-    <t>CAR - Rice Cultivation</t>
-  </si>
-  <si>
-    <t>G47 - Retail trade</t>
-  </si>
-  <si>
-    <t>Trusted Carbon</t>
-  </si>
-  <si>
-    <t>CAR - Soil Enrichment</t>
-  </si>
-  <si>
-    <t>H49 - Land transport and transport via pipelines</t>
-  </si>
-  <si>
-    <t>CAR - U.S. Landfill</t>
-  </si>
-  <si>
-    <t>H50 - Water transport</t>
-  </si>
-  <si>
-    <t>CAR - U.S. Livestock</t>
-  </si>
-  <si>
-    <t>H51 - Air transport</t>
-  </si>
-  <si>
-    <t>CAR - Urban Forest Management</t>
-  </si>
-  <si>
-    <t>H52 - Warehousing and support activities for transportation</t>
-  </si>
-  <si>
-    <t>CAR - Urban Tree Planting</t>
-  </si>
-  <si>
-    <t>H53 - Postal and courier activities</t>
-  </si>
-  <si>
-    <t>CCB - M/E-ER01</t>
-  </si>
-  <si>
-    <t>I55 - Accommodation</t>
-  </si>
-  <si>
-    <t>CCB - M/LU-REDD+</t>
-  </si>
-  <si>
-    <t>I56 - Food and beverage service activities</t>
-  </si>
-  <si>
-    <t>CCB - M/UT/B-H01</t>
-  </si>
-  <si>
-    <t>J58 - Publishing activities</t>
-  </si>
-  <si>
-    <t>CCB - M/UT/F-A01</t>
-  </si>
-  <si>
-    <t>J59 - Motion picture, video and television programme production, sound recording and music publishing activities</t>
-  </si>
-  <si>
-    <t>CCER - Energy-Saving Highway Tunnel Lighting System (CCER-07-001)</t>
-  </si>
-  <si>
-    <t>J60 - Programming, broadcasting, news agency and other content distribution activities</t>
-  </si>
-  <si>
-    <t>CCER - Forestation Carbon Sequestration (CCER-14-001)</t>
-  </si>
-  <si>
-    <t>K61 - Telecommunications</t>
-  </si>
-  <si>
-    <t>CCER - Grid-Connected Offshore Wind Power Generation (CCER-01-0022)</t>
-  </si>
-  <si>
-    <t>K62 - Computer programming, consultancy and related activities</t>
-  </si>
-  <si>
-    <t>CCER - Grid-Connected Solar Thermal Power Generation (CCER-01-001)</t>
-  </si>
-  <si>
-    <t>K63 - Computing infrastructure, data processing, hosting, and other information service activities</t>
-  </si>
-  <si>
-    <t>CCER - Mangrove Afforestation (CCER-14-002)</t>
-  </si>
-  <si>
-    <t>L64 - Financial service activities, except insurance and pension funding</t>
-  </si>
-  <si>
-    <t>CCER - Utilization of Low-Concentration Coal Mine Methane and Ventilation Air Methane (CCER-10-001)</t>
-  </si>
-  <si>
-    <t>L65 - Insurance, reinsurance and pension funding, except compulsory social security</t>
-  </si>
-  <si>
-    <t>CDM - ACM0001</t>
-  </si>
-  <si>
-    <t>L66 - Activities auxiliary to financial service and insurance activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0002</t>
-  </si>
-  <si>
-    <t>M68 - Real estate activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0003</t>
-  </si>
-  <si>
-    <t>N69 - Legal and accounting activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0004</t>
-  </si>
-  <si>
-    <t>N70 - Activities of head offices; management consultancy activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0005</t>
-  </si>
-  <si>
-    <t>N71 - Architectural and engineering activities; technical testing and analysis</t>
-  </si>
-  <si>
-    <t>CDM - ACM0006</t>
-  </si>
-  <si>
-    <t>N72 - Scientific research and development </t>
-  </si>
-  <si>
-    <t>CDM - ACM0007</t>
-  </si>
-  <si>
-    <t>N73 - Activities of advertising, market research and public relations</t>
-  </si>
-  <si>
-    <t>CDM - ACM0008</t>
-  </si>
-  <si>
-    <t>N74 - Other professional, scientific and technical activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0009</t>
-  </si>
-  <si>
-    <t>N75 - Veterinary activities </t>
-  </si>
-  <si>
-    <t>CDM - ACM0010</t>
-  </si>
-  <si>
-    <t>O77 - Rental and leasing activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0011</t>
-  </si>
-  <si>
-    <t>O78 - Employment activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0012</t>
-  </si>
-  <si>
-    <t>O79 - Travel agency, tour operator, and other travel related activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0013</t>
-  </si>
-  <si>
-    <t>O80 - Investigation and security activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0014</t>
-  </si>
-  <si>
-    <t>O81 - Services to buildings and landscape activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0015</t>
-  </si>
-  <si>
-    <t>O82 - Office administrative, office support and other business support activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0016</t>
-  </si>
-  <si>
-    <t>P84 - Public administration and defence; compulsory social security</t>
-  </si>
-  <si>
-    <t>CDM - ACM0017</t>
-  </si>
-  <si>
-    <t>Q85 - Education</t>
-  </si>
-  <si>
-    <t>CDM - ACM0018</t>
-  </si>
-  <si>
-    <t>R86 - Human health activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0019</t>
-  </si>
-  <si>
-    <t>R87 - Residential care activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0020</t>
-  </si>
-  <si>
-    <t>R88 - Social work activities without accommodation </t>
-  </si>
-  <si>
-    <t>CDM - ACM0021</t>
-  </si>
-  <si>
-    <t>S90 - Arts creation and performing arts activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0022</t>
-  </si>
-  <si>
-    <t>S91 - Library, archives, museum and other cultural activities </t>
-  </si>
-  <si>
-    <t>CDM - ACM0023</t>
-  </si>
-  <si>
-    <t>S92 - Gambling and betting activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0024</t>
-  </si>
-  <si>
-    <t>S93 - Sports activities and amusement and recreation activities</t>
-  </si>
-  <si>
-    <t>CDM - ACM0025</t>
-  </si>
-  <si>
-    <t>T94 - Activities of membership organizations</t>
-  </si>
-  <si>
-    <t>CDM - ACM0026</t>
-  </si>
-  <si>
-    <t>T95 - Repair and maintenance of computers, personal and household goods, and motor vehicles and motorcycles</t>
-  </si>
-  <si>
-    <t>CDM - AM0001</t>
-  </si>
-  <si>
-    <t>T96 - Personal service activities</t>
-  </si>
-  <si>
-    <t>CDM - AM0007</t>
-  </si>
-  <si>
-    <t>U97 - Activities of households as employers of domestic personnel</t>
-  </si>
-  <si>
-    <t>CDM - AM0009</t>
-  </si>
-  <si>
-    <t>U98 - Undifferentiated goods- and services-producing activities of private households for own use</t>
-  </si>
-  <si>
-    <t>CDM - AM0017</t>
-  </si>
-  <si>
-    <t>V99 - Activities of extraterritorial organizations and bodies </t>
-  </si>
-  <si>
-    <t>CDM - AM0018</t>
-  </si>
-  <si>
-    <t>CDM - AM0019</t>
-  </si>
-  <si>
-    <t>CDM - AM0020</t>
-  </si>
-  <si>
-    <t>CDM - AM0021</t>
-  </si>
-  <si>
-    <t>CDM - AM0023</t>
-  </si>
-  <si>
-    <t>CDM - AM0026</t>
-  </si>
-  <si>
-    <t>CDM - AM0027</t>
-  </si>
-  <si>
-    <t>CDM - AM0028</t>
-  </si>
-  <si>
-    <t>CDM - AM0030</t>
-  </si>
-  <si>
-    <t>CDM - AM0031</t>
-  </si>
-  <si>
-    <t>CDM - AM0035</t>
-  </si>
-  <si>
-    <t>CDM - AM0036</t>
-  </si>
-  <si>
-    <t>CDM - AM0037</t>
-  </si>
-  <si>
-    <t>CDM - AM0038</t>
-  </si>
-  <si>
-    <t>CDM - AM0043</t>
-  </si>
-  <si>
-    <t>CDM - AM0044</t>
-  </si>
-  <si>
-    <t>CDM - AM0045</t>
-  </si>
-  <si>
-    <t>CDM - AM0046</t>
-  </si>
-  <si>
-    <t>CDM - AM0048</t>
-  </si>
-  <si>
-    <t>CDM - AM0049</t>
-  </si>
-  <si>
-    <t>CDM - AM0050</t>
-  </si>
-  <si>
-    <t>CDM - AM0052</t>
-  </si>
-  <si>
-    <t>CDM - AM0053</t>
-  </si>
-  <si>
-    <t>CDM - AM0055</t>
-  </si>
-  <si>
-    <t>CDM - AM0056</t>
-  </si>
-  <si>
-    <t>CDM - AM0057</t>
-  </si>
-  <si>
-    <t>CDM - AM0058</t>
-  </si>
-  <si>
-    <t>CDM - AM0059</t>
-  </si>
-  <si>
-    <t>CDM - AM0060</t>
-  </si>
-  <si>
-    <t>CDM - AM0061</t>
-  </si>
-  <si>
-    <t>CDM - AM0062</t>
-  </si>
-  <si>
-    <t>CDM - AM0063</t>
-  </si>
-  <si>
-    <t>CDM - AM0064</t>
-  </si>
-  <si>
-    <t>CDM - AM0065</t>
-  </si>
-  <si>
-    <t>CDM - AM0066</t>
-  </si>
-  <si>
-    <t>CDM - AM0067</t>
-  </si>
-  <si>
-    <t>CDM - AM0068</t>
-  </si>
-  <si>
-    <t>CDM - AM0069</t>
-  </si>
-  <si>
-    <t>CDM - AM0070</t>
-  </si>
-  <si>
-    <t>CDM - AM0071</t>
-  </si>
-  <si>
-    <t>CDM - AM0072</t>
-  </si>
-  <si>
-    <t>CDM - AM0073</t>
-  </si>
-  <si>
-    <t>CDM - AM0074</t>
-  </si>
-  <si>
-    <t>CDM - AM0075</t>
-  </si>
-  <si>
-    <t>CDM - AM0076</t>
-  </si>
-  <si>
-    <t>CDM - AM0077</t>
-  </si>
-  <si>
-    <t>CDM - AM0078</t>
-  </si>
-  <si>
-    <t>CDM - AM0079</t>
-  </si>
-  <si>
-    <t>CDM - AM0080</t>
-  </si>
-  <si>
-    <t>CDM - AM0081</t>
-  </si>
-  <si>
-    <t>CDM - AM0082</t>
-  </si>
-  <si>
-    <t>CDM - AM0083</t>
-  </si>
-  <si>
-    <t>CDM - AM0084</t>
-  </si>
-  <si>
-    <t>CDM - AM0086</t>
-  </si>
-  <si>
-    <t>CDM - AM0088</t>
-  </si>
-  <si>
-    <t>CDM - AM0089</t>
-  </si>
-  <si>
-    <t>CDM - AM0090</t>
-  </si>
-  <si>
-    <t>CDM - AM0091</t>
-  </si>
-  <si>
-    <t>CDM - AM0092</t>
-  </si>
-  <si>
-    <t>CDM - AM0093</t>
-  </si>
-  <si>
-    <t>CDM - AM0094</t>
-  </si>
-  <si>
-    <t>CDM - AM0095</t>
-  </si>
-  <si>
-    <t>CDM - AM0096</t>
-  </si>
-  <si>
-    <t>CDM - AM0097</t>
-  </si>
-  <si>
-    <t>CDM - AM0098</t>
-  </si>
-  <si>
-    <t>CDM - AM0099</t>
-  </si>
-  <si>
-    <t>CDM - AM0100</t>
-  </si>
-  <si>
-    <t>CDM - AM0101</t>
-  </si>
-  <si>
-    <t>CDM - AM0103</t>
-  </si>
-  <si>
-    <t>CDM - AM0104</t>
-  </si>
-  <si>
-    <t>CDM - AM0105</t>
-  </si>
-  <si>
-    <t>CDM - AM0106</t>
-  </si>
-  <si>
-    <t>CDM - AM0107</t>
-  </si>
-  <si>
-    <t>CDM - AM0108</t>
-  </si>
-  <si>
-    <t>CDM - AM0109</t>
-  </si>
-  <si>
-    <t>CDM - AM0110</t>
-  </si>
-  <si>
-    <t>CDM - AM0111</t>
-  </si>
-  <si>
-    <t>CDM - AM0112</t>
-  </si>
-  <si>
-    <t>CDM - AM0113</t>
-  </si>
-  <si>
-    <t>CDM - AM0114</t>
-  </si>
-  <si>
-    <t>CDM - AM0115</t>
-  </si>
-  <si>
-    <t>CDM - AM0116</t>
-  </si>
-  <si>
-    <t>CDM - AM0117</t>
-  </si>
-  <si>
-    <t>CDM - AM0118</t>
-  </si>
-  <si>
-    <t>CDM - AM0119</t>
-  </si>
-  <si>
-    <t>CDM - AM0120</t>
-  </si>
-  <si>
-    <t>CDM - AM0121</t>
-  </si>
-  <si>
-    <t>CDM - AM0122</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.A.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.B.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.C.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.D.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.E.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.F.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.G.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.H.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.I.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.J.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.K.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.L.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-I.M.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.A.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.B.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.C.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.D.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.E.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.F.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.G.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.H.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.I.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.J.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.K.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.L.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.M.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.N.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.O.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.P.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.Q.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.R.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.S.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-II.T.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.A.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AA.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AB.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AC.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AD.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AE.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AF.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AG.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AH.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AI.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AJ.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AK.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AL.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AM.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AN.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AO.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AP.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AQ.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AR.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AS.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AT.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AU.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AV.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AW.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AX.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.AY.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.B.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BA.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BB.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BC.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BD.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BE.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BF.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BG.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BH.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BI.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BJ.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BK.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BL.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BM.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BN.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BO.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BP.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.BQ.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.C.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.D.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.E.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.F.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.G.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.H.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.I.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.J.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.K.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.L.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.M.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.N.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.O.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.P.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.Q.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.R.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.S.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.T.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.U.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.V.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.W.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.X.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.Y.</t>
-  </si>
-  <si>
-    <t>CDM - AMS-III.Z.</t>
-  </si>
-  <si>
-    <t>CDM - AR-ACM0003</t>
-  </si>
-  <si>
-    <t>CDM - AR-AM0014</t>
-  </si>
-  <si>
-    <t>CDM - AR-AMS0003</t>
-  </si>
-  <si>
-    <t>CDM - AR-AMS0007</t>
-  </si>
-  <si>
-    <t>GS - AFFORESTATION/REFORESTATION GHG EMISSIONS REDUCTION &amp; SEQUESTRATION</t>
-  </si>
-  <si>
-    <t>GS - CARBON MINERALISATION USING REACTIVE MINERAL WASTE</t>
-  </si>
-  <si>
-    <t>GS - CARBON SEQUESTRATION THROUGH ACCELERATED CARBONATION OF CONCRETE AGGREGATE </t>
-  </si>
-  <si>
-    <t>GS - EMISSIONS REDUCTIONS FROM SAFE DRINKING WATER SUPPLY</t>
-  </si>
-  <si>
-    <t>GS - METHANE EMISSIONS REDUCTION BY ADJUSTED WATER MANAGEMENT PRACTICE IN RICE CULTIVATION</t>
-  </si>
-  <si>
-    <t>GS - METHANE EMISSIONS REDUCTION FROM ENTERIC FERMENTATION IN BEEF CATTLE THROUGH APPLICATION OF FEED SUPPLEMENTS</t>
-  </si>
-  <si>
-    <t>GS - METHODOLOGY FOR ANIMAL MANURE MANAGEMENT AND BIOGAS USE FOR THERMAL ENERGY GENERATION</t>
-  </si>
-  <si>
-    <t>GS - METHODOLOGY FOR BIOMASS FERMENTATION WITH CARBON CAPTURE AND GEOLOGIC STORAGE</t>
-  </si>
-  <si>
-    <t>GS - METHODOLOGY FOR COLLECTION OF MACROALGAE TO AVOID EMISSIONS FROM DECOMPOSITION</t>
-  </si>
-  <si>
-    <t>GS - METHODOLOGY FOR METERED &amp; MEASURED ENERGY COOKING DEVICES</t>
-  </si>
-  <si>
-    <t>GS - METHODOLOGY FOR RETROFIT ENERGY EFFICIENCY MEASURES IN SHIPPING </t>
-  </si>
-  <si>
-    <t>GS - REDUCED EMISSIONS FROM COOKING AND HEATING – TECHNOLOGIES AND PRACTICES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION (TPDDTEC)</t>
-  </si>
-  <si>
-    <t>GS - SOIL ORGANIC CARBON ACTIVITY MODULE FOR APPLICATION OF ORGANIC SOIL IMPROVERS FROM PULP AND PAPER MILL SLUDGES</t>
-  </si>
-  <si>
-    <t>GS - SOIL ORGANIC CARBON FRAMEWORK METHODOLOGY</t>
-  </si>
-  <si>
-    <t>GS - SUSTAINABLE MANAGEMENT OF MANGROVES</t>
-  </si>
-  <si>
-    <t>GS - THE GOLD STANDARD SIMPLIFIED METHODOLOGY FOR CLEAN AND EFFICIENT COOKSTOVES</t>
-  </si>
-  <si>
-    <t>GS - TPDDTEC - TECHNOLOGIES AND PRACTICES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION</t>
-  </si>
-  <si>
-    <t>GS - TPDDTEC - TECHNOLOGIES TO DISPLACE DECENTRALIZED THERMAL ENERGY CONSUMPTION</t>
-  </si>
-  <si>
-    <t>ISO - Biochar Production and Storage</t>
-  </si>
-  <si>
-    <t>ISO - Biogenic Carbon Capture and Storage</t>
-  </si>
-  <si>
-    <t>ISO - Biomass Geological Storage</t>
-  </si>
-  <si>
-    <t>ISO - Bio-oil Geological Storage</t>
-  </si>
-  <si>
-    <t>ISO - Direct Air Capture</t>
-  </si>
-  <si>
-    <t>ISO - Direct Ocean Capture and Storage</t>
-  </si>
-  <si>
-    <t>ISO - Electrolytic Seawater Mineralization</t>
-  </si>
-  <si>
-    <t>ISO - Enhanced Weathering</t>
-  </si>
-  <si>
-    <t>ISO - Enhanced Weathering in Agriculture</t>
-  </si>
-  <si>
-    <t>ISO - Mineralization</t>
-  </si>
-  <si>
-    <t>ISO - Ocean Alkalinity Enhancement from Coastal Outfalls</t>
-  </si>
-  <si>
-    <t>ISO - Open System Ex-Situ Mineralization</t>
-  </si>
-  <si>
-    <t>ISO - Reforestation</t>
-  </si>
-  <si>
-    <t>ISO - River Alkalinity Enhancement</t>
-  </si>
-  <si>
-    <t>ISO - Subsurface Biomass Carbon Removal and Storage</t>
-  </si>
-  <si>
-    <t>ISO - Wastewater Alkalinity Enhancement</t>
-  </si>
-  <si>
-    <t>JCM - BD_AM001</t>
-  </si>
-  <si>
-    <t>JCM - BD_AM002</t>
-  </si>
-  <si>
-    <t>JCM - BD_AM003</t>
-  </si>
-  <si>
-    <t>JCM - CL_AM001</t>
-  </si>
-  <si>
-    <t>JCM - CL_AM002</t>
-  </si>
-  <si>
-    <t>JCM - CR_AM001</t>
-  </si>
-  <si>
-    <t>JCM - CR_AM002</t>
-  </si>
-  <si>
-    <t>JCM - CR_AM003</t>
-  </si>
-  <si>
-    <t>JCM - ET_AM001</t>
-  </si>
-  <si>
-    <t>JCM - ET_AM002</t>
-  </si>
-  <si>
-    <t>JCM - ET_AM003</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM001</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM002</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM003</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM004</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM005</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM006</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM007</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM008</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM009</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM010</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM011</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM012</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM013</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM014</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM015</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM016</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM017</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM018</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM019</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM020</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM021</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM022</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM023</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM024</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM025</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM026</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM027</t>
-  </si>
-  <si>
-    <t>JCM - ID_AM028</t>
-  </si>
-  <si>
-    <t>JCM - KE_AM001</t>
-  </si>
-  <si>
-    <t>JCM - KE_AM002</t>
-  </si>
-  <si>
-    <t>JCM - KE_AM003</t>
-  </si>
-  <si>
-    <t>JCM - KH_AM001</t>
-  </si>
-  <si>
-    <t>JCM - KH_AM002</t>
-  </si>
-  <si>
-    <t>JCM - KH_AM003</t>
-  </si>
-  <si>
-    <t>JCM - KH_AM004</t>
-  </si>
-  <si>
-    <t>JCM - KH_AM005</t>
-  </si>
-  <si>
-    <t>JCM - LA_AM001</t>
-  </si>
-  <si>
-    <t>JCM - LA_AM002</t>
-  </si>
-  <si>
-    <t>JCM - LA_AM003</t>
-  </si>
-  <si>
-    <t>JCM - LA_AM004</t>
-  </si>
-  <si>
-    <t>JCM - MM_AM001</t>
-  </si>
-  <si>
-    <t>JCM - MM_AM002</t>
-  </si>
-  <si>
-    <t>JCM - MM_AM003</t>
-  </si>
-  <si>
-    <t>JCM - MM_AM004</t>
-  </si>
-  <si>
-    <t>JCM - MM_AM005</t>
-  </si>
-  <si>
-    <t>JCM - MN_AM001</t>
-  </si>
-  <si>
-    <t>JCM - MN_AM002</t>
-  </si>
-  <si>
-    <t>JCM - MN_AM003</t>
-  </si>
-  <si>
-    <t>JCM - MV_AM001</t>
-  </si>
-  <si>
-    <t>JCM - MV_AM002</t>
-  </si>
-  <si>
-    <t>JCM - MX_AM001</t>
-  </si>
-  <si>
-    <t>JCM - PH_AM001</t>
-  </si>
-  <si>
-    <t>JCM - PH_AM002</t>
-  </si>
-  <si>
-    <t>JCM - PW_AM001</t>
-  </si>
-  <si>
-    <t>JCM - SA_AM001</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM001</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM002</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM003</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM004</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM005</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM006</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM007</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM008</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM009</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM010</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM011</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM012</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM013</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM014</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM015</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM016</t>
-  </si>
-  <si>
-    <t>JCM - TH_AM017</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM001</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM002</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM003</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM004</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM005</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM006</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM007</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM008</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM009</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM010</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM011</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM012</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM013</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM014</t>
-  </si>
-  <si>
-    <t>JCM - VN_AM015</t>
-  </si>
-  <si>
-    <t>NTC 6208</t>
-  </si>
-  <si>
-    <t>PURO - Biochar</t>
-  </si>
-  <si>
-    <t>PURO - Carbonated Materials</t>
-  </si>
-  <si>
-    <t>PURO - Enhanced Rock Weathering</t>
-  </si>
-  <si>
-    <t>PURO - Geologically Stored Carbon</t>
-  </si>
-  <si>
-    <t>PURO - Marine Anoxic Carbon Storage</t>
-  </si>
-  <si>
-    <t>PURO - Terrestrial Storage of Biomass</t>
-  </si>
-  <si>
-    <t>PV - PM001</t>
-  </si>
-  <si>
-    <t>PV - PT001</t>
-  </si>
-  <si>
-    <t>PV - PT002</t>
-  </si>
-  <si>
-    <t>PV - PT003</t>
-  </si>
-  <si>
-    <t>PV - PT004</t>
-  </si>
-  <si>
-    <t>PV - PU001</t>
-  </si>
-  <si>
-    <t>PV - PU002</t>
-  </si>
-  <si>
-    <t>PV - PU003</t>
-  </si>
-  <si>
-    <t>PV - PU004</t>
-  </si>
-  <si>
-    <t>PV - PU005</t>
-  </si>
-  <si>
-    <t>TERO.001</t>
-  </si>
-  <si>
-    <t>TERO.002</t>
-  </si>
-  <si>
-    <t>TERO.003</t>
-  </si>
-  <si>
-    <t>TERO.004</t>
-  </si>
-  <si>
-    <t>TERO.005</t>
-  </si>
-  <si>
-    <t>VCS - VM0001</t>
-  </si>
-  <si>
-    <t>VCS - VM0002</t>
-  </si>
-  <si>
-    <t>VCS - VM0003</t>
-  </si>
-  <si>
-    <t>VCS - VM0004</t>
-  </si>
-  <si>
-    <t>VCS - VM0005</t>
-  </si>
-  <si>
-    <t>VCS - VM0006</t>
-  </si>
-  <si>
-    <t>VCS - VM0007</t>
-  </si>
-  <si>
-    <t>VCS - VM0008</t>
-  </si>
-  <si>
-    <t>VCS - VM0009</t>
-  </si>
-  <si>
-    <t>VCS - VM0010</t>
-  </si>
-  <si>
-    <t>VCS - VM0011</t>
-  </si>
-  <si>
-    <t>VCS - VM0012</t>
-  </si>
-  <si>
-    <t>VCS - VM0013</t>
-  </si>
-  <si>
-    <t>VCS - VM0014</t>
-  </si>
-  <si>
-    <t>VCS - VM0015</t>
-  </si>
-  <si>
-    <t>VCS - VM0016</t>
-  </si>
-  <si>
-    <t>VCS - VM0017</t>
-  </si>
-  <si>
-    <t>VCS - VM0018</t>
-  </si>
-  <si>
-    <t>VCS - VM0019</t>
-  </si>
-  <si>
-    <t>VCS - VM0020</t>
-  </si>
-  <si>
-    <t>VCS - VM0021</t>
-  </si>
-  <si>
-    <t>VCS - VM0022</t>
-  </si>
-  <si>
-    <t>VCS - VM0023</t>
-  </si>
-  <si>
-    <t>VCS - VM0024</t>
-  </si>
-  <si>
-    <t>VCS - VM0025</t>
-  </si>
-  <si>
-    <t>VCS - VM0026</t>
-  </si>
-  <si>
-    <t>VCS - VM0027</t>
-  </si>
-  <si>
-    <t>VCS - VM0028</t>
-  </si>
-  <si>
-    <t>VCS - VM0029</t>
-  </si>
-  <si>
-    <t>VCS - VM0030</t>
-  </si>
-  <si>
-    <t>VCS - VM0031</t>
-  </si>
-  <si>
-    <t>VCS - VM0032</t>
-  </si>
-  <si>
-    <t>VCS - VM0033</t>
-  </si>
-  <si>
-    <t>VCS - VM0034</t>
-  </si>
-  <si>
-    <t>VCS - VM0035</t>
-  </si>
-  <si>
-    <t>VCS - VM0036</t>
-  </si>
-  <si>
-    <t>VCS - VM0037</t>
-  </si>
-  <si>
-    <t>VCS - VM0038</t>
-  </si>
-  <si>
-    <t>VCS - VM0039</t>
-  </si>
-  <si>
-    <t>VCS - VM0040</t>
-  </si>
-  <si>
-    <t>VCS - VM0041</t>
-  </si>
-  <si>
-    <t>VCS - VM0042</t>
-  </si>
-  <si>
-    <t>VCS - VM0043</t>
-  </si>
-  <si>
-    <t>VCS - VM0044</t>
-  </si>
-  <si>
-    <t>VCS - VM0045</t>
-  </si>
-  <si>
-    <t>VCS - VM0046</t>
-  </si>
-  <si>
-    <t>VCS - VM0047</t>
-  </si>
-  <si>
-    <t>VCS - VM0048</t>
-  </si>
-  <si>
-    <t>VCS - VM0049</t>
-  </si>
-  <si>
-    <t>VCS - VM0050</t>
-  </si>
-  <si>
-    <t>VCS - VM0051</t>
-  </si>
-  <si>
-    <t>VCS - VM0052</t>
-  </si>
-  <si>
-    <t>VCS - VMR000</t>
-  </si>
-  <si>
-    <t>VCS - VMR004</t>
-  </si>
-  <si>
-    <t>VCS - VMR005</t>
-  </si>
-  <si>
-    <t>VCS - VMR006</t>
-  </si>
-  <si>
-    <t>VCS - VMR007</t>
-  </si>
-  <si>
-    <t>VCS - VMR008</t>
-  </si>
-  <si>
-    <t>VCS - VMR009</t>
-  </si>
-  <si>
-    <t>VCS - VMR010</t>
-  </si>
-  <si>
-    <t>VCS - VMR012</t>
-  </si>
-  <si>
-    <t>VCS - VMR013</t>
-  </si>
-  <si>
-    <t>VCS - VMR014</t>
-  </si>
-  <si>
-    <t>attestations</t>
-  </si>
-  <si>
-    <t>organization role</t>
-  </si>
-  <si>
-    <t>child labor attestation</t>
-  </si>
-  <si>
-    <t>labor worker attestation</t>
-  </si>
-  <si>
-    <t>legal land ownership attestation</t>
-  </si>
-  <si>
-    <t>human rights attestation</t>
-  </si>
-  <si>
-    <t>issuance status</t>
-  </si>
-  <si>
-    <t>Verified</t>
-  </si>
-  <si>
-    <t>Pending Issuance</t>
-  </si>
-  <si>
-    <t>Issuing</t>
-  </si>
-  <si>
-    <t>Pre-issuance</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Complete</t>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Tidal</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origination </t>
+  </si>
+  <si>
+    <t>Pre-feasibility</t>
+  </si>
+  <si>
+    <t>Feasibility</t>
+  </si>
+  <si>
+    <t>Project design drafting</t>
+  </si>
+  <si>
+    <t>Project design finalization</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Verified and issuing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4169,6 +4247,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -4214,7 +4299,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4238,6 +4323,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4573,16 +4678,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B85F238-80B8-43F8-AABF-7B9427088CCA}">
-  <dimension ref="A1:AW499"/>
+  <dimension ref="A1:BE499"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="27" max="27" width="11.08984375" customWidth="1"/>
+    <col min="35" max="35" width="28.26953125" customWidth="1"/>
     <col min="45" max="46" width="12" customWidth="1"/>
     <col min="47" max="48" width="14.7265625" customWidth="1"/>
     <col min="49" max="49" width="16.90625" customWidth="1"/>
+    <col min="51" max="51" width="19.36328125" customWidth="1"/>
+    <col min="53" max="53" width="15.453125" customWidth="1"/>
+    <col min="55" max="55" width="20.36328125" customWidth="1"/>
+    <col min="57" max="57" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4605,7 +4715,7 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4626,7 +4736,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:57" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -4714,18 +4824,30 @@
         <v>612</v>
       </c>
       <c r="AS3" s="14" t="s">
-        <v>1341</v>
+        <v>1318</v>
       </c>
       <c r="AT3" s="14"/>
       <c r="AU3" s="14" t="s">
-        <v>1342</v>
+        <v>1319</v>
       </c>
       <c r="AV3" s="14"/>
       <c r="AW3" s="14" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1324</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="BC3" s="17" t="s">
+        <v>1338</v>
+      </c>
+      <c r="BE3" s="19" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -4775,7 +4897,7 @@
         <v>615</v>
       </c>
       <c r="AA4" t="s">
-        <v>616</v>
+        <v>1373</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>617</v>
@@ -4789,36 +4911,48 @@
         <v>619</v>
       </c>
       <c r="AH4" s="10"/>
-      <c r="AI4" s="10" t="s">
-        <v>620</v>
+      <c r="AI4" s="22" t="s">
+        <v>1344</v>
       </c>
       <c r="AJ4" s="10"/>
       <c r="AK4" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AL4" s="10"/>
       <c r="AM4" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AN4" s="10"/>
       <c r="AO4" t="s">
+        <v>621</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>622</v>
       </c>
-      <c r="AQ4" t="s">
-        <v>623</v>
-      </c>
       <c r="AS4" s="4" t="s">
-        <v>1343</v>
+        <v>1320</v>
       </c>
       <c r="AT4" s="4"/>
       <c r="AU4" t="s">
         <v>614</v>
       </c>
       <c r="AW4" s="4" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1325</v>
+      </c>
+      <c r="AY4" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="BC4" s="16" t="s">
+        <v>1339</v>
+      </c>
+      <c r="BE4" s="18" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
@@ -4855,57 +4989,67 @@
         <v>28</v>
       </c>
       <c r="U5" t="s">
+        <v>623</v>
+      </c>
+      <c r="W5" t="s">
         <v>624</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>625</v>
       </c>
-      <c r="Y5" t="s">
-        <v>626</v>
-      </c>
       <c r="AA5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AC5" s="11" t="s">
         <v>627</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>628</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AH5" s="10"/>
-      <c r="AI5" s="10" t="s">
-        <v>631</v>
-      </c>
+      <c r="AI5" s="15"/>
       <c r="AJ5" s="10"/>
       <c r="AK5" t="s">
+        <v>630</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>631</v>
+      </c>
+      <c r="AO5" t="s">
         <v>632</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AQ5" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="AO5" t="s">
-        <v>634</v>
-      </c>
-      <c r="AQ5" s="10" t="s">
-        <v>635</v>
-      </c>
       <c r="AS5" s="4" t="s">
-        <v>1344</v>
+        <v>1321</v>
       </c>
       <c r="AT5" s="4"/>
       <c r="AU5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AW5" s="4" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:49" ht="29" x14ac:dyDescent="0.35">
+        <v>1326</v>
+      </c>
+      <c r="AY5" s="15" t="s">
+        <v>1333</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="BC5" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="BE5" s="18" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
@@ -4940,59 +5084,65 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="U6" t="s">
+        <v>634</v>
+      </c>
+      <c r="W6" t="s">
+        <v>635</v>
+      </c>
+      <c r="Y6" t="s">
         <v>636</v>
       </c>
-      <c r="W6" t="s">
-        <v>637</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>638</v>
-      </c>
       <c r="AA6" s="2" t="s">
-        <v>639</v>
+        <v>1375</v>
       </c>
       <c r="AB6" s="2"/>
       <c r="AC6" s="10" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AD6" s="10"/>
       <c r="AE6" s="10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AF6" s="10"/>
       <c r="AG6" s="10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AH6" s="10"/>
-      <c r="AI6" s="10" t="s">
-        <v>643</v>
+      <c r="AI6" s="20" t="s">
+        <v>1353</v>
       </c>
       <c r="AJ6" s="10"/>
       <c r="AK6" s="10" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AL6" s="10"/>
       <c r="AM6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="AO6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="AS6" s="4" t="s">
-        <v>1345</v>
+        <v>1322</v>
       </c>
       <c r="AT6" s="4"/>
       <c r="AU6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AW6" s="4" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1327</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="BC6" s="16" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>36</v>
       </c>
@@ -5025,54 +5175,57 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="U7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="W7" t="s">
+        <v>646</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>647</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AE7" s="10" t="s">
         <v>649</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>650</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>651</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>652</v>
       </c>
       <c r="AF7" s="10"/>
       <c r="AG7" s="10" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="AH7" s="10"/>
-      <c r="AI7" s="10" t="s">
-        <v>654</v>
+      <c r="AI7" s="20" t="s">
+        <v>1354</v>
       </c>
       <c r="AJ7" s="10"/>
       <c r="AK7" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="AL7" s="10"/>
       <c r="AM7" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="AO7" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>1346</v>
+        <v>1323</v>
       </c>
       <c r="AT7" s="4"/>
       <c r="AU7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1328</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>42</v>
       </c>
@@ -5105,50 +5258,50 @@
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="W8" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="Y8" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="AA8" t="s">
-        <v>661</v>
+        <v>1377</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AF8" s="10"/>
       <c r="AG8" s="10" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="AH8" s="10"/>
-      <c r="AI8" s="10" t="s">
-        <v>664</v>
+      <c r="AI8" s="21" t="s">
+        <v>1355</v>
       </c>
       <c r="AJ8" s="10"/>
       <c r="AK8" s="10" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="AL8" s="10"/>
       <c r="AM8" s="10" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="AN8" s="10"/>
       <c r="AO8" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="AQ8" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="AS8" s="4"/>
       <c r="AT8" s="4"/>
       <c r="AU8" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="AW8" s="4" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -5183,51 +5336,51 @@
       <c r="U9" s="12"/>
       <c r="V9" s="12"/>
       <c r="W9" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="Z9" s="13"/>
       <c r="AA9" t="s">
-        <v>670</v>
+        <v>616</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="AF9" s="10"/>
       <c r="AG9" s="10" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="AH9" s="10"/>
-      <c r="AI9" s="10" t="s">
-        <v>673</v>
+      <c r="AI9" s="21" t="s">
+        <v>1345</v>
       </c>
       <c r="AJ9" s="10"/>
       <c r="AK9" s="10" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="AL9" s="10"/>
       <c r="AM9" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="AN9" s="10"/>
       <c r="AO9" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="AQ9" s="10" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="AS9" s="4"/>
       <c r="AT9" s="4"/>
       <c r="AU9" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="AW9" s="4" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>54</v>
       </c>
@@ -5260,39 +5413,39 @@
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="W10" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="AA10" t="s">
-        <v>678</v>
+        <v>1378</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="AH10" s="10"/>
-      <c r="AI10" s="10" t="s">
-        <v>680</v>
+      <c r="AI10" s="20" t="s">
+        <v>1346</v>
       </c>
       <c r="AJ10" s="10"/>
       <c r="AK10" s="10" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="AL10" s="10"/>
       <c r="AM10" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="AO10" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="AQ10" s="10" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="AS10" s="4"/>
       <c r="AT10" s="4"/>
       <c r="AU10" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>60</v>
       </c>
@@ -5325,40 +5478,40 @@
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="W11" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="AA11" t="s">
-        <v>686</v>
+        <v>626</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AH11" s="10"/>
-      <c r="AI11" s="10" t="s">
-        <v>688</v>
+      <c r="AI11" s="20" t="s">
+        <v>1350</v>
       </c>
       <c r="AJ11" s="10"/>
       <c r="AK11" s="10" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="AL11" s="10"/>
       <c r="AM11" s="10" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="AN11" s="10"/>
       <c r="AO11" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="AQ11" s="10" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="AS11" s="4"/>
       <c r="AT11" s="4"/>
       <c r="AU11" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>66</v>
       </c>
@@ -5389,38 +5542,38 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="W12" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="AA12" t="s">
-        <v>694</v>
+        <v>637</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="AH12" s="10"/>
-      <c r="AI12" s="10" t="s">
-        <v>696</v>
+      <c r="AI12" s="20" t="s">
+        <v>1351</v>
       </c>
       <c r="AJ12" s="10"/>
       <c r="AK12" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="AM12" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="AO12" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="AQ12" s="10" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="AS12" s="4"/>
       <c r="AT12" s="4"/>
       <c r="AU12" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
@@ -5451,40 +5604,40 @@
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="W13" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="AA13" t="s">
-        <v>702</v>
+        <v>648</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="AH13" s="10"/>
-      <c r="AI13" s="10" t="s">
-        <v>704</v>
+      <c r="AI13" s="21" t="s">
+        <v>1349</v>
       </c>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="10" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="AL13" s="10"/>
       <c r="AM13" s="10" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="AN13" s="10"/>
       <c r="AO13" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="AS13" s="4"/>
       <c r="AT13" s="4"/>
       <c r="AU13" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
@@ -5515,41 +5668,41 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="W14" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>709</v>
+        <v>657</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AG14" s="10" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="AH14" s="10"/>
-      <c r="AI14" s="10" t="s">
-        <v>711</v>
+      <c r="AI14" s="20" t="s">
+        <v>1358</v>
       </c>
       <c r="AJ14" s="10"/>
       <c r="AK14" s="10" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="AL14" s="10"/>
       <c r="AM14" s="10" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="AN14" s="10"/>
       <c r="AO14" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="AQ14" s="10" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="AS14" s="4"/>
       <c r="AT14" s="4"/>
       <c r="AU14" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>81</v>
       </c>
@@ -5580,35 +5733,38 @@
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="W15" t="s">
-        <v>716</v>
+        <v>704</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>1379</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="AH15" s="10"/>
-      <c r="AI15" s="10" t="s">
-        <v>718</v>
+      <c r="AI15" s="20" t="s">
+        <v>1359</v>
       </c>
       <c r="AJ15" s="10"/>
       <c r="AK15" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="AM15" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="AO15" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="AS15" s="4"/>
       <c r="AT15" s="4"/>
       <c r="AU15" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>86</v>
       </c>
@@ -5639,34 +5795,37 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="W16" t="s">
-        <v>723</v>
+        <v>710</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>665</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="AH16" s="10"/>
-      <c r="AI16" s="10" t="s">
-        <v>725</v>
+      <c r="AI16" s="20" t="s">
+        <v>1347</v>
       </c>
       <c r="AJ16" s="10"/>
       <c r="AK16" s="10" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="AL16" s="10"/>
       <c r="AM16" s="10" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="AN16" s="10"/>
       <c r="AO16" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="AQ16" s="10" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="AS16" s="4"/>
       <c r="AT16" s="4"/>
       <c r="AU16" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:47" x14ac:dyDescent="0.35">
@@ -5700,33 +5859,36 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="W17" t="s">
-        <v>729</v>
+        <v>715</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>672</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="AH17" s="10"/>
-      <c r="AI17" s="10" t="s">
-        <v>731</v>
+      <c r="AI17" s="20" t="s">
+        <v>1360</v>
       </c>
       <c r="AJ17" s="10"/>
       <c r="AK17" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="AN17" s="10"/>
       <c r="AO17" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="AQ17" s="10" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="AS17" s="4"/>
       <c r="AT17" s="4"/>
       <c r="AU17" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.35">
@@ -5760,33 +5922,36 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="W18" t="s">
-        <v>735</v>
+        <v>720</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>679</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="AH18" s="10"/>
-      <c r="AI18" s="10" t="s">
-        <v>737</v>
+      <c r="AI18" s="20" t="s">
+        <v>1348</v>
       </c>
       <c r="AJ18" s="10"/>
       <c r="AK18" s="10" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="AL18" s="10"/>
       <c r="AM18" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
       <c r="AO18" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="AQ18" s="10" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="AS18" s="4"/>
       <c r="AT18" s="4"/>
       <c r="AU18" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.35">
@@ -5820,32 +5985,35 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="W19" t="s">
-        <v>742</v>
+        <v>726</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>686</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="AH19" s="10"/>
-      <c r="AI19" s="10" t="s">
-        <v>744</v>
+      <c r="AI19" s="20" t="s">
+        <v>1361</v>
       </c>
       <c r="AJ19" s="10"/>
       <c r="AK19" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="AM19" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="AO19" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="AQ19" s="10" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="AS19" s="4"/>
       <c r="AT19" s="4"/>
       <c r="AU19" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.35">
@@ -5877,34 +6045,37 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="W20" t="s">
-        <v>749</v>
+        <v>732</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>693</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="AH20" s="10"/>
-      <c r="AI20" s="10" t="s">
-        <v>751</v>
+      <c r="AI20" s="20" t="s">
+        <v>1362</v>
       </c>
       <c r="AJ20" s="10"/>
       <c r="AK20" s="10" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="AL20" s="10"/>
       <c r="AM20" s="10" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="AN20" s="10"/>
       <c r="AO20" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="AQ20" s="10" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="AS20" s="4"/>
       <c r="AT20" s="4"/>
       <c r="AU20" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
     </row>
     <row r="21" spans="1:47" x14ac:dyDescent="0.35">
@@ -5936,33 +6107,33 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="W21" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="AH21" s="10"/>
-      <c r="AI21" s="10" t="s">
-        <v>757</v>
+      <c r="AI21" s="20" t="s">
+        <v>1363</v>
       </c>
       <c r="AJ21" s="10"/>
       <c r="AK21" s="10" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="AL21" s="10"/>
       <c r="AM21" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="AO21" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="AQ21" s="10" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="AS21" s="4"/>
       <c r="AT21" s="4"/>
       <c r="AU21" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:47" x14ac:dyDescent="0.35">
@@ -5994,25 +6165,25 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="AG22" s="10" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="AH22" s="10"/>
-      <c r="AI22" s="10" t="s">
-        <v>763</v>
+      <c r="AI22" s="20" t="s">
+        <v>1364</v>
       </c>
       <c r="AJ22" s="10"/>
       <c r="AK22" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="AM22" s="10" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="AN22" s="10"/>
       <c r="AO22" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="AQ22" s="10" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
     </row>
     <row r="23" spans="1:47" x14ac:dyDescent="0.35">
@@ -6044,21 +6215,21 @@
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="AG23" s="10" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="AH23" s="10"/>
-      <c r="AI23" s="10" t="s">
-        <v>768</v>
+      <c r="AI23" s="20" t="s">
+        <v>1365</v>
       </c>
       <c r="AJ23" s="10"/>
       <c r="AK23" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="AM23" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="AQ23" s="10" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:47" x14ac:dyDescent="0.35">
@@ -6090,22 +6261,22 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="AG24" s="10" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="AH24" s="10"/>
-      <c r="AI24" s="10" t="s">
-        <v>773</v>
+      <c r="AI24" s="20" t="s">
+        <v>1366</v>
       </c>
       <c r="AJ24" s="10"/>
       <c r="AK24" t="s">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="AM24" s="10" t="s">
-        <v>775</v>
+        <v>753</v>
       </c>
       <c r="AN24" s="10"/>
       <c r="AQ24" s="10" t="s">
-        <v>776</v>
+        <v>754</v>
       </c>
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.35">
@@ -6137,23 +6308,23 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="AG25" s="10" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="AH25" s="10"/>
-      <c r="AI25" s="10" t="s">
-        <v>778</v>
+      <c r="AI25" s="20" t="s">
+        <v>1367</v>
       </c>
       <c r="AJ25" s="10"/>
       <c r="AK25" s="10" t="s">
-        <v>779</v>
+        <v>756</v>
       </c>
       <c r="AL25" s="10"/>
       <c r="AM25" s="10" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="AN25" s="10"/>
       <c r="AQ25" s="10" t="s">
-        <v>780</v>
+        <v>757</v>
       </c>
     </row>
     <row r="26" spans="1:47" x14ac:dyDescent="0.35">
@@ -6185,18 +6356,21 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="AG26" s="10" t="s">
-        <v>781</v>
+        <v>758</v>
       </c>
       <c r="AH26" s="10"/>
+      <c r="AI26" s="20" t="s">
+        <v>1352</v>
+      </c>
       <c r="AK26" s="10" t="s">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="AL26" s="10"/>
       <c r="AM26" t="s">
-        <v>783</v>
+        <v>760</v>
       </c>
       <c r="AQ26" s="10" t="s">
-        <v>784</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.35">
@@ -6228,18 +6402,21 @@
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="AG27" s="10" t="s">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="AH27" s="10"/>
+      <c r="AI27" s="20" t="s">
+        <v>1368</v>
+      </c>
       <c r="AK27" s="10" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="AL27" s="10"/>
       <c r="AM27" t="s">
-        <v>787</v>
+        <v>764</v>
       </c>
       <c r="AQ27" s="10" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
     </row>
     <row r="28" spans="1:47" x14ac:dyDescent="0.35">
@@ -6271,17 +6448,20 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="AG28" s="10" t="s">
-        <v>789</v>
+        <v>766</v>
       </c>
       <c r="AH28" s="10"/>
+      <c r="AI28" s="20" t="s">
+        <v>1369</v>
+      </c>
       <c r="AK28" t="s">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="AM28" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="AQ28" s="10" t="s">
-        <v>791</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29" spans="1:47" x14ac:dyDescent="0.35">
@@ -6313,18 +6493,21 @@
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="AG29" s="10" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="AH29" s="10"/>
+      <c r="AI29" s="20" t="s">
+        <v>1370</v>
+      </c>
       <c r="AK29" s="10" t="s">
-        <v>793</v>
+        <v>770</v>
       </c>
       <c r="AL29" s="10"/>
       <c r="AM29" t="s">
-        <v>794</v>
+        <v>771</v>
       </c>
       <c r="AQ29" s="10" t="s">
-        <v>795</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.35">
@@ -6356,19 +6539,22 @@
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
       <c r="AG30" s="10" t="s">
-        <v>796</v>
+        <v>773</v>
       </c>
       <c r="AH30" s="10"/>
+      <c r="AI30" s="20" t="s">
+        <v>1371</v>
+      </c>
       <c r="AK30" s="10" t="s">
-        <v>797</v>
+        <v>774</v>
       </c>
       <c r="AL30" s="10"/>
       <c r="AM30" s="10" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="AN30" s="10"/>
       <c r="AQ30" s="10" t="s">
-        <v>798</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.35">
@@ -6400,18 +6586,21 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
       <c r="AG31" s="10" t="s">
-        <v>799</v>
+        <v>776</v>
       </c>
       <c r="AH31" s="10"/>
+      <c r="AI31" s="21" t="s">
+        <v>1356</v>
+      </c>
       <c r="AK31" t="s">
-        <v>800</v>
+        <v>777</v>
       </c>
       <c r="AM31" s="10" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="AN31" s="10"/>
       <c r="AQ31" s="10" t="s">
-        <v>801</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32" spans="1:47" x14ac:dyDescent="0.35">
@@ -6443,18 +6632,21 @@
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
       <c r="AG32" s="10" t="s">
-        <v>802</v>
+        <v>779</v>
       </c>
       <c r="AH32" s="10"/>
+      <c r="AI32" s="20" t="s">
+        <v>1372</v>
+      </c>
       <c r="AK32" s="10" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
       <c r="AL32" s="10"/>
       <c r="AM32" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="AQ32" s="10" t="s">
-        <v>804</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.35">
@@ -6486,19 +6678,22 @@
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
       <c r="AG33" s="10" t="s">
-        <v>805</v>
+        <v>782</v>
       </c>
       <c r="AH33" s="10"/>
+      <c r="AI33" s="20" t="s">
+        <v>1357</v>
+      </c>
       <c r="AK33" s="10" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="AL33" s="10"/>
       <c r="AM33" s="10" t="s">
-        <v>779</v>
+        <v>756</v>
       </c>
       <c r="AN33" s="10"/>
       <c r="AQ33" s="10" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.35">
@@ -6530,19 +6725,19 @@
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="AG34" s="10" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="AH34" s="10"/>
       <c r="AK34" s="10" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="AL34" s="10"/>
       <c r="AM34" s="10" t="s">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="AN34" s="10"/>
       <c r="AQ34" s="10" t="s">
-        <v>811</v>
+        <v>788</v>
       </c>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.35">
@@ -6570,19 +6765,19 @@
       <c r="R35" s="4"/>
       <c r="S35" s="4"/>
       <c r="AG35" s="10" t="s">
-        <v>812</v>
+        <v>789</v>
       </c>
       <c r="AH35" s="10"/>
       <c r="AK35" s="10" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="AL35" s="10"/>
       <c r="AM35" s="10" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="AN35" s="10"/>
       <c r="AQ35" s="10" t="s">
-        <v>814</v>
+        <v>791</v>
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.35">
@@ -6610,17 +6805,17 @@
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
       <c r="AG36" s="10" t="s">
-        <v>815</v>
+        <v>792</v>
       </c>
       <c r="AH36" s="10"/>
       <c r="AK36" t="s">
-        <v>816</v>
+        <v>793</v>
       </c>
       <c r="AM36" t="s">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="AQ36" s="10" t="s">
-        <v>817</v>
+        <v>794</v>
       </c>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.35">
@@ -6648,19 +6843,19 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="AG37" s="10" t="s">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="AH37" s="10"/>
       <c r="AK37" s="10" t="s">
-        <v>819</v>
+        <v>796</v>
       </c>
       <c r="AL37" s="10"/>
       <c r="AM37" s="10" t="s">
-        <v>820</v>
+        <v>797</v>
       </c>
       <c r="AN37" s="10"/>
       <c r="AQ37" s="10" t="s">
-        <v>821</v>
+        <v>798</v>
       </c>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.35">
@@ -6688,18 +6883,18 @@
       <c r="R38" s="4"/>
       <c r="S38" s="4"/>
       <c r="AG38" s="10" t="s">
-        <v>822</v>
+        <v>799</v>
       </c>
       <c r="AH38" s="10"/>
       <c r="AK38" s="10" t="s">
-        <v>823</v>
+        <v>800</v>
       </c>
       <c r="AL38" s="10"/>
       <c r="AM38" t="s">
-        <v>800</v>
+        <v>777</v>
       </c>
       <c r="AQ38" s="10" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.35">
@@ -6727,15 +6922,15 @@
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
       <c r="AG39" s="10" t="s">
-        <v>825</v>
+        <v>802</v>
       </c>
       <c r="AH39" s="10"/>
       <c r="AM39" s="10" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
       <c r="AN39" s="10"/>
       <c r="AQ39" s="10" t="s">
-        <v>826</v>
+        <v>803</v>
       </c>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.35">
@@ -6763,15 +6958,15 @@
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
       <c r="AG40" s="10" t="s">
-        <v>827</v>
+        <v>804</v>
       </c>
       <c r="AH40" s="10"/>
       <c r="AM40" s="10" t="s">
-        <v>828</v>
+        <v>805</v>
       </c>
       <c r="AN40" s="10"/>
       <c r="AQ40" s="10" t="s">
-        <v>829</v>
+        <v>806</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.35">
@@ -6799,15 +6994,15 @@
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
       <c r="AG41" s="10" t="s">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="AH41" s="10"/>
       <c r="AM41" s="10" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="AN41" s="10"/>
       <c r="AQ41" s="10" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.35">
@@ -6835,14 +7030,14 @@
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
       <c r="AG42" s="10" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="AH42" s="10"/>
       <c r="AM42" t="s">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="AQ42" s="10" t="s">
-        <v>834</v>
+        <v>811</v>
       </c>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.35">
@@ -6870,15 +7065,15 @@
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
       <c r="AG43" s="10" t="s">
-        <v>835</v>
+        <v>812</v>
       </c>
       <c r="AH43" s="10"/>
       <c r="AM43" s="10" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="AN43" s="10"/>
       <c r="AQ43" s="10" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.35">
@@ -6906,15 +7101,15 @@
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="AG44" s="10" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="AH44" s="10"/>
       <c r="AM44" s="10" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="AN44" s="10"/>
       <c r="AQ44" s="10" t="s">
-        <v>838</v>
+        <v>815</v>
       </c>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.35">
@@ -6942,14 +7137,14 @@
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="AG45" s="10" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="AH45" s="10"/>
       <c r="AM45" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="AQ45" s="10" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.35">
@@ -6977,15 +7172,15 @@
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="AG46" s="10" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="AH46" s="10"/>
       <c r="AM46" s="10" t="s">
-        <v>823</v>
+        <v>800</v>
       </c>
       <c r="AN46" s="10"/>
       <c r="AQ46" s="10" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.35">
@@ -7013,11 +7208,11 @@
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="AG47" s="10" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="AH47" s="10"/>
       <c r="AQ47" s="10" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.35">
@@ -7045,11 +7240,11 @@
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
       <c r="AG48" s="10" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="AH48" s="10"/>
       <c r="AQ48" s="10" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.35">
@@ -7077,11 +7272,11 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
       <c r="AG49" s="10" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="AH49" s="10"/>
       <c r="AQ49" s="10" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.35">
@@ -7109,11 +7304,11 @@
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
       <c r="AG50" s="10" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="AH50" s="10"/>
       <c r="AQ50" s="10" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.35">
@@ -7141,11 +7336,11 @@
       <c r="R51" s="4"/>
       <c r="S51" s="4"/>
       <c r="AG51" s="10" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="AH51" s="10"/>
       <c r="AQ51" s="10" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.35">
@@ -7173,11 +7368,11 @@
       <c r="R52" s="4"/>
       <c r="S52" s="4"/>
       <c r="AG52" s="10" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="AH52" s="10"/>
       <c r="AQ52" s="10" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.35">
@@ -7205,11 +7400,11 @@
       <c r="R53" s="4"/>
       <c r="S53" s="4"/>
       <c r="AG53" s="10" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="AH53" s="10"/>
       <c r="AQ53" s="10" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.35">
@@ -7237,11 +7432,11 @@
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
       <c r="AG54" s="10" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
       <c r="AH54" s="10"/>
       <c r="AQ54" s="10" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.35">
@@ -7269,11 +7464,11 @@
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
       <c r="AG55" s="10" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="AH55" s="10"/>
       <c r="AQ55" s="10" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.35">
@@ -7301,11 +7496,11 @@
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
       <c r="AG56" s="10" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
       <c r="AH56" s="10"/>
       <c r="AQ56" s="10" t="s">
-        <v>863</v>
+        <v>840</v>
       </c>
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.35">
@@ -7333,11 +7528,11 @@
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
       <c r="AG57" s="10" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="AH57" s="10"/>
       <c r="AQ57" s="10" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.35">
@@ -7365,11 +7560,11 @@
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="AG58" s="10" t="s">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="AH58" s="10"/>
       <c r="AQ58" s="10" t="s">
-        <v>867</v>
+        <v>844</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.35">
@@ -7397,11 +7592,11 @@
       <c r="R59" s="4"/>
       <c r="S59" s="4"/>
       <c r="AG59" s="10" t="s">
-        <v>868</v>
+        <v>845</v>
       </c>
       <c r="AH59" s="10"/>
       <c r="AQ59" s="10" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.35">
@@ -7429,11 +7624,11 @@
       <c r="R60" s="4"/>
       <c r="S60" s="4"/>
       <c r="AG60" s="10" t="s">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="AH60" s="10"/>
       <c r="AQ60" s="10" t="s">
-        <v>871</v>
+        <v>848</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.35">
@@ -7461,11 +7656,11 @@
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
       <c r="AG61" s="10" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="AH61" s="10"/>
       <c r="AQ61" s="10" t="s">
-        <v>873</v>
+        <v>850</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.35">
@@ -7493,11 +7688,11 @@
       <c r="R62" s="4"/>
       <c r="S62" s="4"/>
       <c r="AG62" s="10" t="s">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="AH62" s="10"/>
       <c r="AQ62" s="10" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.35">
@@ -7525,11 +7720,11 @@
       <c r="R63" s="4"/>
       <c r="S63" s="4"/>
       <c r="AG63" s="10" t="s">
-        <v>876</v>
+        <v>853</v>
       </c>
       <c r="AH63" s="10"/>
       <c r="AQ63" s="10" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.35">
@@ -7557,11 +7752,11 @@
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
       <c r="AG64" s="10" t="s">
-        <v>878</v>
+        <v>855</v>
       </c>
       <c r="AH64" s="10"/>
       <c r="AQ64" s="10" t="s">
-        <v>879</v>
+        <v>856</v>
       </c>
     </row>
     <row r="65" spans="1:43" x14ac:dyDescent="0.35">
@@ -7589,11 +7784,11 @@
       <c r="R65" s="4"/>
       <c r="S65" s="4"/>
       <c r="AG65" s="10" t="s">
-        <v>880</v>
+        <v>857</v>
       </c>
       <c r="AH65" s="10"/>
       <c r="AQ65" s="10" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
     </row>
     <row r="66" spans="1:43" x14ac:dyDescent="0.35">
@@ -7621,11 +7816,11 @@
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
       <c r="AG66" s="10" t="s">
-        <v>882</v>
+        <v>859</v>
       </c>
       <c r="AH66" s="10"/>
       <c r="AQ66" s="10" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
     </row>
     <row r="67" spans="1:43" x14ac:dyDescent="0.35">
@@ -7653,11 +7848,11 @@
       <c r="R67" s="4"/>
       <c r="S67" s="4"/>
       <c r="AG67" s="10" t="s">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="AH67" s="10"/>
       <c r="AQ67" s="10" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
     </row>
     <row r="68" spans="1:43" x14ac:dyDescent="0.35">
@@ -7685,11 +7880,11 @@
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
       <c r="AG68" s="10" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="AH68" s="10"/>
       <c r="AQ68" s="10" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
     </row>
     <row r="69" spans="1:43" x14ac:dyDescent="0.35">
@@ -7717,11 +7912,11 @@
       <c r="R69" s="4"/>
       <c r="S69" s="4"/>
       <c r="AG69" s="10" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="AH69" s="10"/>
       <c r="AQ69" s="10" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
     </row>
     <row r="70" spans="1:43" x14ac:dyDescent="0.35">
@@ -7749,11 +7944,11 @@
       <c r="R70" s="4"/>
       <c r="S70" s="4"/>
       <c r="AG70" s="10" t="s">
-        <v>890</v>
+        <v>867</v>
       </c>
       <c r="AH70" s="10"/>
       <c r="AQ70" s="10" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.35">
@@ -7781,11 +7976,11 @@
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
       <c r="AG71" s="10" t="s">
-        <v>892</v>
+        <v>869</v>
       </c>
       <c r="AH71" s="10"/>
       <c r="AQ71" s="10" t="s">
-        <v>893</v>
+        <v>870</v>
       </c>
     </row>
     <row r="72" spans="1:43" x14ac:dyDescent="0.35">
@@ -7813,11 +8008,11 @@
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
       <c r="AG72" s="10" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="AH72" s="10"/>
       <c r="AQ72" s="10" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.35">
@@ -7845,11 +8040,11 @@
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
       <c r="AG73" s="10" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="AH73" s="10"/>
       <c r="AQ73" s="10" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
     </row>
     <row r="74" spans="1:43" x14ac:dyDescent="0.35">
@@ -7877,11 +8072,11 @@
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
       <c r="AG74" s="10" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="AH74" s="10"/>
       <c r="AQ74" s="10" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.35">
@@ -7909,11 +8104,11 @@
       <c r="R75" s="4"/>
       <c r="S75" s="4"/>
       <c r="AG75" s="10" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="AH75" s="10"/>
       <c r="AQ75" s="10" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
     </row>
     <row r="76" spans="1:43" x14ac:dyDescent="0.35">
@@ -7941,11 +8136,11 @@
       <c r="R76" s="4"/>
       <c r="S76" s="4"/>
       <c r="AG76" s="10" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="AH76" s="10"/>
       <c r="AQ76" s="10" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
     </row>
     <row r="77" spans="1:43" x14ac:dyDescent="0.35">
@@ -7973,11 +8168,11 @@
       <c r="R77" s="4"/>
       <c r="S77" s="4"/>
       <c r="AG77" s="10" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="AH77" s="10"/>
       <c r="AQ77" s="10" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
     </row>
     <row r="78" spans="1:43" x14ac:dyDescent="0.35">
@@ -8005,11 +8200,11 @@
       <c r="R78" s="4"/>
       <c r="S78" s="4"/>
       <c r="AG78" s="10" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="AH78" s="10"/>
       <c r="AQ78" s="10" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
     </row>
     <row r="79" spans="1:43" x14ac:dyDescent="0.35">
@@ -8037,11 +8232,11 @@
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
       <c r="AG79" s="10" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="AH79" s="10"/>
       <c r="AQ79" s="10" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="80" spans="1:43" x14ac:dyDescent="0.35">
@@ -8069,11 +8264,11 @@
       <c r="R80" s="4"/>
       <c r="S80" s="4"/>
       <c r="AG80" s="10" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="AH80" s="10"/>
       <c r="AQ80" s="10" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
     </row>
     <row r="81" spans="1:43" x14ac:dyDescent="0.35">
@@ -8101,11 +8296,11 @@
       <c r="R81" s="4"/>
       <c r="S81" s="4"/>
       <c r="AG81" s="10" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="AH81" s="10"/>
       <c r="AQ81" s="10" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
     </row>
     <row r="82" spans="1:43" x14ac:dyDescent="0.35">
@@ -8133,11 +8328,11 @@
       <c r="R82" s="4"/>
       <c r="S82" s="4"/>
       <c r="AG82" s="10" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="AH82" s="10"/>
       <c r="AQ82" s="10" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
     </row>
     <row r="83" spans="1:43" x14ac:dyDescent="0.35">
@@ -8165,11 +8360,11 @@
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
       <c r="AG83" s="10" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
       <c r="AH83" s="10"/>
       <c r="AQ83" s="10" t="s">
-        <v>917</v>
+        <v>894</v>
       </c>
     </row>
     <row r="84" spans="1:43" x14ac:dyDescent="0.35">
@@ -8197,11 +8392,11 @@
       <c r="R84" s="4"/>
       <c r="S84" s="4"/>
       <c r="AG84" s="10" t="s">
-        <v>918</v>
+        <v>895</v>
       </c>
       <c r="AH84" s="10"/>
       <c r="AQ84" s="10" t="s">
-        <v>919</v>
+        <v>896</v>
       </c>
     </row>
     <row r="85" spans="1:43" x14ac:dyDescent="0.35">
@@ -8229,11 +8424,11 @@
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
       <c r="AG85" s="10" t="s">
-        <v>920</v>
+        <v>897</v>
       </c>
       <c r="AH85" s="10"/>
       <c r="AQ85" s="10" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
     </row>
     <row r="86" spans="1:43" x14ac:dyDescent="0.35">
@@ -8261,11 +8456,11 @@
       <c r="R86" s="4"/>
       <c r="S86" s="4"/>
       <c r="AG86" s="10" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="AH86" s="10"/>
       <c r="AQ86" s="10" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
     </row>
     <row r="87" spans="1:43" x14ac:dyDescent="0.35">
@@ -8293,11 +8488,11 @@
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
       <c r="AG87" s="10" t="s">
-        <v>924</v>
+        <v>901</v>
       </c>
       <c r="AH87" s="10"/>
       <c r="AQ87" s="10" t="s">
-        <v>925</v>
+        <v>902</v>
       </c>
     </row>
     <row r="88" spans="1:43" x14ac:dyDescent="0.35">
@@ -8325,11 +8520,11 @@
       <c r="R88" s="4"/>
       <c r="S88" s="4"/>
       <c r="AG88" s="10" t="s">
-        <v>926</v>
+        <v>903</v>
       </c>
       <c r="AH88" s="10"/>
       <c r="AQ88" s="10" t="s">
-        <v>927</v>
+        <v>904</v>
       </c>
     </row>
     <row r="89" spans="1:43" x14ac:dyDescent="0.35">
@@ -8357,11 +8552,11 @@
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
       <c r="AG89" s="10" t="s">
-        <v>928</v>
+        <v>905</v>
       </c>
       <c r="AH89" s="10"/>
       <c r="AQ89" s="10" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
     </row>
     <row r="90" spans="1:43" x14ac:dyDescent="0.35">
@@ -8389,11 +8584,11 @@
       <c r="R90" s="4"/>
       <c r="S90" s="4"/>
       <c r="AG90" s="10" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="AH90" s="10"/>
       <c r="AQ90" s="10" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.35">
@@ -8421,7 +8616,7 @@
       <c r="R91" s="4"/>
       <c r="S91" s="4"/>
       <c r="AQ91" s="10" t="s">
-        <v>932</v>
+        <v>909</v>
       </c>
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.35">
@@ -8449,7 +8644,7 @@
       <c r="R92" s="4"/>
       <c r="S92" s="4"/>
       <c r="AQ92" s="10" t="s">
-        <v>933</v>
+        <v>910</v>
       </c>
     </row>
     <row r="93" spans="1:43" x14ac:dyDescent="0.35">
@@ -8477,7 +8672,7 @@
       <c r="R93" s="4"/>
       <c r="S93" s="4"/>
       <c r="AQ93" s="10" t="s">
-        <v>934</v>
+        <v>911</v>
       </c>
     </row>
     <row r="94" spans="1:43" x14ac:dyDescent="0.35">
@@ -8505,7 +8700,7 @@
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
       <c r="AQ94" s="10" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="95" spans="1:43" x14ac:dyDescent="0.35">
@@ -8533,7 +8728,7 @@
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
       <c r="AQ95" s="10" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
     </row>
     <row r="96" spans="1:43" x14ac:dyDescent="0.35">
@@ -8561,7 +8756,7 @@
       <c r="R96" s="4"/>
       <c r="S96" s="4"/>
       <c r="AQ96" s="10" t="s">
-        <v>937</v>
+        <v>914</v>
       </c>
     </row>
     <row r="97" spans="1:43" x14ac:dyDescent="0.35">
@@ -8589,7 +8784,7 @@
       <c r="R97" s="4"/>
       <c r="S97" s="4"/>
       <c r="AQ97" s="10" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
     </row>
     <row r="98" spans="1:43" x14ac:dyDescent="0.35">
@@ -8617,7 +8812,7 @@
       <c r="R98" s="4"/>
       <c r="S98" s="4"/>
       <c r="AQ98" s="10" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
     </row>
     <row r="99" spans="1:43" x14ac:dyDescent="0.35">
@@ -8645,7 +8840,7 @@
       <c r="R99" s="4"/>
       <c r="S99" s="4"/>
       <c r="AQ99" s="10" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
     </row>
     <row r="100" spans="1:43" x14ac:dyDescent="0.35">
@@ -8673,7 +8868,7 @@
       <c r="R100" s="4"/>
       <c r="S100" s="4"/>
       <c r="AQ100" s="10" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
     </row>
     <row r="101" spans="1:43" x14ac:dyDescent="0.35">
@@ -8701,7 +8896,7 @@
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
       <c r="AQ101" s="10" t="s">
-        <v>942</v>
+        <v>919</v>
       </c>
     </row>
     <row r="102" spans="1:43" x14ac:dyDescent="0.35">
@@ -8729,7 +8924,7 @@
       <c r="R102" s="4"/>
       <c r="S102" s="4"/>
       <c r="AQ102" s="10" t="s">
-        <v>943</v>
+        <v>920</v>
       </c>
     </row>
     <row r="103" spans="1:43" x14ac:dyDescent="0.35">
@@ -8757,7 +8952,7 @@
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
       <c r="AQ103" s="10" t="s">
-        <v>944</v>
+        <v>921</v>
       </c>
     </row>
     <row r="104" spans="1:43" x14ac:dyDescent="0.35">
@@ -8785,7 +8980,7 @@
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
       <c r="AQ104" s="10" t="s">
-        <v>945</v>
+        <v>922</v>
       </c>
     </row>
     <row r="105" spans="1:43" x14ac:dyDescent="0.35">
@@ -8813,7 +9008,7 @@
       <c r="R105" s="4"/>
       <c r="S105" s="4"/>
       <c r="AQ105" s="10" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
     </row>
     <row r="106" spans="1:43" x14ac:dyDescent="0.35">
@@ -8841,7 +9036,7 @@
       <c r="R106" s="4"/>
       <c r="S106" s="4"/>
       <c r="AQ106" s="10" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
     </row>
     <row r="107" spans="1:43" x14ac:dyDescent="0.35">
@@ -8869,7 +9064,7 @@
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
       <c r="AQ107" s="10" t="s">
-        <v>948</v>
+        <v>925</v>
       </c>
     </row>
     <row r="108" spans="1:43" x14ac:dyDescent="0.35">
@@ -8897,7 +9092,7 @@
       <c r="R108" s="4"/>
       <c r="S108" s="4"/>
       <c r="AQ108" s="10" t="s">
-        <v>949</v>
+        <v>926</v>
       </c>
     </row>
     <row r="109" spans="1:43" x14ac:dyDescent="0.35">
@@ -8925,7 +9120,7 @@
       <c r="R109" s="4"/>
       <c r="S109" s="4"/>
       <c r="AQ109" s="10" t="s">
-        <v>950</v>
+        <v>927</v>
       </c>
     </row>
     <row r="110" spans="1:43" x14ac:dyDescent="0.35">
@@ -8953,7 +9148,7 @@
       <c r="R110" s="4"/>
       <c r="S110" s="4"/>
       <c r="AQ110" s="10" t="s">
-        <v>951</v>
+        <v>928</v>
       </c>
     </row>
     <row r="111" spans="1:43" x14ac:dyDescent="0.35">
@@ -8981,7 +9176,7 @@
       <c r="R111" s="4"/>
       <c r="S111" s="4"/>
       <c r="AQ111" s="10" t="s">
-        <v>952</v>
+        <v>929</v>
       </c>
     </row>
     <row r="112" spans="1:43" x14ac:dyDescent="0.35">
@@ -9009,7 +9204,7 @@
       <c r="R112" s="4"/>
       <c r="S112" s="4"/>
       <c r="AQ112" s="10" t="s">
-        <v>953</v>
+        <v>930</v>
       </c>
     </row>
     <row r="113" spans="1:43" x14ac:dyDescent="0.35">
@@ -9037,7 +9232,7 @@
       <c r="R113" s="4"/>
       <c r="S113" s="4"/>
       <c r="AQ113" s="10" t="s">
-        <v>954</v>
+        <v>931</v>
       </c>
     </row>
     <row r="114" spans="1:43" x14ac:dyDescent="0.35">
@@ -9065,7 +9260,7 @@
       <c r="R114" s="4"/>
       <c r="S114" s="4"/>
       <c r="AQ114" s="10" t="s">
-        <v>955</v>
+        <v>932</v>
       </c>
     </row>
     <row r="115" spans="1:43" x14ac:dyDescent="0.35">
@@ -9093,7 +9288,7 @@
       <c r="R115" s="4"/>
       <c r="S115" s="4"/>
       <c r="AQ115" s="10" t="s">
-        <v>956</v>
+        <v>933</v>
       </c>
     </row>
     <row r="116" spans="1:43" x14ac:dyDescent="0.35">
@@ -9121,7 +9316,7 @@
       <c r="R116" s="4"/>
       <c r="S116" s="4"/>
       <c r="AQ116" s="10" t="s">
-        <v>957</v>
+        <v>934</v>
       </c>
     </row>
     <row r="117" spans="1:43" x14ac:dyDescent="0.35">
@@ -9149,7 +9344,7 @@
       <c r="R117" s="4"/>
       <c r="S117" s="4"/>
       <c r="AQ117" s="10" t="s">
-        <v>958</v>
+        <v>935</v>
       </c>
     </row>
     <row r="118" spans="1:43" x14ac:dyDescent="0.35">
@@ -9177,7 +9372,7 @@
       <c r="R118" s="4"/>
       <c r="S118" s="4"/>
       <c r="AQ118" s="10" t="s">
-        <v>959</v>
+        <v>936</v>
       </c>
     </row>
     <row r="119" spans="1:43" x14ac:dyDescent="0.35">
@@ -9205,7 +9400,7 @@
       <c r="R119" s="4"/>
       <c r="S119" s="4"/>
       <c r="AQ119" s="10" t="s">
-        <v>960</v>
+        <v>937</v>
       </c>
     </row>
     <row r="120" spans="1:43" x14ac:dyDescent="0.35">
@@ -9233,7 +9428,7 @@
       <c r="R120" s="4"/>
       <c r="S120" s="4"/>
       <c r="AQ120" s="10" t="s">
-        <v>961</v>
+        <v>938</v>
       </c>
     </row>
     <row r="121" spans="1:43" x14ac:dyDescent="0.35">
@@ -9261,7 +9456,7 @@
       <c r="R121" s="4"/>
       <c r="S121" s="4"/>
       <c r="AQ121" s="10" t="s">
-        <v>962</v>
+        <v>939</v>
       </c>
     </row>
     <row r="122" spans="1:43" x14ac:dyDescent="0.35">
@@ -9289,7 +9484,7 @@
       <c r="R122" s="4"/>
       <c r="S122" s="4"/>
       <c r="AQ122" s="10" t="s">
-        <v>963</v>
+        <v>940</v>
       </c>
     </row>
     <row r="123" spans="1:43" x14ac:dyDescent="0.35">
@@ -9317,7 +9512,7 @@
       <c r="R123" s="4"/>
       <c r="S123" s="4"/>
       <c r="AQ123" s="10" t="s">
-        <v>964</v>
+        <v>941</v>
       </c>
     </row>
     <row r="124" spans="1:43" x14ac:dyDescent="0.35">
@@ -9345,7 +9540,7 @@
       <c r="R124" s="4"/>
       <c r="S124" s="4"/>
       <c r="AQ124" s="10" t="s">
-        <v>965</v>
+        <v>942</v>
       </c>
     </row>
     <row r="125" spans="1:43" x14ac:dyDescent="0.35">
@@ -9373,7 +9568,7 @@
       <c r="R125" s="4"/>
       <c r="S125" s="4"/>
       <c r="AQ125" s="10" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
     </row>
     <row r="126" spans="1:43" x14ac:dyDescent="0.35">
@@ -9401,7 +9596,7 @@
       <c r="R126" s="4"/>
       <c r="S126" s="4"/>
       <c r="AQ126" s="10" t="s">
-        <v>967</v>
+        <v>944</v>
       </c>
     </row>
     <row r="127" spans="1:43" x14ac:dyDescent="0.35">
@@ -9429,7 +9624,7 @@
       <c r="R127" s="4"/>
       <c r="S127" s="4"/>
       <c r="AQ127" s="10" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
     </row>
     <row r="128" spans="1:43" x14ac:dyDescent="0.35">
@@ -9457,7 +9652,7 @@
       <c r="R128" s="4"/>
       <c r="S128" s="4"/>
       <c r="AQ128" s="10" t="s">
-        <v>969</v>
+        <v>946</v>
       </c>
     </row>
     <row r="129" spans="1:43" x14ac:dyDescent="0.35">
@@ -9485,7 +9680,7 @@
       <c r="R129" s="4"/>
       <c r="S129" s="4"/>
       <c r="AQ129" s="10" t="s">
-        <v>970</v>
+        <v>947</v>
       </c>
     </row>
     <row r="130" spans="1:43" x14ac:dyDescent="0.35">
@@ -9513,7 +9708,7 @@
       <c r="R130" s="4"/>
       <c r="S130" s="4"/>
       <c r="AQ130" s="10" t="s">
-        <v>971</v>
+        <v>948</v>
       </c>
     </row>
     <row r="131" spans="1:43" x14ac:dyDescent="0.35">
@@ -9541,7 +9736,7 @@
       <c r="R131" s="4"/>
       <c r="S131" s="4"/>
       <c r="AQ131" s="10" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
     </row>
     <row r="132" spans="1:43" x14ac:dyDescent="0.35">
@@ -9569,7 +9764,7 @@
       <c r="R132" s="4"/>
       <c r="S132" s="4"/>
       <c r="AQ132" s="10" t="s">
-        <v>973</v>
+        <v>950</v>
       </c>
     </row>
     <row r="133" spans="1:43" x14ac:dyDescent="0.35">
@@ -9597,7 +9792,7 @@
       <c r="R133" s="4"/>
       <c r="S133" s="4"/>
       <c r="AQ133" s="10" t="s">
-        <v>974</v>
+        <v>951</v>
       </c>
     </row>
     <row r="134" spans="1:43" x14ac:dyDescent="0.35">
@@ -9625,7 +9820,7 @@
       <c r="R134" s="4"/>
       <c r="S134" s="4"/>
       <c r="AQ134" s="10" t="s">
-        <v>975</v>
+        <v>952</v>
       </c>
     </row>
     <row r="135" spans="1:43" x14ac:dyDescent="0.35">
@@ -9653,7 +9848,7 @@
       <c r="R135" s="4"/>
       <c r="S135" s="4"/>
       <c r="AQ135" s="10" t="s">
-        <v>976</v>
+        <v>953</v>
       </c>
     </row>
     <row r="136" spans="1:43" x14ac:dyDescent="0.35">
@@ -9681,7 +9876,7 @@
       <c r="R136" s="4"/>
       <c r="S136" s="4"/>
       <c r="AQ136" s="10" t="s">
-        <v>977</v>
+        <v>954</v>
       </c>
     </row>
     <row r="137" spans="1:43" x14ac:dyDescent="0.35">
@@ -9709,7 +9904,7 @@
       <c r="R137" s="4"/>
       <c r="S137" s="4"/>
       <c r="AQ137" s="10" t="s">
-        <v>978</v>
+        <v>955</v>
       </c>
     </row>
     <row r="138" spans="1:43" x14ac:dyDescent="0.35">
@@ -9737,7 +9932,7 @@
       <c r="R138" s="4"/>
       <c r="S138" s="4"/>
       <c r="AQ138" s="10" t="s">
-        <v>979</v>
+        <v>956</v>
       </c>
     </row>
     <row r="139" spans="1:43" x14ac:dyDescent="0.35">
@@ -9765,7 +9960,7 @@
       <c r="R139" s="4"/>
       <c r="S139" s="4"/>
       <c r="AQ139" s="10" t="s">
-        <v>980</v>
+        <v>957</v>
       </c>
     </row>
     <row r="140" spans="1:43" x14ac:dyDescent="0.35">
@@ -9793,7 +9988,7 @@
       <c r="R140" s="4"/>
       <c r="S140" s="4"/>
       <c r="AQ140" s="10" t="s">
-        <v>981</v>
+        <v>958</v>
       </c>
     </row>
     <row r="141" spans="1:43" x14ac:dyDescent="0.35">
@@ -9821,7 +10016,7 @@
       <c r="R141" s="4"/>
       <c r="S141" s="4"/>
       <c r="AQ141" s="10" t="s">
-        <v>982</v>
+        <v>959</v>
       </c>
     </row>
     <row r="142" spans="1:43" x14ac:dyDescent="0.35">
@@ -9849,7 +10044,7 @@
       <c r="R142" s="4"/>
       <c r="S142" s="4"/>
       <c r="AQ142" s="10" t="s">
-        <v>983</v>
+        <v>960</v>
       </c>
     </row>
     <row r="143" spans="1:43" x14ac:dyDescent="0.35">
@@ -9877,7 +10072,7 @@
       <c r="R143" s="4"/>
       <c r="S143" s="4"/>
       <c r="AQ143" s="10" t="s">
-        <v>984</v>
+        <v>961</v>
       </c>
     </row>
     <row r="144" spans="1:43" x14ac:dyDescent="0.35">
@@ -9905,7 +10100,7 @@
       <c r="R144" s="4"/>
       <c r="S144" s="4"/>
       <c r="AQ144" s="10" t="s">
-        <v>985</v>
+        <v>962</v>
       </c>
     </row>
     <row r="145" spans="1:43" x14ac:dyDescent="0.35">
@@ -9933,7 +10128,7 @@
       <c r="R145" s="4"/>
       <c r="S145" s="4"/>
       <c r="AQ145" s="10" t="s">
-        <v>986</v>
+        <v>963</v>
       </c>
     </row>
     <row r="146" spans="1:43" x14ac:dyDescent="0.35">
@@ -9961,7 +10156,7 @@
       <c r="R146" s="4"/>
       <c r="S146" s="4"/>
       <c r="AQ146" s="10" t="s">
-        <v>987</v>
+        <v>964</v>
       </c>
     </row>
     <row r="147" spans="1:43" x14ac:dyDescent="0.35">
@@ -9989,7 +10184,7 @@
       <c r="R147" s="4"/>
       <c r="S147" s="4"/>
       <c r="AQ147" s="10" t="s">
-        <v>988</v>
+        <v>965</v>
       </c>
     </row>
     <row r="148" spans="1:43" x14ac:dyDescent="0.35">
@@ -10017,7 +10212,7 @@
       <c r="R148" s="4"/>
       <c r="S148" s="4"/>
       <c r="AQ148" s="10" t="s">
-        <v>989</v>
+        <v>966</v>
       </c>
     </row>
     <row r="149" spans="1:43" x14ac:dyDescent="0.35">
@@ -10045,7 +10240,7 @@
       <c r="R149" s="4"/>
       <c r="S149" s="4"/>
       <c r="AQ149" s="10" t="s">
-        <v>990</v>
+        <v>967</v>
       </c>
     </row>
     <row r="150" spans="1:43" x14ac:dyDescent="0.35">
@@ -10073,7 +10268,7 @@
       <c r="R150" s="4"/>
       <c r="S150" s="4"/>
       <c r="AQ150" s="10" t="s">
-        <v>991</v>
+        <v>968</v>
       </c>
     </row>
     <row r="151" spans="1:43" x14ac:dyDescent="0.35">
@@ -10101,7 +10296,7 @@
       <c r="R151" s="4"/>
       <c r="S151" s="4"/>
       <c r="AQ151" s="10" t="s">
-        <v>992</v>
+        <v>969</v>
       </c>
     </row>
     <row r="152" spans="1:43" x14ac:dyDescent="0.35">
@@ -10129,7 +10324,7 @@
       <c r="R152" s="4"/>
       <c r="S152" s="4"/>
       <c r="AQ152" s="10" t="s">
-        <v>993</v>
+        <v>970</v>
       </c>
     </row>
     <row r="153" spans="1:43" x14ac:dyDescent="0.35">
@@ -10157,7 +10352,7 @@
       <c r="R153" s="4"/>
       <c r="S153" s="4"/>
       <c r="AQ153" s="10" t="s">
-        <v>994</v>
+        <v>971</v>
       </c>
     </row>
     <row r="154" spans="1:43" x14ac:dyDescent="0.35">
@@ -10185,7 +10380,7 @@
       <c r="R154" s="4"/>
       <c r="S154" s="4"/>
       <c r="AQ154" s="10" t="s">
-        <v>995</v>
+        <v>972</v>
       </c>
     </row>
     <row r="155" spans="1:43" x14ac:dyDescent="0.35">
@@ -10213,7 +10408,7 @@
       <c r="R155" s="4"/>
       <c r="S155" s="4"/>
       <c r="AQ155" s="10" t="s">
-        <v>996</v>
+        <v>973</v>
       </c>
     </row>
     <row r="156" spans="1:43" x14ac:dyDescent="0.35">
@@ -10241,7 +10436,7 @@
       <c r="R156" s="4"/>
       <c r="S156" s="4"/>
       <c r="AQ156" s="10" t="s">
-        <v>997</v>
+        <v>974</v>
       </c>
     </row>
     <row r="157" spans="1:43" x14ac:dyDescent="0.35">
@@ -10269,7 +10464,7 @@
       <c r="R157" s="4"/>
       <c r="S157" s="4"/>
       <c r="AQ157" s="10" t="s">
-        <v>998</v>
+        <v>975</v>
       </c>
     </row>
     <row r="158" spans="1:43" x14ac:dyDescent="0.35">
@@ -10297,7 +10492,7 @@
       <c r="R158" s="4"/>
       <c r="S158" s="4"/>
       <c r="AQ158" s="10" t="s">
-        <v>999</v>
+        <v>976</v>
       </c>
     </row>
     <row r="159" spans="1:43" x14ac:dyDescent="0.35">
@@ -10325,7 +10520,7 @@
       <c r="R159" s="4"/>
       <c r="S159" s="4"/>
       <c r="AQ159" s="10" t="s">
-        <v>1000</v>
+        <v>977</v>
       </c>
     </row>
     <row r="160" spans="1:43" x14ac:dyDescent="0.35">
@@ -10353,7 +10548,7 @@
       <c r="R160" s="4"/>
       <c r="S160" s="4"/>
       <c r="AQ160" s="10" t="s">
-        <v>1001</v>
+        <v>978</v>
       </c>
     </row>
     <row r="161" spans="1:43" x14ac:dyDescent="0.35">
@@ -10381,7 +10576,7 @@
       <c r="R161" s="4"/>
       <c r="S161" s="4"/>
       <c r="AQ161" s="10" t="s">
-        <v>1002</v>
+        <v>979</v>
       </c>
     </row>
     <row r="162" spans="1:43" x14ac:dyDescent="0.35">
@@ -10409,7 +10604,7 @@
       <c r="R162" s="4"/>
       <c r="S162" s="4"/>
       <c r="AQ162" s="10" t="s">
-        <v>1003</v>
+        <v>980</v>
       </c>
     </row>
     <row r="163" spans="1:43" x14ac:dyDescent="0.35">
@@ -10437,7 +10632,7 @@
       <c r="R163" s="4"/>
       <c r="S163" s="4"/>
       <c r="AQ163" s="10" t="s">
-        <v>1004</v>
+        <v>981</v>
       </c>
     </row>
     <row r="164" spans="1:43" x14ac:dyDescent="0.35">
@@ -10465,7 +10660,7 @@
       <c r="R164" s="4"/>
       <c r="S164" s="4"/>
       <c r="AQ164" s="10" t="s">
-        <v>1005</v>
+        <v>982</v>
       </c>
     </row>
     <row r="165" spans="1:43" x14ac:dyDescent="0.35">
@@ -10493,7 +10688,7 @@
       <c r="R165" s="4"/>
       <c r="S165" s="4"/>
       <c r="AQ165" s="10" t="s">
-        <v>1006</v>
+        <v>983</v>
       </c>
     </row>
     <row r="166" spans="1:43" x14ac:dyDescent="0.35">
@@ -10521,7 +10716,7 @@
       <c r="R166" s="4"/>
       <c r="S166" s="4"/>
       <c r="AQ166" s="10" t="s">
-        <v>1007</v>
+        <v>984</v>
       </c>
     </row>
     <row r="167" spans="1:43" x14ac:dyDescent="0.35">
@@ -10549,7 +10744,7 @@
       <c r="R167" s="4"/>
       <c r="S167" s="4"/>
       <c r="AQ167" s="10" t="s">
-        <v>1008</v>
+        <v>985</v>
       </c>
     </row>
     <row r="168" spans="1:43" x14ac:dyDescent="0.35">
@@ -10577,7 +10772,7 @@
       <c r="R168" s="4"/>
       <c r="S168" s="4"/>
       <c r="AQ168" s="10" t="s">
-        <v>1009</v>
+        <v>986</v>
       </c>
     </row>
     <row r="169" spans="1:43" x14ac:dyDescent="0.35">
@@ -10605,7 +10800,7 @@
       <c r="R169" s="4"/>
       <c r="S169" s="4"/>
       <c r="AQ169" s="10" t="s">
-        <v>1010</v>
+        <v>987</v>
       </c>
     </row>
     <row r="170" spans="1:43" x14ac:dyDescent="0.35">
@@ -10633,7 +10828,7 @@
       <c r="R170" s="4"/>
       <c r="S170" s="4"/>
       <c r="AQ170" s="10" t="s">
-        <v>1011</v>
+        <v>988</v>
       </c>
     </row>
     <row r="171" spans="1:43" x14ac:dyDescent="0.35">
@@ -10661,7 +10856,7 @@
       <c r="R171" s="4"/>
       <c r="S171" s="4"/>
       <c r="AQ171" s="10" t="s">
-        <v>1012</v>
+        <v>989</v>
       </c>
     </row>
     <row r="172" spans="1:43" x14ac:dyDescent="0.35">
@@ -10689,7 +10884,7 @@
       <c r="R172" s="4"/>
       <c r="S172" s="4"/>
       <c r="AQ172" s="10" t="s">
-        <v>1013</v>
+        <v>990</v>
       </c>
     </row>
     <row r="173" spans="1:43" x14ac:dyDescent="0.35">
@@ -10717,7 +10912,7 @@
       <c r="R173" s="4"/>
       <c r="S173" s="4"/>
       <c r="AQ173" s="10" t="s">
-        <v>1014</v>
+        <v>991</v>
       </c>
     </row>
     <row r="174" spans="1:43" x14ac:dyDescent="0.35">
@@ -10745,7 +10940,7 @@
       <c r="R174" s="4"/>
       <c r="S174" s="4"/>
       <c r="AQ174" s="10" t="s">
-        <v>1015</v>
+        <v>992</v>
       </c>
     </row>
     <row r="175" spans="1:43" x14ac:dyDescent="0.35">
@@ -10773,7 +10968,7 @@
       <c r="R175" s="4"/>
       <c r="S175" s="4"/>
       <c r="AQ175" s="10" t="s">
-        <v>1016</v>
+        <v>993</v>
       </c>
     </row>
     <row r="176" spans="1:43" x14ac:dyDescent="0.35">
@@ -10801,7 +10996,7 @@
       <c r="R176" s="4"/>
       <c r="S176" s="4"/>
       <c r="AQ176" s="10" t="s">
-        <v>1017</v>
+        <v>994</v>
       </c>
     </row>
     <row r="177" spans="1:43" x14ac:dyDescent="0.35">
@@ -10829,7 +11024,7 @@
       <c r="R177" s="4"/>
       <c r="S177" s="4"/>
       <c r="AQ177" s="10" t="s">
-        <v>1018</v>
+        <v>995</v>
       </c>
     </row>
     <row r="178" spans="1:43" x14ac:dyDescent="0.35">
@@ -10857,7 +11052,7 @@
       <c r="R178" s="4"/>
       <c r="S178" s="4"/>
       <c r="AQ178" s="10" t="s">
-        <v>1019</v>
+        <v>996</v>
       </c>
     </row>
     <row r="179" spans="1:43" x14ac:dyDescent="0.35">
@@ -10885,7 +11080,7 @@
       <c r="R179" s="4"/>
       <c r="S179" s="4"/>
       <c r="AQ179" s="10" t="s">
-        <v>1020</v>
+        <v>997</v>
       </c>
     </row>
     <row r="180" spans="1:43" x14ac:dyDescent="0.35">
@@ -10913,7 +11108,7 @@
       <c r="R180" s="4"/>
       <c r="S180" s="4"/>
       <c r="AQ180" s="10" t="s">
-        <v>1021</v>
+        <v>998</v>
       </c>
     </row>
     <row r="181" spans="1:43" x14ac:dyDescent="0.35">
@@ -10941,7 +11136,7 @@
       <c r="R181" s="4"/>
       <c r="S181" s="4"/>
       <c r="AQ181" s="10" t="s">
-        <v>1022</v>
+        <v>999</v>
       </c>
     </row>
     <row r="182" spans="1:43" x14ac:dyDescent="0.35">
@@ -10969,7 +11164,7 @@
       <c r="R182" s="4"/>
       <c r="S182" s="4"/>
       <c r="AQ182" s="10" t="s">
-        <v>1023</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="183" spans="1:43" x14ac:dyDescent="0.35">
@@ -10997,7 +11192,7 @@
       <c r="R183" s="4"/>
       <c r="S183" s="4"/>
       <c r="AQ183" s="10" t="s">
-        <v>1024</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="184" spans="1:43" x14ac:dyDescent="0.35">
@@ -11025,7 +11220,7 @@
       <c r="R184" s="4"/>
       <c r="S184" s="4"/>
       <c r="AQ184" s="10" t="s">
-        <v>1025</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="185" spans="1:43" x14ac:dyDescent="0.35">
@@ -11053,7 +11248,7 @@
       <c r="R185" s="4"/>
       <c r="S185" s="4"/>
       <c r="AQ185" s="10" t="s">
-        <v>1026</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="186" spans="1:43" x14ac:dyDescent="0.35">
@@ -11081,7 +11276,7 @@
       <c r="R186" s="4"/>
       <c r="S186" s="4"/>
       <c r="AQ186" s="10" t="s">
-        <v>1027</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="187" spans="1:43" x14ac:dyDescent="0.35">
@@ -11109,7 +11304,7 @@
       <c r="R187" s="4"/>
       <c r="S187" s="4"/>
       <c r="AQ187" s="10" t="s">
-        <v>1028</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="188" spans="1:43" x14ac:dyDescent="0.35">
@@ -11137,7 +11332,7 @@
       <c r="R188" s="4"/>
       <c r="S188" s="4"/>
       <c r="AQ188" s="10" t="s">
-        <v>1029</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="189" spans="1:43" x14ac:dyDescent="0.35">
@@ -11165,7 +11360,7 @@
       <c r="R189" s="4"/>
       <c r="S189" s="4"/>
       <c r="AQ189" s="10" t="s">
-        <v>1030</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="190" spans="1:43" x14ac:dyDescent="0.35">
@@ -11193,7 +11388,7 @@
       <c r="R190" s="4"/>
       <c r="S190" s="4"/>
       <c r="AQ190" s="10" t="s">
-        <v>1031</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="191" spans="1:43" x14ac:dyDescent="0.35">
@@ -11221,7 +11416,7 @@
       <c r="R191" s="4"/>
       <c r="S191" s="4"/>
       <c r="AQ191" s="10" t="s">
-        <v>1032</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="192" spans="1:43" x14ac:dyDescent="0.35">
@@ -11249,7 +11444,7 @@
       <c r="R192" s="4"/>
       <c r="S192" s="4"/>
       <c r="AQ192" s="10" t="s">
-        <v>1033</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="193" spans="1:43" x14ac:dyDescent="0.35">
@@ -11277,7 +11472,7 @@
       <c r="R193" s="4"/>
       <c r="S193" s="4"/>
       <c r="AQ193" s="10" t="s">
-        <v>1034</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="194" spans="1:43" x14ac:dyDescent="0.35">
@@ -11305,7 +11500,7 @@
       <c r="R194" s="4"/>
       <c r="S194" s="4"/>
       <c r="AQ194" s="10" t="s">
-        <v>1035</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="195" spans="1:43" x14ac:dyDescent="0.35">
@@ -11333,7 +11528,7 @@
       <c r="R195" s="4"/>
       <c r="S195" s="4"/>
       <c r="AQ195" s="10" t="s">
-        <v>1036</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="196" spans="1:43" x14ac:dyDescent="0.35">
@@ -11361,7 +11556,7 @@
       <c r="R196" s="4"/>
       <c r="S196" s="4"/>
       <c r="AQ196" s="10" t="s">
-        <v>1037</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="197" spans="1:43" x14ac:dyDescent="0.35">
@@ -11389,7 +11584,7 @@
       <c r="R197" s="4"/>
       <c r="S197" s="4"/>
       <c r="AQ197" s="10" t="s">
-        <v>1038</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="198" spans="1:43" x14ac:dyDescent="0.35">
@@ -11417,7 +11612,7 @@
       <c r="R198" s="4"/>
       <c r="S198" s="4"/>
       <c r="AQ198" s="10" t="s">
-        <v>1039</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="199" spans="1:43" x14ac:dyDescent="0.35">
@@ -11445,7 +11640,7 @@
       <c r="R199" s="4"/>
       <c r="S199" s="4"/>
       <c r="AQ199" s="10" t="s">
-        <v>1040</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="200" spans="1:43" x14ac:dyDescent="0.35">
@@ -11473,7 +11668,7 @@
       <c r="R200" s="4"/>
       <c r="S200" s="4"/>
       <c r="AQ200" s="10" t="s">
-        <v>1041</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="201" spans="1:43" x14ac:dyDescent="0.35">
@@ -11501,7 +11696,7 @@
       <c r="R201" s="4"/>
       <c r="S201" s="4"/>
       <c r="AQ201" s="10" t="s">
-        <v>1042</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="202" spans="1:43" x14ac:dyDescent="0.35">
@@ -11529,7 +11724,7 @@
       <c r="R202" s="4"/>
       <c r="S202" s="4"/>
       <c r="AQ202" s="10" t="s">
-        <v>1043</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="203" spans="1:43" x14ac:dyDescent="0.35">
@@ -11557,7 +11752,7 @@
       <c r="R203" s="4"/>
       <c r="S203" s="4"/>
       <c r="AQ203" s="10" t="s">
-        <v>1044</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="204" spans="1:43" x14ac:dyDescent="0.35">
@@ -11585,7 +11780,7 @@
       <c r="R204" s="4"/>
       <c r="S204" s="4"/>
       <c r="AQ204" s="10" t="s">
-        <v>1045</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="205" spans="1:43" x14ac:dyDescent="0.35">
@@ -11613,7 +11808,7 @@
       <c r="R205" s="4"/>
       <c r="S205" s="4"/>
       <c r="AQ205" s="10" t="s">
-        <v>1046</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="206" spans="1:43" x14ac:dyDescent="0.35">
@@ -11641,7 +11836,7 @@
       <c r="R206" s="4"/>
       <c r="S206" s="4"/>
       <c r="AQ206" s="10" t="s">
-        <v>1047</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="207" spans="1:43" x14ac:dyDescent="0.35">
@@ -11669,7 +11864,7 @@
       <c r="R207" s="4"/>
       <c r="S207" s="4"/>
       <c r="AQ207" s="10" t="s">
-        <v>1048</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="208" spans="1:43" x14ac:dyDescent="0.35">
@@ -11697,7 +11892,7 @@
       <c r="R208" s="4"/>
       <c r="S208" s="4"/>
       <c r="AQ208" s="10" t="s">
-        <v>1049</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="209" spans="1:43" x14ac:dyDescent="0.35">
@@ -11725,7 +11920,7 @@
       <c r="R209" s="4"/>
       <c r="S209" s="4"/>
       <c r="AQ209" s="10" t="s">
-        <v>1050</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="210" spans="1:43" x14ac:dyDescent="0.35">
@@ -11753,7 +11948,7 @@
       <c r="R210" s="4"/>
       <c r="S210" s="4"/>
       <c r="AQ210" s="10" t="s">
-        <v>1051</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="211" spans="1:43" x14ac:dyDescent="0.35">
@@ -11781,7 +11976,7 @@
       <c r="R211" s="4"/>
       <c r="S211" s="4"/>
       <c r="AQ211" s="10" t="s">
-        <v>1052</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="212" spans="1:43" x14ac:dyDescent="0.35">
@@ -11809,7 +12004,7 @@
       <c r="R212" s="4"/>
       <c r="S212" s="4"/>
       <c r="AQ212" s="10" t="s">
-        <v>1053</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="213" spans="1:43" x14ac:dyDescent="0.35">
@@ -11837,7 +12032,7 @@
       <c r="R213" s="4"/>
       <c r="S213" s="4"/>
       <c r="AQ213" s="10" t="s">
-        <v>1054</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="214" spans="1:43" x14ac:dyDescent="0.35">
@@ -11865,7 +12060,7 @@
       <c r="R214" s="4"/>
       <c r="S214" s="4"/>
       <c r="AQ214" s="10" t="s">
-        <v>1055</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="215" spans="1:43" x14ac:dyDescent="0.35">
@@ -11893,7 +12088,7 @@
       <c r="R215" s="4"/>
       <c r="S215" s="4"/>
       <c r="AQ215" s="10" t="s">
-        <v>1056</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="216" spans="1:43" x14ac:dyDescent="0.35">
@@ -11921,7 +12116,7 @@
       <c r="R216" s="4"/>
       <c r="S216" s="4"/>
       <c r="AQ216" s="10" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="217" spans="1:43" x14ac:dyDescent="0.35">
@@ -11949,7 +12144,7 @@
       <c r="R217" s="4"/>
       <c r="S217" s="4"/>
       <c r="AQ217" s="10" t="s">
-        <v>1058</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="218" spans="1:43" x14ac:dyDescent="0.35">
@@ -11977,7 +12172,7 @@
       <c r="R218" s="4"/>
       <c r="S218" s="4"/>
       <c r="AQ218" s="10" t="s">
-        <v>1059</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="219" spans="1:43" x14ac:dyDescent="0.35">
@@ -12005,7 +12200,7 @@
       <c r="R219" s="4"/>
       <c r="S219" s="4"/>
       <c r="AQ219" s="10" t="s">
-        <v>1060</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="220" spans="1:43" x14ac:dyDescent="0.35">
@@ -12033,7 +12228,7 @@
       <c r="R220" s="4"/>
       <c r="S220" s="4"/>
       <c r="AQ220" s="10" t="s">
-        <v>1061</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="221" spans="1:43" x14ac:dyDescent="0.35">
@@ -12061,7 +12256,7 @@
       <c r="R221" s="4"/>
       <c r="S221" s="4"/>
       <c r="AQ221" s="10" t="s">
-        <v>1062</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="222" spans="1:43" x14ac:dyDescent="0.35">
@@ -12089,7 +12284,7 @@
       <c r="R222" s="4"/>
       <c r="S222" s="4"/>
       <c r="AQ222" s="10" t="s">
-        <v>1063</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="223" spans="1:43" x14ac:dyDescent="0.35">
@@ -12117,7 +12312,7 @@
       <c r="R223" s="4"/>
       <c r="S223" s="4"/>
       <c r="AQ223" s="10" t="s">
-        <v>1064</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="224" spans="1:43" x14ac:dyDescent="0.35">
@@ -12145,7 +12340,7 @@
       <c r="R224" s="4"/>
       <c r="S224" s="4"/>
       <c r="AQ224" s="10" t="s">
-        <v>1065</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="225" spans="1:43" x14ac:dyDescent="0.35">
@@ -12173,7 +12368,7 @@
       <c r="R225" s="4"/>
       <c r="S225" s="4"/>
       <c r="AQ225" s="10" t="s">
-        <v>1066</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="226" spans="1:43" x14ac:dyDescent="0.35">
@@ -12201,7 +12396,7 @@
       <c r="R226" s="4"/>
       <c r="S226" s="4"/>
       <c r="AQ226" s="10" t="s">
-        <v>1067</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="227" spans="1:43" x14ac:dyDescent="0.35">
@@ -12229,7 +12424,7 @@
       <c r="R227" s="4"/>
       <c r="S227" s="4"/>
       <c r="AQ227" s="10" t="s">
-        <v>1068</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="228" spans="1:43" x14ac:dyDescent="0.35">
@@ -12257,7 +12452,7 @@
       <c r="R228" s="4"/>
       <c r="S228" s="4"/>
       <c r="AQ228" s="10" t="s">
-        <v>1069</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="229" spans="1:43" x14ac:dyDescent="0.35">
@@ -12285,7 +12480,7 @@
       <c r="R229" s="4"/>
       <c r="S229" s="4"/>
       <c r="AQ229" s="10" t="s">
-        <v>1070</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="230" spans="1:43" x14ac:dyDescent="0.35">
@@ -12313,7 +12508,7 @@
       <c r="R230" s="4"/>
       <c r="S230" s="4"/>
       <c r="AQ230" s="10" t="s">
-        <v>1071</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="231" spans="1:43" x14ac:dyDescent="0.35">
@@ -12341,7 +12536,7 @@
       <c r="R231" s="4"/>
       <c r="S231" s="4"/>
       <c r="AQ231" s="10" t="s">
-        <v>1072</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="232" spans="1:43" x14ac:dyDescent="0.35">
@@ -12369,7 +12564,7 @@
       <c r="R232" s="4"/>
       <c r="S232" s="4"/>
       <c r="AQ232" s="10" t="s">
-        <v>1073</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="233" spans="1:43" x14ac:dyDescent="0.35">
@@ -12397,7 +12592,7 @@
       <c r="R233" s="4"/>
       <c r="S233" s="4"/>
       <c r="AQ233" s="10" t="s">
-        <v>1074</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="234" spans="1:43" x14ac:dyDescent="0.35">
@@ -12425,7 +12620,7 @@
       <c r="R234" s="4"/>
       <c r="S234" s="4"/>
       <c r="AQ234" s="10" t="s">
-        <v>1075</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="235" spans="1:43" x14ac:dyDescent="0.35">
@@ -12453,7 +12648,7 @@
       <c r="R235" s="4"/>
       <c r="S235" s="4"/>
       <c r="AQ235" s="10" t="s">
-        <v>1076</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="236" spans="1:43" x14ac:dyDescent="0.35">
@@ -12481,7 +12676,7 @@
       <c r="R236" s="4"/>
       <c r="S236" s="4"/>
       <c r="AQ236" s="10" t="s">
-        <v>1077</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="237" spans="1:43" x14ac:dyDescent="0.35">
@@ -12509,7 +12704,7 @@
       <c r="R237" s="4"/>
       <c r="S237" s="4"/>
       <c r="AQ237" s="10" t="s">
-        <v>1078</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="238" spans="1:43" x14ac:dyDescent="0.35">
@@ -12537,7 +12732,7 @@
       <c r="R238" s="4"/>
       <c r="S238" s="4"/>
       <c r="AQ238" s="10" t="s">
-        <v>1079</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="239" spans="1:43" x14ac:dyDescent="0.35">
@@ -12565,7 +12760,7 @@
       <c r="R239" s="4"/>
       <c r="S239" s="4"/>
       <c r="AQ239" s="10" t="s">
-        <v>1080</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="240" spans="1:43" x14ac:dyDescent="0.35">
@@ -12593,7 +12788,7 @@
       <c r="R240" s="4"/>
       <c r="S240" s="4"/>
       <c r="AQ240" s="10" t="s">
-        <v>1081</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="241" spans="1:43" x14ac:dyDescent="0.35">
@@ -12621,7 +12816,7 @@
       <c r="R241" s="4"/>
       <c r="S241" s="4"/>
       <c r="AQ241" s="10" t="s">
-        <v>1082</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="242" spans="1:43" x14ac:dyDescent="0.35">
@@ -12649,7 +12844,7 @@
       <c r="R242" s="4"/>
       <c r="S242" s="4"/>
       <c r="AQ242" s="10" t="s">
-        <v>1083</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="243" spans="1:43" x14ac:dyDescent="0.35">
@@ -12677,7 +12872,7 @@
       <c r="R243" s="4"/>
       <c r="S243" s="4"/>
       <c r="AQ243" s="10" t="s">
-        <v>1084</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="244" spans="1:43" x14ac:dyDescent="0.35">
@@ -12705,7 +12900,7 @@
       <c r="R244" s="4"/>
       <c r="S244" s="4"/>
       <c r="AQ244" s="10" t="s">
-        <v>1085</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="245" spans="1:43" x14ac:dyDescent="0.35">
@@ -12733,7 +12928,7 @@
       <c r="R245" s="4"/>
       <c r="S245" s="4"/>
       <c r="AQ245" s="10" t="s">
-        <v>1086</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="246" spans="1:43" x14ac:dyDescent="0.35">
@@ -12761,7 +12956,7 @@
       <c r="R246" s="4"/>
       <c r="S246" s="4"/>
       <c r="AQ246" s="10" t="s">
-        <v>1087</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="247" spans="1:43" x14ac:dyDescent="0.35">
@@ -12789,7 +12984,7 @@
       <c r="R247" s="4"/>
       <c r="S247" s="4"/>
       <c r="AQ247" s="10" t="s">
-        <v>1088</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="248" spans="1:43" x14ac:dyDescent="0.35">
@@ -12817,7 +13012,7 @@
       <c r="R248" s="4"/>
       <c r="S248" s="4"/>
       <c r="AQ248" s="10" t="s">
-        <v>1089</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="249" spans="1:43" x14ac:dyDescent="0.35">
@@ -12845,7 +13040,7 @@
       <c r="R249" s="4"/>
       <c r="S249" s="4"/>
       <c r="AQ249" s="10" t="s">
-        <v>1090</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="250" spans="1:43" x14ac:dyDescent="0.35">
@@ -12873,7 +13068,7 @@
       <c r="R250" s="4"/>
       <c r="S250" s="4"/>
       <c r="AQ250" s="10" t="s">
-        <v>1091</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="251" spans="1:43" x14ac:dyDescent="0.35">
@@ -12901,7 +13096,7 @@
       <c r="R251" s="4"/>
       <c r="S251" s="4"/>
       <c r="AQ251" s="10" t="s">
-        <v>1092</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="252" spans="1:43" x14ac:dyDescent="0.35">
@@ -12929,1248 +13124,1249 @@
       <c r="R252" s="4"/>
       <c r="S252" s="4"/>
       <c r="AQ252" s="10" t="s">
-        <v>1093</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="253" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ253" s="10" t="s">
-        <v>1094</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="254" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ254" s="10" t="s">
-        <v>1095</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="255" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ255" s="10" t="s">
-        <v>1096</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="256" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ256" s="10" t="s">
-        <v>1097</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="257" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ257" s="10" t="s">
-        <v>1098</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="258" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ258" s="10" t="s">
-        <v>1099</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="259" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ259" s="10" t="s">
-        <v>1100</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="260" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ260" s="10" t="s">
-        <v>1101</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="261" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ261" s="10" t="s">
-        <v>1102</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="262" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ262" s="10" t="s">
-        <v>1103</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="263" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ263" s="10" t="s">
-        <v>1104</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="264" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ264" s="10" t="s">
-        <v>1105</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="265" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ265" s="10" t="s">
-        <v>1106</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="266" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ266" s="10" t="s">
-        <v>1107</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="267" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ267" s="10" t="s">
-        <v>1108</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="268" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ268" s="10" t="s">
-        <v>1109</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="269" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ269" s="10" t="s">
-        <v>1110</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="270" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ270" s="10" t="s">
-        <v>1111</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="271" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ271" s="10" t="s">
-        <v>1112</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="272" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ272" s="10" t="s">
-        <v>1113</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="273" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ273" s="10" t="s">
-        <v>1114</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="274" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ274" s="10" t="s">
-        <v>1115</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="275" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ275" s="10" t="s">
-        <v>1116</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="276" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ276" s="10" t="s">
-        <v>1117</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="277" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ277" s="10" t="s">
-        <v>1118</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="278" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ278" s="10" t="s">
-        <v>1119</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="279" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ279" s="10" t="s">
-        <v>1120</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="280" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ280" s="10" t="s">
-        <v>1121</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="281" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ281" s="10" t="s">
-        <v>1122</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="282" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ282" s="10" t="s">
-        <v>1123</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="283" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ283" t="s">
-        <v>1124</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="284" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ284" t="s">
-        <v>1125</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="285" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ285" s="10" t="s">
-        <v>1126</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="286" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ286" t="s">
-        <v>1127</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="287" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ287" t="s">
-        <v>1128</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="288" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ288" t="s">
-        <v>1129</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="289" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ289" t="s">
-        <v>1130</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="290" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ290" t="s">
-        <v>1131</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="291" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ291" t="s">
-        <v>1132</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="292" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ292" s="10" t="s">
-        <v>1133</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="293" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ293" s="10" t="s">
-        <v>1134</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="294" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ294" s="10" t="s">
-        <v>1135</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="295" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ295" s="10" t="s">
-        <v>1136</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="296" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ296" t="s">
-        <v>1137</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="297" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ297" t="s">
-        <v>1138</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="298" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ298" t="s">
-        <v>1139</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="299" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ299" t="s">
-        <v>1140</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="300" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ300" t="s">
-        <v>1141</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="301" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ301" t="s">
-        <v>1142</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="302" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ302" t="s">
-        <v>1143</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="303" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ303" t="s">
-        <v>1144</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="304" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ304" t="s">
-        <v>1145</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="305" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ305" t="s">
-        <v>1146</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="306" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ306" t="s">
-        <v>1147</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="307" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ307" t="s">
-        <v>1148</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="308" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ308" t="s">
-        <v>1149</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="309" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ309" t="s">
-        <v>1150</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="310" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ310" t="s">
-        <v>1151</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="311" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ311" t="s">
-        <v>1152</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="312" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ312" t="s">
-        <v>1153</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="313" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ313" t="s">
-        <v>1154</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="314" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ314" t="s">
-        <v>1155</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="315" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ315" t="s">
-        <v>1156</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="316" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ316" t="s">
-        <v>1157</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="317" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ317" s="10" t="s">
-        <v>1158</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="318" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ318" s="10" t="s">
-        <v>1159</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="319" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ319" s="10" t="s">
-        <v>1160</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="320" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ320" s="10" t="s">
-        <v>1161</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="321" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ321" s="10" t="s">
-        <v>1162</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="322" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ322" s="10" t="s">
-        <v>1163</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="323" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ323" s="10" t="s">
-        <v>1164</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="324" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ324" s="10" t="s">
-        <v>1165</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="325" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ325" s="10" t="s">
-        <v>1166</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="326" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ326" s="10" t="s">
-        <v>1167</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="327" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ327" s="10" t="s">
-        <v>1168</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="328" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ328" s="10" t="s">
-        <v>1169</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="329" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ329" s="10" t="s">
-        <v>1170</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="330" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ330" s="10" t="s">
-        <v>1171</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="331" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ331" s="10" t="s">
-        <v>1172</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="332" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ332" s="10" t="s">
-        <v>1173</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="333" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ333" s="10" t="s">
-        <v>1174</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="334" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ334" s="10" t="s">
-        <v>1175</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="335" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ335" s="10" t="s">
-        <v>1176</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="336" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ336" s="10" t="s">
-        <v>1177</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="337" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ337" s="10" t="s">
-        <v>1178</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="338" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ338" s="10" t="s">
-        <v>1179</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="339" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ339" s="10" t="s">
-        <v>1180</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="340" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ340" s="10" t="s">
-        <v>1181</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="341" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ341" s="10" t="s">
-        <v>1182</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="342" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ342" s="10" t="s">
-        <v>1183</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="343" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ343" s="10" t="s">
-        <v>1184</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="344" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ344" s="10" t="s">
-        <v>1185</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="345" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ345" s="10" t="s">
-        <v>1186</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="346" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ346" s="10" t="s">
-        <v>1187</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="347" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ347" s="10" t="s">
-        <v>1188</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="348" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ348" s="10" t="s">
-        <v>1189</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="349" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ349" s="10" t="s">
-        <v>1190</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="350" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ350" s="10" t="s">
-        <v>1191</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="351" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ351" s="10" t="s">
-        <v>1192</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="352" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ352" s="10" t="s">
-        <v>1193</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="353" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ353" s="10" t="s">
-        <v>1194</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="354" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ354" s="10" t="s">
-        <v>1195</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="355" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ355" s="10" t="s">
-        <v>1196</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="356" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ356" s="10" t="s">
-        <v>1197</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="357" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ357" s="10" t="s">
-        <v>1198</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="358" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ358" s="10" t="s">
-        <v>1199</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="359" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ359" s="10" t="s">
-        <v>1200</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="360" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ360" s="10" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="361" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ361" s="10" t="s">
-        <v>1202</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="362" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ362" s="10" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="363" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ363" s="10" t="s">
-        <v>1204</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="364" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ364" s="10" t="s">
-        <v>1205</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="365" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ365" s="10" t="s">
-        <v>1206</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="366" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ366" s="10" t="s">
-        <v>1207</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="367" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ367" s="10" t="s">
-        <v>1208</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="368" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ368" s="10" t="s">
-        <v>1209</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="369" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ369" s="10" t="s">
-        <v>1210</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="370" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ370" s="10" t="s">
-        <v>1211</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="371" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ371" s="10" t="s">
-        <v>1212</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="372" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ372" s="10" t="s">
-        <v>1213</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="373" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ373" s="10" t="s">
-        <v>1214</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="374" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ374" s="10" t="s">
-        <v>1215</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="375" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ375" s="10" t="s">
-        <v>1216</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="376" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ376" s="10" t="s">
-        <v>1217</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="377" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ377" s="10" t="s">
-        <v>1218</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="378" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ378" s="10" t="s">
-        <v>1219</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="379" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ379" s="10" t="s">
-        <v>1220</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="380" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ380" s="10" t="s">
-        <v>1221</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="381" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ381" s="10" t="s">
-        <v>1222</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="382" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ382" s="10" t="s">
-        <v>1223</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="383" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ383" s="10" t="s">
-        <v>1224</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="384" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ384" s="10" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="385" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ385" s="10" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="386" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ386" s="10" t="s">
-        <v>1227</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="387" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ387" s="10" t="s">
-        <v>1228</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="388" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ388" s="10" t="s">
-        <v>1229</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="389" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ389" s="10" t="s">
-        <v>1230</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="390" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ390" s="10" t="s">
-        <v>1231</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="391" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ391" s="10" t="s">
-        <v>1232</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="392" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ392" s="10" t="s">
-        <v>1233</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="393" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ393" s="10" t="s">
-        <v>1234</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="394" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ394" s="10" t="s">
-        <v>1235</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="395" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ395" s="10" t="s">
-        <v>1236</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="396" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ396" s="10" t="s">
-        <v>1237</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="397" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ397" s="10" t="s">
-        <v>1238</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="398" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ398" s="10" t="s">
-        <v>1239</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="399" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ399" s="10" t="s">
-        <v>1240</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="400" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ400" s="10" t="s">
-        <v>1241</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="401" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ401" s="10" t="s">
-        <v>1242</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="402" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ402" s="10" t="s">
-        <v>1243</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="403" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ403" s="10" t="s">
-        <v>1244</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="404" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ404" s="10" t="s">
-        <v>1245</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="405" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ405" s="10" t="s">
-        <v>1246</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="406" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ406" s="10" t="s">
-        <v>1247</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="407" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ407" s="10" t="s">
-        <v>1248</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="408" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ408" s="10" t="s">
-        <v>1249</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="409" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ409" s="10" t="s">
-        <v>1250</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="410" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ410" s="10" t="s">
-        <v>1251</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="411" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ411" s="10" t="s">
-        <v>1252</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="412" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ412" s="10" t="s">
-        <v>1253</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="413" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ413" s="10" t="s">
-        <v>1254</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="414" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ414" s="10" t="s">
-        <v>1255</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="415" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ415" s="10" t="s">
-        <v>1256</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="416" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ416" s="10" t="s">
-        <v>1257</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="417" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ417" t="s">
-        <v>1258</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="418" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ418" t="s">
-        <v>1259</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="419" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ419" t="s">
-        <v>1260</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="420" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ420" t="s">
-        <v>1261</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="421" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ421" t="s">
-        <v>1262</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="422" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ422" t="s">
-        <v>1263</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="423" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ423" t="s">
-        <v>1264</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="424" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ424" t="s">
-        <v>1265</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="425" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ425" t="s">
-        <v>1266</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="426" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ426" t="s">
-        <v>1267</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="427" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ427" t="s">
-        <v>1268</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="428" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ428" t="s">
-        <v>1269</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="429" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ429" t="s">
-        <v>1270</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="430" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ430" t="s">
-        <v>1271</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="431" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ431" t="s">
-        <v>1272</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="432" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ432" s="10" t="s">
-        <v>1273</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="433" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ433" s="10" t="s">
-        <v>1274</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="434" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ434" s="10" t="s">
-        <v>1275</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="435" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ435" s="10" t="s">
-        <v>1276</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="436" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ436" s="10" t="s">
-        <v>1277</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="437" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ437" s="10" t="s">
-        <v>1278</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="438" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ438" s="10" t="s">
-        <v>1279</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="439" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ439" s="10" t="s">
-        <v>1280</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="440" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ440" s="10" t="s">
-        <v>1281</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="441" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ441" s="10" t="s">
-        <v>1282</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="442" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ442" s="10" t="s">
-        <v>1283</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="443" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ443" s="10" t="s">
-        <v>1284</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="444" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ444" s="10" t="s">
-        <v>1285</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="445" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ445" s="10" t="s">
-        <v>1286</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="446" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ446" s="10" t="s">
-        <v>1287</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="447" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ447" s="10" t="s">
-        <v>1288</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="448" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ448" s="10" t="s">
-        <v>1289</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="449" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ449" s="10" t="s">
-        <v>1290</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="450" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ450" s="10" t="s">
-        <v>1291</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="451" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ451" s="10" t="s">
-        <v>1292</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="452" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ452" s="10" t="s">
-        <v>1293</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="453" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ453" s="10" t="s">
-        <v>1294</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="454" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ454" s="10" t="s">
-        <v>1295</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="455" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ455" s="10" t="s">
-        <v>1296</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="456" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ456" s="10" t="s">
-        <v>1297</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="457" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ457" s="10" t="s">
-        <v>1298</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="458" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ458" s="10" t="s">
-        <v>1299</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="459" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ459" s="10" t="s">
-        <v>1300</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="460" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ460" s="10" t="s">
-        <v>1301</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="461" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ461" s="10" t="s">
-        <v>1302</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="462" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ462" s="10" t="s">
-        <v>1303</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="463" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ463" s="10" t="s">
-        <v>1304</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="464" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ464" s="10" t="s">
-        <v>1305</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="465" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ465" s="10" t="s">
-        <v>1306</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="466" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ466" s="10" t="s">
-        <v>1307</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="467" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ467" s="10" t="s">
-        <v>1308</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="468" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ468" s="10" t="s">
-        <v>1309</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="469" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ469" s="10" t="s">
-        <v>1310</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="470" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ470" s="10" t="s">
-        <v>1311</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="471" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ471" s="10" t="s">
-        <v>1312</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="472" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ472" s="10" t="s">
-        <v>1313</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="473" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ473" s="10" t="s">
-        <v>1314</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="474" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ474" s="10" t="s">
-        <v>1315</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="475" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ475" s="10" t="s">
-        <v>1316</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="476" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ476" s="10" t="s">
-        <v>1317</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="477" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ477" s="10" t="s">
-        <v>1318</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="478" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ478" s="10" t="s">
-        <v>1319</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="479" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ479" s="10" t="s">
-        <v>1320</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="480" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ480" t="s">
-        <v>1321</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="481" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ481" t="s">
-        <v>1322</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="482" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ482" t="s">
-        <v>1323</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="483" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ483" t="s">
-        <v>1324</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="484" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ484" t="s">
-        <v>1325</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="485" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ485" t="s">
-        <v>1326</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="486" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ486" t="s">
-        <v>1327</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="487" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ487" t="s">
-        <v>1328</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="488" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ488" t="s">
-        <v>1329</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="489" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ489" s="10" t="s">
-        <v>1330</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="490" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ490" t="s">
-        <v>1331</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="491" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ491" t="s">
-        <v>1332</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="492" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ492" s="10" t="s">
-        <v>1333</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="493" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ493" s="10" t="s">
-        <v>1334</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="494" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ494" s="10" t="s">
-        <v>1335</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="495" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ495" s="10" t="s">
-        <v>1336</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="496" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ496" s="10" t="s">
-        <v>1337</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="497" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ497" s="10" t="s">
-        <v>1338</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="498" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ498" s="10" t="s">
-        <v>1339</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="499" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ499" s="10" t="s">
-        <v>1340</v>
+        <v>1317</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1" xr:uid="{E0E850CD-3E14-435D-8C47-1A715B498BE2}"/>
     <hyperlink ref="K4" r:id="rId2" display="Reference the ISO 3166-2 country subdivision code English short name using the respective ISO standard" xr:uid="{63CBBA96-0B3B-4ACE-864F-477D7D8E9A25}"/>
+    <hyperlink ref="AI4" r:id="rId3" xr:uid="{352A57CF-08C7-4F81-9896-5F12E5641FF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_21_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_31_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{53260164-40DC-4E97-9598-294412E24B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0AC66D-9F17-45D3-9052-8AA95087963F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{55F88FD4-860F-4289-8195-ADD9A282EF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A36FCB71-9766-4590-A298-53D5019C9C67}"/>
   <bookViews>
-    <workbookView xWindow="-28155" yWindow="480" windowWidth="27600" windowHeight="14985" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-21000" yWindow="1065" windowWidth="18240" windowHeight="9975" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1773">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -5163,13 +5163,205 @@
   </si>
   <si>
     <t>Index</t>
+  </si>
+  <si>
+    <t>carbon_standard_level_accreditation</t>
+  </si>
+  <si>
+    <t>project_level_accreditation</t>
+  </si>
+  <si>
+    <t>unit_level_accreditation</t>
+  </si>
+  <si>
+    <t>unit_level_compliance_approval</t>
+  </si>
+  <si>
+    <t>unit_level_compliance_eligibility</t>
+  </si>
+  <si>
+    <t>project_level_compliance_approval</t>
+  </si>
+  <si>
+    <t>project_level_compliance_eligibility</t>
+  </si>
+  <si>
+    <t>ICVCM</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>CCP</t>
+  </si>
+  <si>
+    <t>Alberta TIER</t>
+  </si>
+  <si>
+    <t>CORSIA First Phase approved (2024-2026)</t>
+  </si>
+  <si>
+    <t>SD VISta</t>
+  </si>
+  <si>
+    <t>Argentina carbon tax</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase approved (2027-2029)</t>
+  </si>
+  <si>
+    <t>W+ Standard</t>
+  </si>
+  <si>
+    <t>Argentina ETS</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase approved (2030-2032)</t>
+  </si>
+  <si>
+    <t>Social Carbon</t>
+  </si>
+  <si>
+    <t>Australia Safeguard Mechanism</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase approved (2033-2035)</t>
+  </si>
+  <si>
+    <t>ABACUS</t>
+  </si>
+  <si>
+    <t>British Columbia OBPS</t>
+  </si>
+  <si>
+    <t>Canada ETS</t>
+  </si>
+  <si>
+    <t>Canada federal OBPS</t>
+  </si>
+  <si>
+    <t>Canada federal fuel charge</t>
+  </si>
+  <si>
+    <t>California CaT</t>
+  </si>
+  <si>
+    <t>Chile carbon tax</t>
+  </si>
+  <si>
+    <t>Chile ETS</t>
+  </si>
+  <si>
+    <t>China National ETS</t>
+  </si>
+  <si>
+    <t>Chinese pilots ETSs</t>
+  </si>
+  <si>
+    <t>Colombia carbon tax</t>
+  </si>
+  <si>
+    <t>Colombia ETS</t>
+  </si>
+  <si>
+    <t>GCOM</t>
+  </si>
+  <si>
+    <t>GX-ETS</t>
+  </si>
+  <si>
+    <t>Tokyo Cap and Trade Program</t>
+  </si>
+  <si>
+    <t>Indonesian Economic Value of Carbon (Nilai Ekonomi Karbon) Trading Scheme</t>
+  </si>
+  <si>
+    <t>Indonesia Carbon Tax</t>
+  </si>
+  <si>
+    <t>K-ETS</t>
+  </si>
+  <si>
+    <t>Kazakhstan ETS</t>
+  </si>
+  <si>
+    <t>Mexico carbon tax</t>
+  </si>
+  <si>
+    <t>Mexico ETS</t>
+  </si>
+  <si>
+    <t>Quebec ETS</t>
+  </si>
+  <si>
+    <t>Queretaro carbon tax</t>
+  </si>
+  <si>
+    <t>RGGI</t>
+  </si>
+  <si>
+    <t>Saitama ETS</t>
+  </si>
+  <si>
+    <t>Brazil SBCE</t>
+  </si>
+  <si>
+    <t>Singapore carbon tax</t>
+  </si>
+  <si>
+    <t>South Africa carbon tax</t>
+  </si>
+  <si>
+    <t>Washington CCA</t>
+  </si>
+  <si>
+    <t>Taiwan carbon fee</t>
+  </si>
+  <si>
+    <t>Taiwan ETS</t>
+  </si>
+  <si>
+    <t>Türkiye ETS</t>
+  </si>
+  <si>
+    <t>GX League</t>
+  </si>
+  <si>
+    <t>Vietnam ETS</t>
+  </si>
+  <si>
+    <t>Colorado Methane Recovery</t>
+  </si>
+  <si>
+    <t>Japan Joint Crediting Mechanism (JCM)</t>
+  </si>
+  <si>
+    <t>J-credit</t>
+  </si>
+  <si>
+    <t>CORSIA First Phase eligible (2024-2026)</t>
+  </si>
+  <si>
+    <t>CORSIA First Phase scope (2024-2026)</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase eligible (2027-2029)</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase scope (2027-2029)</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase scope (2030-2032)</t>
+  </si>
+  <si>
+    <t>CORSIA Second Phase scope (2033-2035)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5236,6 +5428,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5281,7 +5494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5304,22 +5517,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5329,7 +5540,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5339,6 +5550,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5674,59 +5888,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B85F238-80B8-43F8-AABF-7B9427088CCA}">
-  <dimension ref="A1:DK500"/>
+  <dimension ref="A1:DQ500"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="8.81640625" style="13"/>
-    <col min="5" max="5" width="26.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="26.6328125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="8.81640625" style="13"/>
-    <col min="9" max="9" width="31.36328125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" style="13"/>
-    <col min="11" max="11" width="22" style="13" customWidth="1"/>
-    <col min="12" max="18" width="8.81640625" style="13"/>
-    <col min="19" max="19" width="13.08984375" style="13" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" style="13"/>
-    <col min="21" max="21" width="13.90625" style="13" customWidth="1"/>
-    <col min="22" max="22" width="8.81640625" style="13"/>
-    <col min="23" max="23" width="24.81640625" style="13" customWidth="1"/>
-    <col min="24" max="24" width="8.81640625" style="13"/>
-    <col min="25" max="25" width="29.81640625" style="13" customWidth="1"/>
-    <col min="26" max="26" width="8.81640625" style="13"/>
-    <col min="27" max="27" width="11.1796875" style="13" customWidth="1"/>
-    <col min="28" max="34" width="8.81640625" style="13"/>
-    <col min="35" max="35" width="28.36328125" style="13" customWidth="1"/>
-    <col min="36" max="36" width="8.81640625" style="13"/>
-    <col min="37" max="37" width="27.81640625" style="13" customWidth="1"/>
-    <col min="38" max="38" width="8.81640625" style="13"/>
-    <col min="39" max="39" width="21.453125" style="13" customWidth="1"/>
-    <col min="40" max="40" width="8.81640625" style="13"/>
-    <col min="41" max="41" width="14.1796875" style="13" customWidth="1"/>
-    <col min="42" max="42" width="8.81640625" style="13"/>
-    <col min="43" max="43" width="12.81640625" style="13" customWidth="1"/>
-    <col min="44" max="44" width="8.81640625" style="13"/>
-    <col min="45" max="46" width="12" style="13" customWidth="1"/>
-    <col min="47" max="48" width="14.6328125" style="13" customWidth="1"/>
-    <col min="49" max="49" width="16.81640625" style="13" customWidth="1"/>
-    <col min="50" max="50" width="8.81640625" style="13"/>
-    <col min="51" max="51" width="19.36328125" style="13" customWidth="1"/>
-    <col min="52" max="52" width="8.81640625" style="13"/>
-    <col min="53" max="53" width="20.36328125" style="13" customWidth="1"/>
-    <col min="54" max="54" width="8.81640625" style="13"/>
-    <col min="55" max="55" width="26.08984375" style="13" customWidth="1"/>
-    <col min="56" max="56" width="8.81640625" style="13"/>
-    <col min="57" max="57" width="21.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="8.81640625" style="13"/>
-    <col min="59" max="59" width="13.6328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.81640625" style="13"/>
-    <col min="61" max="61" width="15.6328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="62" max="84" width="8.81640625" style="13"/>
-    <col min="85" max="85" width="19.36328125" style="13" customWidth="1"/>
-    <col min="86" max="16384" width="8.81640625" style="13"/>
+    <col min="5" max="5" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="26.6328125" customWidth="1"/>
+    <col min="9" max="9" width="31.36328125" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="19" max="19" width="13.08984375" customWidth="1"/>
+    <col min="21" max="21" width="13.90625" customWidth="1"/>
+    <col min="23" max="23" width="24.81640625" customWidth="1"/>
+    <col min="25" max="25" width="29.81640625" customWidth="1"/>
+    <col min="27" max="27" width="11.1796875" customWidth="1"/>
+    <col min="35" max="35" width="28.36328125" customWidth="1"/>
+    <col min="37" max="37" width="27.81640625" customWidth="1"/>
+    <col min="39" max="39" width="21.453125" customWidth="1"/>
+    <col min="41" max="41" width="14.1796875" customWidth="1"/>
+    <col min="43" max="43" width="12.81640625" customWidth="1"/>
+    <col min="45" max="46" width="12" customWidth="1"/>
+    <col min="47" max="48" width="14.6328125" customWidth="1"/>
+    <col min="49" max="49" width="16.81640625" customWidth="1"/>
+    <col min="51" max="51" width="19.36328125" customWidth="1"/>
+    <col min="53" max="53" width="20.36328125" customWidth="1"/>
+    <col min="55" max="55" width="26.08984375" customWidth="1"/>
+    <col min="57" max="57" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="19.36328125" customWidth="1"/>
+    <col min="97" max="97" width="35.453125" customWidth="1"/>
+    <col min="98" max="98" width="18.36328125" customWidth="1"/>
+    <col min="99" max="99" width="30.26953125" customWidth="1"/>
+    <col min="100" max="100" width="17" customWidth="1"/>
+    <col min="101" max="101" width="24.90625" customWidth="1"/>
+    <col min="102" max="102" width="13.453125" customWidth="1"/>
+    <col min="103" max="103" width="29.54296875" customWidth="1"/>
+    <col min="104" max="104" width="17.6328125" customWidth="1"/>
+    <col min="105" max="105" width="29.81640625" customWidth="1"/>
+    <col min="106" max="106" width="12.7265625" customWidth="1"/>
+    <col min="107" max="107" width="33.08984375" customWidth="1"/>
+    <col min="108" max="108" width="12.90625" customWidth="1"/>
+    <col min="109" max="109" width="33.7265625" customWidth="1"/>
+    <col min="110" max="110" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5749,7 +5955,7 @@
       <c r="R1" s="12"/>
       <c r="S1" s="12"/>
     </row>
-    <row r="2" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -5770,7 +5976,7 @@
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
     </row>
-    <row r="3" spans="1:115" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>1332</v>
       </c>
@@ -5787,64 +5993,64 @@
         <v>1335</v>
       </c>
       <c r="H3" s="12"/>
-      <c r="I3" s="13" t="s">
+      <c r="I3" t="s">
         <v>1336</v>
       </c>
       <c r="J3" s="12"/>
-      <c r="K3" s="13" t="s">
+      <c r="K3" t="s">
         <v>1337</v>
       </c>
       <c r="L3" s="12"/>
-      <c r="M3" s="13" t="s">
+      <c r="M3" t="s">
         <v>1338</v>
       </c>
       <c r="N3" s="2"/>
-      <c r="O3" s="13" t="s">
+      <c r="O3" t="s">
         <v>1339</v>
       </c>
       <c r="P3" s="2"/>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" t="s">
         <v>1340</v>
       </c>
       <c r="R3" s="2"/>
-      <c r="S3" s="13" t="s">
+      <c r="S3" t="s">
         <v>1341</v>
       </c>
       <c r="T3" s="2"/>
-      <c r="U3" s="13" t="s">
+      <c r="U3" t="s">
         <v>1342</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="W3" t="s">
         <v>1343</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" t="s">
         <v>1344</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AA3" t="s">
         <v>1345</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AC3" t="s">
         <v>1346</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AE3" t="s">
         <v>1347</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AG3" t="s">
         <v>1348</v>
       </c>
-      <c r="AI3" s="13" t="s">
+      <c r="AI3" t="s">
         <v>1349</v>
       </c>
-      <c r="AK3" s="13" t="s">
+      <c r="AK3" t="s">
         <v>1431</v>
       </c>
-      <c r="AM3" s="13" t="s">
+      <c r="AM3" t="s">
         <v>1432</v>
       </c>
-      <c r="AO3" s="13" t="s">
+      <c r="AO3" t="s">
         <v>1350</v>
       </c>
-      <c r="AQ3" s="13" t="s">
+      <c r="AQ3" t="s">
         <v>612</v>
       </c>
       <c r="AS3" s="6" t="s">
@@ -5853,25 +6059,25 @@
       <c r="AU3" s="6" t="s">
         <v>1351</v>
       </c>
-      <c r="AW3" s="13" t="s">
+      <c r="AW3" t="s">
         <v>1352</v>
       </c>
-      <c r="AY3" s="14" t="s">
+      <c r="AY3" s="13" t="s">
         <v>1353</v>
       </c>
-      <c r="BA3" s="14" t="s">
+      <c r="BA3" s="13" t="s">
         <v>1354</v>
       </c>
-      <c r="BC3" s="13" t="s">
+      <c r="BC3" t="s">
         <v>1355</v>
       </c>
-      <c r="BE3" s="13" t="s">
+      <c r="BE3" t="s">
         <v>1356</v>
       </c>
-      <c r="BG3" s="13" t="s">
+      <c r="BG3" t="s">
         <v>1357</v>
       </c>
-      <c r="BI3" s="13" t="s">
+      <c r="BI3" t="s">
         <v>1358</v>
       </c>
       <c r="BK3" s="9" t="s">
@@ -5894,10 +6100,10 @@
         <v>1437</v>
       </c>
       <c r="BT3" s="9"/>
-      <c r="BU3" s="26" t="s">
+      <c r="BU3" s="24" t="s">
         <v>1438</v>
       </c>
-      <c r="BV3" s="26"/>
+      <c r="BV3" s="24"/>
       <c r="BW3" s="9" t="s">
         <v>1439</v>
       </c>
@@ -5917,27 +6123,53 @@
       <c r="CE3" s="9" t="s">
         <v>1443</v>
       </c>
-      <c r="CG3" s="15" t="s">
+      <c r="CG3" t="s">
         <v>1664</v>
       </c>
-      <c r="CI3" s="15" t="s">
+      <c r="CI3" t="s">
         <v>1685</v>
       </c>
-      <c r="CK3" s="25" t="s">
+      <c r="CK3" s="23" t="s">
         <v>1684</v>
       </c>
-      <c r="CM3" s="15" t="s">
+      <c r="CM3" t="s">
         <v>1686</v>
       </c>
-      <c r="CN3" s="15"/>
-      <c r="CO3" s="15" t="s">
+      <c r="CO3" t="s">
         <v>1687</v>
       </c>
-      <c r="CQ3" s="15" t="s">
+      <c r="CQ3" t="s">
         <v>1704</v>
       </c>
-    </row>
-    <row r="4" spans="1:115" x14ac:dyDescent="0.35">
+      <c r="CS3" s="28" t="s">
+        <v>1709</v>
+      </c>
+      <c r="CT3" s="28"/>
+      <c r="CU3" s="28" t="s">
+        <v>1710</v>
+      </c>
+      <c r="CV3" s="28"/>
+      <c r="CW3" s="28" t="s">
+        <v>1711</v>
+      </c>
+      <c r="CX3" s="28"/>
+      <c r="CY3" s="28" t="s">
+        <v>1712</v>
+      </c>
+      <c r="CZ3" s="28"/>
+      <c r="DA3" s="28" t="s">
+        <v>1713</v>
+      </c>
+      <c r="DB3" s="28"/>
+      <c r="DC3" s="28" t="s">
+        <v>1714</v>
+      </c>
+      <c r="DD3" s="28"/>
+      <c r="DE3" s="28" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="4" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -6053,47 +6285,47 @@
       <c r="BI4" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="BK4" s="27" t="s">
+      <c r="BK4" s="25" t="s">
         <v>1433</v>
       </c>
       <c r="BL4" s="9"/>
-      <c r="BM4" s="27" t="s">
+      <c r="BM4" s="25" t="s">
         <v>1434</v>
       </c>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27" t="s">
+      <c r="BN4" s="25"/>
+      <c r="BO4" s="25" t="s">
         <v>1435</v>
       </c>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27" t="s">
+      <c r="BP4" s="25"/>
+      <c r="BQ4" s="25" t="s">
         <v>1436</v>
       </c>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27" t="s">
+      <c r="BR4" s="25"/>
+      <c r="BS4" s="25" t="s">
         <v>1437</v>
       </c>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="28" t="s">
+      <c r="BT4" s="25"/>
+      <c r="BU4" s="26" t="s">
         <v>1438</v>
       </c>
-      <c r="BV4" s="28"/>
-      <c r="BW4" s="27" t="s">
+      <c r="BV4" s="26"/>
+      <c r="BW4" s="25" t="s">
         <v>1439</v>
       </c>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27" t="s">
+      <c r="BX4" s="25"/>
+      <c r="BY4" s="25" t="s">
         <v>1440</v>
       </c>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27" t="s">
+      <c r="BZ4" s="25"/>
+      <c r="CA4" s="25" t="s">
         <v>1441</v>
       </c>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="27" t="s">
+      <c r="CB4" s="25"/>
+      <c r="CC4" s="25" t="s">
         <v>1442</v>
       </c>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="27" t="s">
+      <c r="CD4" s="25"/>
+      <c r="CE4" s="25" t="s">
         <v>1443</v>
       </c>
       <c r="CG4" s="1" t="s">
@@ -6120,36 +6352,56 @@
         <v>1705</v>
       </c>
       <c r="CR4" s="1"/>
-      <c r="CS4" s="1"/>
-      <c r="CT4" s="1"/>
-      <c r="CU4" s="1"/>
-      <c r="CV4" s="1"/>
-      <c r="CW4" s="1"/>
-      <c r="CX4" s="1"/>
-      <c r="CY4" s="1"/>
-      <c r="CZ4" s="1"/>
-      <c r="DA4" s="1"/>
-      <c r="DB4" s="1"/>
-      <c r="DC4" s="1"/>
-      <c r="DD4" s="1"/>
-      <c r="DE4" s="1"/>
-      <c r="DF4" s="1"/>
+      <c r="CS4" s="27" t="s">
+        <v>1709</v>
+      </c>
+      <c r="CT4" s="27"/>
+      <c r="CU4" s="27" t="s">
+        <v>1710</v>
+      </c>
+      <c r="CV4" s="27"/>
+      <c r="CW4" s="27" t="s">
+        <v>1711</v>
+      </c>
+      <c r="CX4" s="27"/>
+      <c r="CY4" s="27" t="s">
+        <v>1712</v>
+      </c>
+      <c r="CZ4" s="27"/>
+      <c r="DA4" s="27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="DB4" s="27"/>
+      <c r="DC4" s="27" t="s">
+        <v>1714</v>
+      </c>
+      <c r="DD4" s="27"/>
+      <c r="DE4" s="27" t="s">
+        <v>1715</v>
+      </c>
+      <c r="DF4" s="27"/>
       <c r="DG4" s="1"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
       <c r="DJ4" s="1"/>
       <c r="DK4" s="1"/>
-    </row>
-    <row r="5" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
+      <c r="DL4" s="1"/>
+      <c r="DM4" s="1"/>
+      <c r="DN4" s="1"/>
+      <c r="DO4" s="1"/>
+      <c r="DP4" s="1"/>
+      <c r="DQ4" s="1"/>
+    </row>
+    <row r="5" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="12"/>
@@ -6157,11 +6409,11 @@
         <v>14</v>
       </c>
       <c r="H5" s="12"/>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="16" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="12"/>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="16" t="s">
         <v>16</v>
       </c>
       <c r="L5" s="12"/>
@@ -6180,16 +6432,16 @@
       <c r="S5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" t="s">
         <v>613</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" t="s">
         <v>614</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" t="s">
         <v>615</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AA5" t="s">
         <v>1365</v>
       </c>
       <c r="AC5" s="9" t="s">
@@ -6204,7 +6456,7 @@
         <v>619</v>
       </c>
       <c r="AH5" s="9"/>
-      <c r="AI5" s="19" t="s">
+      <c r="AI5" s="17" t="s">
         <v>1366</v>
       </c>
       <c r="AJ5" s="9"/>
@@ -6216,17 +6468,17 @@
         <v>620</v>
       </c>
       <c r="AN5" s="9"/>
-      <c r="AO5" s="13" t="s">
+      <c r="AO5" t="s">
         <v>621</v>
       </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AQ5" t="s">
         <v>622</v>
       </c>
       <c r="AS5" s="12" t="s">
         <v>1321</v>
       </c>
       <c r="AT5" s="12"/>
-      <c r="AU5" s="13" t="s">
+      <c r="AU5" t="s">
         <v>614</v>
       </c>
       <c r="AW5" s="12" t="s">
@@ -6235,19 +6487,19 @@
       <c r="AY5" s="9" t="s">
         <v>1367</v>
       </c>
-      <c r="BA5" s="20" t="s">
+      <c r="BA5" s="18" t="s">
         <v>1368</v>
       </c>
-      <c r="BC5" s="21" t="s">
+      <c r="BC5" s="19" t="s">
         <v>1369</v>
       </c>
-      <c r="BE5" s="13" t="s">
+      <c r="BE5" t="s">
         <v>1370</v>
       </c>
       <c r="BG5" s="9" t="s">
         <v>1371</v>
       </c>
-      <c r="BI5" s="13" t="s">
+      <c r="BI5" t="s">
         <v>1372</v>
       </c>
       <c r="BK5" s="9" t="s">
@@ -6293,35 +6545,63 @@
       <c r="CE5" s="9" t="s">
         <v>1452</v>
       </c>
-      <c r="CG5" s="22" t="s">
+      <c r="CG5" s="20" t="s">
         <v>1647</v>
       </c>
-      <c r="CI5" s="22" t="s">
+      <c r="CI5" s="20" t="s">
         <v>1667</v>
       </c>
-      <c r="CK5" s="22" t="s">
+      <c r="CK5" s="20" t="s">
         <v>1678</v>
       </c>
-      <c r="CM5" s="22" t="s">
+      <c r="CM5" s="20" t="s">
         <v>1699</v>
       </c>
-      <c r="CO5" s="22" t="s">
+      <c r="CO5" s="20" t="s">
         <v>1690</v>
       </c>
-      <c r="CQ5" s="22" t="s">
+      <c r="CQ5" s="20" t="s">
         <v>1706</v>
       </c>
-    </row>
-    <row r="6" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+      <c r="CS5" s="28" t="s">
+        <v>1716</v>
+      </c>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28" t="s">
+        <v>1717</v>
+      </c>
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="29" t="s">
+        <v>1719</v>
+      </c>
+      <c r="CZ5" s="29"/>
+      <c r="DA5" s="29" t="s">
+        <v>1719</v>
+      </c>
+      <c r="DB5" s="29"/>
+      <c r="DC5" s="29" t="s">
+        <v>1719</v>
+      </c>
+      <c r="DD5" s="29"/>
+      <c r="DE5" s="29" t="s">
+        <v>1719</v>
+      </c>
+      <c r="DF5" s="29"/>
+    </row>
+    <row r="6" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="21" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="12"/>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="15" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="12"/>
@@ -6348,22 +6628,22 @@
       <c r="S6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="U6" t="s">
         <v>623</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="W6" t="s">
         <v>624</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="Y6" t="s">
         <v>625</v>
       </c>
-      <c r="AA6" s="13" t="s">
+      <c r="AA6" t="s">
         <v>1373</v>
       </c>
-      <c r="AC6" s="24" t="s">
+      <c r="AC6" s="22" t="s">
         <v>627</v>
       </c>
-      <c r="AD6" s="24"/>
+      <c r="AD6" s="22"/>
       <c r="AE6" s="9" t="s">
         <v>628</v>
       </c>
@@ -6374,13 +6654,13 @@
       <c r="AH6" s="9"/>
       <c r="AI6" s="9"/>
       <c r="AJ6" s="9"/>
-      <c r="AK6" s="13" t="s">
+      <c r="AK6" t="s">
         <v>630</v>
       </c>
-      <c r="AM6" s="13" t="s">
+      <c r="AM6" t="s">
         <v>631</v>
       </c>
-      <c r="AO6" s="13" t="s">
+      <c r="AO6" t="s">
         <v>632</v>
       </c>
       <c r="AQ6" s="9" t="s">
@@ -6390,7 +6670,7 @@
         <v>1322</v>
       </c>
       <c r="AT6" s="12"/>
-      <c r="AU6" s="13" t="s">
+      <c r="AU6" t="s">
         <v>624</v>
       </c>
       <c r="AW6" s="12" t="s">
@@ -6399,19 +6679,19 @@
       <c r="AY6" s="9" t="s">
         <v>1374</v>
       </c>
-      <c r="BA6" s="20" t="s">
+      <c r="BA6" s="18" t="s">
         <v>626</v>
       </c>
-      <c r="BC6" s="21" t="s">
+      <c r="BC6" s="19" t="s">
         <v>1375</v>
       </c>
-      <c r="BE6" s="13" t="s">
+      <c r="BE6" t="s">
         <v>1376</v>
       </c>
       <c r="BG6" s="9" t="s">
         <v>1377</v>
       </c>
-      <c r="BI6" s="13" t="s">
+      <c r="BI6" t="s">
         <v>1378</v>
       </c>
       <c r="BK6" s="9" t="s">
@@ -6457,35 +6737,61 @@
       <c r="CE6" s="9" t="s">
         <v>1461</v>
       </c>
-      <c r="CG6" s="22" t="s">
+      <c r="CG6" s="20" t="s">
         <v>1648</v>
       </c>
-      <c r="CI6" s="22" t="s">
+      <c r="CI6" s="20" t="s">
         <v>1668</v>
       </c>
-      <c r="CK6" s="22" t="s">
+      <c r="CK6" s="20" t="s">
         <v>1679</v>
       </c>
-      <c r="CM6" s="22" t="s">
+      <c r="CM6" s="20" t="s">
         <v>1700</v>
       </c>
-      <c r="CO6" s="22" t="s">
+      <c r="CO6" s="20" t="s">
         <v>1691</v>
       </c>
-      <c r="CQ6" s="22" t="s">
+      <c r="CQ6" s="20" t="s">
         <v>1707</v>
       </c>
-    </row>
-    <row r="7" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
+      <c r="CS6" s="29" t="s">
+        <v>1720</v>
+      </c>
+      <c r="CT6" s="29"/>
+      <c r="CU6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="CV6" s="28"/>
+      <c r="CW6" s="28"/>
+      <c r="CX6" s="28"/>
+      <c r="CY6" s="29" t="s">
+        <v>1722</v>
+      </c>
+      <c r="CZ6" s="29"/>
+      <c r="DA6" s="29" t="s">
+        <v>1722</v>
+      </c>
+      <c r="DB6" s="29"/>
+      <c r="DC6" s="29" t="s">
+        <v>1722</v>
+      </c>
+      <c r="DD6" s="29"/>
+      <c r="DE6" s="29" t="s">
+        <v>1722</v>
+      </c>
+      <c r="DF6" s="29"/>
+    </row>
+    <row r="7" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A7" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="12"/>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="12"/>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="15" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="12"/>
@@ -6510,19 +6816,19 @@
       </c>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
-      <c r="U7" s="13" t="s">
+      <c r="U7" t="s">
         <v>634</v>
       </c>
-      <c r="W7" s="13" t="s">
+      <c r="W7" t="s">
         <v>635</v>
       </c>
-      <c r="Y7" s="13" t="s">
+      <c r="Y7" t="s">
         <v>636</v>
       </c>
-      <c r="AA7" s="25" t="s">
+      <c r="AA7" s="23" t="s">
         <v>1379</v>
       </c>
-      <c r="AB7" s="25"/>
+      <c r="AB7" s="23"/>
       <c r="AC7" s="9" t="s">
         <v>638</v>
       </c>
@@ -6543,10 +6849,10 @@
         <v>641</v>
       </c>
       <c r="AL7" s="9"/>
-      <c r="AM7" s="13" t="s">
+      <c r="AM7" t="s">
         <v>642</v>
       </c>
-      <c r="AO7" s="13" t="s">
+      <c r="AO7" t="s">
         <v>643</v>
       </c>
       <c r="AQ7" s="9" t="s">
@@ -6556,19 +6862,19 @@
         <v>1323</v>
       </c>
       <c r="AT7" s="12"/>
-      <c r="AU7" s="13" t="s">
+      <c r="AU7" t="s">
         <v>635</v>
       </c>
       <c r="AW7" s="12" t="s">
         <v>1328</v>
       </c>
-      <c r="AY7" s="13" t="s">
+      <c r="AY7" t="s">
         <v>1381</v>
       </c>
-      <c r="BA7" s="20" t="s">
+      <c r="BA7" s="18" t="s">
         <v>1382</v>
       </c>
-      <c r="BE7" s="13" t="s">
+      <c r="BE7" t="s">
         <v>1383</v>
       </c>
       <c r="BG7" s="9" t="s">
@@ -6617,35 +6923,61 @@
       <c r="CE7" s="9" t="s">
         <v>1470</v>
       </c>
-      <c r="CG7" s="22" t="s">
+      <c r="CG7" s="20" t="s">
         <v>1649</v>
       </c>
-      <c r="CI7" s="22" t="s">
+      <c r="CI7" s="20" t="s">
         <v>1669</v>
       </c>
-      <c r="CK7" s="22" t="s">
+      <c r="CK7" s="20" t="s">
         <v>1680</v>
       </c>
-      <c r="CM7" s="22" t="s">
+      <c r="CM7" s="20" t="s">
         <v>1701</v>
       </c>
-      <c r="CO7" s="22" t="s">
+      <c r="CO7" s="20" t="s">
         <v>1692</v>
       </c>
-      <c r="CQ7" s="22" t="s">
+      <c r="CQ7" s="20" t="s">
         <v>1708</v>
       </c>
-    </row>
-    <row r="8" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A8" s="23" t="s">
+      <c r="CS7" s="29" t="s">
+        <v>1723</v>
+      </c>
+      <c r="CT7" s="29"/>
+      <c r="CU7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="CV7" s="28"/>
+      <c r="CW7" s="28"/>
+      <c r="CX7" s="28"/>
+      <c r="CY7" s="29" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DF7" s="29"/>
+    </row>
+    <row r="8" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A8" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="12"/>
@@ -6668,16 +7000,16 @@
       </c>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
-      <c r="U8" s="13" t="s">
+      <c r="U8" t="s">
         <v>645</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="W8" t="s">
         <v>646</v>
       </c>
-      <c r="Y8" s="13" t="s">
+      <c r="Y8" t="s">
         <v>647</v>
       </c>
-      <c r="AA8" s="13" t="s">
+      <c r="AA8" t="s">
         <v>1385</v>
       </c>
       <c r="AE8" s="9" t="s">
@@ -6696,10 +7028,10 @@
         <v>651</v>
       </c>
       <c r="AL8" s="9"/>
-      <c r="AM8" s="13" t="s">
+      <c r="AM8" t="s">
         <v>652</v>
       </c>
-      <c r="AO8" s="13" t="s">
+      <c r="AO8" t="s">
         <v>653</v>
       </c>
       <c r="AQ8" s="9" t="s">
@@ -6709,16 +7041,16 @@
         <v>1324</v>
       </c>
       <c r="AT8" s="12"/>
-      <c r="AU8" s="13" t="s">
+      <c r="AU8" t="s">
         <v>646</v>
       </c>
       <c r="AW8" s="12" t="s">
         <v>1329</v>
       </c>
-      <c r="AY8" s="13" t="s">
+      <c r="AY8" t="s">
         <v>737</v>
       </c>
-      <c r="BE8" s="13" t="s">
+      <c r="BE8" t="s">
         <v>1387</v>
       </c>
       <c r="BG8" s="9" t="s">
@@ -6767,35 +7099,61 @@
       <c r="CE8" s="9" t="s">
         <v>1478</v>
       </c>
-      <c r="CG8" s="22" t="s">
+      <c r="CG8" s="20" t="s">
         <v>1650</v>
       </c>
-      <c r="CI8" s="22" t="s">
+      <c r="CI8" s="20" t="s">
         <v>1670</v>
       </c>
-      <c r="CK8" s="22" t="s">
+      <c r="CK8" s="20" t="s">
         <v>1681</v>
       </c>
-      <c r="CM8" s="22" t="s">
+      <c r="CM8" s="20" t="s">
         <v>1372</v>
       </c>
-      <c r="CO8" s="22" t="s">
+      <c r="CO8" s="20" t="s">
         <v>1693</v>
       </c>
-      <c r="CQ8" s="22" t="s">
+      <c r="CQ8" s="20" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="9" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+      <c r="CS8" s="29" t="s">
+        <v>1726</v>
+      </c>
+      <c r="CT8" s="29"/>
+      <c r="CU8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="CV8" s="28"/>
+      <c r="CW8" s="28"/>
+      <c r="CX8" s="28"/>
+      <c r="CY8" s="29" t="s">
+        <v>1728</v>
+      </c>
+      <c r="CZ8" s="29"/>
+      <c r="DA8" s="29" t="s">
+        <v>1728</v>
+      </c>
+      <c r="DB8" s="29"/>
+      <c r="DC8" s="29" t="s">
+        <v>1728</v>
+      </c>
+      <c r="DD8" s="29"/>
+      <c r="DE8" s="29" t="s">
+        <v>1728</v>
+      </c>
+      <c r="DF8" s="28"/>
+    </row>
+    <row r="9" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A9" s="14" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="12"/>
@@ -6818,13 +7176,13 @@
       </c>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
-      <c r="W9" s="13" t="s">
+      <c r="W9" t="s">
         <v>655</v>
       </c>
-      <c r="Y9" s="13" t="s">
+      <c r="Y9" t="s">
         <v>656</v>
       </c>
-      <c r="AA9" s="13" t="s">
+      <c r="AA9" t="s">
         <v>1389</v>
       </c>
       <c r="AE9" s="9" t="s">
@@ -6847,21 +7205,21 @@
         <v>641</v>
       </c>
       <c r="AN9" s="9"/>
-      <c r="AO9" s="13" t="s">
+      <c r="AO9" t="s">
         <v>661</v>
       </c>
-      <c r="AQ9" s="13" t="s">
+      <c r="AQ9" t="s">
         <v>662</v>
       </c>
       <c r="AS9" s="12"/>
       <c r="AT9" s="12"/>
-      <c r="AU9" s="13" t="s">
+      <c r="AU9" t="s">
         <v>655</v>
       </c>
       <c r="AW9" s="12" t="s">
         <v>1330</v>
       </c>
-      <c r="BE9" s="13" t="s">
+      <c r="BE9" t="s">
         <v>1391</v>
       </c>
       <c r="BG9" s="9" t="s">
@@ -6908,32 +7266,58 @@
       <c r="CE9" s="9" t="s">
         <v>1484</v>
       </c>
-      <c r="CG9" s="22" t="s">
+      <c r="CG9" s="20" t="s">
         <v>1651</v>
       </c>
-      <c r="CI9" s="22" t="s">
+      <c r="CI9" s="20" t="s">
         <v>1671</v>
       </c>
-      <c r="CK9" s="22" t="s">
+      <c r="CK9" s="20" t="s">
         <v>1682</v>
       </c>
-      <c r="CM9" s="22" t="s">
+      <c r="CM9" s="20" t="s">
         <v>1475</v>
       </c>
-      <c r="CO9" s="22" t="s">
+      <c r="CO9" s="20" t="s">
         <v>1694</v>
       </c>
-    </row>
-    <row r="10" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+      <c r="CS9" s="29" t="s">
+        <v>1729</v>
+      </c>
+      <c r="CT9" s="29"/>
+      <c r="CU9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="CV9" s="28"/>
+      <c r="CW9" s="28"/>
+      <c r="CX9" s="28"/>
+      <c r="CY9" s="29" t="s">
+        <v>1731</v>
+      </c>
+      <c r="CZ9" s="29"/>
+      <c r="DA9" s="29" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DB9" s="29"/>
+      <c r="DC9" s="29" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DD9" s="29"/>
+      <c r="DE9" s="29" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DF9" s="28"/>
+    </row>
+    <row r="10" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>50</v>
       </c>
       <c r="F10" s="12"/>
@@ -6958,14 +7342,14 @@
       <c r="S10" s="12"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="13" t="s">
+      <c r="W10" t="s">
         <v>663</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>664</v>
       </c>
       <c r="Z10" s="4"/>
-      <c r="AA10" s="13" t="s">
+      <c r="AA10" t="s">
         <v>616</v>
       </c>
       <c r="AE10" s="9" t="s">
@@ -6988,7 +7372,7 @@
         <v>651</v>
       </c>
       <c r="AN10" s="9"/>
-      <c r="AO10" s="13" t="s">
+      <c r="AO10" t="s">
         <v>669</v>
       </c>
       <c r="AQ10" s="9" t="s">
@@ -6996,13 +7380,13 @@
       </c>
       <c r="AS10" s="12"/>
       <c r="AT10" s="12"/>
-      <c r="AU10" s="13" t="s">
+      <c r="AU10" t="s">
         <v>663</v>
       </c>
       <c r="AW10" s="12" t="s">
         <v>1331</v>
       </c>
-      <c r="BE10" s="13" t="s">
+      <c r="BE10" t="s">
         <v>1394</v>
       </c>
       <c r="BG10" s="9" t="s">
@@ -7045,32 +7429,54 @@
       <c r="CE10" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="CG10" s="22" t="s">
+      <c r="CG10" s="20" t="s">
         <v>1652</v>
       </c>
-      <c r="CI10" s="22" t="s">
+      <c r="CI10" s="20" t="s">
         <v>1672</v>
       </c>
-      <c r="CK10" s="22" t="s">
+      <c r="CK10" s="20" t="s">
         <v>1683</v>
       </c>
-      <c r="CM10" s="22" t="s">
+      <c r="CM10" s="20" t="s">
         <v>1702</v>
       </c>
-      <c r="CO10" s="22" t="s">
+      <c r="CO10" s="20" t="s">
         <v>1695</v>
       </c>
-    </row>
-    <row r="11" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
+      <c r="CS10" s="28"/>
+      <c r="CT10" s="28"/>
+      <c r="CU10" s="28"/>
+      <c r="CV10" s="28"/>
+      <c r="CW10" s="28"/>
+      <c r="CX10" s="28"/>
+      <c r="CY10" s="29" t="s">
+        <v>1732</v>
+      </c>
+      <c r="CZ10" s="29"/>
+      <c r="DA10" s="29" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DB10" s="29"/>
+      <c r="DC10" s="29" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DD10" s="29"/>
+      <c r="DE10" s="29" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DF10" s="28"/>
+    </row>
+    <row r="11" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D11" s="12"/>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="15" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="12"/>
@@ -7093,10 +7499,10 @@
       </c>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
-      <c r="W11" s="13" t="s">
+      <c r="W11" t="s">
         <v>671</v>
       </c>
-      <c r="AA11" s="13" t="s">
+      <c r="AA11" t="s">
         <v>1396</v>
       </c>
       <c r="AG11" s="9" t="s">
@@ -7111,10 +7517,10 @@
         <v>674</v>
       </c>
       <c r="AL11" s="9"/>
-      <c r="AM11" s="13" t="s">
+      <c r="AM11" t="s">
         <v>675</v>
       </c>
-      <c r="AO11" s="13" t="s">
+      <c r="AO11" t="s">
         <v>676</v>
       </c>
       <c r="AQ11" s="9" t="s">
@@ -7122,10 +7528,10 @@
       </c>
       <c r="AS11" s="12"/>
       <c r="AT11" s="12"/>
-      <c r="AU11" s="13" t="s">
+      <c r="AU11" t="s">
         <v>671</v>
       </c>
-      <c r="BE11" s="13" t="s">
+      <c r="BE11" t="s">
         <v>1398</v>
       </c>
       <c r="BG11" s="9" t="s">
@@ -7164,29 +7570,51 @@
       <c r="CE11" s="9" t="s">
         <v>1490</v>
       </c>
-      <c r="CG11" s="22" t="s">
+      <c r="CG11" s="20" t="s">
         <v>1653</v>
       </c>
-      <c r="CI11" s="22" t="s">
+      <c r="CI11" s="20" t="s">
         <v>1673</v>
       </c>
-      <c r="CM11" s="22" t="s">
+      <c r="CM11" s="20" t="s">
         <v>1703</v>
       </c>
-      <c r="CO11" s="22" t="s">
+      <c r="CO11" s="20" t="s">
         <v>1696</v>
       </c>
-    </row>
-    <row r="12" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
+      <c r="CS11" s="28"/>
+      <c r="CT11" s="28"/>
+      <c r="CU11" s="28"/>
+      <c r="CV11" s="28"/>
+      <c r="CW11" s="28"/>
+      <c r="CX11" s="28"/>
+      <c r="CY11" s="29" t="s">
+        <v>1733</v>
+      </c>
+      <c r="CZ11" s="29"/>
+      <c r="DA11" s="29" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DB11" s="29"/>
+      <c r="DC11" s="29" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DD11" s="29"/>
+      <c r="DE11" s="29" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DF11" s="28"/>
+    </row>
+    <row r="12" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A12" s="21" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>62</v>
       </c>
       <c r="F12" s="12"/>
@@ -7209,10 +7637,10 @@
       </c>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
-      <c r="W12" s="13" t="s">
+      <c r="W12" t="s">
         <v>678</v>
       </c>
-      <c r="AA12" s="13" t="s">
+      <c r="AA12" t="s">
         <v>626</v>
       </c>
       <c r="AG12" s="9" t="s">
@@ -7231,7 +7659,7 @@
         <v>682</v>
       </c>
       <c r="AN12" s="9"/>
-      <c r="AO12" s="13" t="s">
+      <c r="AO12" t="s">
         <v>683</v>
       </c>
       <c r="AQ12" s="9" t="s">
@@ -7239,7 +7667,7 @@
       </c>
       <c r="AS12" s="12"/>
       <c r="AT12" s="12"/>
-      <c r="AU12" s="13" t="s">
+      <c r="AU12" t="s">
         <v>678</v>
       </c>
       <c r="BG12" s="9" t="s">
@@ -7272,26 +7700,48 @@
       <c r="CC12" s="9"/>
       <c r="CD12" s="9"/>
       <c r="CE12" s="9"/>
-      <c r="CG12" s="22" t="s">
+      <c r="CG12" s="20" t="s">
         <v>1654</v>
       </c>
-      <c r="CI12" s="22" t="s">
+      <c r="CI12" s="20" t="s">
         <v>1674</v>
       </c>
-      <c r="CO12" s="22" t="s">
+      <c r="CO12" s="20" t="s">
         <v>1697</v>
       </c>
-    </row>
-    <row r="13" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
+      <c r="CS12" s="28"/>
+      <c r="CT12" s="28"/>
+      <c r="CU12" s="28"/>
+      <c r="CV12" s="28"/>
+      <c r="CW12" s="28"/>
+      <c r="CX12" s="28"/>
+      <c r="CY12" s="29" t="s">
+        <v>1734</v>
+      </c>
+      <c r="CZ12" s="29"/>
+      <c r="DA12" s="29" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DB12" s="29"/>
+      <c r="DC12" s="29" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DD12" s="29"/>
+      <c r="DE12" s="29" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DF12" s="28"/>
+    </row>
+    <row r="13" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A13" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>68</v>
       </c>
       <c r="F13" s="12"/>
@@ -7312,10 +7762,10 @@
       </c>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
-      <c r="W13" s="13" t="s">
+      <c r="W13" t="s">
         <v>685</v>
       </c>
-      <c r="AA13" s="13" t="s">
+      <c r="AA13" t="s">
         <v>637</v>
       </c>
       <c r="AG13" s="9" t="s">
@@ -7326,13 +7776,13 @@
         <v>1402</v>
       </c>
       <c r="AJ13" s="9"/>
-      <c r="AK13" s="13" t="s">
+      <c r="AK13" t="s">
         <v>688</v>
       </c>
-      <c r="AM13" s="13" t="s">
+      <c r="AM13" t="s">
         <v>689</v>
       </c>
-      <c r="AO13" s="13" t="s">
+      <c r="AO13" t="s">
         <v>690</v>
       </c>
       <c r="AQ13" s="9" t="s">
@@ -7340,7 +7790,7 @@
       </c>
       <c r="AS13" s="12"/>
       <c r="AT13" s="12"/>
-      <c r="AU13" s="13" t="s">
+      <c r="AU13" t="s">
         <v>685</v>
       </c>
       <c r="BG13" s="9" t="s">
@@ -7373,26 +7823,48 @@
       <c r="CC13" s="9"/>
       <c r="CD13" s="9"/>
       <c r="CE13" s="9"/>
-      <c r="CG13" s="22" t="s">
+      <c r="CG13" s="20" t="s">
         <v>1655</v>
       </c>
-      <c r="CI13" s="22" t="s">
+      <c r="CI13" s="20" t="s">
         <v>1675</v>
       </c>
-      <c r="CO13" s="22" t="s">
+      <c r="CO13" s="20" t="s">
         <v>1698</v>
       </c>
-    </row>
-    <row r="14" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
+      <c r="CS13" s="28"/>
+      <c r="CT13" s="28"/>
+      <c r="CU13" s="28"/>
+      <c r="CV13" s="28"/>
+      <c r="CW13" s="28"/>
+      <c r="CX13" s="28"/>
+      <c r="CY13" s="29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="CZ13" s="29"/>
+      <c r="DA13" s="29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DB13" s="29"/>
+      <c r="DC13" s="29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DD13" s="29"/>
+      <c r="DE13" s="29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DF13" s="28"/>
+    </row>
+    <row r="14" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A14" s="21" t="s">
         <v>71</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D14" s="12"/>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="12"/>
@@ -7413,10 +7885,10 @@
       </c>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
-      <c r="W14" s="13" t="s">
+      <c r="W14" t="s">
         <v>692</v>
       </c>
-      <c r="AA14" s="13" t="s">
+      <c r="AA14" t="s">
         <v>648</v>
       </c>
       <c r="AG14" s="9" t="s">
@@ -7435,7 +7907,7 @@
         <v>668</v>
       </c>
       <c r="AN14" s="9"/>
-      <c r="AO14" s="13" t="s">
+      <c r="AO14" t="s">
         <v>696</v>
       </c>
       <c r="AQ14" s="9" t="s">
@@ -7443,7 +7915,7 @@
       </c>
       <c r="AS14" s="12"/>
       <c r="AT14" s="12"/>
-      <c r="AU14" s="13" t="s">
+      <c r="AU14" t="s">
         <v>692</v>
       </c>
       <c r="BG14" s="9" t="s">
@@ -7476,26 +7948,48 @@
       <c r="CC14" s="9"/>
       <c r="CD14" s="9"/>
       <c r="CE14" s="9"/>
-      <c r="CG14" s="22" t="s">
+      <c r="CG14" s="20" t="s">
         <v>1656</v>
       </c>
-      <c r="CI14" s="22" t="s">
+      <c r="CI14" s="20" t="s">
         <v>1676</v>
       </c>
-      <c r="CO14" s="22" t="s">
+      <c r="CO14" s="20" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="15" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
+      <c r="CS14" s="28"/>
+      <c r="CT14" s="28"/>
+      <c r="CU14" s="28"/>
+      <c r="CV14" s="28"/>
+      <c r="CW14" s="28"/>
+      <c r="CX14" s="28"/>
+      <c r="CY14" s="29" t="s">
+        <v>1736</v>
+      </c>
+      <c r="CZ14" s="29"/>
+      <c r="DA14" s="29" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DB14" s="29"/>
+      <c r="DC14" s="29" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DD14" s="29"/>
+      <c r="DE14" s="29" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DF14" s="28"/>
+    </row>
+    <row r="15" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
         <v>76</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D15" s="12"/>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>78</v>
       </c>
       <c r="F15" s="12"/>
@@ -7516,7 +8010,7 @@
       </c>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
-      <c r="W15" s="13" t="s">
+      <c r="W15" t="s">
         <v>698</v>
       </c>
       <c r="AA15" s="12" t="s">
@@ -7539,7 +8033,7 @@
         <v>701</v>
       </c>
       <c r="AN15" s="9"/>
-      <c r="AO15" s="13" t="s">
+      <c r="AO15" t="s">
         <v>702</v>
       </c>
       <c r="AQ15" s="9" t="s">
@@ -7547,7 +8041,7 @@
       </c>
       <c r="AS15" s="12"/>
       <c r="AT15" s="12"/>
-      <c r="AU15" s="13" t="s">
+      <c r="AU15" t="s">
         <v>698</v>
       </c>
       <c r="BG15" s="9" t="s">
@@ -7580,23 +8074,45 @@
       <c r="CC15" s="9"/>
       <c r="CD15" s="9"/>
       <c r="CE15" s="9"/>
-      <c r="CG15" s="22" t="s">
+      <c r="CG15" s="20" t="s">
         <v>1657</v>
       </c>
-      <c r="CI15" s="22" t="s">
+      <c r="CI15" s="20" t="s">
         <v>1677</v>
       </c>
-    </row>
-    <row r="16" spans="1:115" x14ac:dyDescent="0.35">
-      <c r="A16" s="23" t="s">
+      <c r="CS15" s="28"/>
+      <c r="CT15" s="28"/>
+      <c r="CU15" s="28"/>
+      <c r="CV15" s="28"/>
+      <c r="CW15" s="28"/>
+      <c r="CX15" s="28"/>
+      <c r="CY15" s="29" t="s">
+        <v>1737</v>
+      </c>
+      <c r="CZ15" s="29"/>
+      <c r="DA15" s="29" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DB15" s="29"/>
+      <c r="DC15" s="29" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DD15" s="29"/>
+      <c r="DE15" s="29" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DF15" s="28"/>
+    </row>
+    <row r="16" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="A16" s="21" t="s">
         <v>81</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="15" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="12"/>
@@ -7617,10 +8133,10 @@
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
-      <c r="W16" s="13" t="s">
+      <c r="W16" t="s">
         <v>704</v>
       </c>
-      <c r="AA16" s="13" t="s">
+      <c r="AA16" t="s">
         <v>1408</v>
       </c>
       <c r="AG16" s="9" t="s">
@@ -7631,13 +8147,13 @@
         <v>1409</v>
       </c>
       <c r="AJ16" s="9"/>
-      <c r="AK16" s="13" t="s">
+      <c r="AK16" t="s">
         <v>706</v>
       </c>
-      <c r="AM16" s="13" t="s">
+      <c r="AM16" t="s">
         <v>707</v>
       </c>
-      <c r="AO16" s="13" t="s">
+      <c r="AO16" t="s">
         <v>708</v>
       </c>
       <c r="AQ16" s="9" t="s">
@@ -7645,7 +8161,7 @@
       </c>
       <c r="AS16" s="12"/>
       <c r="AT16" s="12"/>
-      <c r="AU16" s="13" t="s">
+      <c r="AU16" t="s">
         <v>704</v>
       </c>
       <c r="BG16" s="9" t="s">
@@ -7678,20 +8194,42 @@
       <c r="CC16" s="9"/>
       <c r="CD16" s="9"/>
       <c r="CE16" s="9"/>
-      <c r="CG16" s="22" t="s">
+      <c r="CG16" s="20" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="17" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
+      <c r="CS16" s="28"/>
+      <c r="CT16" s="28"/>
+      <c r="CU16" s="28"/>
+      <c r="CV16" s="28"/>
+      <c r="CW16" s="28"/>
+      <c r="CX16" s="28"/>
+      <c r="CY16" s="29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="CZ16" s="29"/>
+      <c r="DA16" s="29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DB16" s="29"/>
+      <c r="DC16" s="29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DD16" s="29"/>
+      <c r="DE16" s="29" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DF16" s="28"/>
+    </row>
+    <row r="17" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D17" s="12"/>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="15" t="s">
         <v>88</v>
       </c>
       <c r="F17" s="12"/>
@@ -7712,10 +8250,10 @@
       </c>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
-      <c r="W17" s="13" t="s">
+      <c r="W17" t="s">
         <v>710</v>
       </c>
-      <c r="AA17" s="13" t="s">
+      <c r="AA17" t="s">
         <v>665</v>
       </c>
       <c r="AG17" s="9" t="s">
@@ -7734,7 +8272,7 @@
         <v>674</v>
       </c>
       <c r="AN17" s="9"/>
-      <c r="AO17" s="13" t="s">
+      <c r="AO17" t="s">
         <v>713</v>
       </c>
       <c r="AQ17" s="9" t="s">
@@ -7742,7 +8280,7 @@
       </c>
       <c r="AS17" s="12"/>
       <c r="AT17" s="12"/>
-      <c r="AU17" s="13" t="s">
+      <c r="AU17" t="s">
         <v>710</v>
       </c>
       <c r="BG17" s="9" t="s">
@@ -7773,20 +8311,42 @@
       <c r="CC17" s="9"/>
       <c r="CD17" s="9"/>
       <c r="CE17" s="9"/>
-      <c r="CG17" s="22" t="s">
+      <c r="CG17" s="20" t="s">
         <v>1659</v>
       </c>
-    </row>
-    <row r="18" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
+      <c r="CS17" s="28"/>
+      <c r="CT17" s="28"/>
+      <c r="CU17" s="28"/>
+      <c r="CV17" s="28"/>
+      <c r="CW17" s="28"/>
+      <c r="CX17" s="28"/>
+      <c r="CY17" s="29" t="s">
+        <v>1739</v>
+      </c>
+      <c r="CZ17" s="29"/>
+      <c r="DA17" s="29" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DB17" s="29"/>
+      <c r="DC17" s="29" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DD17" s="29"/>
+      <c r="DE17" s="29" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DF17" s="28"/>
+    </row>
+    <row r="18" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>92</v>
       </c>
       <c r="D18" s="12"/>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="15" t="s">
         <v>93</v>
       </c>
       <c r="F18" s="12"/>
@@ -7807,10 +8367,10 @@
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
-      <c r="W18" s="13" t="s">
+      <c r="W18" t="s">
         <v>715</v>
       </c>
-      <c r="AA18" s="13" t="s">
+      <c r="AA18" t="s">
         <v>672</v>
       </c>
       <c r="AG18" s="9" t="s">
@@ -7821,14 +8381,14 @@
         <v>1413</v>
       </c>
       <c r="AJ18" s="9"/>
-      <c r="AK18" s="13" t="s">
+      <c r="AK18" t="s">
         <v>717</v>
       </c>
       <c r="AM18" s="9" t="s">
         <v>681</v>
       </c>
       <c r="AN18" s="9"/>
-      <c r="AO18" s="13" t="s">
+      <c r="AO18" t="s">
         <v>718</v>
       </c>
       <c r="AQ18" s="9" t="s">
@@ -7836,7 +8396,7 @@
       </c>
       <c r="AS18" s="12"/>
       <c r="AT18" s="12"/>
-      <c r="AU18" s="13" t="s">
+      <c r="AU18" t="s">
         <v>715</v>
       </c>
       <c r="BG18" s="9" t="s">
@@ -7867,20 +8427,42 @@
       <c r="CC18" s="9"/>
       <c r="CD18" s="9"/>
       <c r="CE18" s="9"/>
-      <c r="CG18" s="22" t="s">
+      <c r="CG18" s="20" t="s">
         <v>1660</v>
       </c>
-    </row>
-    <row r="19" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="CS18" s="28"/>
+      <c r="CT18" s="28"/>
+      <c r="CU18" s="28"/>
+      <c r="CV18" s="28"/>
+      <c r="CW18" s="28"/>
+      <c r="CX18" s="28"/>
+      <c r="CY18" s="29" t="s">
+        <v>1740</v>
+      </c>
+      <c r="CZ18" s="29"/>
+      <c r="DA18" s="29" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DB18" s="29"/>
+      <c r="DC18" s="29" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DD18" s="29"/>
+      <c r="DE18" s="29" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DF18" s="28"/>
+    </row>
+    <row r="19" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="14" t="s">
         <v>96</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="14" t="s">
         <v>97</v>
       </c>
       <c r="D19" s="12"/>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="15" t="s">
         <v>98</v>
       </c>
       <c r="F19" s="12"/>
@@ -7901,10 +8483,10 @@
       </c>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
-      <c r="W19" s="13" t="s">
+      <c r="W19" t="s">
         <v>720</v>
       </c>
-      <c r="AA19" s="13" t="s">
+      <c r="AA19" t="s">
         <v>679</v>
       </c>
       <c r="AG19" s="9" t="s">
@@ -7919,10 +8501,10 @@
         <v>722</v>
       </c>
       <c r="AL19" s="9"/>
-      <c r="AM19" s="13" t="s">
+      <c r="AM19" t="s">
         <v>723</v>
       </c>
-      <c r="AO19" s="13" t="s">
+      <c r="AO19" t="s">
         <v>724</v>
       </c>
       <c r="AQ19" s="9" t="s">
@@ -7930,7 +8512,7 @@
       </c>
       <c r="AS19" s="12"/>
       <c r="AT19" s="12"/>
-      <c r="AU19" s="13" t="s">
+      <c r="AU19" t="s">
         <v>720</v>
       </c>
       <c r="BG19" s="9" t="s">
@@ -7961,20 +8543,42 @@
       <c r="CC19" s="9"/>
       <c r="CD19" s="9"/>
       <c r="CE19" s="9"/>
-      <c r="CG19" s="22" t="s">
+      <c r="CG19" s="20" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="20" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A20" s="23" t="s">
+      <c r="CS19" s="28"/>
+      <c r="CT19" s="28"/>
+      <c r="CU19" s="28"/>
+      <c r="CV19" s="28"/>
+      <c r="CW19" s="28"/>
+      <c r="CX19" s="28"/>
+      <c r="CY19" s="29" t="s">
+        <v>1741</v>
+      </c>
+      <c r="CZ19" s="29"/>
+      <c r="DA19" s="29" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DB19" s="29"/>
+      <c r="DC19" s="29" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DD19" s="29"/>
+      <c r="DE19" s="29" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DF19" s="28"/>
+    </row>
+    <row r="20" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A20" s="21" t="s">
         <v>100</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>101</v>
       </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>102</v>
       </c>
       <c r="F20" s="12"/>
@@ -7995,10 +8599,10 @@
       </c>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
-      <c r="W20" s="13" t="s">
+      <c r="W20" t="s">
         <v>726</v>
       </c>
-      <c r="AA20" s="13" t="s">
+      <c r="AA20" t="s">
         <v>686</v>
       </c>
       <c r="AG20" s="9" t="s">
@@ -8009,13 +8613,13 @@
         <v>1417</v>
       </c>
       <c r="AJ20" s="9"/>
-      <c r="AK20" s="13" t="s">
+      <c r="AK20" t="s">
         <v>728</v>
       </c>
-      <c r="AM20" s="13" t="s">
+      <c r="AM20" t="s">
         <v>729</v>
       </c>
-      <c r="AO20" s="13" t="s">
+      <c r="AO20" t="s">
         <v>730</v>
       </c>
       <c r="AQ20" s="9" t="s">
@@ -8023,7 +8627,7 @@
       </c>
       <c r="AS20" s="12"/>
       <c r="AT20" s="12"/>
-      <c r="AU20" s="13" t="s">
+      <c r="AU20" t="s">
         <v>726</v>
       </c>
       <c r="BK20" s="9"/>
@@ -8051,20 +8655,42 @@
       <c r="CC20" s="9"/>
       <c r="CD20" s="9"/>
       <c r="CE20" s="9"/>
-      <c r="CG20" s="22" t="s">
+      <c r="CG20" s="20" t="s">
         <v>1662</v>
       </c>
-    </row>
-    <row r="21" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="CS20" s="28"/>
+      <c r="CT20" s="28"/>
+      <c r="CU20" s="28"/>
+      <c r="CV20" s="28"/>
+      <c r="CW20" s="28"/>
+      <c r="CX20" s="28"/>
+      <c r="CY20" s="29" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CZ20" s="29"/>
+      <c r="DA20" s="29" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DB20" s="29"/>
+      <c r="DC20" s="29" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DD20" s="29"/>
+      <c r="DE20" s="29" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DF20" s="28"/>
+    </row>
+    <row r="21" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
         <v>105</v>
       </c>
       <c r="B21" s="12"/>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="14" t="s">
         <v>106</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="15" t="s">
         <v>107</v>
       </c>
       <c r="F21" s="12"/>
@@ -8083,10 +8709,10 @@
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
-      <c r="W21" s="13" t="s">
+      <c r="W21" t="s">
         <v>732</v>
       </c>
-      <c r="AA21" s="13" t="s">
+      <c r="AA21" t="s">
         <v>693</v>
       </c>
       <c r="AG21" s="9" t="s">
@@ -8105,7 +8731,7 @@
         <v>695</v>
       </c>
       <c r="AN21" s="9"/>
-      <c r="AO21" s="13" t="s">
+      <c r="AO21" t="s">
         <v>735</v>
       </c>
       <c r="AQ21" s="9" t="s">
@@ -8113,7 +8739,7 @@
       </c>
       <c r="AS21" s="12"/>
       <c r="AT21" s="12"/>
-      <c r="AU21" s="13" t="s">
+      <c r="AU21" t="s">
         <v>732</v>
       </c>
       <c r="BK21" s="9"/>
@@ -8141,20 +8767,42 @@
       <c r="CC21" s="9"/>
       <c r="CD21" s="9"/>
       <c r="CE21" s="9"/>
-      <c r="CG21" s="22" t="s">
+      <c r="CG21" s="20" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="22" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A22" s="23" t="s">
+      <c r="CS21" s="28"/>
+      <c r="CT21" s="28"/>
+      <c r="CU21" s="28"/>
+      <c r="CV21" s="28"/>
+      <c r="CW21" s="28"/>
+      <c r="CX21" s="28"/>
+      <c r="CY21" s="29" t="s">
+        <v>1743</v>
+      </c>
+      <c r="CZ21" s="29"/>
+      <c r="DA21" s="29" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DB21" s="29"/>
+      <c r="DC21" s="29" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DD21" s="29"/>
+      <c r="DE21" s="29" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DF21" s="28"/>
+    </row>
+    <row r="22" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A22" s="21" t="s">
         <v>109</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="15" t="s">
         <v>111</v>
       </c>
       <c r="F22" s="12"/>
@@ -8173,7 +8821,7 @@
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
-      <c r="W22" s="13" t="s">
+      <c r="W22" t="s">
         <v>737</v>
       </c>
       <c r="AG22" s="9" t="s">
@@ -8188,10 +8836,10 @@
         <v>739</v>
       </c>
       <c r="AL22" s="9"/>
-      <c r="AM22" s="13" t="s">
+      <c r="AM22" t="s">
         <v>740</v>
       </c>
-      <c r="AO22" s="13" t="s">
+      <c r="AO22" t="s">
         <v>741</v>
       </c>
       <c r="AQ22" s="9" t="s">
@@ -8199,7 +8847,7 @@
       </c>
       <c r="AS22" s="12"/>
       <c r="AT22" s="12"/>
-      <c r="AU22" s="13" t="s">
+      <c r="AU22" t="s">
         <v>737</v>
       </c>
       <c r="BK22" s="9"/>
@@ -8227,17 +8875,39 @@
       <c r="CC22" s="9"/>
       <c r="CD22" s="9"/>
       <c r="CE22" s="9"/>
-    </row>
-    <row r="23" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="CS22" s="28"/>
+      <c r="CT22" s="28"/>
+      <c r="CU22" s="28"/>
+      <c r="CV22" s="28"/>
+      <c r="CW22" s="28"/>
+      <c r="CX22" s="28"/>
+      <c r="CY22" s="29" t="s">
+        <v>1744</v>
+      </c>
+      <c r="CZ22" s="29"/>
+      <c r="DA22" s="29" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DB22" s="29"/>
+      <c r="DC22" s="29" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DD22" s="29"/>
+      <c r="DE22" s="29" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DF22" s="28"/>
+    </row>
+    <row r="23" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A23" s="14" t="s">
         <v>113</v>
       </c>
       <c r="B23" s="12"/>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="14" t="s">
         <v>114</v>
       </c>
       <c r="D23" s="12"/>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F23" s="12"/>
@@ -8264,14 +8934,14 @@
         <v>1420</v>
       </c>
       <c r="AJ23" s="9"/>
-      <c r="AK23" s="13" t="s">
+      <c r="AK23" t="s">
         <v>744</v>
       </c>
       <c r="AM23" s="9" t="s">
         <v>700</v>
       </c>
       <c r="AN23" s="9"/>
-      <c r="AO23" s="13" t="s">
+      <c r="AO23" t="s">
         <v>745</v>
       </c>
       <c r="AQ23" s="9" t="s">
@@ -8302,17 +8972,39 @@
       <c r="CC23" s="9"/>
       <c r="CD23" s="9"/>
       <c r="CE23" s="9"/>
-    </row>
-    <row r="24" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="CS23" s="28"/>
+      <c r="CT23" s="28"/>
+      <c r="CU23" s="28"/>
+      <c r="CV23" s="28"/>
+      <c r="CW23" s="28"/>
+      <c r="CX23" s="28"/>
+      <c r="CY23" s="29" t="s">
+        <v>1745</v>
+      </c>
+      <c r="CZ23" s="29"/>
+      <c r="DA23" s="29" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DB23" s="29"/>
+      <c r="DC23" s="29" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DD23" s="29"/>
+      <c r="DE23" s="29" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DF23" s="28"/>
+    </row>
+    <row r="24" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>118</v>
       </c>
       <c r="D24" s="12"/>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F24" s="12"/>
@@ -8339,10 +9031,10 @@
         <v>1421</v>
       </c>
       <c r="AJ24" s="9"/>
-      <c r="AK24" s="13" t="s">
+      <c r="AK24" t="s">
         <v>749</v>
       </c>
-      <c r="AM24" s="13" t="s">
+      <c r="AM24" t="s">
         <v>750</v>
       </c>
       <c r="AQ24" s="9" t="s">
@@ -8373,17 +9065,39 @@
       <c r="CC24" s="9"/>
       <c r="CD24" s="9"/>
       <c r="CE24" s="9"/>
-    </row>
-    <row r="25" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
+      <c r="CS24" s="28"/>
+      <c r="CT24" s="28"/>
+      <c r="CU24" s="28"/>
+      <c r="CV24" s="28"/>
+      <c r="CW24" s="28"/>
+      <c r="CX24" s="28"/>
+      <c r="CY24" s="29" t="s">
+        <v>1746</v>
+      </c>
+      <c r="CZ24" s="29"/>
+      <c r="DA24" s="29" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DB24" s="29"/>
+      <c r="DC24" s="29" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DD24" s="29"/>
+      <c r="DE24" s="29" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DF24" s="28"/>
+    </row>
+    <row r="25" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A25" s="14" t="s">
         <v>121</v>
       </c>
       <c r="B25" s="12"/>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="14" t="s">
         <v>122</v>
       </c>
       <c r="D25" s="12"/>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="15" t="s">
         <v>123</v>
       </c>
       <c r="F25" s="12"/>
@@ -8410,7 +9124,7 @@
         <v>1422</v>
       </c>
       <c r="AJ25" s="9"/>
-      <c r="AK25" s="13" t="s">
+      <c r="AK25" t="s">
         <v>753</v>
       </c>
       <c r="AM25" s="9" t="s">
@@ -8445,17 +9159,39 @@
       <c r="CC25" s="9"/>
       <c r="CD25" s="9"/>
       <c r="CE25" s="9"/>
-    </row>
-    <row r="26" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A26" s="23" t="s">
+      <c r="CS25" s="28"/>
+      <c r="CT25" s="28"/>
+      <c r="CU25" s="28"/>
+      <c r="CV25" s="28"/>
+      <c r="CW25" s="28"/>
+      <c r="CX25" s="28"/>
+      <c r="CY25" s="29" t="s">
+        <v>1747</v>
+      </c>
+      <c r="CZ25" s="29"/>
+      <c r="DA25" s="29" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DB25" s="29"/>
+      <c r="DC25" s="29" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DD25" s="29"/>
+      <c r="DE25" s="29" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DF25" s="28"/>
+    </row>
+    <row r="26" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A26" s="21" t="s">
         <v>125</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>126</v>
       </c>
       <c r="D26" s="12"/>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>127</v>
       </c>
       <c r="F26" s="12"/>
@@ -8518,17 +9254,39 @@
       <c r="CC26" s="9"/>
       <c r="CD26" s="9"/>
       <c r="CE26" s="9"/>
-    </row>
-    <row r="27" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
+      <c r="CS26" s="28"/>
+      <c r="CT26" s="28"/>
+      <c r="CU26" s="29"/>
+      <c r="CV26" s="29"/>
+      <c r="CW26" s="28"/>
+      <c r="CX26" s="28"/>
+      <c r="CY26" s="29" t="s">
+        <v>1748</v>
+      </c>
+      <c r="CZ26" s="29"/>
+      <c r="DA26" s="29" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DB26" s="29"/>
+      <c r="DC26" s="29" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DD26" s="29"/>
+      <c r="DE26" s="29" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DF26" s="28"/>
+    </row>
+    <row r="27" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B27" s="12"/>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="14" t="s">
         <v>130</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="15" t="s">
         <v>131</v>
       </c>
       <c r="F27" s="12"/>
@@ -8558,7 +9316,7 @@
         <v>760</v>
       </c>
       <c r="AL27" s="9"/>
-      <c r="AM27" s="13" t="s">
+      <c r="AM27" t="s">
         <v>761</v>
       </c>
       <c r="AQ27" s="9" t="s">
@@ -8589,17 +9347,39 @@
       <c r="CC27" s="9"/>
       <c r="CD27" s="9"/>
       <c r="CE27" s="9"/>
-    </row>
-    <row r="28" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A28" s="23" t="s">
+      <c r="CS27" s="28"/>
+      <c r="CT27" s="28"/>
+      <c r="CU27" s="29"/>
+      <c r="CV27" s="29"/>
+      <c r="CW27" s="28"/>
+      <c r="CX27" s="28"/>
+      <c r="CY27" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="CZ27" s="29"/>
+      <c r="DA27" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DB27" s="29"/>
+      <c r="DC27" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DD27" s="29"/>
+      <c r="DE27" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DF27" s="28"/>
+    </row>
+    <row r="28" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A28" s="21" t="s">
         <v>133</v>
       </c>
       <c r="B28" s="12"/>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F28" s="12"/>
@@ -8629,7 +9409,7 @@
         <v>764</v>
       </c>
       <c r="AL28" s="9"/>
-      <c r="AM28" s="13" t="s">
+      <c r="AM28" t="s">
         <v>765</v>
       </c>
       <c r="AQ28" s="9" t="s">
@@ -8660,17 +9440,39 @@
       <c r="CC28" s="9"/>
       <c r="CD28" s="9"/>
       <c r="CE28" s="9"/>
-    </row>
-    <row r="29" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
+      <c r="CS28" s="28"/>
+      <c r="CT28" s="28"/>
+      <c r="CU28" s="29"/>
+      <c r="CV28" s="29"/>
+      <c r="CW28" s="28"/>
+      <c r="CX28" s="28"/>
+      <c r="CY28" s="29" t="s">
+        <v>1750</v>
+      </c>
+      <c r="CZ28" s="29"/>
+      <c r="DA28" s="29" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DB28" s="29"/>
+      <c r="DC28" s="29" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DD28" s="29"/>
+      <c r="DE28" s="29" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DF28" s="28"/>
+    </row>
+    <row r="29" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A29" s="14" t="s">
         <v>137</v>
       </c>
       <c r="B29" s="12"/>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="14" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="12"/>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="15" t="s">
         <v>139</v>
       </c>
       <c r="F29" s="12"/>
@@ -8696,10 +9498,10 @@
       <c r="AI29" s="10" t="s">
         <v>1425</v>
       </c>
-      <c r="AK29" s="13" t="s">
+      <c r="AK29" t="s">
         <v>768</v>
       </c>
-      <c r="AM29" s="13" t="s">
+      <c r="AM29" t="s">
         <v>728</v>
       </c>
       <c r="AQ29" s="9" t="s">
@@ -8730,17 +9532,39 @@
       <c r="CC29" s="9"/>
       <c r="CD29" s="9"/>
       <c r="CE29" s="9"/>
-    </row>
-    <row r="30" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A30" s="23" t="s">
+      <c r="CS29" s="28"/>
+      <c r="CT29" s="28"/>
+      <c r="CU29" s="28"/>
+      <c r="CV29" s="28"/>
+      <c r="CW29" s="28"/>
+      <c r="CX29" s="28"/>
+      <c r="CY29" s="29" t="s">
+        <v>1751</v>
+      </c>
+      <c r="CZ29" s="29"/>
+      <c r="DA29" s="29" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DB29" s="29"/>
+      <c r="DC29" s="29" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DD29" s="29"/>
+      <c r="DE29" s="29" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DF29" s="28"/>
+    </row>
+    <row r="30" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A30" s="21" t="s">
         <v>141</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="21" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="12"/>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="15" t="s">
         <v>143</v>
       </c>
       <c r="F30" s="12"/>
@@ -8770,7 +9594,7 @@
         <v>771</v>
       </c>
       <c r="AL30" s="9"/>
-      <c r="AM30" s="13" t="s">
+      <c r="AM30" t="s">
         <v>772</v>
       </c>
       <c r="AQ30" s="9" t="s">
@@ -8801,17 +9625,39 @@
       <c r="CC30" s="9"/>
       <c r="CD30" s="9"/>
       <c r="CE30" s="9"/>
-    </row>
-    <row r="31" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
+      <c r="CS30" s="28"/>
+      <c r="CT30" s="28"/>
+      <c r="CU30" s="28"/>
+      <c r="CV30" s="28"/>
+      <c r="CW30" s="28"/>
+      <c r="CX30" s="28"/>
+      <c r="CY30" s="29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="CZ30" s="29"/>
+      <c r="DA30" s="29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DB30" s="29"/>
+      <c r="DC30" s="29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DD30" s="29"/>
+      <c r="DE30" s="29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DF30" s="28"/>
+    </row>
+    <row r="31" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A31" s="14" t="s">
         <v>145</v>
       </c>
       <c r="B31" s="12"/>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="14" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="12"/>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="15" t="s">
         <v>147</v>
       </c>
       <c r="F31" s="12"/>
@@ -8873,17 +9719,39 @@
       <c r="CC31" s="9"/>
       <c r="CD31" s="9"/>
       <c r="CE31" s="9"/>
-    </row>
-    <row r="32" spans="1:85" x14ac:dyDescent="0.35">
-      <c r="A32" s="23" t="s">
+      <c r="CS31" s="28"/>
+      <c r="CT31" s="28"/>
+      <c r="CU31" s="28"/>
+      <c r="CV31" s="28"/>
+      <c r="CW31" s="28"/>
+      <c r="CX31" s="28"/>
+      <c r="CY31" s="29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="CZ31" s="29"/>
+      <c r="DA31" s="29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DB31" s="29"/>
+      <c r="DC31" s="29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DD31" s="29"/>
+      <c r="DE31" s="29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DF31" s="28"/>
+    </row>
+    <row r="32" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A32" s="21" t="s">
         <v>149</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="21" t="s">
         <v>150</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="15" t="s">
         <v>151</v>
       </c>
       <c r="F32" s="12"/>
@@ -8909,7 +9777,7 @@
       <c r="AI32" s="11" t="s">
         <v>1428</v>
       </c>
-      <c r="AK32" s="13" t="s">
+      <c r="AK32" t="s">
         <v>778</v>
       </c>
       <c r="AM32" s="9" t="s">
@@ -8944,17 +9812,39 @@
       <c r="CC32" s="9"/>
       <c r="CD32" s="9"/>
       <c r="CE32" s="9"/>
-    </row>
-    <row r="33" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A33" s="16" t="s">
+      <c r="CS32" s="28"/>
+      <c r="CT32" s="28"/>
+      <c r="CU32" s="28"/>
+      <c r="CV32" s="28"/>
+      <c r="CW32" s="28"/>
+      <c r="CX32" s="28"/>
+      <c r="CY32" s="29" t="s">
+        <v>1754</v>
+      </c>
+      <c r="CZ32" s="29"/>
+      <c r="DA32" s="29" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DB32" s="29"/>
+      <c r="DC32" s="29" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DD32" s="29"/>
+      <c r="DE32" s="29" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DF32" s="28"/>
+    </row>
+    <row r="33" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A33" s="14" t="s">
         <v>153</v>
       </c>
       <c r="B33" s="12"/>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="14" t="s">
         <v>154</v>
       </c>
       <c r="D33" s="12"/>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="15" t="s">
         <v>155</v>
       </c>
       <c r="F33" s="12"/>
@@ -8984,7 +9874,7 @@
         <v>781</v>
       </c>
       <c r="AL33" s="9"/>
-      <c r="AM33" s="13" t="s">
+      <c r="AM33" t="s">
         <v>744</v>
       </c>
       <c r="AQ33" s="9" t="s">
@@ -9015,17 +9905,39 @@
       <c r="CC33" s="9"/>
       <c r="CD33" s="9"/>
       <c r="CE33" s="9"/>
-    </row>
-    <row r="34" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A34" s="23" t="s">
+      <c r="CS33" s="28"/>
+      <c r="CT33" s="28"/>
+      <c r="CU33" s="28"/>
+      <c r="CV33" s="28"/>
+      <c r="CW33" s="28"/>
+      <c r="CX33" s="28"/>
+      <c r="CY33" s="29" t="s">
+        <v>1755</v>
+      </c>
+      <c r="CZ33" s="29"/>
+      <c r="DA33" s="29" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DB33" s="29"/>
+      <c r="DC33" s="29" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DD33" s="29"/>
+      <c r="DE33" s="29" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DF33" s="28"/>
+    </row>
+    <row r="34" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A34" s="21" t="s">
         <v>157</v>
       </c>
       <c r="B34" s="12"/>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="21" t="s">
         <v>158</v>
       </c>
       <c r="D34" s="12"/>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="15" t="s">
         <v>159</v>
       </c>
       <c r="F34" s="12"/>
@@ -9087,17 +9999,39 @@
       <c r="CC34" s="9"/>
       <c r="CD34" s="9"/>
       <c r="CE34" s="9"/>
-    </row>
-    <row r="35" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A35" s="16" t="s">
+      <c r="CS34" s="28"/>
+      <c r="CT34" s="28"/>
+      <c r="CU34" s="28"/>
+      <c r="CV34" s="28"/>
+      <c r="CW34" s="28"/>
+      <c r="CX34" s="28"/>
+      <c r="CY34" s="29" t="s">
+        <v>1756</v>
+      </c>
+      <c r="CZ34" s="29"/>
+      <c r="DA34" s="29" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DB34" s="29"/>
+      <c r="DC34" s="29" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DD34" s="29"/>
+      <c r="DE34" s="29" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DF34" s="28"/>
+    </row>
+    <row r="35" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A35" s="14" t="s">
         <v>161</v>
       </c>
       <c r="B35" s="12"/>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="14" t="s">
         <v>162</v>
       </c>
       <c r="D35" s="12"/>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="15" t="s">
         <v>163</v>
       </c>
       <c r="F35" s="12"/>
@@ -9156,13 +10090,35 @@
       <c r="CC35" s="9"/>
       <c r="CD35" s="9"/>
       <c r="CE35" s="9"/>
-    </row>
-    <row r="36" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A36" s="23" t="s">
+      <c r="CS35" s="28"/>
+      <c r="CT35" s="28"/>
+      <c r="CU35" s="28"/>
+      <c r="CV35" s="28"/>
+      <c r="CW35" s="28"/>
+      <c r="CX35" s="28"/>
+      <c r="CY35" s="29" t="s">
+        <v>1757</v>
+      </c>
+      <c r="CZ35" s="29"/>
+      <c r="DA35" s="29" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DB35" s="29"/>
+      <c r="DC35" s="29" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DD35" s="29"/>
+      <c r="DE35" s="29" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DF35" s="28"/>
+    </row>
+    <row r="36" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A36" s="21" t="s">
         <v>165</v>
       </c>
       <c r="B36" s="12"/>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="21" t="s">
         <v>166</v>
       </c>
       <c r="D36" s="12"/>
@@ -9221,13 +10177,35 @@
       <c r="CC36" s="9"/>
       <c r="CD36" s="9"/>
       <c r="CE36" s="9"/>
-    </row>
-    <row r="37" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A37" s="16" t="s">
+      <c r="CS36" s="28"/>
+      <c r="CT36" s="28"/>
+      <c r="CU36" s="28"/>
+      <c r="CV36" s="28"/>
+      <c r="CW36" s="28"/>
+      <c r="CX36" s="28"/>
+      <c r="CY36" s="29" t="s">
+        <v>1758</v>
+      </c>
+      <c r="CZ36" s="29"/>
+      <c r="DA36" s="29" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DB36" s="29"/>
+      <c r="DC36" s="29" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DD36" s="29"/>
+      <c r="DE36" s="29" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DF36" s="28"/>
+    </row>
+    <row r="37" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A37" s="14" t="s">
         <v>167</v>
       </c>
       <c r="B37" s="12"/>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="14" t="s">
         <v>168</v>
       </c>
       <c r="D37" s="12"/>
@@ -9250,10 +10228,10 @@
         <v>793</v>
       </c>
       <c r="AH37" s="9"/>
-      <c r="AK37" s="13" t="s">
+      <c r="AK37" t="s">
         <v>794</v>
       </c>
-      <c r="AM37" s="13" t="s">
+      <c r="AM37" t="s">
         <v>768</v>
       </c>
       <c r="AQ37" s="9" t="s">
@@ -9284,13 +10262,35 @@
       <c r="CC37" s="9"/>
       <c r="CD37" s="9"/>
       <c r="CE37" s="9"/>
-    </row>
-    <row r="38" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A38" s="23" t="s">
+      <c r="CS37" s="28"/>
+      <c r="CT37" s="28"/>
+      <c r="CU37" s="28"/>
+      <c r="CV37" s="28"/>
+      <c r="CW37" s="28"/>
+      <c r="CX37" s="28"/>
+      <c r="CY37" s="29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="CZ37" s="29"/>
+      <c r="DA37" s="29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DB37" s="29"/>
+      <c r="DC37" s="29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DD37" s="29"/>
+      <c r="DE37" s="29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DF37" s="28"/>
+    </row>
+    <row r="38" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A38" s="21" t="s">
         <v>169</v>
       </c>
       <c r="B38" s="12"/>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="21" t="s">
         <v>170</v>
       </c>
       <c r="D38" s="12"/>
@@ -9349,13 +10349,35 @@
       <c r="CC38" s="9"/>
       <c r="CD38" s="9"/>
       <c r="CE38" s="9"/>
-    </row>
-    <row r="39" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
+      <c r="CS38" s="28"/>
+      <c r="CT38" s="28"/>
+      <c r="CU38" s="28"/>
+      <c r="CV38" s="28"/>
+      <c r="CW38" s="28"/>
+      <c r="CX38" s="28"/>
+      <c r="CY38" s="29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="CZ38" s="29"/>
+      <c r="DA38" s="29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DB38" s="29"/>
+      <c r="DC38" s="29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DD38" s="29"/>
+      <c r="DE38" s="29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DF38" s="28"/>
+    </row>
+    <row r="39" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A39" s="14" t="s">
         <v>171</v>
       </c>
       <c r="B39" s="12"/>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="14" t="s">
         <v>172</v>
       </c>
       <c r="D39" s="12"/>
@@ -9382,7 +10404,7 @@
         <v>801</v>
       </c>
       <c r="AL39" s="9"/>
-      <c r="AM39" s="13" t="s">
+      <c r="AM39" t="s">
         <v>778</v>
       </c>
       <c r="AQ39" s="9" t="s">
@@ -9413,13 +10435,35 @@
       <c r="CC39" s="9"/>
       <c r="CD39" s="9"/>
       <c r="CE39" s="9"/>
-    </row>
-    <row r="40" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A40" s="23" t="s">
+      <c r="CS39" s="28"/>
+      <c r="CT39" s="28"/>
+      <c r="CU39" s="28"/>
+      <c r="CV39" s="28"/>
+      <c r="CW39" s="28"/>
+      <c r="CX39" s="28"/>
+      <c r="CY39" s="29" t="s">
+        <v>1761</v>
+      </c>
+      <c r="CZ39" s="29"/>
+      <c r="DA39" s="29" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DB39" s="29"/>
+      <c r="DC39" s="29" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DD39" s="29"/>
+      <c r="DE39" s="29" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DF39" s="28"/>
+    </row>
+    <row r="40" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A40" s="21" t="s">
         <v>173</v>
       </c>
       <c r="B40" s="12"/>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="12"/>
@@ -9474,13 +10518,35 @@
       <c r="CC40" s="9"/>
       <c r="CD40" s="9"/>
       <c r="CE40" s="9"/>
-    </row>
-    <row r="41" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A41" s="16" t="s">
+      <c r="CS40" s="28"/>
+      <c r="CT40" s="28"/>
+      <c r="CU40" s="28"/>
+      <c r="CV40" s="28"/>
+      <c r="CW40" s="28"/>
+      <c r="CX40" s="28"/>
+      <c r="CY40" s="29" t="s">
+        <v>1762</v>
+      </c>
+      <c r="CZ40" s="29"/>
+      <c r="DA40" s="29" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DB40" s="29"/>
+      <c r="DC40" s="29" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DD40" s="29"/>
+      <c r="DE40" s="29" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DF40" s="28"/>
+    </row>
+    <row r="41" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A41" s="14" t="s">
         <v>175</v>
       </c>
       <c r="B41" s="12"/>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D41" s="12"/>
@@ -9535,13 +10601,35 @@
       <c r="CC41" s="9"/>
       <c r="CD41" s="9"/>
       <c r="CE41" s="9"/>
-    </row>
-    <row r="42" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A42" s="23" t="s">
+      <c r="CS41" s="28"/>
+      <c r="CT41" s="28"/>
+      <c r="CU41" s="28"/>
+      <c r="CV41" s="28"/>
+      <c r="CW41" s="28"/>
+      <c r="CX41" s="28"/>
+      <c r="CY41" s="29" t="s">
+        <v>1763</v>
+      </c>
+      <c r="CZ41" s="29"/>
+      <c r="DA41" s="29" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DB41" s="29"/>
+      <c r="DC41" s="29" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DD41" s="29"/>
+      <c r="DE41" s="29" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DF41" s="28"/>
+    </row>
+    <row r="42" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A42" s="21" t="s">
         <v>177</v>
       </c>
       <c r="B42" s="12"/>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="21" t="s">
         <v>178</v>
       </c>
       <c r="D42" s="12"/>
@@ -9596,13 +10684,35 @@
       <c r="CC42" s="9"/>
       <c r="CD42" s="9"/>
       <c r="CE42" s="9"/>
-    </row>
-    <row r="43" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A43" s="16" t="s">
+      <c r="CS42" s="28"/>
+      <c r="CT42" s="28"/>
+      <c r="CU42" s="28"/>
+      <c r="CV42" s="28"/>
+      <c r="CW42" s="28"/>
+      <c r="CX42" s="28"/>
+      <c r="CY42" s="29" t="s">
+        <v>1764</v>
+      </c>
+      <c r="CZ42" s="29"/>
+      <c r="DA42" s="29" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DB42" s="29"/>
+      <c r="DC42" s="29" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DD42" s="29"/>
+      <c r="DE42" s="29" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DF42" s="28"/>
+    </row>
+    <row r="43" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A43" s="14" t="s">
         <v>179</v>
       </c>
       <c r="B43" s="12"/>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D43" s="12"/>
@@ -9625,7 +10735,7 @@
         <v>810</v>
       </c>
       <c r="AH43" s="9"/>
-      <c r="AM43" s="13" t="s">
+      <c r="AM43" t="s">
         <v>811</v>
       </c>
       <c r="AQ43" s="9" t="s">
@@ -9656,13 +10766,35 @@
       <c r="CC43" s="9"/>
       <c r="CD43" s="9"/>
       <c r="CE43" s="9"/>
-    </row>
-    <row r="44" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A44" s="23" t="s">
+      <c r="CS43" s="28"/>
+      <c r="CT43" s="28"/>
+      <c r="CU43" s="28"/>
+      <c r="CV43" s="28"/>
+      <c r="CW43" s="28"/>
+      <c r="CX43" s="28"/>
+      <c r="CY43" s="29" t="s">
+        <v>1765</v>
+      </c>
+      <c r="CZ43" s="29"/>
+      <c r="DA43" s="29" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DB43" s="29"/>
+      <c r="DC43" s="29" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DD43" s="29"/>
+      <c r="DE43" s="29" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DF43" s="28"/>
+    </row>
+    <row r="44" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A44" s="21" t="s">
         <v>181</v>
       </c>
       <c r="B44" s="12"/>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="21" t="s">
         <v>182</v>
       </c>
       <c r="D44" s="12"/>
@@ -9717,13 +10849,35 @@
       <c r="CC44" s="9"/>
       <c r="CD44" s="9"/>
       <c r="CE44" s="9"/>
-    </row>
-    <row r="45" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A45" s="16" t="s">
+      <c r="CS44" s="28"/>
+      <c r="CT44" s="28"/>
+      <c r="CU44" s="28"/>
+      <c r="CV44" s="28"/>
+      <c r="CW44" s="28"/>
+      <c r="CX44" s="28"/>
+      <c r="CY44" s="29" t="s">
+        <v>1766</v>
+      </c>
+      <c r="CZ44" s="29"/>
+      <c r="DA44" s="29" t="s">
+        <v>1766</v>
+      </c>
+      <c r="DB44" s="29"/>
+      <c r="DC44" s="29" t="s">
+        <v>1766</v>
+      </c>
+      <c r="DD44" s="29"/>
+      <c r="DE44" s="29" t="s">
+        <v>1766</v>
+      </c>
+      <c r="DF44" s="28"/>
+    </row>
+    <row r="45" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A45" s="14" t="s">
         <v>183</v>
       </c>
       <c r="B45" s="12"/>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="14" t="s">
         <v>184</v>
       </c>
       <c r="D45" s="12"/>
@@ -9778,13 +10932,35 @@
       <c r="CC45" s="9"/>
       <c r="CD45" s="9"/>
       <c r="CE45" s="9"/>
-    </row>
-    <row r="46" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A46" s="23" t="s">
+      <c r="CS45" s="28"/>
+      <c r="CT45" s="28"/>
+      <c r="CU45" s="28"/>
+      <c r="CV45" s="28"/>
+      <c r="CW45" s="28"/>
+      <c r="CX45" s="28"/>
+      <c r="CY45" s="29" t="s">
+        <v>1767</v>
+      </c>
+      <c r="CZ45" s="29"/>
+      <c r="DA45" s="29" t="s">
+        <v>1768</v>
+      </c>
+      <c r="DB45" s="29"/>
+      <c r="DC45" s="29" t="s">
+        <v>1767</v>
+      </c>
+      <c r="DD45" s="29"/>
+      <c r="DE45" s="29" t="s">
+        <v>1768</v>
+      </c>
+      <c r="DF45" s="28"/>
+    </row>
+    <row r="46" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A46" s="21" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="12"/>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="21" t="s">
         <v>186</v>
       </c>
       <c r="D46" s="12"/>
@@ -9807,7 +10983,7 @@
         <v>817</v>
       </c>
       <c r="AH46" s="9"/>
-      <c r="AM46" s="13" t="s">
+      <c r="AM46" t="s">
         <v>818</v>
       </c>
       <c r="AQ46" s="9" t="s">
@@ -9838,13 +11014,35 @@
       <c r="CC46" s="9"/>
       <c r="CD46" s="9"/>
       <c r="CE46" s="9"/>
-    </row>
-    <row r="47" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A47" s="16" t="s">
+      <c r="CS46" s="28"/>
+      <c r="CT46" s="28"/>
+      <c r="CU46" s="28"/>
+      <c r="CV46" s="28"/>
+      <c r="CW46" s="28"/>
+      <c r="CX46" s="28"/>
+      <c r="CY46" s="29" t="s">
+        <v>1769</v>
+      </c>
+      <c r="CZ46" s="29"/>
+      <c r="DA46" s="29" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DB46" s="29"/>
+      <c r="DC46" s="29" t="s">
+        <v>1769</v>
+      </c>
+      <c r="DD46" s="29"/>
+      <c r="DE46" s="29" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DF46" s="28"/>
+    </row>
+    <row r="47" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A47" s="14" t="s">
         <v>187</v>
       </c>
       <c r="B47" s="12"/>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="14" t="s">
         <v>188</v>
       </c>
       <c r="D47" s="12"/>
@@ -9899,13 +11097,35 @@
       <c r="CC47" s="9"/>
       <c r="CD47" s="9"/>
       <c r="CE47" s="9"/>
-    </row>
-    <row r="48" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
+      <c r="CS47" s="28"/>
+      <c r="CT47" s="28"/>
+      <c r="CU47" s="28"/>
+      <c r="CV47" s="28"/>
+      <c r="CW47" s="28"/>
+      <c r="CX47" s="28"/>
+      <c r="CY47" s="29" t="s">
+        <v>1726</v>
+      </c>
+      <c r="CZ47" s="29"/>
+      <c r="DA47" s="29" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DB47" s="29"/>
+      <c r="DC47" s="29" t="s">
+        <v>1726</v>
+      </c>
+      <c r="DD47" s="29"/>
+      <c r="DE47" s="29" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DF47" s="28"/>
+    </row>
+    <row r="48" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="A48" s="21" t="s">
         <v>189</v>
       </c>
       <c r="B48" s="12"/>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="21" t="s">
         <v>190</v>
       </c>
       <c r="D48" s="12"/>
@@ -9956,13 +11176,35 @@
       <c r="CC48" s="9"/>
       <c r="CD48" s="9"/>
       <c r="CE48" s="9"/>
+      <c r="CS48" s="28"/>
+      <c r="CT48" s="28"/>
+      <c r="CU48" s="28"/>
+      <c r="CV48" s="28"/>
+      <c r="CW48" s="28"/>
+      <c r="CX48" s="28"/>
+      <c r="CY48" s="29" t="s">
+        <v>1729</v>
+      </c>
+      <c r="CZ48" s="29"/>
+      <c r="DA48" s="29" t="s">
+        <v>1772</v>
+      </c>
+      <c r="DB48" s="29"/>
+      <c r="DC48" s="29" t="s">
+        <v>1729</v>
+      </c>
+      <c r="DD48" s="29"/>
+      <c r="DE48" s="29" t="s">
+        <v>1772</v>
+      </c>
+      <c r="DF48" s="28"/>
     </row>
     <row r="49" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="14" t="s">
         <v>191</v>
       </c>
       <c r="B49" s="12"/>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="14" t="s">
         <v>192</v>
       </c>
       <c r="D49" s="12"/>
@@ -10015,11 +11257,11 @@
       <c r="CE49" s="9"/>
     </row>
     <row r="50" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="21" t="s">
         <v>193</v>
       </c>
       <c r="B50" s="12"/>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="21" t="s">
         <v>194</v>
       </c>
       <c r="D50" s="12"/>
@@ -10072,11 +11314,11 @@
       <c r="CE50" s="9"/>
     </row>
     <row r="51" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="14" t="s">
         <v>195</v>
       </c>
       <c r="B51" s="12"/>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="14" t="s">
         <v>196</v>
       </c>
       <c r="D51" s="12"/>
@@ -10129,11 +11371,11 @@
       <c r="CE51" s="9"/>
     </row>
     <row r="52" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="21" t="s">
         <v>197</v>
       </c>
       <c r="B52" s="12"/>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="21" t="s">
         <v>198</v>
       </c>
       <c r="D52" s="12"/>
@@ -10186,11 +11428,11 @@
       <c r="CE52" s="9"/>
     </row>
     <row r="53" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="14" t="s">
         <v>199</v>
       </c>
       <c r="B53" s="12"/>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="14" t="s">
         <v>200</v>
       </c>
       <c r="D53" s="12"/>
@@ -10243,11 +11485,11 @@
       <c r="CE53" s="9"/>
     </row>
     <row r="54" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="21" t="s">
         <v>201</v>
       </c>
       <c r="B54" s="12"/>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="21" t="s">
         <v>202</v>
       </c>
       <c r="D54" s="12"/>
@@ -10300,11 +11542,11 @@
       <c r="CE54" s="9"/>
     </row>
     <row r="55" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="14" t="s">
         <v>203</v>
       </c>
       <c r="B55" s="12"/>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="14" t="s">
         <v>204</v>
       </c>
       <c r="D55" s="12"/>
@@ -10357,11 +11599,11 @@
       <c r="CE55" s="9"/>
     </row>
     <row r="56" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="21" t="s">
         <v>205</v>
       </c>
       <c r="B56" s="12"/>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="21" t="s">
         <v>206</v>
       </c>
       <c r="D56" s="12"/>
@@ -10414,11 +11656,11 @@
       <c r="CE56" s="9"/>
     </row>
     <row r="57" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="14" t="s">
         <v>207</v>
       </c>
       <c r="B57" s="12"/>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="14" t="s">
         <v>208</v>
       </c>
       <c r="D57" s="12"/>
@@ -10471,11 +11713,11 @@
       <c r="CE57" s="9"/>
     </row>
     <row r="58" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="21" t="s">
         <v>209</v>
       </c>
       <c r="B58" s="12"/>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="21" t="s">
         <v>210</v>
       </c>
       <c r="D58" s="12"/>
@@ -10528,11 +11770,11 @@
       <c r="CE58" s="9"/>
     </row>
     <row r="59" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="14" t="s">
         <v>211</v>
       </c>
       <c r="B59" s="12"/>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="14" t="s">
         <v>212</v>
       </c>
       <c r="D59" s="12"/>
@@ -10585,11 +11827,11 @@
       <c r="CE59" s="9"/>
     </row>
     <row r="60" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="21" t="s">
         <v>213</v>
       </c>
       <c r="B60" s="12"/>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="21" t="s">
         <v>214</v>
       </c>
       <c r="D60" s="12"/>
@@ -10642,11 +11884,11 @@
       <c r="CE60" s="9"/>
     </row>
     <row r="61" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="14" t="s">
         <v>215</v>
       </c>
       <c r="B61" s="12"/>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="14" t="s">
         <v>216</v>
       </c>
       <c r="D61" s="12"/>
@@ -10699,11 +11941,11 @@
       <c r="CE61" s="9"/>
     </row>
     <row r="62" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="21" t="s">
         <v>217</v>
       </c>
       <c r="B62" s="12"/>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="21" t="s">
         <v>218</v>
       </c>
       <c r="D62" s="12"/>
@@ -10756,11 +11998,11 @@
       <c r="CE62" s="9"/>
     </row>
     <row r="63" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="14" t="s">
         <v>219</v>
       </c>
       <c r="B63" s="12"/>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="14" t="s">
         <v>220</v>
       </c>
       <c r="D63" s="12"/>
@@ -10813,11 +12055,11 @@
       <c r="CE63" s="9"/>
     </row>
     <row r="64" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="21" t="s">
         <v>221</v>
       </c>
       <c r="B64" s="12"/>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="21" t="s">
         <v>222</v>
       </c>
       <c r="D64" s="12"/>
@@ -10870,11 +12112,11 @@
       <c r="CE64" s="9"/>
     </row>
     <row r="65" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="14" t="s">
         <v>223</v>
       </c>
       <c r="B65" s="12"/>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="14" t="s">
         <v>224</v>
       </c>
       <c r="D65" s="12"/>
@@ -10927,11 +12169,11 @@
       <c r="CE65" s="9"/>
     </row>
     <row r="66" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="21" t="s">
         <v>225</v>
       </c>
       <c r="B66" s="12"/>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="21" t="s">
         <v>226</v>
       </c>
       <c r="D66" s="12"/>
@@ -10984,11 +12226,11 @@
       <c r="CE66" s="9"/>
     </row>
     <row r="67" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="14" t="s">
         <v>227</v>
       </c>
       <c r="B67" s="12"/>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="14" t="s">
         <v>228</v>
       </c>
       <c r="D67" s="12"/>
@@ -11041,11 +12283,11 @@
       <c r="CE67" s="9"/>
     </row>
     <row r="68" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="21" t="s">
         <v>229</v>
       </c>
       <c r="B68" s="12"/>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="21" t="s">
         <v>230</v>
       </c>
       <c r="D68" s="12"/>
@@ -11098,11 +12340,11 @@
       <c r="CE68" s="9"/>
     </row>
     <row r="69" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="14" t="s">
         <v>231</v>
       </c>
       <c r="B69" s="12"/>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="14" t="s">
         <v>232</v>
       </c>
       <c r="D69" s="12"/>
@@ -11155,11 +12397,11 @@
       <c r="CE69" s="9"/>
     </row>
     <row r="70" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="21" t="s">
         <v>233</v>
       </c>
       <c r="B70" s="12"/>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="21" t="s">
         <v>234</v>
       </c>
       <c r="D70" s="12"/>
@@ -11212,11 +12454,11 @@
       <c r="CE70" s="9"/>
     </row>
     <row r="71" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="14" t="s">
         <v>235</v>
       </c>
       <c r="B71" s="12"/>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="14" t="s">
         <v>236</v>
       </c>
       <c r="D71" s="12"/>
@@ -11269,11 +12511,11 @@
       <c r="CE71" s="9"/>
     </row>
     <row r="72" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="21" t="s">
         <v>237</v>
       </c>
       <c r="B72" s="12"/>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="21" t="s">
         <v>238</v>
       </c>
       <c r="D72" s="12"/>
@@ -11326,11 +12568,11 @@
       <c r="CE72" s="9"/>
     </row>
     <row r="73" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="14" t="s">
         <v>239</v>
       </c>
       <c r="B73" s="12"/>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="14" t="s">
         <v>240</v>
       </c>
       <c r="D73" s="12"/>
@@ -11383,11 +12625,11 @@
       <c r="CE73" s="9"/>
     </row>
     <row r="74" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="21" t="s">
         <v>241</v>
       </c>
       <c r="B74" s="12"/>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="21" t="s">
         <v>242</v>
       </c>
       <c r="D74" s="12"/>
@@ -11440,11 +12682,11 @@
       <c r="CE74" s="9"/>
     </row>
     <row r="75" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="14" t="s">
         <v>243</v>
       </c>
       <c r="B75" s="12"/>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="14" t="s">
         <v>244</v>
       </c>
       <c r="D75" s="12"/>
@@ -11497,11 +12739,11 @@
       <c r="CE75" s="9"/>
     </row>
     <row r="76" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="21" t="s">
         <v>245</v>
       </c>
       <c r="B76" s="12"/>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="21" t="s">
         <v>246</v>
       </c>
       <c r="D76" s="12"/>
@@ -11554,11 +12796,11 @@
       <c r="CE76" s="9"/>
     </row>
     <row r="77" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="14" t="s">
         <v>247</v>
       </c>
       <c r="B77" s="12"/>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="14" t="s">
         <v>248</v>
       </c>
       <c r="D77" s="12"/>
@@ -11611,11 +12853,11 @@
       <c r="CE77" s="9"/>
     </row>
     <row r="78" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="21" t="s">
         <v>249</v>
       </c>
       <c r="B78" s="12"/>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="21" t="s">
         <v>250</v>
       </c>
       <c r="D78" s="12"/>
@@ -11668,11 +12910,11 @@
       <c r="CE78" s="9"/>
     </row>
     <row r="79" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="14" t="s">
         <v>251</v>
       </c>
       <c r="B79" s="12"/>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="14" t="s">
         <v>252</v>
       </c>
       <c r="D79" s="12"/>
@@ -11725,11 +12967,11 @@
       <c r="CE79" s="9"/>
     </row>
     <row r="80" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A80" s="23" t="s">
+      <c r="A80" s="21" t="s">
         <v>253</v>
       </c>
       <c r="B80" s="12"/>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="21" t="s">
         <v>254</v>
       </c>
       <c r="D80" s="12"/>
@@ -11782,11 +13024,11 @@
       <c r="CE80" s="9"/>
     </row>
     <row r="81" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="14" t="s">
         <v>255</v>
       </c>
       <c r="B81" s="12"/>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="14" t="s">
         <v>256</v>
       </c>
       <c r="D81" s="12"/>
@@ -11839,11 +13081,11 @@
       <c r="CE81" s="9"/>
     </row>
     <row r="82" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="21" t="s">
         <v>257</v>
       </c>
       <c r="B82" s="12"/>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="21" t="s">
         <v>258</v>
       </c>
       <c r="D82" s="12"/>
@@ -11896,11 +13138,11 @@
       <c r="CE82" s="9"/>
     </row>
     <row r="83" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="14" t="s">
         <v>259</v>
       </c>
       <c r="B83" s="12"/>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="14" t="s">
         <v>260</v>
       </c>
       <c r="D83" s="12"/>
@@ -11953,11 +13195,11 @@
       <c r="CE83" s="9"/>
     </row>
     <row r="84" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="21" t="s">
         <v>261</v>
       </c>
       <c r="B84" s="12"/>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="21" t="s">
         <v>262</v>
       </c>
       <c r="D84" s="12"/>
@@ -12010,11 +13252,11 @@
       <c r="CE84" s="9"/>
     </row>
     <row r="85" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="14" t="s">
         <v>263</v>
       </c>
       <c r="B85" s="12"/>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="14" t="s">
         <v>264</v>
       </c>
       <c r="D85" s="12"/>
@@ -12067,11 +13309,11 @@
       <c r="CE85" s="9"/>
     </row>
     <row r="86" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A86" s="23" t="s">
+      <c r="A86" s="21" t="s">
         <v>265</v>
       </c>
       <c r="B86" s="12"/>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="21" t="s">
         <v>266</v>
       </c>
       <c r="D86" s="12"/>
@@ -12124,11 +13366,11 @@
       <c r="CE86" s="9"/>
     </row>
     <row r="87" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="14" t="s">
         <v>267</v>
       </c>
       <c r="B87" s="12"/>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="14" t="s">
         <v>268</v>
       </c>
       <c r="D87" s="12"/>
@@ -12181,11 +13423,11 @@
       <c r="CE87" s="9"/>
     </row>
     <row r="88" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="21" t="s">
         <v>269</v>
       </c>
       <c r="B88" s="12"/>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="21" t="s">
         <v>270</v>
       </c>
       <c r="D88" s="12"/>
@@ -12238,11 +13480,11 @@
       <c r="CE88" s="9"/>
     </row>
     <row r="89" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="14" t="s">
         <v>271</v>
       </c>
       <c r="B89" s="12"/>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="14" t="s">
         <v>272</v>
       </c>
       <c r="D89" s="12"/>
@@ -12295,11 +13537,11 @@
       <c r="CE89" s="9"/>
     </row>
     <row r="90" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="21" t="s">
         <v>273</v>
       </c>
       <c r="B90" s="12"/>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="21" t="s">
         <v>274</v>
       </c>
       <c r="D90" s="12"/>
@@ -12352,11 +13594,11 @@
       <c r="CE90" s="9"/>
     </row>
     <row r="91" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="14" t="s">
         <v>275</v>
       </c>
       <c r="B91" s="12"/>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="14" t="s">
         <v>276</v>
       </c>
       <c r="D91" s="12"/>
@@ -12409,11 +13651,11 @@
       <c r="CE91" s="9"/>
     </row>
     <row r="92" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A92" s="23" t="s">
+      <c r="A92" s="21" t="s">
         <v>277</v>
       </c>
       <c r="B92" s="12"/>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="21" t="s">
         <v>278</v>
       </c>
       <c r="D92" s="12"/>
@@ -12460,11 +13702,11 @@
       <c r="CE92" s="9"/>
     </row>
     <row r="93" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="14" t="s">
         <v>279</v>
       </c>
       <c r="B93" s="12"/>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="14" t="s">
         <v>280</v>
       </c>
       <c r="D93" s="12"/>
@@ -12511,11 +13753,11 @@
       <c r="CE93" s="9"/>
     </row>
     <row r="94" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="21" t="s">
         <v>281</v>
       </c>
       <c r="B94" s="12"/>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="21" t="s">
         <v>282</v>
       </c>
       <c r="D94" s="12"/>
@@ -12562,11 +13804,11 @@
       <c r="CE94" s="9"/>
     </row>
     <row r="95" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="14" t="s">
         <v>283</v>
       </c>
       <c r="B95" s="12"/>
-      <c r="C95" s="16" t="s">
+      <c r="C95" s="14" t="s">
         <v>284</v>
       </c>
       <c r="D95" s="12"/>
@@ -12613,11 +13855,11 @@
       <c r="CE95" s="9"/>
     </row>
     <row r="96" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="21" t="s">
         <v>285</v>
       </c>
       <c r="B96" s="12"/>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="21" t="s">
         <v>286</v>
       </c>
       <c r="D96" s="12"/>
@@ -12664,11 +13906,11 @@
       <c r="CE96" s="9"/>
     </row>
     <row r="97" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="14" t="s">
         <v>287</v>
       </c>
       <c r="B97" s="12"/>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="14" t="s">
         <v>288</v>
       </c>
       <c r="D97" s="12"/>
@@ -12715,11 +13957,11 @@
       <c r="CE97" s="9"/>
     </row>
     <row r="98" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A98" s="23" t="s">
+      <c r="A98" s="21" t="s">
         <v>289</v>
       </c>
       <c r="B98" s="12"/>
-      <c r="C98" s="23" t="s">
+      <c r="C98" s="21" t="s">
         <v>290</v>
       </c>
       <c r="D98" s="12"/>
@@ -12766,11 +14008,11 @@
       <c r="CE98" s="9"/>
     </row>
     <row r="99" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="14" t="s">
         <v>291</v>
       </c>
       <c r="B99" s="12"/>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="14" t="s">
         <v>292</v>
       </c>
       <c r="D99" s="12"/>
@@ -12817,11 +14059,11 @@
       <c r="CE99" s="9"/>
     </row>
     <row r="100" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A100" s="23" t="s">
+      <c r="A100" s="21" t="s">
         <v>293</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="21" t="s">
         <v>294</v>
       </c>
       <c r="D100" s="12"/>
@@ -12868,11 +14110,11 @@
       <c r="CE100" s="9"/>
     </row>
     <row r="101" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="14" t="s">
         <v>295</v>
       </c>
       <c r="B101" s="12"/>
-      <c r="C101" s="16" t="s">
+      <c r="C101" s="14" t="s">
         <v>296</v>
       </c>
       <c r="D101" s="12"/>
@@ -12919,11 +14161,11 @@
       <c r="CE101" s="9"/>
     </row>
     <row r="102" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="21" t="s">
         <v>297</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="23" t="s">
+      <c r="C102" s="21" t="s">
         <v>298</v>
       </c>
       <c r="D102" s="12"/>
@@ -12970,11 +14212,11 @@
       <c r="CE102" s="9"/>
     </row>
     <row r="103" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="14" t="s">
         <v>299</v>
       </c>
       <c r="B103" s="12"/>
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="14" t="s">
         <v>300</v>
       </c>
       <c r="D103" s="12"/>
@@ -13021,11 +14263,11 @@
       <c r="CE103" s="9"/>
     </row>
     <row r="104" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A104" s="23" t="s">
+      <c r="A104" s="21" t="s">
         <v>301</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="21" t="s">
         <v>302</v>
       </c>
       <c r="D104" s="12"/>
@@ -13072,11 +14314,11 @@
       <c r="CE104" s="9"/>
     </row>
     <row r="105" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="14" t="s">
         <v>303</v>
       </c>
       <c r="B105" s="12"/>
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="14" t="s">
         <v>304</v>
       </c>
       <c r="D105" s="12"/>
@@ -13123,11 +14365,11 @@
       <c r="CE105" s="9"/>
     </row>
     <row r="106" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A106" s="23" t="s">
+      <c r="A106" s="21" t="s">
         <v>305</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="23" t="s">
+      <c r="C106" s="21" t="s">
         <v>306</v>
       </c>
       <c r="D106" s="12"/>
@@ -13174,11 +14416,11 @@
       <c r="CE106" s="9"/>
     </row>
     <row r="107" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="14" t="s">
         <v>307</v>
       </c>
       <c r="B107" s="12"/>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="14" t="s">
         <v>308</v>
       </c>
       <c r="D107" s="12"/>
@@ -13225,11 +14467,11 @@
       <c r="CE107" s="9"/>
     </row>
     <row r="108" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A108" s="23" t="s">
+      <c r="A108" s="21" t="s">
         <v>309</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="23" t="s">
+      <c r="C108" s="21" t="s">
         <v>310</v>
       </c>
       <c r="D108" s="12"/>
@@ -13276,11 +14518,11 @@
       <c r="CE108" s="9"/>
     </row>
     <row r="109" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B109" s="12"/>
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="14" t="s">
         <v>312</v>
       </c>
       <c r="D109" s="12"/>
@@ -13327,11 +14569,11 @@
       <c r="CE109" s="9"/>
     </row>
     <row r="110" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A110" s="23" t="s">
+      <c r="A110" s="21" t="s">
         <v>313</v>
       </c>
       <c r="B110" s="12"/>
-      <c r="C110" s="23" t="s">
+      <c r="C110" s="21" t="s">
         <v>314</v>
       </c>
       <c r="D110" s="12"/>
@@ -13378,11 +14620,11 @@
       <c r="CE110" s="9"/>
     </row>
     <row r="111" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="14" t="s">
         <v>315</v>
       </c>
       <c r="B111" s="12"/>
-      <c r="C111" s="16" t="s">
+      <c r="C111" s="14" t="s">
         <v>316</v>
       </c>
       <c r="D111" s="12"/>
@@ -13429,11 +14671,11 @@
       <c r="CE111" s="9"/>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A112" s="23" t="s">
+      <c r="A112" s="21" t="s">
         <v>317</v>
       </c>
       <c r="B112" s="12"/>
-      <c r="C112" s="23" t="s">
+      <c r="C112" s="21" t="s">
         <v>318</v>
       </c>
       <c r="D112" s="12"/>
@@ -13480,11 +14722,11 @@
       <c r="CE112" s="9"/>
     </row>
     <row r="113" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="14" t="s">
         <v>319</v>
       </c>
       <c r="B113" s="12"/>
-      <c r="C113" s="16" t="s">
+      <c r="C113" s="14" t="s">
         <v>320</v>
       </c>
       <c r="D113" s="12"/>
@@ -13531,11 +14773,11 @@
       <c r="CE113" s="9"/>
     </row>
     <row r="114" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="21" t="s">
         <v>321</v>
       </c>
       <c r="B114" s="12"/>
-      <c r="C114" s="23" t="s">
+      <c r="C114" s="21" t="s">
         <v>322</v>
       </c>
       <c r="D114" s="12"/>
@@ -13582,11 +14824,11 @@
       <c r="CE114" s="9"/>
     </row>
     <row r="115" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="14" t="s">
         <v>323</v>
       </c>
       <c r="B115" s="12"/>
-      <c r="C115" s="16" t="s">
+      <c r="C115" s="14" t="s">
         <v>324</v>
       </c>
       <c r="D115" s="12"/>
@@ -13633,11 +14875,11 @@
       <c r="CE115" s="9"/>
     </row>
     <row r="116" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="21" t="s">
         <v>325</v>
       </c>
       <c r="B116" s="12"/>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="21" t="s">
         <v>326</v>
       </c>
       <c r="D116" s="12"/>
@@ -13684,11 +14926,11 @@
       <c r="CE116" s="9"/>
     </row>
     <row r="117" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="14" t="s">
         <v>327</v>
       </c>
       <c r="B117" s="12"/>
-      <c r="C117" s="16" t="s">
+      <c r="C117" s="14" t="s">
         <v>328</v>
       </c>
       <c r="D117" s="12"/>
@@ -13735,11 +14977,11 @@
       <c r="CE117" s="9"/>
     </row>
     <row r="118" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A118" s="23" t="s">
+      <c r="A118" s="21" t="s">
         <v>329</v>
       </c>
       <c r="B118" s="12"/>
-      <c r="C118" s="23" t="s">
+      <c r="C118" s="21" t="s">
         <v>330</v>
       </c>
       <c r="D118" s="12"/>
@@ -13786,11 +15028,11 @@
       <c r="CE118" s="9"/>
     </row>
     <row r="119" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="14" t="s">
         <v>331</v>
       </c>
       <c r="B119" s="12"/>
-      <c r="C119" s="16" t="s">
+      <c r="C119" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D119" s="12"/>
@@ -13837,11 +15079,11 @@
       <c r="CE119" s="9"/>
     </row>
     <row r="120" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A120" s="23" t="s">
+      <c r="A120" s="21" t="s">
         <v>333</v>
       </c>
       <c r="B120" s="12"/>
-      <c r="C120" s="23" t="s">
+      <c r="C120" s="21" t="s">
         <v>334</v>
       </c>
       <c r="D120" s="12"/>
@@ -13888,11 +15130,11 @@
       <c r="CE120" s="9"/>
     </row>
     <row r="121" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="14" t="s">
         <v>335</v>
       </c>
       <c r="B121" s="12"/>
-      <c r="C121" s="16" t="s">
+      <c r="C121" s="14" t="s">
         <v>336</v>
       </c>
       <c r="D121" s="12"/>
@@ -13939,11 +15181,11 @@
       <c r="CE121" s="9"/>
     </row>
     <row r="122" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A122" s="23" t="s">
+      <c r="A122" s="21" t="s">
         <v>337</v>
       </c>
       <c r="B122" s="12"/>
-      <c r="C122" s="23" t="s">
+      <c r="C122" s="21" t="s">
         <v>338</v>
       </c>
       <c r="D122" s="12"/>
@@ -13990,11 +15232,11 @@
       <c r="CE122" s="9"/>
     </row>
     <row r="123" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="14" t="s">
         <v>339</v>
       </c>
       <c r="B123" s="12"/>
-      <c r="C123" s="16" t="s">
+      <c r="C123" s="14" t="s">
         <v>340</v>
       </c>
       <c r="D123" s="12"/>
@@ -14041,11 +15283,11 @@
       <c r="CE123" s="9"/>
     </row>
     <row r="124" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A124" s="23" t="s">
+      <c r="A124" s="21" t="s">
         <v>341</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="23" t="s">
+      <c r="C124" s="21" t="s">
         <v>342</v>
       </c>
       <c r="D124" s="12"/>
@@ -14092,11 +15334,11 @@
       <c r="CE124" s="9"/>
     </row>
     <row r="125" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="14" t="s">
         <v>343</v>
       </c>
       <c r="B125" s="12"/>
-      <c r="C125" s="16" t="s">
+      <c r="C125" s="14" t="s">
         <v>344</v>
       </c>
       <c r="D125" s="12"/>
@@ -14143,11 +15385,11 @@
       <c r="CE125" s="9"/>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A126" s="23" t="s">
+      <c r="A126" s="21" t="s">
         <v>345</v>
       </c>
       <c r="B126" s="12"/>
-      <c r="C126" s="23" t="s">
+      <c r="C126" s="21" t="s">
         <v>346</v>
       </c>
       <c r="D126" s="12"/>
@@ -14194,11 +15436,11 @@
       <c r="CE126" s="9"/>
     </row>
     <row r="127" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="14" t="s">
         <v>347</v>
       </c>
       <c r="B127" s="12"/>
-      <c r="C127" s="16" t="s">
+      <c r="C127" s="14" t="s">
         <v>348</v>
       </c>
       <c r="D127" s="12"/>
@@ -14245,11 +15487,11 @@
       <c r="CE127" s="9"/>
     </row>
     <row r="128" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A128" s="23" t="s">
+      <c r="A128" s="21" t="s">
         <v>349</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="23" t="s">
+      <c r="C128" s="21" t="s">
         <v>350</v>
       </c>
       <c r="D128" s="12"/>
@@ -14296,11 +15538,11 @@
       <c r="CE128" s="9"/>
     </row>
     <row r="129" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A129" s="16" t="s">
+      <c r="A129" s="14" t="s">
         <v>351</v>
       </c>
       <c r="B129" s="12"/>
-      <c r="C129" s="16" t="s">
+      <c r="C129" s="14" t="s">
         <v>352</v>
       </c>
       <c r="D129" s="12"/>
@@ -14347,11 +15589,11 @@
       <c r="CE129" s="9"/>
     </row>
     <row r="130" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A130" s="23" t="s">
+      <c r="A130" s="21" t="s">
         <v>353</v>
       </c>
       <c r="B130" s="12"/>
-      <c r="C130" s="23" t="s">
+      <c r="C130" s="21" t="s">
         <v>354</v>
       </c>
       <c r="D130" s="12"/>
@@ -14398,11 +15640,11 @@
       <c r="CE130" s="9"/>
     </row>
     <row r="131" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="14" t="s">
         <v>355</v>
       </c>
       <c r="B131" s="12"/>
-      <c r="C131" s="16" t="s">
+      <c r="C131" s="14" t="s">
         <v>356</v>
       </c>
       <c r="D131" s="12"/>
@@ -14449,11 +15691,11 @@
       <c r="CE131" s="9"/>
     </row>
     <row r="132" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A132" s="23" t="s">
+      <c r="A132" s="21" t="s">
         <v>357</v>
       </c>
       <c r="B132" s="12"/>
-      <c r="C132" s="23" t="s">
+      <c r="C132" s="21" t="s">
         <v>358</v>
       </c>
       <c r="D132" s="12"/>
@@ -14500,11 +15742,11 @@
       <c r="CE132" s="9"/>
     </row>
     <row r="133" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A133" s="16" t="s">
+      <c r="A133" s="14" t="s">
         <v>359</v>
       </c>
       <c r="B133" s="12"/>
-      <c r="C133" s="16" t="s">
+      <c r="C133" s="14" t="s">
         <v>360</v>
       </c>
       <c r="D133" s="12"/>
@@ -14551,11 +15793,11 @@
       <c r="CE133" s="9"/>
     </row>
     <row r="134" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A134" s="23" t="s">
+      <c r="A134" s="21" t="s">
         <v>361</v>
       </c>
       <c r="B134" s="12"/>
-      <c r="C134" s="23" t="s">
+      <c r="C134" s="21" t="s">
         <v>362</v>
       </c>
       <c r="D134" s="12"/>
@@ -14602,11 +15844,11 @@
       <c r="CE134" s="9"/>
     </row>
     <row r="135" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="14" t="s">
         <v>363</v>
       </c>
       <c r="B135" s="12"/>
-      <c r="C135" s="16" t="s">
+      <c r="C135" s="14" t="s">
         <v>364</v>
       </c>
       <c r="D135" s="12"/>
@@ -14653,11 +15895,11 @@
       <c r="CE135" s="9"/>
     </row>
     <row r="136" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A136" s="23" t="s">
+      <c r="A136" s="21" t="s">
         <v>365</v>
       </c>
       <c r="B136" s="12"/>
-      <c r="C136" s="23" t="s">
+      <c r="C136" s="21" t="s">
         <v>366</v>
       </c>
       <c r="D136" s="12"/>
@@ -14704,11 +15946,11 @@
       <c r="CE136" s="9"/>
     </row>
     <row r="137" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="14" t="s">
         <v>367</v>
       </c>
       <c r="B137" s="12"/>
-      <c r="C137" s="16" t="s">
+      <c r="C137" s="14" t="s">
         <v>368</v>
       </c>
       <c r="D137" s="12"/>
@@ -14755,11 +15997,11 @@
       <c r="CE137" s="9"/>
     </row>
     <row r="138" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A138" s="23" t="s">
+      <c r="A138" s="21" t="s">
         <v>369</v>
       </c>
       <c r="B138" s="12"/>
-      <c r="C138" s="23" t="s">
+      <c r="C138" s="21" t="s">
         <v>370</v>
       </c>
       <c r="D138" s="12"/>
@@ -14806,11 +16048,11 @@
       <c r="CE138" s="9"/>
     </row>
     <row r="139" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A139" s="16" t="s">
+      <c r="A139" s="14" t="s">
         <v>371</v>
       </c>
       <c r="B139" s="12"/>
-      <c r="C139" s="16" t="s">
+      <c r="C139" s="14" t="s">
         <v>372</v>
       </c>
       <c r="D139" s="12"/>
@@ -14857,11 +16099,11 @@
       <c r="CE139" s="9"/>
     </row>
     <row r="140" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A140" s="23" t="s">
+      <c r="A140" s="21" t="s">
         <v>373</v>
       </c>
       <c r="B140" s="12"/>
-      <c r="C140" s="23" t="s">
+      <c r="C140" s="21" t="s">
         <v>374</v>
       </c>
       <c r="D140" s="12"/>
@@ -14908,11 +16150,11 @@
       <c r="CE140" s="9"/>
     </row>
     <row r="141" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="14" t="s">
         <v>375</v>
       </c>
       <c r="B141" s="12"/>
-      <c r="C141" s="16" t="s">
+      <c r="C141" s="14" t="s">
         <v>376</v>
       </c>
       <c r="D141" s="12"/>
@@ -14959,11 +16201,11 @@
       <c r="CE141" s="9"/>
     </row>
     <row r="142" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A142" s="23" t="s">
+      <c r="A142" s="21" t="s">
         <v>377</v>
       </c>
       <c r="B142" s="12"/>
-      <c r="C142" s="23" t="s">
+      <c r="C142" s="21" t="s">
         <v>378</v>
       </c>
       <c r="D142" s="12"/>
@@ -15010,11 +16252,11 @@
       <c r="CE142" s="9"/>
     </row>
     <row r="143" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A143" s="16" t="s">
+      <c r="A143" s="14" t="s">
         <v>379</v>
       </c>
       <c r="B143" s="12"/>
-      <c r="C143" s="16" t="s">
+      <c r="C143" s="14" t="s">
         <v>380</v>
       </c>
       <c r="D143" s="12"/>
@@ -15061,11 +16303,11 @@
       <c r="CE143" s="9"/>
     </row>
     <row r="144" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A144" s="23" t="s">
+      <c r="A144" s="21" t="s">
         <v>381</v>
       </c>
       <c r="B144" s="12"/>
-      <c r="C144" s="23" t="s">
+      <c r="C144" s="21" t="s">
         <v>382</v>
       </c>
       <c r="D144" s="12"/>
@@ -15112,11 +16354,11 @@
       <c r="CE144" s="9"/>
     </row>
     <row r="145" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="14" t="s">
         <v>383</v>
       </c>
       <c r="B145" s="12"/>
-      <c r="C145" s="16" t="s">
+      <c r="C145" s="14" t="s">
         <v>384</v>
       </c>
       <c r="D145" s="12"/>
@@ -15163,11 +16405,11 @@
       <c r="CE145" s="9"/>
     </row>
     <row r="146" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A146" s="23" t="s">
+      <c r="A146" s="21" t="s">
         <v>385</v>
       </c>
       <c r="B146" s="12"/>
-      <c r="C146" s="23" t="s">
+      <c r="C146" s="21" t="s">
         <v>386</v>
       </c>
       <c r="D146" s="12"/>
@@ -15214,11 +16456,11 @@
       <c r="CE146" s="9"/>
     </row>
     <row r="147" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="14" t="s">
         <v>387</v>
       </c>
       <c r="B147" s="12"/>
-      <c r="C147" s="16" t="s">
+      <c r="C147" s="14" t="s">
         <v>388</v>
       </c>
       <c r="D147" s="12"/>
@@ -15265,11 +16507,11 @@
       <c r="CE147" s="9"/>
     </row>
     <row r="148" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A148" s="23" t="s">
+      <c r="A148" s="21" t="s">
         <v>389</v>
       </c>
       <c r="B148" s="12"/>
-      <c r="C148" s="23" t="s">
+      <c r="C148" s="21" t="s">
         <v>390</v>
       </c>
       <c r="D148" s="12"/>
@@ -15316,11 +16558,11 @@
       <c r="CE148" s="9"/>
     </row>
     <row r="149" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="14" t="s">
         <v>391</v>
       </c>
       <c r="B149" s="12"/>
-      <c r="C149" s="16" t="s">
+      <c r="C149" s="14" t="s">
         <v>392</v>
       </c>
       <c r="D149" s="12"/>
@@ -15367,11 +16609,11 @@
       <c r="CE149" s="9"/>
     </row>
     <row r="150" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A150" s="23" t="s">
+      <c r="A150" s="21" t="s">
         <v>393</v>
       </c>
       <c r="B150" s="12"/>
-      <c r="C150" s="23" t="s">
+      <c r="C150" s="21" t="s">
         <v>394</v>
       </c>
       <c r="D150" s="12"/>
@@ -15418,11 +16660,11 @@
       <c r="CE150" s="9"/>
     </row>
     <row r="151" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="14" t="s">
         <v>395</v>
       </c>
       <c r="B151" s="12"/>
-      <c r="C151" s="16" t="s">
+      <c r="C151" s="14" t="s">
         <v>396</v>
       </c>
       <c r="D151" s="12"/>
@@ -15469,11 +16711,11 @@
       <c r="CE151" s="9"/>
     </row>
     <row r="152" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A152" s="23" t="s">
+      <c r="A152" s="21" t="s">
         <v>397</v>
       </c>
       <c r="B152" s="12"/>
-      <c r="C152" s="23" t="s">
+      <c r="C152" s="21" t="s">
         <v>398</v>
       </c>
       <c r="D152" s="12"/>
@@ -15520,11 +16762,11 @@
       <c r="CE152" s="9"/>
     </row>
     <row r="153" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="14" t="s">
         <v>399</v>
       </c>
       <c r="B153" s="12"/>
-      <c r="C153" s="16" t="s">
+      <c r="C153" s="14" t="s">
         <v>400</v>
       </c>
       <c r="D153" s="12"/>
@@ -15571,11 +16813,11 @@
       <c r="CE153" s="9"/>
     </row>
     <row r="154" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A154" s="23" t="s">
+      <c r="A154" s="21" t="s">
         <v>401</v>
       </c>
       <c r="B154" s="12"/>
-      <c r="C154" s="23" t="s">
+      <c r="C154" s="21" t="s">
         <v>402</v>
       </c>
       <c r="D154" s="12"/>
@@ -15622,11 +16864,11 @@
       <c r="CE154" s="9"/>
     </row>
     <row r="155" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="14" t="s">
         <v>403</v>
       </c>
       <c r="B155" s="12"/>
-      <c r="C155" s="16" t="s">
+      <c r="C155" s="14" t="s">
         <v>404</v>
       </c>
       <c r="D155" s="12"/>
@@ -15673,11 +16915,11 @@
       <c r="CE155" s="9"/>
     </row>
     <row r="156" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A156" s="23" t="s">
+      <c r="A156" s="21" t="s">
         <v>405</v>
       </c>
       <c r="B156" s="12"/>
-      <c r="C156" s="23" t="s">
+      <c r="C156" s="21" t="s">
         <v>406</v>
       </c>
       <c r="D156" s="12"/>
@@ -15724,11 +16966,11 @@
       <c r="CE156" s="9"/>
     </row>
     <row r="157" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="14" t="s">
         <v>407</v>
       </c>
       <c r="B157" s="12"/>
-      <c r="C157" s="16" t="s">
+      <c r="C157" s="14" t="s">
         <v>408</v>
       </c>
       <c r="D157" s="12"/>
@@ -15775,11 +17017,11 @@
       <c r="CE157" s="9"/>
     </row>
     <row r="158" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A158" s="23" t="s">
+      <c r="A158" s="21" t="s">
         <v>409</v>
       </c>
       <c r="B158" s="12"/>
-      <c r="C158" s="23" t="s">
+      <c r="C158" s="21" t="s">
         <v>410</v>
       </c>
       <c r="D158" s="12"/>
@@ -15826,11 +17068,11 @@
       <c r="CE158" s="9"/>
     </row>
     <row r="159" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A159" s="16" t="s">
+      <c r="A159" s="14" t="s">
         <v>411</v>
       </c>
       <c r="B159" s="12"/>
-      <c r="C159" s="16" t="s">
+      <c r="C159" s="14" t="s">
         <v>412</v>
       </c>
       <c r="D159" s="12"/>
@@ -15877,11 +17119,11 @@
       <c r="CE159" s="9"/>
     </row>
     <row r="160" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A160" s="23" t="s">
+      <c r="A160" s="21" t="s">
         <v>413</v>
       </c>
       <c r="B160" s="12"/>
-      <c r="C160" s="23" t="s">
+      <c r="C160" s="21" t="s">
         <v>414</v>
       </c>
       <c r="D160" s="12"/>
@@ -15928,11 +17170,11 @@
       <c r="CE160" s="9"/>
     </row>
     <row r="161" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="14" t="s">
         <v>415</v>
       </c>
       <c r="B161" s="12"/>
-      <c r="C161" s="16" t="s">
+      <c r="C161" s="14" t="s">
         <v>416</v>
       </c>
       <c r="D161" s="12"/>
@@ -15979,11 +17221,11 @@
       <c r="CE161" s="9"/>
     </row>
     <row r="162" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A162" s="23" t="s">
+      <c r="A162" s="21" t="s">
         <v>417</v>
       </c>
       <c r="B162" s="12"/>
-      <c r="C162" s="23" t="s">
+      <c r="C162" s="21" t="s">
         <v>418</v>
       </c>
       <c r="D162" s="12"/>
@@ -16030,11 +17272,11 @@
       <c r="CE162" s="9"/>
     </row>
     <row r="163" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="14" t="s">
         <v>419</v>
       </c>
       <c r="B163" s="12"/>
-      <c r="C163" s="16" t="s">
+      <c r="C163" s="14" t="s">
         <v>420</v>
       </c>
       <c r="D163" s="12"/>
@@ -16081,11 +17323,11 @@
       <c r="CE163" s="9"/>
     </row>
     <row r="164" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A164" s="23" t="s">
+      <c r="A164" s="21" t="s">
         <v>421</v>
       </c>
       <c r="B164" s="12"/>
-      <c r="C164" s="23" t="s">
+      <c r="C164" s="21" t="s">
         <v>422</v>
       </c>
       <c r="D164" s="12"/>
@@ -16132,11 +17374,11 @@
       <c r="CE164" s="9"/>
     </row>
     <row r="165" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A165" s="16" t="s">
+      <c r="A165" s="14" t="s">
         <v>423</v>
       </c>
       <c r="B165" s="12"/>
-      <c r="C165" s="16" t="s">
+      <c r="C165" s="14" t="s">
         <v>424</v>
       </c>
       <c r="D165" s="12"/>
@@ -16183,11 +17425,11 @@
       <c r="CE165" s="9"/>
     </row>
     <row r="166" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A166" s="23" t="s">
+      <c r="A166" s="21" t="s">
         <v>425</v>
       </c>
       <c r="B166" s="12"/>
-      <c r="C166" s="23" t="s">
+      <c r="C166" s="21" t="s">
         <v>426</v>
       </c>
       <c r="D166" s="12"/>
@@ -16234,11 +17476,11 @@
       <c r="CE166" s="9"/>
     </row>
     <row r="167" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A167" s="16" t="s">
+      <c r="A167" s="14" t="s">
         <v>427</v>
       </c>
       <c r="B167" s="12"/>
-      <c r="C167" s="16" t="s">
+      <c r="C167" s="14" t="s">
         <v>428</v>
       </c>
       <c r="D167" s="12"/>
@@ -16285,11 +17527,11 @@
       <c r="CE167" s="9"/>
     </row>
     <row r="168" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A168" s="23" t="s">
+      <c r="A168" s="21" t="s">
         <v>429</v>
       </c>
       <c r="B168" s="12"/>
-      <c r="C168" s="23" t="s">
+      <c r="C168" s="21" t="s">
         <v>430</v>
       </c>
       <c r="D168" s="12"/>
@@ -16336,11 +17578,11 @@
       <c r="CE168" s="9"/>
     </row>
     <row r="169" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A169" s="16" t="s">
+      <c r="A169" s="14" t="s">
         <v>431</v>
       </c>
       <c r="B169" s="12"/>
-      <c r="C169" s="16" t="s">
+      <c r="C169" s="14" t="s">
         <v>432</v>
       </c>
       <c r="D169" s="12"/>
@@ -16387,11 +17629,11 @@
       <c r="CE169" s="9"/>
     </row>
     <row r="170" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A170" s="23" t="s">
+      <c r="A170" s="21" t="s">
         <v>433</v>
       </c>
       <c r="B170" s="12"/>
-      <c r="C170" s="23" t="s">
+      <c r="C170" s="21" t="s">
         <v>434</v>
       </c>
       <c r="D170" s="12"/>
@@ -16438,11 +17680,11 @@
       <c r="CE170" s="9"/>
     </row>
     <row r="171" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="14" t="s">
         <v>435</v>
       </c>
       <c r="B171" s="12"/>
-      <c r="C171" s="16" t="s">
+      <c r="C171" s="14" t="s">
         <v>436</v>
       </c>
       <c r="D171" s="12"/>
@@ -16489,11 +17731,11 @@
       <c r="CE171" s="9"/>
     </row>
     <row r="172" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A172" s="23" t="s">
+      <c r="A172" s="21" t="s">
         <v>437</v>
       </c>
       <c r="B172" s="12"/>
-      <c r="C172" s="23" t="s">
+      <c r="C172" s="21" t="s">
         <v>438</v>
       </c>
       <c r="D172" s="12"/>
@@ -16517,11 +17759,11 @@
       </c>
     </row>
     <row r="173" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A173" s="16" t="s">
+      <c r="A173" s="14" t="s">
         <v>439</v>
       </c>
       <c r="B173" s="12"/>
-      <c r="C173" s="16" t="s">
+      <c r="C173" s="14" t="s">
         <v>440</v>
       </c>
       <c r="D173" s="12"/>
@@ -16545,11 +17787,11 @@
       </c>
     </row>
     <row r="174" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A174" s="23" t="s">
+      <c r="A174" s="21" t="s">
         <v>441</v>
       </c>
       <c r="B174" s="12"/>
-      <c r="C174" s="23" t="s">
+      <c r="C174" s="21" t="s">
         <v>442</v>
       </c>
       <c r="D174" s="12"/>
@@ -16573,11 +17815,11 @@
       </c>
     </row>
     <row r="175" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A175" s="16" t="s">
+      <c r="A175" s="14" t="s">
         <v>443</v>
       </c>
       <c r="B175" s="12"/>
-      <c r="C175" s="16" t="s">
+      <c r="C175" s="14" t="s">
         <v>444</v>
       </c>
       <c r="D175" s="12"/>
@@ -16601,11 +17843,11 @@
       </c>
     </row>
     <row r="176" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A176" s="23" t="s">
+      <c r="A176" s="21" t="s">
         <v>445</v>
       </c>
       <c r="B176" s="12"/>
-      <c r="C176" s="23" t="s">
+      <c r="C176" s="21" t="s">
         <v>446</v>
       </c>
       <c r="D176" s="12"/>
@@ -16629,11 +17871,11 @@
       </c>
     </row>
     <row r="177" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A177" s="16" t="s">
+      <c r="A177" s="14" t="s">
         <v>447</v>
       </c>
       <c r="B177" s="12"/>
-      <c r="C177" s="16" t="s">
+      <c r="C177" s="14" t="s">
         <v>448</v>
       </c>
       <c r="D177" s="12"/>
@@ -16657,11 +17899,11 @@
       </c>
     </row>
     <row r="178" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A178" s="23" t="s">
+      <c r="A178" s="21" t="s">
         <v>449</v>
       </c>
       <c r="B178" s="12"/>
-      <c r="C178" s="23" t="s">
+      <c r="C178" s="21" t="s">
         <v>450</v>
       </c>
       <c r="D178" s="12"/>
@@ -16685,11 +17927,11 @@
       </c>
     </row>
     <row r="179" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A179" s="16" t="s">
+      <c r="A179" s="14" t="s">
         <v>451</v>
       </c>
       <c r="B179" s="12"/>
-      <c r="C179" s="16" t="s">
+      <c r="C179" s="14" t="s">
         <v>452</v>
       </c>
       <c r="D179" s="12"/>
@@ -16713,11 +17955,11 @@
       </c>
     </row>
     <row r="180" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A180" s="23" t="s">
+      <c r="A180" s="21" t="s">
         <v>453</v>
       </c>
       <c r="B180" s="12"/>
-      <c r="C180" s="23" t="s">
+      <c r="C180" s="21" t="s">
         <v>454</v>
       </c>
       <c r="D180" s="12"/>
@@ -16741,11 +17983,11 @@
       </c>
     </row>
     <row r="181" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A181" s="16" t="s">
+      <c r="A181" s="14" t="s">
         <v>455</v>
       </c>
       <c r="B181" s="12"/>
-      <c r="C181" s="16" t="s">
+      <c r="C181" s="14" t="s">
         <v>456</v>
       </c>
       <c r="D181" s="12"/>
@@ -16769,11 +18011,11 @@
       </c>
     </row>
     <row r="182" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A182" s="23" t="s">
+      <c r="A182" s="21" t="s">
         <v>457</v>
       </c>
       <c r="B182" s="12"/>
-      <c r="C182" s="23" t="s">
+      <c r="C182" s="21" t="s">
         <v>458</v>
       </c>
       <c r="D182" s="12"/>
@@ -16797,11 +18039,11 @@
       </c>
     </row>
     <row r="183" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A183" s="16" t="s">
+      <c r="A183" s="14" t="s">
         <v>459</v>
       </c>
       <c r="B183" s="12"/>
-      <c r="C183" s="16" t="s">
+      <c r="C183" s="14" t="s">
         <v>460</v>
       </c>
       <c r="D183" s="12"/>
@@ -16825,11 +18067,11 @@
       </c>
     </row>
     <row r="184" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A184" s="23" t="s">
+      <c r="A184" s="21" t="s">
         <v>461</v>
       </c>
       <c r="B184" s="12"/>
-      <c r="C184" s="23" t="s">
+      <c r="C184" s="21" t="s">
         <v>462</v>
       </c>
       <c r="D184" s="12"/>
@@ -16853,11 +18095,11 @@
       </c>
     </row>
     <row r="185" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A185" s="16" t="s">
+      <c r="A185" s="14" t="s">
         <v>463</v>
       </c>
       <c r="B185" s="12"/>
-      <c r="C185" s="16" t="s">
+      <c r="C185" s="14" t="s">
         <v>464</v>
       </c>
       <c r="D185" s="12"/>
@@ -16881,11 +18123,11 @@
       </c>
     </row>
     <row r="186" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A186" s="23" t="s">
+      <c r="A186" s="21" t="s">
         <v>465</v>
       </c>
       <c r="B186" s="12"/>
-      <c r="C186" s="23" t="s">
+      <c r="C186" s="21" t="s">
         <v>466</v>
       </c>
       <c r="D186" s="12"/>
@@ -16909,11 +18151,11 @@
       </c>
     </row>
     <row r="187" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A187" s="16" t="s">
+      <c r="A187" s="14" t="s">
         <v>467</v>
       </c>
       <c r="B187" s="12"/>
-      <c r="C187" s="16" t="s">
+      <c r="C187" s="14" t="s">
         <v>468</v>
       </c>
       <c r="D187" s="12"/>
@@ -16937,11 +18179,11 @@
       </c>
     </row>
     <row r="188" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A188" s="23" t="s">
+      <c r="A188" s="21" t="s">
         <v>469</v>
       </c>
       <c r="B188" s="12"/>
-      <c r="C188" s="23" t="s">
+      <c r="C188" s="21" t="s">
         <v>470</v>
       </c>
       <c r="D188" s="12"/>
@@ -16965,11 +18207,11 @@
       </c>
     </row>
     <row r="189" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A189" s="16" t="s">
+      <c r="A189" s="14" t="s">
         <v>471</v>
       </c>
       <c r="B189" s="12"/>
-      <c r="C189" s="16" t="s">
+      <c r="C189" s="14" t="s">
         <v>472</v>
       </c>
       <c r="D189" s="12"/>
@@ -16993,11 +18235,11 @@
       </c>
     </row>
     <row r="190" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A190" s="23" t="s">
+      <c r="A190" s="21" t="s">
         <v>473</v>
       </c>
       <c r="B190" s="12"/>
-      <c r="C190" s="23" t="s">
+      <c r="C190" s="21" t="s">
         <v>474</v>
       </c>
       <c r="D190" s="12"/>
@@ -17021,11 +18263,11 @@
       </c>
     </row>
     <row r="191" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A191" s="16" t="s">
+      <c r="A191" s="14" t="s">
         <v>475</v>
       </c>
       <c r="B191" s="12"/>
-      <c r="C191" s="16" t="s">
+      <c r="C191" s="14" t="s">
         <v>476</v>
       </c>
       <c r="D191" s="12"/>
@@ -17049,11 +18291,11 @@
       </c>
     </row>
     <row r="192" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A192" s="23" t="s">
+      <c r="A192" s="21" t="s">
         <v>477</v>
       </c>
       <c r="B192" s="12"/>
-      <c r="C192" s="23" t="s">
+      <c r="C192" s="21" t="s">
         <v>478</v>
       </c>
       <c r="D192" s="12"/>
@@ -17077,11 +18319,11 @@
       </c>
     </row>
     <row r="193" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A193" s="16" t="s">
+      <c r="A193" s="14" t="s">
         <v>479</v>
       </c>
       <c r="B193" s="12"/>
-      <c r="C193" s="16" t="s">
+      <c r="C193" s="14" t="s">
         <v>480</v>
       </c>
       <c r="D193" s="12"/>
@@ -17105,11 +18347,11 @@
       </c>
     </row>
     <row r="194" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A194" s="23" t="s">
+      <c r="A194" s="21" t="s">
         <v>481</v>
       </c>
       <c r="B194" s="12"/>
-      <c r="C194" s="23" t="s">
+      <c r="C194" s="21" t="s">
         <v>482</v>
       </c>
       <c r="D194" s="12"/>
@@ -17133,11 +18375,11 @@
       </c>
     </row>
     <row r="195" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A195" s="16" t="s">
+      <c r="A195" s="14" t="s">
         <v>483</v>
       </c>
       <c r="B195" s="12"/>
-      <c r="C195" s="16" t="s">
+      <c r="C195" s="14" t="s">
         <v>484</v>
       </c>
       <c r="D195" s="12"/>
@@ -17161,11 +18403,11 @@
       </c>
     </row>
     <row r="196" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A196" s="23" t="s">
+      <c r="A196" s="21" t="s">
         <v>485</v>
       </c>
       <c r="B196" s="12"/>
-      <c r="C196" s="23" t="s">
+      <c r="C196" s="21" t="s">
         <v>486</v>
       </c>
       <c r="D196" s="12"/>
@@ -17189,11 +18431,11 @@
       </c>
     </row>
     <row r="197" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A197" s="16" t="s">
+      <c r="A197" s="14" t="s">
         <v>487</v>
       </c>
       <c r="B197" s="12"/>
-      <c r="C197" s="16" t="s">
+      <c r="C197" s="14" t="s">
         <v>488</v>
       </c>
       <c r="D197" s="12"/>
@@ -17217,11 +18459,11 @@
       </c>
     </row>
     <row r="198" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A198" s="23" t="s">
+      <c r="A198" s="21" t="s">
         <v>489</v>
       </c>
       <c r="B198" s="12"/>
-      <c r="C198" s="23" t="s">
+      <c r="C198" s="21" t="s">
         <v>490</v>
       </c>
       <c r="D198" s="12"/>
@@ -17245,11 +18487,11 @@
       </c>
     </row>
     <row r="199" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A199" s="16" t="s">
+      <c r="A199" s="14" t="s">
         <v>491</v>
       </c>
       <c r="B199" s="12"/>
-      <c r="C199" s="16" t="s">
+      <c r="C199" s="14" t="s">
         <v>492</v>
       </c>
       <c r="D199" s="12"/>
@@ -17273,11 +18515,11 @@
       </c>
     </row>
     <row r="200" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A200" s="23" t="s">
+      <c r="A200" s="21" t="s">
         <v>493</v>
       </c>
       <c r="B200" s="12"/>
-      <c r="C200" s="23" t="s">
+      <c r="C200" s="21" t="s">
         <v>494</v>
       </c>
       <c r="D200" s="12"/>
@@ -17301,11 +18543,11 @@
       </c>
     </row>
     <row r="201" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A201" s="16" t="s">
+      <c r="A201" s="14" t="s">
         <v>495</v>
       </c>
       <c r="B201" s="12"/>
-      <c r="C201" s="16" t="s">
+      <c r="C201" s="14" t="s">
         <v>496</v>
       </c>
       <c r="D201" s="12"/>
@@ -17329,11 +18571,11 @@
       </c>
     </row>
     <row r="202" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A202" s="23" t="s">
+      <c r="A202" s="21" t="s">
         <v>497</v>
       </c>
       <c r="B202" s="12"/>
-      <c r="C202" s="23" t="s">
+      <c r="C202" s="21" t="s">
         <v>498</v>
       </c>
       <c r="D202" s="12"/>
@@ -17357,11 +18599,11 @@
       </c>
     </row>
     <row r="203" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A203" s="16" t="s">
+      <c r="A203" s="14" t="s">
         <v>499</v>
       </c>
       <c r="B203" s="12"/>
-      <c r="C203" s="16" t="s">
+      <c r="C203" s="14" t="s">
         <v>500</v>
       </c>
       <c r="D203" s="12"/>
@@ -17385,11 +18627,11 @@
       </c>
     </row>
     <row r="204" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A204" s="23" t="s">
+      <c r="A204" s="21" t="s">
         <v>501</v>
       </c>
       <c r="B204" s="12"/>
-      <c r="C204" s="23" t="s">
+      <c r="C204" s="21" t="s">
         <v>502</v>
       </c>
       <c r="D204" s="12"/>
@@ -17413,11 +18655,11 @@
       </c>
     </row>
     <row r="205" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A205" s="16" t="s">
+      <c r="A205" s="14" t="s">
         <v>503</v>
       </c>
       <c r="B205" s="12"/>
-      <c r="C205" s="16" t="s">
+      <c r="C205" s="14" t="s">
         <v>504</v>
       </c>
       <c r="D205" s="12"/>
@@ -17441,11 +18683,11 @@
       </c>
     </row>
     <row r="206" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A206" s="23" t="s">
+      <c r="A206" s="21" t="s">
         <v>505</v>
       </c>
       <c r="B206" s="12"/>
-      <c r="C206" s="23" t="s">
+      <c r="C206" s="21" t="s">
         <v>506</v>
       </c>
       <c r="D206" s="12"/>
@@ -17469,11 +18711,11 @@
       </c>
     </row>
     <row r="207" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A207" s="16" t="s">
+      <c r="A207" s="14" t="s">
         <v>507</v>
       </c>
       <c r="B207" s="12"/>
-      <c r="C207" s="16" t="s">
+      <c r="C207" s="14" t="s">
         <v>508</v>
       </c>
       <c r="D207" s="12"/>
@@ -17497,11 +18739,11 @@
       </c>
     </row>
     <row r="208" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A208" s="23" t="s">
+      <c r="A208" s="21" t="s">
         <v>509</v>
       </c>
       <c r="B208" s="12"/>
-      <c r="C208" s="23" t="s">
+      <c r="C208" s="21" t="s">
         <v>510</v>
       </c>
       <c r="D208" s="12"/>
@@ -17525,11 +18767,11 @@
       </c>
     </row>
     <row r="209" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A209" s="16" t="s">
+      <c r="A209" s="14" t="s">
         <v>511</v>
       </c>
       <c r="B209" s="12"/>
-      <c r="C209" s="16" t="s">
+      <c r="C209" s="14" t="s">
         <v>512</v>
       </c>
       <c r="D209" s="12"/>
@@ -17553,11 +18795,11 @@
       </c>
     </row>
     <row r="210" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A210" s="23" t="s">
+      <c r="A210" s="21" t="s">
         <v>513</v>
       </c>
       <c r="B210" s="12"/>
-      <c r="C210" s="23" t="s">
+      <c r="C210" s="21" t="s">
         <v>514</v>
       </c>
       <c r="D210" s="12"/>
@@ -17581,11 +18823,11 @@
       </c>
     </row>
     <row r="211" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A211" s="16" t="s">
+      <c r="A211" s="14" t="s">
         <v>515</v>
       </c>
       <c r="B211" s="12"/>
-      <c r="C211" s="16" t="s">
+      <c r="C211" s="14" t="s">
         <v>516</v>
       </c>
       <c r="D211" s="12"/>
@@ -17609,11 +18851,11 @@
       </c>
     </row>
     <row r="212" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="21" t="s">
         <v>517</v>
       </c>
       <c r="B212" s="12"/>
-      <c r="C212" s="23" t="s">
+      <c r="C212" s="21" t="s">
         <v>518</v>
       </c>
       <c r="D212" s="12"/>
@@ -17637,11 +18879,11 @@
       </c>
     </row>
     <row r="213" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A213" s="16" t="s">
+      <c r="A213" s="14" t="s">
         <v>519</v>
       </c>
       <c r="B213" s="12"/>
-      <c r="C213" s="16" t="s">
+      <c r="C213" s="14" t="s">
         <v>520</v>
       </c>
       <c r="D213" s="12"/>
@@ -17665,11 +18907,11 @@
       </c>
     </row>
     <row r="214" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A214" s="23" t="s">
+      <c r="A214" s="21" t="s">
         <v>521</v>
       </c>
       <c r="B214" s="12"/>
-      <c r="C214" s="23" t="s">
+      <c r="C214" s="21" t="s">
         <v>522</v>
       </c>
       <c r="D214" s="12"/>
@@ -17693,11 +18935,11 @@
       </c>
     </row>
     <row r="215" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A215" s="16" t="s">
+      <c r="A215" s="14" t="s">
         <v>523</v>
       </c>
       <c r="B215" s="12"/>
-      <c r="C215" s="16" t="s">
+      <c r="C215" s="14" t="s">
         <v>524</v>
       </c>
       <c r="D215" s="12"/>
@@ -17721,11 +18963,11 @@
       </c>
     </row>
     <row r="216" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A216" s="23" t="s">
+      <c r="A216" s="21" t="s">
         <v>525</v>
       </c>
       <c r="B216" s="12"/>
-      <c r="C216" s="23" t="s">
+      <c r="C216" s="21" t="s">
         <v>526</v>
       </c>
       <c r="D216" s="12"/>
@@ -17749,11 +18991,11 @@
       </c>
     </row>
     <row r="217" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A217" s="16" t="s">
+      <c r="A217" s="14" t="s">
         <v>527</v>
       </c>
       <c r="B217" s="12"/>
-      <c r="C217" s="16" t="s">
+      <c r="C217" s="14" t="s">
         <v>528</v>
       </c>
       <c r="D217" s="12"/>
@@ -17777,11 +19019,11 @@
       </c>
     </row>
     <row r="218" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A218" s="23" t="s">
+      <c r="A218" s="21" t="s">
         <v>529</v>
       </c>
       <c r="B218" s="12"/>
-      <c r="C218" s="23" t="s">
+      <c r="C218" s="21" t="s">
         <v>530</v>
       </c>
       <c r="D218" s="12"/>
@@ -17805,11 +19047,11 @@
       </c>
     </row>
     <row r="219" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A219" s="16" t="s">
+      <c r="A219" s="14" t="s">
         <v>531</v>
       </c>
       <c r="B219" s="12"/>
-      <c r="C219" s="16" t="s">
+      <c r="C219" s="14" t="s">
         <v>532</v>
       </c>
       <c r="D219" s="12"/>
@@ -17833,11 +19075,11 @@
       </c>
     </row>
     <row r="220" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A220" s="23" t="s">
+      <c r="A220" s="21" t="s">
         <v>533</v>
       </c>
       <c r="B220" s="12"/>
-      <c r="C220" s="23" t="s">
+      <c r="C220" s="21" t="s">
         <v>534</v>
       </c>
       <c r="D220" s="12"/>
@@ -17861,11 +19103,11 @@
       </c>
     </row>
     <row r="221" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A221" s="16" t="s">
+      <c r="A221" s="14" t="s">
         <v>535</v>
       </c>
       <c r="B221" s="12"/>
-      <c r="C221" s="16" t="s">
+      <c r="C221" s="14" t="s">
         <v>536</v>
       </c>
       <c r="D221" s="12"/>
@@ -17889,11 +19131,11 @@
       </c>
     </row>
     <row r="222" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A222" s="23" t="s">
+      <c r="A222" s="21" t="s">
         <v>537</v>
       </c>
       <c r="B222" s="12"/>
-      <c r="C222" s="23" t="s">
+      <c r="C222" s="21" t="s">
         <v>538</v>
       </c>
       <c r="D222" s="12"/>
@@ -17917,11 +19159,11 @@
       </c>
     </row>
     <row r="223" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A223" s="16" t="s">
+      <c r="A223" s="14" t="s">
         <v>539</v>
       </c>
       <c r="B223" s="12"/>
-      <c r="C223" s="16" t="s">
+      <c r="C223" s="14" t="s">
         <v>540</v>
       </c>
       <c r="D223" s="12"/>
@@ -17945,11 +19187,11 @@
       </c>
     </row>
     <row r="224" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A224" s="23" t="s">
+      <c r="A224" s="21" t="s">
         <v>541</v>
       </c>
       <c r="B224" s="12"/>
-      <c r="C224" s="23" t="s">
+      <c r="C224" s="21" t="s">
         <v>542</v>
       </c>
       <c r="D224" s="12"/>
@@ -17973,11 +19215,11 @@
       </c>
     </row>
     <row r="225" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A225" s="16" t="s">
+      <c r="A225" s="14" t="s">
         <v>543</v>
       </c>
       <c r="B225" s="12"/>
-      <c r="C225" s="16" t="s">
+      <c r="C225" s="14" t="s">
         <v>544</v>
       </c>
       <c r="D225" s="12"/>
@@ -18001,11 +19243,11 @@
       </c>
     </row>
     <row r="226" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A226" s="23" t="s">
+      <c r="A226" s="21" t="s">
         <v>545</v>
       </c>
       <c r="B226" s="12"/>
-      <c r="C226" s="23" t="s">
+      <c r="C226" s="21" t="s">
         <v>546</v>
       </c>
       <c r="D226" s="12"/>
@@ -18029,11 +19271,11 @@
       </c>
     </row>
     <row r="227" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A227" s="16" t="s">
+      <c r="A227" s="14" t="s">
         <v>547</v>
       </c>
       <c r="B227" s="12"/>
-      <c r="C227" s="16" t="s">
+      <c r="C227" s="14" t="s">
         <v>548</v>
       </c>
       <c r="D227" s="12"/>
@@ -18057,11 +19299,11 @@
       </c>
     </row>
     <row r="228" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A228" s="23" t="s">
+      <c r="A228" s="21" t="s">
         <v>549</v>
       </c>
       <c r="B228" s="12"/>
-      <c r="C228" s="23" t="s">
+      <c r="C228" s="21" t="s">
         <v>550</v>
       </c>
       <c r="D228" s="12"/>
@@ -18085,11 +19327,11 @@
       </c>
     </row>
     <row r="229" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A229" s="16" t="s">
+      <c r="A229" s="14" t="s">
         <v>551</v>
       </c>
       <c r="B229" s="12"/>
-      <c r="C229" s="16" t="s">
+      <c r="C229" s="14" t="s">
         <v>552</v>
       </c>
       <c r="D229" s="12"/>
@@ -18113,11 +19355,11 @@
       </c>
     </row>
     <row r="230" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A230" s="23" t="s">
+      <c r="A230" s="21" t="s">
         <v>553</v>
       </c>
       <c r="B230" s="12"/>
-      <c r="C230" s="23" t="s">
+      <c r="C230" s="21" t="s">
         <v>554</v>
       </c>
       <c r="D230" s="12"/>
@@ -18141,11 +19383,11 @@
       </c>
     </row>
     <row r="231" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A231" s="16" t="s">
+      <c r="A231" s="14" t="s">
         <v>555</v>
       </c>
       <c r="B231" s="12"/>
-      <c r="C231" s="16" t="s">
+      <c r="C231" s="14" t="s">
         <v>556</v>
       </c>
       <c r="D231" s="12"/>
@@ -18169,11 +19411,11 @@
       </c>
     </row>
     <row r="232" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A232" s="23" t="s">
+      <c r="A232" s="21" t="s">
         <v>557</v>
       </c>
       <c r="B232" s="12"/>
-      <c r="C232" s="23" t="s">
+      <c r="C232" s="21" t="s">
         <v>558</v>
       </c>
       <c r="D232" s="12"/>
@@ -18197,11 +19439,11 @@
       </c>
     </row>
     <row r="233" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A233" s="16" t="s">
+      <c r="A233" s="14" t="s">
         <v>559</v>
       </c>
       <c r="B233" s="12"/>
-      <c r="C233" s="16" t="s">
+      <c r="C233" s="14" t="s">
         <v>560</v>
       </c>
       <c r="D233" s="12"/>
@@ -18225,11 +19467,11 @@
       </c>
     </row>
     <row r="234" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A234" s="23" t="s">
+      <c r="A234" s="21" t="s">
         <v>561</v>
       </c>
       <c r="B234" s="12"/>
-      <c r="C234" s="23" t="s">
+      <c r="C234" s="21" t="s">
         <v>562</v>
       </c>
       <c r="D234" s="12"/>
@@ -18253,11 +19495,11 @@
       </c>
     </row>
     <row r="235" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A235" s="16" t="s">
+      <c r="A235" s="14" t="s">
         <v>563</v>
       </c>
       <c r="B235" s="12"/>
-      <c r="C235" s="16" t="s">
+      <c r="C235" s="14" t="s">
         <v>564</v>
       </c>
       <c r="D235" s="12"/>
@@ -18281,11 +19523,11 @@
       </c>
     </row>
     <row r="236" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A236" s="23" t="s">
+      <c r="A236" s="21" t="s">
         <v>565</v>
       </c>
       <c r="B236" s="12"/>
-      <c r="C236" s="23" t="s">
+      <c r="C236" s="21" t="s">
         <v>566</v>
       </c>
       <c r="D236" s="12"/>
@@ -18309,11 +19551,11 @@
       </c>
     </row>
     <row r="237" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A237" s="16" t="s">
+      <c r="A237" s="14" t="s">
         <v>567</v>
       </c>
       <c r="B237" s="12"/>
-      <c r="C237" s="16" t="s">
+      <c r="C237" s="14" t="s">
         <v>568</v>
       </c>
       <c r="D237" s="12"/>
@@ -18337,11 +19579,11 @@
       </c>
     </row>
     <row r="238" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A238" s="23" t="s">
+      <c r="A238" s="21" t="s">
         <v>569</v>
       </c>
       <c r="B238" s="12"/>
-      <c r="C238" s="23" t="s">
+      <c r="C238" s="21" t="s">
         <v>570</v>
       </c>
       <c r="D238" s="12"/>
@@ -18365,11 +19607,11 @@
       </c>
     </row>
     <row r="239" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A239" s="16" t="s">
+      <c r="A239" s="14" t="s">
         <v>571</v>
       </c>
       <c r="B239" s="12"/>
-      <c r="C239" s="16" t="s">
+      <c r="C239" s="14" t="s">
         <v>572</v>
       </c>
       <c r="D239" s="12"/>
@@ -18393,11 +19635,11 @@
       </c>
     </row>
     <row r="240" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A240" s="23" t="s">
+      <c r="A240" s="21" t="s">
         <v>573</v>
       </c>
       <c r="B240" s="12"/>
-      <c r="C240" s="23" t="s">
+      <c r="C240" s="21" t="s">
         <v>574</v>
       </c>
       <c r="D240" s="12"/>
@@ -18421,11 +19663,11 @@
       </c>
     </row>
     <row r="241" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A241" s="16" t="s">
+      <c r="A241" s="14" t="s">
         <v>575</v>
       </c>
       <c r="B241" s="12"/>
-      <c r="C241" s="16" t="s">
+      <c r="C241" s="14" t="s">
         <v>576</v>
       </c>
       <c r="D241" s="12"/>
@@ -18449,11 +19691,11 @@
       </c>
     </row>
     <row r="242" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A242" s="23" t="s">
+      <c r="A242" s="21" t="s">
         <v>577</v>
       </c>
       <c r="B242" s="12"/>
-      <c r="C242" s="23" t="s">
+      <c r="C242" s="21" t="s">
         <v>578</v>
       </c>
       <c r="D242" s="12"/>
@@ -18477,11 +19719,11 @@
       </c>
     </row>
     <row r="243" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A243" s="16" t="s">
+      <c r="A243" s="14" t="s">
         <v>579</v>
       </c>
       <c r="B243" s="12"/>
-      <c r="C243" s="16" t="s">
+      <c r="C243" s="14" t="s">
         <v>580</v>
       </c>
       <c r="D243" s="12"/>
@@ -18505,11 +19747,11 @@
       </c>
     </row>
     <row r="244" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A244" s="23" t="s">
+      <c r="A244" s="21" t="s">
         <v>581</v>
       </c>
       <c r="B244" s="12"/>
-      <c r="C244" s="23" t="s">
+      <c r="C244" s="21" t="s">
         <v>582</v>
       </c>
       <c r="D244" s="12"/>
@@ -18533,11 +19775,11 @@
       </c>
     </row>
     <row r="245" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A245" s="16" t="s">
+      <c r="A245" s="14" t="s">
         <v>583</v>
       </c>
       <c r="B245" s="12"/>
-      <c r="C245" s="16" t="s">
+      <c r="C245" s="14" t="s">
         <v>584</v>
       </c>
       <c r="D245" s="12"/>
@@ -18561,11 +19803,11 @@
       </c>
     </row>
     <row r="246" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A246" s="23" t="s">
+      <c r="A246" s="21" t="s">
         <v>585</v>
       </c>
       <c r="B246" s="12"/>
-      <c r="C246" s="23" t="s">
+      <c r="C246" s="21" t="s">
         <v>586</v>
       </c>
       <c r="D246" s="12"/>
@@ -18589,11 +19831,11 @@
       </c>
     </row>
     <row r="247" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A247" s="16" t="s">
+      <c r="A247" s="14" t="s">
         <v>587</v>
       </c>
       <c r="B247" s="12"/>
-      <c r="C247" s="16" t="s">
+      <c r="C247" s="14" t="s">
         <v>588</v>
       </c>
       <c r="D247" s="12"/>
@@ -18617,11 +19859,11 @@
       </c>
     </row>
     <row r="248" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A248" s="23" t="s">
+      <c r="A248" s="21" t="s">
         <v>589</v>
       </c>
       <c r="B248" s="12"/>
-      <c r="C248" s="23" t="s">
+      <c r="C248" s="21" t="s">
         <v>590</v>
       </c>
       <c r="D248" s="12"/>
@@ -18645,11 +19887,11 @@
       </c>
     </row>
     <row r="249" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A249" s="16" t="s">
+      <c r="A249" s="14" t="s">
         <v>591</v>
       </c>
       <c r="B249" s="12"/>
-      <c r="C249" s="16" t="s">
+      <c r="C249" s="14" t="s">
         <v>592</v>
       </c>
       <c r="D249" s="12"/>
@@ -18673,11 +19915,11 @@
       </c>
     </row>
     <row r="250" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A250" s="23" t="s">
+      <c r="A250" s="21" t="s">
         <v>593</v>
       </c>
       <c r="B250" s="12"/>
-      <c r="C250" s="23" t="s">
+      <c r="C250" s="21" t="s">
         <v>594</v>
       </c>
       <c r="D250" s="12"/>
@@ -18701,11 +19943,11 @@
       </c>
     </row>
     <row r="251" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A251" s="16" t="s">
+      <c r="A251" s="14" t="s">
         <v>595</v>
       </c>
       <c r="B251" s="12"/>
-      <c r="C251" s="16" t="s">
+      <c r="C251" s="14" t="s">
         <v>596</v>
       </c>
       <c r="D251" s="12"/>
@@ -18729,11 +19971,11 @@
       </c>
     </row>
     <row r="252" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A252" s="23" t="s">
+      <c r="A252" s="21" t="s">
         <v>597</v>
       </c>
       <c r="B252" s="12"/>
-      <c r="C252" s="23" t="s">
+      <c r="C252" s="21" t="s">
         <v>598</v>
       </c>
       <c r="D252" s="12"/>
@@ -18757,11 +19999,11 @@
       </c>
     </row>
     <row r="253" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A253" s="16" t="s">
+      <c r="A253" s="14" t="s">
         <v>599</v>
       </c>
       <c r="B253" s="12"/>
-      <c r="C253" s="16" t="s">
+      <c r="C253" s="14" t="s">
         <v>600</v>
       </c>
       <c r="D253" s="12"/>
@@ -18935,12 +20177,12 @@
       </c>
     </row>
     <row r="284" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ284" s="13" t="s">
+      <c r="AQ284" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="285" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ285" s="13" t="s">
+      <c r="AQ285" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -18950,32 +20192,32 @@
       </c>
     </row>
     <row r="287" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ287" s="13" t="s">
+      <c r="AQ287" t="s">
         <v>1105</v>
       </c>
     </row>
     <row r="288" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ288" s="13" t="s">
+      <c r="AQ288" t="s">
         <v>1106</v>
       </c>
     </row>
     <row r="289" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ289" s="13" t="s">
+      <c r="AQ289" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="290" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ290" s="13" t="s">
+      <c r="AQ290" t="s">
         <v>1108</v>
       </c>
     </row>
     <row r="291" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ291" s="13" t="s">
+      <c r="AQ291" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="292" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ292" s="13" t="s">
+      <c r="AQ292" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -19000,107 +20242,107 @@
       </c>
     </row>
     <row r="297" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ297" s="13" t="s">
+      <c r="AQ297" t="s">
         <v>1115</v>
       </c>
     </row>
     <row r="298" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ298" s="13" t="s">
+      <c r="AQ298" t="s">
         <v>1116</v>
       </c>
     </row>
     <row r="299" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ299" s="13" t="s">
+      <c r="AQ299" t="s">
         <v>1117</v>
       </c>
     </row>
     <row r="300" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ300" s="13" t="s">
+      <c r="AQ300" t="s">
         <v>1118</v>
       </c>
     </row>
     <row r="301" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ301" s="13" t="s">
+      <c r="AQ301" t="s">
         <v>1119</v>
       </c>
     </row>
     <row r="302" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ302" s="13" t="s">
+      <c r="AQ302" t="s">
         <v>1120</v>
       </c>
     </row>
     <row r="303" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ303" s="13" t="s">
+      <c r="AQ303" t="s">
         <v>1121</v>
       </c>
     </row>
     <row r="304" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ304" s="13" t="s">
+      <c r="AQ304" t="s">
         <v>1122</v>
       </c>
     </row>
     <row r="305" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ305" s="13" t="s">
+      <c r="AQ305" t="s">
         <v>1123</v>
       </c>
     </row>
     <row r="306" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ306" s="13" t="s">
+      <c r="AQ306" t="s">
         <v>1124</v>
       </c>
     </row>
     <row r="307" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ307" s="13" t="s">
+      <c r="AQ307" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="308" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ308" s="13" t="s">
+      <c r="AQ308" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="309" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ309" s="13" t="s">
+      <c r="AQ309" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="310" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ310" s="13" t="s">
+      <c r="AQ310" t="s">
         <v>1128</v>
       </c>
     </row>
     <row r="311" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ311" s="13" t="s">
+      <c r="AQ311" t="s">
         <v>1129</v>
       </c>
     </row>
     <row r="312" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ312" s="13" t="s">
+      <c r="AQ312" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="313" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ313" s="13" t="s">
+      <c r="AQ313" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="314" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ314" s="13" t="s">
+      <c r="AQ314" t="s">
         <v>1132</v>
       </c>
     </row>
     <row r="315" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ315" s="13" t="s">
+      <c r="AQ315" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="316" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ316" s="13" t="s">
+      <c r="AQ316" t="s">
         <v>1134</v>
       </c>
     </row>
     <row r="317" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ317" s="13" t="s">
+      <c r="AQ317" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -19605,77 +20847,77 @@
       </c>
     </row>
     <row r="418" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ418" s="13" t="s">
+      <c r="AQ418" t="s">
         <v>1236</v>
       </c>
     </row>
     <row r="419" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ419" s="13" t="s">
+      <c r="AQ419" t="s">
         <v>1237</v>
       </c>
     </row>
     <row r="420" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ420" s="13" t="s">
+      <c r="AQ420" t="s">
         <v>1238</v>
       </c>
     </row>
     <row r="421" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ421" s="13" t="s">
+      <c r="AQ421" t="s">
         <v>1239</v>
       </c>
     </row>
     <row r="422" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ422" s="13" t="s">
+      <c r="AQ422" t="s">
         <v>1240</v>
       </c>
     </row>
     <row r="423" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ423" s="13" t="s">
+      <c r="AQ423" t="s">
         <v>1241</v>
       </c>
     </row>
     <row r="424" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ424" s="13" t="s">
+      <c r="AQ424" t="s">
         <v>1242</v>
       </c>
     </row>
     <row r="425" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ425" s="13" t="s">
+      <c r="AQ425" t="s">
         <v>1243</v>
       </c>
     </row>
     <row r="426" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ426" s="13" t="s">
+      <c r="AQ426" t="s">
         <v>1244</v>
       </c>
     </row>
     <row r="427" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ427" s="13" t="s">
+      <c r="AQ427" t="s">
         <v>1245</v>
       </c>
     </row>
     <row r="428" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ428" s="13" t="s">
+      <c r="AQ428" t="s">
         <v>1246</v>
       </c>
     </row>
     <row r="429" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ429" s="13" t="s">
+      <c r="AQ429" t="s">
         <v>1247</v>
       </c>
     </row>
     <row r="430" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ430" s="13" t="s">
+      <c r="AQ430" t="s">
         <v>1248</v>
       </c>
     </row>
     <row r="431" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ431" s="13" t="s">
+      <c r="AQ431" t="s">
         <v>1249</v>
       </c>
     </row>
     <row r="432" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ432" s="13" t="s">
+      <c r="AQ432" t="s">
         <v>1250</v>
       </c>
     </row>
@@ -19920,47 +21162,47 @@
       </c>
     </row>
     <row r="481" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ481" s="13" t="s">
+      <c r="AQ481" t="s">
         <v>1299</v>
       </c>
     </row>
     <row r="482" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ482" s="13" t="s">
+      <c r="AQ482" t="s">
         <v>1300</v>
       </c>
     </row>
     <row r="483" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ483" s="13" t="s">
+      <c r="AQ483" t="s">
         <v>1301</v>
       </c>
     </row>
     <row r="484" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ484" s="13" t="s">
+      <c r="AQ484" t="s">
         <v>1302</v>
       </c>
     </row>
     <row r="485" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ485" s="13" t="s">
+      <c r="AQ485" t="s">
         <v>1303</v>
       </c>
     </row>
     <row r="486" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ486" s="13" t="s">
+      <c r="AQ486" t="s">
         <v>1304</v>
       </c>
     </row>
     <row r="487" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ487" s="13" t="s">
+      <c r="AQ487" t="s">
         <v>1305</v>
       </c>
     </row>
     <row r="488" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ488" s="13" t="s">
+      <c r="AQ488" t="s">
         <v>1306</v>
       </c>
     </row>
     <row r="489" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ489" s="13" t="s">
+      <c r="AQ489" t="s">
         <v>1307</v>
       </c>
     </row>
@@ -19970,12 +21212,12 @@
       </c>
     </row>
     <row r="491" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ491" s="13" t="s">
+      <c r="AQ491" t="s">
         <v>1309</v>
       </c>
     </row>
     <row r="492" spans="43:43" x14ac:dyDescent="0.35">
-      <c r="AQ492" s="13" t="s">
+      <c r="AQ492" t="s">
         <v>1310</v>
       </c>
     </row>

--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_31_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{55F88FD4-860F-4289-8195-ADD9A282EF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A36FCB71-9766-4590-A298-53D5019C9C67}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{55F88FD4-860F-4289-8195-ADD9A282EF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F2DD12-B6C9-4BE6-9B5A-7D9A53F3C3F7}"/>
   <bookViews>
-    <workbookView xWindow="-21000" yWindow="1065" windowWidth="18240" windowHeight="9975" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1775">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -5355,6 +5355,12 @@
   </si>
   <si>
     <t>CORSIA Second Phase scope (2033-2035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit_level_compliance_eligibility &amp; unit_level_compliance_potential_eligibility </t>
+  </si>
+  <si>
+    <t>project_level_compliance_eligibility &amp; project_level_compliance_potential_ eligibility</t>
   </si>
 </sst>
 </file>
@@ -6158,7 +6164,7 @@
       </c>
       <c r="CZ3" s="28"/>
       <c r="DA3" s="28" t="s">
-        <v>1713</v>
+        <v>1773</v>
       </c>
       <c r="DB3" s="28"/>
       <c r="DC3" s="28" t="s">
@@ -6166,7 +6172,7 @@
       </c>
       <c r="DD3" s="28"/>
       <c r="DE3" s="28" t="s">
-        <v>1715</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="4" spans="1:121" ht="16" x14ac:dyDescent="0.4">

--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_31_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/8_31_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{55F88FD4-860F-4289-8195-ADD9A282EF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F2DD12-B6C9-4BE6-9B5A-7D9A53F3C3F7}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{E4D6B18E-029C-4907-BB24-8B6B93F1772F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B6D16E9-B126-401C-9687-5E821CDE32D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="1857">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -4136,9 +4136,6 @@
     <t xml:space="preserve">Origination </t>
   </si>
   <si>
-    <t>UNFCCC Article 6.2 common nomenclatures (Activity Type)</t>
-  </si>
-  <si>
     <t>Validation of Project Design Document</t>
   </si>
   <si>
@@ -5361,6 +5358,255 @@
   </si>
   <si>
     <t>project_level_compliance_eligibility &amp; project_level_compliance_potential_ eligibility</t>
+  </si>
+  <si>
+    <t>Bundled Compost Production and Soil Application</t>
+  </si>
+  <si>
+    <t>Carbon Mineralization</t>
+  </si>
+  <si>
+    <t>Enhanced Rock Weathering</t>
+  </si>
+  <si>
+    <t>Feed Additives</t>
+  </si>
+  <si>
+    <t>Improved Irrigation Management</t>
+  </si>
+  <si>
+    <t>Manure Methane Digester</t>
+  </si>
+  <si>
+    <t>Nitrogen Management</t>
+  </si>
+  <si>
+    <t>Rice Emission Reductions</t>
+  </si>
+  <si>
+    <t>Solid Waste Separation</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture</t>
+  </si>
+  <si>
+    <t>Carbon Capture &amp; Enhanced Oil Recovery</t>
+  </si>
+  <si>
+    <t>Carbon Capture in Concrete</t>
+  </si>
+  <si>
+    <t>Carbon Capture in Plastic</t>
+  </si>
+  <si>
+    <t>N2O Destruction in Adipic Acid Production</t>
+  </si>
+  <si>
+    <t>N2O Destruction in Nitric Acid Production</t>
+  </si>
+  <si>
+    <t>Propylene Oxide Production</t>
+  </si>
+  <si>
+    <t>SF6 Replacement</t>
+  </si>
+  <si>
+    <t>Advanced Refrigerants</t>
+  </si>
+  <si>
+    <t>HFC Refrigerants Reclamation</t>
+  </si>
+  <si>
+    <t>HFC Replacement in Foam Production</t>
+  </si>
+  <si>
+    <t>HFC23 Destruction</t>
+  </si>
+  <si>
+    <t>Ozone Depleting Substances Recovery &amp; Destruction</t>
+  </si>
+  <si>
+    <t>Refrigerant Leak Detection</t>
+  </si>
+  <si>
+    <t>BECCS (Bioenergy with Carbon Capture and Storage)</t>
+  </si>
+  <si>
+    <t>Biomass Carbon Removal &amp; Storage (BiCRS)</t>
+  </si>
+  <si>
+    <t>Direct Air Capture</t>
+  </si>
+  <si>
+    <t>Ocean Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>River Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>Wastewater Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>Afforestation/Reforestation</t>
+  </si>
+  <si>
+    <t>Avoided Forest Conversion</t>
+  </si>
+  <si>
+    <t>Avoided Grassland Conversion</t>
+  </si>
+  <si>
+    <t>Improved Forest Management</t>
+  </si>
+  <si>
+    <t>REDD+ (Reducing Emissions from Deforestation and Forest Degradation)</t>
+  </si>
+  <si>
+    <t>REDD+ Jurisdictional</t>
+  </si>
+  <si>
+    <t>Sustainable Grassland Management</t>
+  </si>
+  <si>
+    <t>Wetland Restoration</t>
+  </si>
+  <si>
+    <t>Biodigesters</t>
+  </si>
+  <si>
+    <t>Bundled Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Clean Water</t>
+  </si>
+  <si>
+    <t>Community Boreholes</t>
+  </si>
+  <si>
+    <t>Cookstoves</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>Weatherization</t>
+  </si>
+  <si>
+    <t>Aluminum Smelters Emission Reductions</t>
+  </si>
+  <si>
+    <t>Brick Manufacturing Emission Reductions</t>
+  </si>
+  <si>
+    <t>Carbon-Absorbing Concrete</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Fuel Switching</t>
+  </si>
+  <si>
+    <t>Grid Expansion &amp; Mini-Grids</t>
+  </si>
+  <si>
+    <t>Leak Detection &amp; Repair in Gas Systems</t>
+  </si>
+  <si>
+    <t>Lower Carbon Cement &amp; Concrete</t>
+  </si>
+  <si>
+    <t>Mine Methane Capture</t>
+  </si>
+  <si>
+    <t>Natural Gas Electricity Generation</t>
+  </si>
+  <si>
+    <t>Oil Recycling</t>
+  </si>
+  <si>
+    <t>Plugging Oil &amp; Gas Wells</t>
+  </si>
+  <si>
+    <t>Pneumatic Retrofit</t>
+  </si>
+  <si>
+    <t>Road Construction Emission Reductions</t>
+  </si>
+  <si>
+    <t>University Campus Emission Reductions</t>
+  </si>
+  <si>
+    <t>Waste Gas Recovery</t>
+  </si>
+  <si>
+    <t>Waste Heat Recovery</t>
+  </si>
+  <si>
+    <t>Energy Storage</t>
+  </si>
+  <si>
+    <t>Hydropower</t>
+  </si>
+  <si>
+    <t>RE Bundled (Bundled Renewables)</t>
+  </si>
+  <si>
+    <t>Solar - Centralized</t>
+  </si>
+  <si>
+    <t>Solar - Distributed</t>
+  </si>
+  <si>
+    <t>Solar Lighting</t>
+  </si>
+  <si>
+    <t>Solar Water Heaters</t>
+  </si>
+  <si>
+    <t>Bicycles</t>
+  </si>
+  <si>
+    <t>Electric Vehicles &amp; Charging</t>
+  </si>
+  <si>
+    <t>Fleet Efficiency</t>
+  </si>
+  <si>
+    <t>Fuel Transport</t>
+  </si>
+  <si>
+    <t>Mass Transit</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Truck Stop Electrification</t>
+  </si>
+  <si>
+    <t>Biochar</t>
+  </si>
+  <si>
+    <t>Composting</t>
+  </si>
+  <si>
+    <t>Landfill Methane</t>
+  </si>
+  <si>
+    <t>Methane Recovery in Wastewater</t>
+  </si>
+  <si>
+    <t>Waste Diversion</t>
+  </si>
+  <si>
+    <t>Waste Incineration</t>
+  </si>
+  <si>
+    <t>Waste Recycling</t>
+  </si>
+  <si>
+    <t>Waste Reduction</t>
   </si>
 </sst>
 </file>
@@ -5500,7 +5746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5532,7 +5778,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5559,6 +5804,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5907,7 +6159,7 @@
     <col min="23" max="23" width="24.81640625" customWidth="1"/>
     <col min="25" max="25" width="29.81640625" customWidth="1"/>
     <col min="27" max="27" width="11.1796875" customWidth="1"/>
-    <col min="35" max="35" width="28.36328125" customWidth="1"/>
+    <col min="35" max="35" width="28.36328125" style="30" customWidth="1"/>
     <col min="37" max="37" width="27.81640625" customWidth="1"/>
     <col min="39" max="39" width="21.453125" customWidth="1"/>
     <col min="41" max="41" width="14.1796875" customWidth="1"/>
@@ -6044,14 +6296,14 @@
       <c r="AG3" t="s">
         <v>1348</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AI3" s="30" t="s">
         <v>1349</v>
       </c>
       <c r="AK3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AM3" t="s">
         <v>1431</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>1432</v>
       </c>
       <c r="AO3" t="s">
         <v>1350</v>
@@ -6087,92 +6339,92 @@
         <v>1358</v>
       </c>
       <c r="BK3" s="9" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="BL3" s="9"/>
       <c r="BM3" s="9" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="BN3" s="9"/>
       <c r="BO3" s="9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="BP3" s="9"/>
       <c r="BQ3" s="9" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="BR3" s="9"/>
       <c r="BS3" s="9" t="s">
+        <v>1436</v>
+      </c>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="23" t="s">
         <v>1437</v>
       </c>
-      <c r="BT3" s="9"/>
-      <c r="BU3" s="24" t="s">
+      <c r="BV3" s="23"/>
+      <c r="BW3" s="9" t="s">
         <v>1438</v>
-      </c>
-      <c r="BV3" s="24"/>
-      <c r="BW3" s="9" t="s">
-        <v>1439</v>
       </c>
       <c r="BX3" s="9"/>
       <c r="BY3" s="9" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="BZ3" s="9"/>
       <c r="CA3" s="9" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="CB3" s="9"/>
       <c r="CC3" s="9" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="CD3" s="9"/>
       <c r="CE3" s="9" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="CG3" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="CI3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="CK3" s="22" t="s">
+        <v>1683</v>
+      </c>
+      <c r="CM3" t="s">
         <v>1685</v>
       </c>
-      <c r="CK3" s="23" t="s">
-        <v>1684</v>
-      </c>
-      <c r="CM3" t="s">
+      <c r="CO3" t="s">
         <v>1686</v>
       </c>
-      <c r="CO3" t="s">
-        <v>1687</v>
-      </c>
       <c r="CQ3" t="s">
-        <v>1704</v>
-      </c>
-      <c r="CS3" s="28" t="s">
+        <v>1703</v>
+      </c>
+      <c r="CS3" s="27" t="s">
+        <v>1708</v>
+      </c>
+      <c r="CT3" s="27"/>
+      <c r="CU3" s="27" t="s">
         <v>1709</v>
       </c>
-      <c r="CT3" s="28"/>
-      <c r="CU3" s="28" t="s">
+      <c r="CV3" s="27"/>
+      <c r="CW3" s="27" t="s">
         <v>1710</v>
       </c>
-      <c r="CV3" s="28"/>
-      <c r="CW3" s="28" t="s">
+      <c r="CX3" s="27"/>
+      <c r="CY3" s="27" t="s">
         <v>1711</v>
       </c>
-      <c r="CX3" s="28"/>
-      <c r="CY3" s="28" t="s">
-        <v>1712</v>
-      </c>
-      <c r="CZ3" s="28"/>
-      <c r="DA3" s="28" t="s">
+      <c r="CZ3" s="27"/>
+      <c r="DA3" s="27" t="s">
+        <v>1772</v>
+      </c>
+      <c r="DB3" s="27"/>
+      <c r="DC3" s="27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="DD3" s="27"/>
+      <c r="DE3" s="27" t="s">
         <v>1773</v>
-      </c>
-      <c r="DB3" s="28"/>
-      <c r="DC3" s="28" t="s">
-        <v>1714</v>
-      </c>
-      <c r="DD3" s="28"/>
-      <c r="DE3" s="28" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="4" spans="1:121" ht="16" x14ac:dyDescent="0.4">
@@ -6291,55 +6543,55 @@
       <c r="BI4" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="BK4" s="25" t="s">
+      <c r="BK4" s="24" t="s">
+        <v>1432</v>
+      </c>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="24" t="s">
         <v>1433</v>
       </c>
-      <c r="BL4" s="9"/>
-      <c r="BM4" s="25" t="s">
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24" t="s">
         <v>1434</v>
       </c>
-      <c r="BN4" s="25"/>
-      <c r="BO4" s="25" t="s">
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24" t="s">
         <v>1435</v>
       </c>
-      <c r="BP4" s="25"/>
-      <c r="BQ4" s="25" t="s">
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24" t="s">
         <v>1436</v>
       </c>
-      <c r="BR4" s="25"/>
-      <c r="BS4" s="25" t="s">
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="25" t="s">
         <v>1437</v>
       </c>
-      <c r="BT4" s="25"/>
-      <c r="BU4" s="26" t="s">
+      <c r="BV4" s="25"/>
+      <c r="BW4" s="24" t="s">
         <v>1438</v>
       </c>
-      <c r="BV4" s="26"/>
-      <c r="BW4" s="25" t="s">
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24" t="s">
         <v>1439</v>
       </c>
-      <c r="BX4" s="25"/>
-      <c r="BY4" s="25" t="s">
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24" t="s">
         <v>1440</v>
       </c>
-      <c r="BZ4" s="25"/>
-      <c r="CA4" s="25" t="s">
+      <c r="CB4" s="24"/>
+      <c r="CC4" s="24" t="s">
         <v>1441</v>
       </c>
-      <c r="CB4" s="25"/>
-      <c r="CC4" s="25" t="s">
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="24" t="s">
         <v>1442</v>
       </c>
-      <c r="CD4" s="25"/>
-      <c r="CE4" s="25" t="s">
-        <v>1443</v>
-      </c>
       <c r="CG4" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="CH4" s="1"/>
       <c r="CI4" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="CJ4" s="1"/>
       <c r="CK4" s="1" t="s">
@@ -6347,45 +6599,45 @@
       </c>
       <c r="CL4" s="1"/>
       <c r="CM4" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="CN4" s="1"/>
       <c r="CO4" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="CP4" s="1"/>
       <c r="CQ4" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="CR4" s="1"/>
-      <c r="CS4" s="27" t="s">
+      <c r="CS4" s="26" t="s">
+        <v>1708</v>
+      </c>
+      <c r="CT4" s="26"/>
+      <c r="CU4" s="26" t="s">
         <v>1709</v>
       </c>
-      <c r="CT4" s="27"/>
-      <c r="CU4" s="27" t="s">
+      <c r="CV4" s="26"/>
+      <c r="CW4" s="26" t="s">
         <v>1710</v>
       </c>
-      <c r="CV4" s="27"/>
-      <c r="CW4" s="27" t="s">
+      <c r="CX4" s="26"/>
+      <c r="CY4" s="26" t="s">
         <v>1711</v>
       </c>
-      <c r="CX4" s="27"/>
-      <c r="CY4" s="27" t="s">
+      <c r="CZ4" s="26"/>
+      <c r="DA4" s="26" t="s">
         <v>1712</v>
       </c>
-      <c r="CZ4" s="27"/>
-      <c r="DA4" s="27" t="s">
+      <c r="DB4" s="26"/>
+      <c r="DC4" s="26" t="s">
         <v>1713</v>
       </c>
-      <c r="DB4" s="27"/>
-      <c r="DC4" s="27" t="s">
+      <c r="DD4" s="26"/>
+      <c r="DE4" s="26" t="s">
         <v>1714</v>
       </c>
-      <c r="DD4" s="27"/>
-      <c r="DE4" s="27" t="s">
-        <v>1715</v>
-      </c>
-      <c r="DF4" s="27"/>
+      <c r="DF4" s="26"/>
       <c r="DG4" s="1"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
@@ -6462,8 +6714,8 @@
         <v>619</v>
       </c>
       <c r="AH5" s="9"/>
-      <c r="AI5" s="17" t="s">
-        <v>1366</v>
+      <c r="AI5" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9" t="s">
@@ -6491,33 +6743,33 @@
         <v>1326</v>
       </c>
       <c r="AY5" s="9" t="s">
+        <v>1366</v>
+      </c>
+      <c r="BA5" s="17" t="s">
         <v>1367</v>
       </c>
-      <c r="BA5" s="18" t="s">
+      <c r="BC5" s="18" t="s">
         <v>1368</v>
       </c>
-      <c r="BC5" s="19" t="s">
+      <c r="BE5" t="s">
         <v>1369</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BG5" s="9" t="s">
         <v>1370</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BI5" t="s">
         <v>1371</v>
       </c>
-      <c r="BI5" t="s">
-        <v>1372</v>
-      </c>
       <c r="BK5" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="BL5" s="9"/>
       <c r="BM5" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="BN5" s="9"/>
       <c r="BO5" s="9" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="BP5" s="9"/>
       <c r="BQ5" s="9" t="s">
@@ -6525,85 +6777,85 @@
       </c>
       <c r="BR5" s="9"/>
       <c r="BS5" s="9" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="BT5" s="9"/>
       <c r="BU5" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BV5" s="9"/>
       <c r="BW5" s="9" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="BX5" s="9"/>
       <c r="BY5" s="9" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="BZ5" s="9"/>
       <c r="CA5" s="9" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="CB5" s="9"/>
       <c r="CC5" s="9" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="CD5" s="9"/>
       <c r="CE5" s="9" t="s">
-        <v>1452</v>
-      </c>
-      <c r="CG5" s="20" t="s">
-        <v>1647</v>
-      </c>
-      <c r="CI5" s="20" t="s">
-        <v>1667</v>
-      </c>
-      <c r="CK5" s="20" t="s">
-        <v>1678</v>
-      </c>
-      <c r="CM5" s="20" t="s">
-        <v>1699</v>
-      </c>
-      <c r="CO5" s="20" t="s">
-        <v>1690</v>
-      </c>
-      <c r="CQ5" s="20" t="s">
-        <v>1706</v>
-      </c>
-      <c r="CS5" s="28" t="s">
+        <v>1451</v>
+      </c>
+      <c r="CG5" s="19" t="s">
+        <v>1646</v>
+      </c>
+      <c r="CI5" s="19" t="s">
+        <v>1666</v>
+      </c>
+      <c r="CK5" s="19" t="s">
+        <v>1677</v>
+      </c>
+      <c r="CM5" s="19" t="s">
+        <v>1698</v>
+      </c>
+      <c r="CO5" s="19" t="s">
+        <v>1689</v>
+      </c>
+      <c r="CQ5" s="19" t="s">
+        <v>1705</v>
+      </c>
+      <c r="CS5" s="27" t="s">
+        <v>1715</v>
+      </c>
+      <c r="CT5" s="27"/>
+      <c r="CU5" s="27" t="s">
         <v>1716</v>
       </c>
-      <c r="CT5" s="28"/>
-      <c r="CU5" s="28" t="s">
+      <c r="CV5" s="27"/>
+      <c r="CW5" s="27" t="s">
         <v>1717</v>
       </c>
-      <c r="CV5" s="28"/>
-      <c r="CW5" s="28" t="s">
+      <c r="CX5" s="27"/>
+      <c r="CY5" s="28" t="s">
         <v>1718</v>
       </c>
-      <c r="CX5" s="28"/>
-      <c r="CY5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="CZ5" s="29"/>
-      <c r="DA5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DB5" s="29"/>
-      <c r="DC5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DD5" s="29"/>
-      <c r="DE5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DF5" s="29"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DF5" s="28"/>
     </row>
     <row r="6" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="12"/>
@@ -6644,12 +6896,12 @@
         <v>625</v>
       </c>
       <c r="AA6" t="s">
-        <v>1373</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AC6" s="21" t="s">
         <v>627</v>
       </c>
-      <c r="AD6" s="22"/>
+      <c r="AD6" s="21"/>
       <c r="AE6" s="9" t="s">
         <v>628</v>
       </c>
@@ -6658,7 +6910,9 @@
         <v>629</v>
       </c>
       <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="AI6" s="10" t="s">
+        <v>1385</v>
+      </c>
       <c r="AJ6" s="9"/>
       <c r="AK6" t="s">
         <v>630</v>
@@ -6683,33 +6937,33 @@
         <v>1327</v>
       </c>
       <c r="AY6" s="9" t="s">
+        <v>1373</v>
+      </c>
+      <c r="BA6" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="BC6" s="18" t="s">
         <v>1374</v>
       </c>
-      <c r="BA6" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="BC6" s="19" t="s">
+      <c r="BE6" t="s">
         <v>1375</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BG6" s="9" t="s">
         <v>1376</v>
       </c>
-      <c r="BG6" s="9" t="s">
+      <c r="BI6" t="s">
         <v>1377</v>
       </c>
-      <c r="BI6" t="s">
-        <v>1378</v>
-      </c>
       <c r="BK6" s="9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="BL6" s="9"/>
       <c r="BM6" s="9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="BN6" s="9"/>
       <c r="BO6" s="9" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="BP6" s="9"/>
       <c r="BQ6" s="9" t="s">
@@ -6717,76 +6971,76 @@
       </c>
       <c r="BR6" s="9"/>
       <c r="BS6" s="9" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="BT6" s="9"/>
       <c r="BU6" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="BV6" s="9"/>
       <c r="BW6" s="9" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="BX6" s="9"/>
       <c r="BY6" s="9" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="BZ6" s="9"/>
       <c r="CA6" s="9" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="CB6" s="9"/>
       <c r="CC6" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="CD6" s="9"/>
       <c r="CE6" s="9" t="s">
-        <v>1461</v>
-      </c>
-      <c r="CG6" s="20" t="s">
-        <v>1648</v>
-      </c>
-      <c r="CI6" s="20" t="s">
-        <v>1668</v>
-      </c>
-      <c r="CK6" s="20" t="s">
-        <v>1679</v>
-      </c>
-      <c r="CM6" s="20" t="s">
-        <v>1700</v>
-      </c>
-      <c r="CO6" s="20" t="s">
-        <v>1691</v>
-      </c>
-      <c r="CQ6" s="20" t="s">
-        <v>1707</v>
-      </c>
-      <c r="CS6" s="29" t="s">
+        <v>1460</v>
+      </c>
+      <c r="CG6" s="19" t="s">
+        <v>1647</v>
+      </c>
+      <c r="CI6" s="19" t="s">
+        <v>1667</v>
+      </c>
+      <c r="CK6" s="19" t="s">
+        <v>1678</v>
+      </c>
+      <c r="CM6" s="19" t="s">
+        <v>1699</v>
+      </c>
+      <c r="CO6" s="19" t="s">
+        <v>1690</v>
+      </c>
+      <c r="CQ6" s="19" t="s">
+        <v>1706</v>
+      </c>
+      <c r="CS6" s="28" t="s">
+        <v>1719</v>
+      </c>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="27" t="s">
         <v>1720</v>
       </c>
-      <c r="CT6" s="29"/>
-      <c r="CU6" s="28" t="s">
+      <c r="CV6" s="27"/>
+      <c r="CW6" s="27"/>
+      <c r="CX6" s="27"/>
+      <c r="CY6" s="28" t="s">
         <v>1721</v>
       </c>
-      <c r="CV6" s="28"/>
-      <c r="CW6" s="28"/>
-      <c r="CX6" s="28"/>
-      <c r="CY6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="CZ6" s="29"/>
-      <c r="DA6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DB6" s="29"/>
-      <c r="DC6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DD6" s="29"/>
-      <c r="DE6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DF6" s="29"/>
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DF6" s="28"/>
     </row>
     <row r="7" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
@@ -6831,10 +7085,10 @@
       <c r="Y7" t="s">
         <v>636</v>
       </c>
-      <c r="AA7" s="23" t="s">
-        <v>1379</v>
-      </c>
-      <c r="AB7" s="23"/>
+      <c r="AA7" s="22" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AB7" s="22"/>
       <c r="AC7" s="9" t="s">
         <v>638</v>
       </c>
@@ -6847,8 +7101,8 @@
         <v>640</v>
       </c>
       <c r="AH7" s="9"/>
-      <c r="AI7" s="10" t="s">
-        <v>1380</v>
+      <c r="AI7" s="11" t="s">
+        <v>1389</v>
       </c>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9" t="s">
@@ -6875,27 +7129,27 @@
         <v>1328</v>
       </c>
       <c r="AY7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="BA7" s="17" t="s">
         <v>1381</v>
       </c>
-      <c r="BA7" s="18" t="s">
+      <c r="BE7" t="s">
         <v>1382</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BG7" s="9" t="s">
         <v>1383</v>
       </c>
-      <c r="BG7" s="9" t="s">
-        <v>1384</v>
-      </c>
       <c r="BK7" s="9" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="BL7" s="9"/>
       <c r="BM7" s="9" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="BN7" s="9"/>
       <c r="BO7" s="9" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="BP7" s="9"/>
       <c r="BQ7" s="9" t="s">
@@ -6903,83 +7157,83 @@
       </c>
       <c r="BR7" s="9"/>
       <c r="BS7" s="9" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="BT7" s="9"/>
       <c r="BU7" s="9" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="BV7" s="9"/>
       <c r="BW7" s="9" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="BX7" s="9"/>
       <c r="BY7" s="9" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="BZ7" s="9"/>
       <c r="CA7" s="9" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="CB7" s="9"/>
       <c r="CC7" s="9" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="CD7" s="9"/>
       <c r="CE7" s="9" t="s">
-        <v>1470</v>
-      </c>
-      <c r="CG7" s="20" t="s">
-        <v>1649</v>
-      </c>
-      <c r="CI7" s="20" t="s">
-        <v>1669</v>
-      </c>
-      <c r="CK7" s="20" t="s">
-        <v>1680</v>
-      </c>
-      <c r="CM7" s="20" t="s">
-        <v>1701</v>
-      </c>
-      <c r="CO7" s="20" t="s">
-        <v>1692</v>
-      </c>
-      <c r="CQ7" s="20" t="s">
-        <v>1708</v>
-      </c>
-      <c r="CS7" s="29" t="s">
+        <v>1469</v>
+      </c>
+      <c r="CG7" s="19" t="s">
+        <v>1648</v>
+      </c>
+      <c r="CI7" s="19" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CK7" s="19" t="s">
+        <v>1679</v>
+      </c>
+      <c r="CM7" s="19" t="s">
+        <v>1700</v>
+      </c>
+      <c r="CO7" s="19" t="s">
+        <v>1691</v>
+      </c>
+      <c r="CQ7" s="19" t="s">
+        <v>1707</v>
+      </c>
+      <c r="CS7" s="28" t="s">
+        <v>1722</v>
+      </c>
+      <c r="CT7" s="28"/>
+      <c r="CU7" s="27" t="s">
         <v>1723</v>
       </c>
-      <c r="CT7" s="29"/>
-      <c r="CU7" s="28" t="s">
+      <c r="CV7" s="27"/>
+      <c r="CW7" s="27"/>
+      <c r="CX7" s="27"/>
+      <c r="CY7" s="28" t="s">
         <v>1724</v>
       </c>
-      <c r="CV7" s="28"/>
-      <c r="CW7" s="28"/>
-      <c r="CX7" s="28"/>
-      <c r="CY7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="CZ7" s="29"/>
-      <c r="DA7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DB7" s="29"/>
-      <c r="DC7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DF7" s="29"/>
+      <c r="CZ7" s="28"/>
+      <c r="DA7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DB7" s="28"/>
+      <c r="DC7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DD7" s="28"/>
+      <c r="DE7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DF7" s="28"/>
     </row>
     <row r="8" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12"/>
@@ -7016,7 +7270,7 @@
         <v>647</v>
       </c>
       <c r="AA8" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="AE8" s="9" t="s">
         <v>649</v>
@@ -7026,8 +7280,8 @@
         <v>650</v>
       </c>
       <c r="AH8" s="9"/>
-      <c r="AI8" s="10" t="s">
-        <v>1386</v>
+      <c r="AI8" s="11" t="s">
+        <v>1392</v>
       </c>
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9" t="s">
@@ -7057,21 +7311,21 @@
         <v>737</v>
       </c>
       <c r="BE8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="BG8" s="9" t="s">
         <v>1387</v>
       </c>
-      <c r="BG8" s="9" t="s">
-        <v>1388</v>
-      </c>
       <c r="BK8" s="9" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="BL8" s="9"/>
       <c r="BM8" s="9" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="BN8" s="9"/>
       <c r="BO8" s="9" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="BP8" s="9"/>
       <c r="BQ8" s="9" t="s">
@@ -7079,76 +7333,76 @@
       </c>
       <c r="BR8" s="9"/>
       <c r="BS8" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="BT8" s="9"/>
       <c r="BU8" s="9" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="BV8" s="9"/>
       <c r="BW8" s="9" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="BX8" s="9"/>
       <c r="BY8" s="9" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="BZ8" s="9"/>
       <c r="CA8" s="9" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="CB8" s="9"/>
       <c r="CC8" s="9" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="CD8" s="9"/>
       <c r="CE8" s="9" t="s">
-        <v>1478</v>
-      </c>
-      <c r="CG8" s="20" t="s">
-        <v>1650</v>
-      </c>
-      <c r="CI8" s="20" t="s">
-        <v>1670</v>
-      </c>
-      <c r="CK8" s="20" t="s">
-        <v>1681</v>
-      </c>
-      <c r="CM8" s="20" t="s">
-        <v>1372</v>
-      </c>
-      <c r="CO8" s="20" t="s">
-        <v>1693</v>
-      </c>
-      <c r="CQ8" s="20" t="s">
+        <v>1477</v>
+      </c>
+      <c r="CG8" s="19" t="s">
+        <v>1649</v>
+      </c>
+      <c r="CI8" s="19" t="s">
+        <v>1669</v>
+      </c>
+      <c r="CK8" s="19" t="s">
+        <v>1680</v>
+      </c>
+      <c r="CM8" s="19" t="s">
+        <v>1371</v>
+      </c>
+      <c r="CO8" s="19" t="s">
+        <v>1692</v>
+      </c>
+      <c r="CQ8" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="CS8" s="29" t="s">
+      <c r="CS8" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CT8" s="28"/>
+      <c r="CU8" s="27" t="s">
         <v>1726</v>
       </c>
-      <c r="CT8" s="29"/>
-      <c r="CU8" s="28" t="s">
+      <c r="CV8" s="27"/>
+      <c r="CW8" s="27"/>
+      <c r="CX8" s="27"/>
+      <c r="CY8" s="28" t="s">
         <v>1727</v>
       </c>
-      <c r="CV8" s="28"/>
-      <c r="CW8" s="28"/>
-      <c r="CX8" s="28"/>
-      <c r="CY8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="CZ8" s="29"/>
-      <c r="DA8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DB8" s="29"/>
-      <c r="DC8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DD8" s="29"/>
-      <c r="DE8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DF8" s="28"/>
+      <c r="CZ8" s="28"/>
+      <c r="DA8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DB8" s="28"/>
+      <c r="DC8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DD8" s="28"/>
+      <c r="DE8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DF8" s="27"/>
     </row>
     <row r="9" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
@@ -7189,7 +7443,7 @@
         <v>656</v>
       </c>
       <c r="AA9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="AE9" s="9" t="s">
         <v>658</v>
@@ -7199,8 +7453,8 @@
         <v>659</v>
       </c>
       <c r="AH9" s="9"/>
-      <c r="AI9" s="11" t="s">
-        <v>1390</v>
+      <c r="AI9" s="10" t="s">
+        <v>1396</v>
       </c>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9" t="s">
@@ -7226,21 +7480,21 @@
         <v>1330</v>
       </c>
       <c r="BE9" t="s">
+        <v>1390</v>
+      </c>
+      <c r="BG9" s="9" t="s">
         <v>1391</v>
       </c>
-      <c r="BG9" s="9" t="s">
-        <v>1392</v>
-      </c>
       <c r="BK9" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BL9" s="9"/>
       <c r="BM9" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BN9" s="9"/>
       <c r="BO9" s="9" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="BP9" s="9"/>
       <c r="BQ9" s="9" t="s">
@@ -7248,78 +7502,78 @@
       </c>
       <c r="BR9" s="9"/>
       <c r="BS9" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="BT9" s="9"/>
       <c r="BU9" s="9" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="BV9" s="9"/>
       <c r="BW9" s="9" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="BX9" s="9"/>
       <c r="BY9" s="9"/>
       <c r="BZ9" s="9"/>
       <c r="CA9" s="9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="CB9" s="9"/>
       <c r="CC9" s="9" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="CD9" s="9"/>
       <c r="CE9" s="9" t="s">
-        <v>1484</v>
-      </c>
-      <c r="CG9" s="20" t="s">
-        <v>1651</v>
-      </c>
-      <c r="CI9" s="20" t="s">
-        <v>1671</v>
-      </c>
-      <c r="CK9" s="20" t="s">
-        <v>1682</v>
-      </c>
-      <c r="CM9" s="20" t="s">
-        <v>1475</v>
-      </c>
-      <c r="CO9" s="20" t="s">
-        <v>1694</v>
-      </c>
-      <c r="CS9" s="29" t="s">
+        <v>1483</v>
+      </c>
+      <c r="CG9" s="19" t="s">
+        <v>1650</v>
+      </c>
+      <c r="CI9" s="19" t="s">
+        <v>1670</v>
+      </c>
+      <c r="CK9" s="19" t="s">
+        <v>1681</v>
+      </c>
+      <c r="CM9" s="19" t="s">
+        <v>1474</v>
+      </c>
+      <c r="CO9" s="19" t="s">
+        <v>1693</v>
+      </c>
+      <c r="CS9" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="27" t="s">
         <v>1729</v>
       </c>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="28" t="s">
+      <c r="CV9" s="27"/>
+      <c r="CW9" s="27"/>
+      <c r="CX9" s="27"/>
+      <c r="CY9" s="28" t="s">
         <v>1730</v>
       </c>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28"/>
-      <c r="CY9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DF9" s="28"/>
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DF9" s="27"/>
     </row>
     <row r="10" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="12"/>
@@ -7366,8 +7620,8 @@
         <v>667</v>
       </c>
       <c r="AH10" s="9"/>
-      <c r="AI10" s="11" t="s">
-        <v>1393</v>
+      <c r="AI10" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="AJ10" s="9"/>
       <c r="AK10" s="9" t="s">
@@ -7393,21 +7647,21 @@
         <v>1331</v>
       </c>
       <c r="BE10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BG10" s="9" t="s">
         <v>1394</v>
       </c>
-      <c r="BG10" s="9" t="s">
-        <v>1395</v>
-      </c>
       <c r="BK10" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BL10" s="9"/>
       <c r="BM10" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BN10" s="9"/>
       <c r="BO10" s="9" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="BP10" s="9"/>
       <c r="BQ10" s="9" t="s">
@@ -7419,7 +7673,7 @@
       <c r="BU10" s="9"/>
       <c r="BV10" s="9"/>
       <c r="BW10" s="9" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="BX10" s="9"/>
       <c r="BY10" s="9"/>
@@ -7435,43 +7689,43 @@
       <c r="CE10" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="CG10" s="20" t="s">
-        <v>1652</v>
-      </c>
-      <c r="CI10" s="20" t="s">
-        <v>1672</v>
-      </c>
-      <c r="CK10" s="20" t="s">
-        <v>1683</v>
-      </c>
-      <c r="CM10" s="20" t="s">
-        <v>1702</v>
-      </c>
-      <c r="CO10" s="20" t="s">
-        <v>1695</v>
-      </c>
-      <c r="CS10" s="28"/>
-      <c r="CT10" s="28"/>
-      <c r="CU10" s="28"/>
-      <c r="CV10" s="28"/>
-      <c r="CW10" s="28"/>
-      <c r="CX10" s="28"/>
-      <c r="CY10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="CZ10" s="29"/>
-      <c r="DA10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DB10" s="29"/>
-      <c r="DC10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DD10" s="29"/>
-      <c r="DE10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DF10" s="28"/>
+      <c r="CG10" s="19" t="s">
+        <v>1651</v>
+      </c>
+      <c r="CI10" s="19" t="s">
+        <v>1671</v>
+      </c>
+      <c r="CK10" s="19" t="s">
+        <v>1682</v>
+      </c>
+      <c r="CM10" s="19" t="s">
+        <v>1701</v>
+      </c>
+      <c r="CO10" s="19" t="s">
+        <v>1694</v>
+      </c>
+      <c r="CS10" s="27"/>
+      <c r="CT10" s="27"/>
+      <c r="CU10" s="27"/>
+      <c r="CV10" s="27"/>
+      <c r="CW10" s="27"/>
+      <c r="CX10" s="27"/>
+      <c r="CY10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="CZ10" s="28"/>
+      <c r="DA10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DB10" s="28"/>
+      <c r="DC10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DD10" s="28"/>
+      <c r="DE10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DF10" s="27"/>
     </row>
     <row r="11" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
@@ -7509,14 +7763,14 @@
         <v>671</v>
       </c>
       <c r="AA11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="AG11" s="9" t="s">
         <v>673</v>
       </c>
       <c r="AH11" s="9"/>
       <c r="AI11" s="10" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="AJ11" s="9"/>
       <c r="AK11" s="9" t="s">
@@ -7538,17 +7792,17 @@
         <v>671</v>
       </c>
       <c r="BE11" t="s">
+        <v>1397</v>
+      </c>
+      <c r="BG11" s="9" t="s">
         <v>1398</v>
       </c>
-      <c r="BG11" s="9" t="s">
-        <v>1399</v>
-      </c>
       <c r="BK11" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="BL11" s="9"/>
       <c r="BM11" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="BN11" s="9"/>
       <c r="BO11" s="9"/>
@@ -7562,61 +7816,61 @@
       <c r="BU11" s="9"/>
       <c r="BV11" s="9"/>
       <c r="BW11" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="BX11" s="9"/>
       <c r="BY11" s="9"/>
       <c r="BZ11" s="9"/>
       <c r="CA11" s="9" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="CB11" s="9"/>
       <c r="CC11" s="9"/>
       <c r="CD11" s="9"/>
       <c r="CE11" s="9" t="s">
-        <v>1490</v>
-      </c>
-      <c r="CG11" s="20" t="s">
-        <v>1653</v>
-      </c>
-      <c r="CI11" s="20" t="s">
-        <v>1673</v>
-      </c>
-      <c r="CM11" s="20" t="s">
-        <v>1703</v>
-      </c>
-      <c r="CO11" s="20" t="s">
-        <v>1696</v>
-      </c>
-      <c r="CS11" s="28"/>
-      <c r="CT11" s="28"/>
-      <c r="CU11" s="28"/>
-      <c r="CV11" s="28"/>
-      <c r="CW11" s="28"/>
-      <c r="CX11" s="28"/>
-      <c r="CY11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="CZ11" s="29"/>
-      <c r="DA11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DB11" s="29"/>
-      <c r="DC11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DD11" s="29"/>
-      <c r="DE11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DF11" s="28"/>
+        <v>1489</v>
+      </c>
+      <c r="CG11" s="19" t="s">
+        <v>1652</v>
+      </c>
+      <c r="CI11" s="19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="CM11" s="19" t="s">
+        <v>1702</v>
+      </c>
+      <c r="CO11" s="19" t="s">
+        <v>1695</v>
+      </c>
+      <c r="CS11" s="27"/>
+      <c r="CT11" s="27"/>
+      <c r="CU11" s="27"/>
+      <c r="CV11" s="27"/>
+      <c r="CW11" s="27"/>
+      <c r="CX11" s="27"/>
+      <c r="CY11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="CZ11" s="28"/>
+      <c r="DA11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DB11" s="28"/>
+      <c r="DC11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DD11" s="28"/>
+      <c r="DE11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DF11" s="27"/>
     </row>
     <row r="12" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D12" s="12"/>
@@ -7653,8 +7907,8 @@
         <v>680</v>
       </c>
       <c r="AH12" s="9"/>
-      <c r="AI12" s="10" t="s">
-        <v>1400</v>
+      <c r="AI12" s="11" t="s">
+        <v>1403</v>
       </c>
       <c r="AJ12" s="9"/>
       <c r="AK12" s="9" t="s">
@@ -7677,7 +7931,7 @@
         <v>678</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="BK12" s="9"/>
       <c r="BL12" s="9"/>
@@ -7694,7 +7948,7 @@
       <c r="BU12" s="9"/>
       <c r="BV12" s="9"/>
       <c r="BW12" s="9" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="BX12" s="9"/>
       <c r="BY12" s="9"/>
@@ -7706,37 +7960,37 @@
       <c r="CC12" s="9"/>
       <c r="CD12" s="9"/>
       <c r="CE12" s="9"/>
-      <c r="CG12" s="20" t="s">
-        <v>1654</v>
-      </c>
-      <c r="CI12" s="20" t="s">
-        <v>1674</v>
-      </c>
-      <c r="CO12" s="20" t="s">
-        <v>1697</v>
-      </c>
-      <c r="CS12" s="28"/>
-      <c r="CT12" s="28"/>
-      <c r="CU12" s="28"/>
-      <c r="CV12" s="28"/>
-      <c r="CW12" s="28"/>
-      <c r="CX12" s="28"/>
-      <c r="CY12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="CZ12" s="29"/>
-      <c r="DA12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DB12" s="29"/>
-      <c r="DC12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DD12" s="29"/>
-      <c r="DE12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DF12" s="28"/>
+      <c r="CG12" s="19" t="s">
+        <v>1653</v>
+      </c>
+      <c r="CI12" s="19" t="s">
+        <v>1673</v>
+      </c>
+      <c r="CO12" s="19" t="s">
+        <v>1696</v>
+      </c>
+      <c r="CS12" s="27"/>
+      <c r="CT12" s="27"/>
+      <c r="CU12" s="27"/>
+      <c r="CV12" s="27"/>
+      <c r="CW12" s="27"/>
+      <c r="CX12" s="27"/>
+      <c r="CY12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="CZ12" s="28"/>
+      <c r="DA12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DB12" s="28"/>
+      <c r="DC12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DD12" s="28"/>
+      <c r="DE12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DF12" s="27"/>
     </row>
     <row r="13" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
@@ -7779,7 +8033,7 @@
       </c>
       <c r="AH13" s="9"/>
       <c r="AI13" s="10" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="AJ13" s="9"/>
       <c r="AK13" t="s">
@@ -7800,7 +8054,7 @@
         <v>685</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="BK13" s="9"/>
       <c r="BL13" s="9"/>
@@ -7817,7 +8071,7 @@
       <c r="BU13" s="9"/>
       <c r="BV13" s="9"/>
       <c r="BW13" s="9" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="BX13" s="9"/>
       <c r="BY13" s="9"/>
@@ -7829,44 +8083,44 @@
       <c r="CC13" s="9"/>
       <c r="CD13" s="9"/>
       <c r="CE13" s="9"/>
-      <c r="CG13" s="20" t="s">
-        <v>1655</v>
-      </c>
-      <c r="CI13" s="20" t="s">
-        <v>1675</v>
-      </c>
-      <c r="CO13" s="20" t="s">
-        <v>1698</v>
-      </c>
-      <c r="CS13" s="28"/>
-      <c r="CT13" s="28"/>
-      <c r="CU13" s="28"/>
-      <c r="CV13" s="28"/>
-      <c r="CW13" s="28"/>
-      <c r="CX13" s="28"/>
-      <c r="CY13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="CZ13" s="29"/>
-      <c r="DA13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DB13" s="29"/>
-      <c r="DC13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DD13" s="29"/>
-      <c r="DE13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DF13" s="28"/>
+      <c r="CG13" s="19" t="s">
+        <v>1654</v>
+      </c>
+      <c r="CI13" s="19" t="s">
+        <v>1674</v>
+      </c>
+      <c r="CO13" s="19" t="s">
+        <v>1697</v>
+      </c>
+      <c r="CS13" s="27"/>
+      <c r="CT13" s="27"/>
+      <c r="CU13" s="27"/>
+      <c r="CV13" s="27"/>
+      <c r="CW13" s="27"/>
+      <c r="CX13" s="27"/>
+      <c r="CY13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="CZ13" s="28"/>
+      <c r="DA13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DB13" s="28"/>
+      <c r="DC13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DD13" s="28"/>
+      <c r="DE13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DF13" s="27"/>
     </row>
     <row r="14" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="20" t="s">
         <v>72</v>
       </c>
       <c r="D14" s="12"/>
@@ -7901,8 +8155,8 @@
         <v>694</v>
       </c>
       <c r="AH14" s="9"/>
-      <c r="AI14" s="11" t="s">
-        <v>1404</v>
+      <c r="AI14" s="10" t="s">
+        <v>1408</v>
       </c>
       <c r="AJ14" s="9"/>
       <c r="AK14" s="9" t="s">
@@ -7925,7 +8179,7 @@
         <v>692</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="BK14" s="9"/>
       <c r="BL14" s="9"/>
@@ -7942,7 +8196,7 @@
       <c r="BU14" s="9"/>
       <c r="BV14" s="9"/>
       <c r="BW14" s="9" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="BX14" s="9"/>
       <c r="BY14" s="9"/>
@@ -7954,37 +8208,37 @@
       <c r="CC14" s="9"/>
       <c r="CD14" s="9"/>
       <c r="CE14" s="9"/>
-      <c r="CG14" s="20" t="s">
-        <v>1656</v>
-      </c>
-      <c r="CI14" s="20" t="s">
-        <v>1676</v>
-      </c>
-      <c r="CO14" s="20" t="s">
+      <c r="CG14" s="19" t="s">
+        <v>1655</v>
+      </c>
+      <c r="CI14" s="19" t="s">
+        <v>1675</v>
+      </c>
+      <c r="CO14" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="CS14" s="28"/>
-      <c r="CT14" s="28"/>
-      <c r="CU14" s="28"/>
-      <c r="CV14" s="28"/>
-      <c r="CW14" s="28"/>
-      <c r="CX14" s="28"/>
-      <c r="CY14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="CZ14" s="29"/>
-      <c r="DA14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DB14" s="29"/>
-      <c r="DC14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DD14" s="29"/>
-      <c r="DE14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DF14" s="28"/>
+      <c r="CS14" s="27"/>
+      <c r="CT14" s="27"/>
+      <c r="CU14" s="27"/>
+      <c r="CV14" s="27"/>
+      <c r="CW14" s="27"/>
+      <c r="CX14" s="27"/>
+      <c r="CY14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="CZ14" s="28"/>
+      <c r="DA14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DB14" s="28"/>
+      <c r="DC14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DD14" s="28"/>
+      <c r="DE14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DF14" s="27"/>
     </row>
     <row r="15" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -8028,7 +8282,7 @@
       </c>
       <c r="AH15" s="9"/>
       <c r="AI15" s="10" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9" t="s">
@@ -8051,7 +8305,7 @@
         <v>698</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="BK15" s="9"/>
       <c r="BL15" s="9"/>
@@ -8068,7 +8322,7 @@
       <c r="BU15" s="9"/>
       <c r="BV15" s="9"/>
       <c r="BW15" s="9" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="BX15" s="9"/>
       <c r="BY15" s="9"/>
@@ -8080,41 +8334,41 @@
       <c r="CC15" s="9"/>
       <c r="CD15" s="9"/>
       <c r="CE15" s="9"/>
-      <c r="CG15" s="20" t="s">
-        <v>1657</v>
-      </c>
-      <c r="CI15" s="20" t="s">
-        <v>1677</v>
-      </c>
-      <c r="CS15" s="28"/>
-      <c r="CT15" s="28"/>
-      <c r="CU15" s="28"/>
-      <c r="CV15" s="28"/>
-      <c r="CW15" s="28"/>
-      <c r="CX15" s="28"/>
-      <c r="CY15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="CZ15" s="29"/>
-      <c r="DA15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DB15" s="29"/>
-      <c r="DC15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DD15" s="29"/>
-      <c r="DE15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DF15" s="28"/>
+      <c r="CG15" s="19" t="s">
+        <v>1656</v>
+      </c>
+      <c r="CI15" s="19" t="s">
+        <v>1676</v>
+      </c>
+      <c r="CS15" s="27"/>
+      <c r="CT15" s="27"/>
+      <c r="CU15" s="27"/>
+      <c r="CV15" s="27"/>
+      <c r="CW15" s="27"/>
+      <c r="CX15" s="27"/>
+      <c r="CY15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="CZ15" s="28"/>
+      <c r="DA15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DB15" s="28"/>
+      <c r="DC15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DD15" s="28"/>
+      <c r="DE15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DF15" s="27"/>
     </row>
     <row r="16" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="20" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="12"/>
@@ -8143,14 +8397,14 @@
         <v>704</v>
       </c>
       <c r="AA16" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="AG16" s="9" t="s">
         <v>705</v>
       </c>
       <c r="AH16" s="9"/>
       <c r="AI16" s="10" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="AJ16" s="9"/>
       <c r="AK16" t="s">
@@ -8171,7 +8425,7 @@
         <v>704</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="BK16" s="9"/>
       <c r="BL16" s="9"/>
@@ -8188,43 +8442,43 @@
       <c r="BU16" s="9"/>
       <c r="BV16" s="9"/>
       <c r="BW16" s="9" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="BX16" s="9"/>
       <c r="BY16" s="9"/>
       <c r="BZ16" s="9"/>
       <c r="CA16" s="9" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="CB16" s="9"/>
       <c r="CC16" s="9"/>
       <c r="CD16" s="9"/>
       <c r="CE16" s="9"/>
-      <c r="CG16" s="20" t="s">
-        <v>1658</v>
-      </c>
-      <c r="CS16" s="28"/>
-      <c r="CT16" s="28"/>
-      <c r="CU16" s="28"/>
-      <c r="CV16" s="28"/>
-      <c r="CW16" s="28"/>
-      <c r="CX16" s="28"/>
-      <c r="CY16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="CZ16" s="29"/>
-      <c r="DA16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DB16" s="29"/>
-      <c r="DC16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DD16" s="29"/>
-      <c r="DE16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DF16" s="28"/>
+      <c r="CG16" s="19" t="s">
+        <v>1657</v>
+      </c>
+      <c r="CS16" s="27"/>
+      <c r="CT16" s="27"/>
+      <c r="CU16" s="27"/>
+      <c r="CV16" s="27"/>
+      <c r="CW16" s="27"/>
+      <c r="CX16" s="27"/>
+      <c r="CY16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="CZ16" s="28"/>
+      <c r="DA16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DB16" s="28"/>
+      <c r="DC16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DD16" s="28"/>
+      <c r="DE16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DF16" s="27"/>
     </row>
     <row r="17" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
@@ -8267,7 +8521,7 @@
       </c>
       <c r="AH17" s="9"/>
       <c r="AI17" s="10" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9" t="s">
@@ -8290,7 +8544,7 @@
         <v>710</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="BK17" s="9"/>
       <c r="BL17" s="9"/>
@@ -8307,7 +8561,7 @@
       <c r="BU17" s="9"/>
       <c r="BV17" s="9"/>
       <c r="BW17" s="9" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="BX17" s="9"/>
       <c r="BY17" s="9"/>
@@ -8317,38 +8571,38 @@
       <c r="CC17" s="9"/>
       <c r="CD17" s="9"/>
       <c r="CE17" s="9"/>
-      <c r="CG17" s="20" t="s">
-        <v>1659</v>
-      </c>
-      <c r="CS17" s="28"/>
-      <c r="CT17" s="28"/>
-      <c r="CU17" s="28"/>
-      <c r="CV17" s="28"/>
-      <c r="CW17" s="28"/>
-      <c r="CX17" s="28"/>
-      <c r="CY17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="CZ17" s="29"/>
-      <c r="DA17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DB17" s="29"/>
-      <c r="DC17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DD17" s="29"/>
-      <c r="DE17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DF17" s="28"/>
+      <c r="CG17" s="19" t="s">
+        <v>1658</v>
+      </c>
+      <c r="CS17" s="27"/>
+      <c r="CT17" s="27"/>
+      <c r="CU17" s="27"/>
+      <c r="CV17" s="27"/>
+      <c r="CW17" s="27"/>
+      <c r="CX17" s="27"/>
+      <c r="CY17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="CZ17" s="28"/>
+      <c r="DA17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DB17" s="28"/>
+      <c r="DC17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DD17" s="28"/>
+      <c r="DE17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DF17" s="27"/>
     </row>
     <row r="18" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>92</v>
       </c>
       <c r="D18" s="12"/>
@@ -8384,7 +8638,7 @@
       </c>
       <c r="AH18" s="9"/>
       <c r="AI18" s="10" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" t="s">
@@ -8406,7 +8660,7 @@
         <v>715</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="BK18" s="9"/>
       <c r="BL18" s="9"/>
@@ -8423,7 +8677,7 @@
       <c r="BU18" s="9"/>
       <c r="BV18" s="9"/>
       <c r="BW18" s="9" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="BX18" s="9"/>
       <c r="BY18" s="9"/>
@@ -8433,31 +8687,31 @@
       <c r="CC18" s="9"/>
       <c r="CD18" s="9"/>
       <c r="CE18" s="9"/>
-      <c r="CG18" s="20" t="s">
-        <v>1660</v>
-      </c>
-      <c r="CS18" s="28"/>
-      <c r="CT18" s="28"/>
-      <c r="CU18" s="28"/>
-      <c r="CV18" s="28"/>
-      <c r="CW18" s="28"/>
-      <c r="CX18" s="28"/>
-      <c r="CY18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="CZ18" s="29"/>
-      <c r="DA18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DB18" s="29"/>
-      <c r="DC18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DD18" s="29"/>
-      <c r="DE18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DF18" s="28"/>
+      <c r="CG18" s="19" t="s">
+        <v>1659</v>
+      </c>
+      <c r="CS18" s="27"/>
+      <c r="CT18" s="27"/>
+      <c r="CU18" s="27"/>
+      <c r="CV18" s="27"/>
+      <c r="CW18" s="27"/>
+      <c r="CX18" s="27"/>
+      <c r="CY18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="CZ18" s="28"/>
+      <c r="DA18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DB18" s="28"/>
+      <c r="DC18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DD18" s="28"/>
+      <c r="DE18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DF18" s="27"/>
     </row>
     <row r="19" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
@@ -8500,7 +8754,7 @@
       </c>
       <c r="AH19" s="9"/>
       <c r="AI19" s="10" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="AJ19" s="9"/>
       <c r="AK19" s="9" t="s">
@@ -8522,7 +8776,7 @@
         <v>720</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="BK19" s="9"/>
       <c r="BL19" s="9"/>
@@ -8539,7 +8793,7 @@
       <c r="BU19" s="9"/>
       <c r="BV19" s="9"/>
       <c r="BW19" s="9" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="BX19" s="9"/>
       <c r="BY19" s="9"/>
@@ -8549,38 +8803,38 @@
       <c r="CC19" s="9"/>
       <c r="CD19" s="9"/>
       <c r="CE19" s="9"/>
-      <c r="CG19" s="20" t="s">
-        <v>1661</v>
-      </c>
-      <c r="CS19" s="28"/>
-      <c r="CT19" s="28"/>
-      <c r="CU19" s="28"/>
-      <c r="CV19" s="28"/>
-      <c r="CW19" s="28"/>
-      <c r="CX19" s="28"/>
-      <c r="CY19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="CZ19" s="29"/>
-      <c r="DA19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DB19" s="29"/>
-      <c r="DC19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DD19" s="29"/>
-      <c r="DE19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DF19" s="28"/>
+      <c r="CG19" s="19" t="s">
+        <v>1660</v>
+      </c>
+      <c r="CS19" s="27"/>
+      <c r="CT19" s="27"/>
+      <c r="CU19" s="27"/>
+      <c r="CV19" s="27"/>
+      <c r="CW19" s="27"/>
+      <c r="CX19" s="27"/>
+      <c r="CY19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="CZ19" s="28"/>
+      <c r="DA19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DB19" s="28"/>
+      <c r="DC19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DD19" s="28"/>
+      <c r="DE19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DF19" s="27"/>
     </row>
     <row r="20" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>100</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="20" t="s">
         <v>101</v>
       </c>
       <c r="D20" s="12"/>
@@ -8616,7 +8870,7 @@
       </c>
       <c r="AH20" s="9"/>
       <c r="AI20" s="10" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="AJ20" s="9"/>
       <c r="AK20" t="s">
@@ -8651,7 +8905,7 @@
       <c r="BU20" s="9"/>
       <c r="BV20" s="9"/>
       <c r="BW20" s="9" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="BX20" s="9"/>
       <c r="BY20" s="9"/>
@@ -8661,31 +8915,31 @@
       <c r="CC20" s="9"/>
       <c r="CD20" s="9"/>
       <c r="CE20" s="9"/>
-      <c r="CG20" s="20" t="s">
-        <v>1662</v>
-      </c>
-      <c r="CS20" s="28"/>
-      <c r="CT20" s="28"/>
-      <c r="CU20" s="28"/>
-      <c r="CV20" s="28"/>
-      <c r="CW20" s="28"/>
-      <c r="CX20" s="28"/>
-      <c r="CY20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="CZ20" s="29"/>
-      <c r="DA20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DB20" s="29"/>
-      <c r="DC20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DD20" s="29"/>
-      <c r="DE20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DF20" s="28"/>
+      <c r="CG20" s="19" t="s">
+        <v>1661</v>
+      </c>
+      <c r="CS20" s="27"/>
+      <c r="CT20" s="27"/>
+      <c r="CU20" s="27"/>
+      <c r="CV20" s="27"/>
+      <c r="CW20" s="27"/>
+      <c r="CX20" s="27"/>
+      <c r="CY20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="CZ20" s="28"/>
+      <c r="DA20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DB20" s="28"/>
+      <c r="DC20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DD20" s="28"/>
+      <c r="DE20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DF20" s="27"/>
     </row>
     <row r="21" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
@@ -8726,7 +8980,7 @@
       </c>
       <c r="AH21" s="9"/>
       <c r="AI21" s="10" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9" t="s">
@@ -8763,7 +9017,7 @@
       <c r="BU21" s="9"/>
       <c r="BV21" s="9"/>
       <c r="BW21" s="9" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="BX21" s="9"/>
       <c r="BY21" s="9"/>
@@ -8773,38 +9027,38 @@
       <c r="CC21" s="9"/>
       <c r="CD21" s="9"/>
       <c r="CE21" s="9"/>
-      <c r="CG21" s="20" t="s">
-        <v>1663</v>
-      </c>
-      <c r="CS21" s="28"/>
-      <c r="CT21" s="28"/>
-      <c r="CU21" s="28"/>
-      <c r="CV21" s="28"/>
-      <c r="CW21" s="28"/>
-      <c r="CX21" s="28"/>
-      <c r="CY21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="CZ21" s="29"/>
-      <c r="DA21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DB21" s="29"/>
-      <c r="DC21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DD21" s="29"/>
-      <c r="DE21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DF21" s="28"/>
+      <c r="CG21" s="19" t="s">
+        <v>1662</v>
+      </c>
+      <c r="CS21" s="27"/>
+      <c r="CT21" s="27"/>
+      <c r="CU21" s="27"/>
+      <c r="CV21" s="27"/>
+      <c r="CW21" s="27"/>
+      <c r="CX21" s="27"/>
+      <c r="CY21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CZ21" s="28"/>
+      <c r="DA21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DB21" s="28"/>
+      <c r="DC21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DD21" s="28"/>
+      <c r="DE21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DF21" s="27"/>
     </row>
     <row r="22" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>109</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="12"/>
@@ -8835,7 +9089,7 @@
       </c>
       <c r="AH22" s="9"/>
       <c r="AI22" s="10" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="AJ22" s="9"/>
       <c r="AK22" s="9" t="s">
@@ -8871,7 +9125,7 @@
       <c r="BU22" s="9"/>
       <c r="BV22" s="9"/>
       <c r="BW22" s="9" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="BX22" s="9"/>
       <c r="BY22" s="9"/>
@@ -8881,28 +9135,28 @@
       <c r="CC22" s="9"/>
       <c r="CD22" s="9"/>
       <c r="CE22" s="9"/>
-      <c r="CS22" s="28"/>
-      <c r="CT22" s="28"/>
-      <c r="CU22" s="28"/>
-      <c r="CV22" s="28"/>
-      <c r="CW22" s="28"/>
-      <c r="CX22" s="28"/>
-      <c r="CY22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="CZ22" s="29"/>
-      <c r="DA22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DB22" s="29"/>
-      <c r="DC22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DD22" s="29"/>
-      <c r="DE22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DF22" s="28"/>
+      <c r="CS22" s="27"/>
+      <c r="CT22" s="27"/>
+      <c r="CU22" s="27"/>
+      <c r="CV22" s="27"/>
+      <c r="CW22" s="27"/>
+      <c r="CX22" s="27"/>
+      <c r="CY22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="CZ22" s="28"/>
+      <c r="DA22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DB22" s="28"/>
+      <c r="DC22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DD22" s="28"/>
+      <c r="DE22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DF22" s="27"/>
     </row>
     <row r="23" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
@@ -8937,7 +9191,7 @@
       </c>
       <c r="AH23" s="9"/>
       <c r="AI23" s="10" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="AJ23" s="9"/>
       <c r="AK23" t="s">
@@ -8968,7 +9222,7 @@
       <c r="BU23" s="9"/>
       <c r="BV23" s="9"/>
       <c r="BW23" s="9" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="BX23" s="9"/>
       <c r="BY23" s="9"/>
@@ -8978,35 +9232,35 @@
       <c r="CC23" s="9"/>
       <c r="CD23" s="9"/>
       <c r="CE23" s="9"/>
-      <c r="CS23" s="28"/>
-      <c r="CT23" s="28"/>
-      <c r="CU23" s="28"/>
-      <c r="CV23" s="28"/>
-      <c r="CW23" s="28"/>
-      <c r="CX23" s="28"/>
-      <c r="CY23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="CZ23" s="29"/>
-      <c r="DA23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DB23" s="29"/>
-      <c r="DC23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DD23" s="29"/>
-      <c r="DE23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DF23" s="28"/>
+      <c r="CS23" s="27"/>
+      <c r="CT23" s="27"/>
+      <c r="CU23" s="27"/>
+      <c r="CV23" s="27"/>
+      <c r="CW23" s="27"/>
+      <c r="CX23" s="27"/>
+      <c r="CY23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="CZ23" s="28"/>
+      <c r="DA23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DB23" s="28"/>
+      <c r="DC23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DD23" s="28"/>
+      <c r="DE23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DF23" s="27"/>
     </row>
     <row r="24" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>118</v>
       </c>
       <c r="D24" s="12"/>
@@ -9034,7 +9288,7 @@
       </c>
       <c r="AH24" s="9"/>
       <c r="AI24" s="10" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="AJ24" s="9"/>
       <c r="AK24" t="s">
@@ -9061,7 +9315,7 @@
       <c r="BU24" s="9"/>
       <c r="BV24" s="9"/>
       <c r="BW24" s="9" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="BX24" s="9"/>
       <c r="BY24" s="9"/>
@@ -9071,28 +9325,28 @@
       <c r="CC24" s="9"/>
       <c r="CD24" s="9"/>
       <c r="CE24" s="9"/>
-      <c r="CS24" s="28"/>
-      <c r="CT24" s="28"/>
-      <c r="CU24" s="28"/>
-      <c r="CV24" s="28"/>
-      <c r="CW24" s="28"/>
-      <c r="CX24" s="28"/>
-      <c r="CY24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="CZ24" s="29"/>
-      <c r="DA24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DB24" s="29"/>
-      <c r="DC24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DD24" s="29"/>
-      <c r="DE24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DF24" s="28"/>
+      <c r="CS24" s="27"/>
+      <c r="CT24" s="27"/>
+      <c r="CU24" s="27"/>
+      <c r="CV24" s="27"/>
+      <c r="CW24" s="27"/>
+      <c r="CX24" s="27"/>
+      <c r="CY24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="CZ24" s="28"/>
+      <c r="DA24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DB24" s="28"/>
+      <c r="DC24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DD24" s="28"/>
+      <c r="DE24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DF24" s="27"/>
     </row>
     <row r="25" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
@@ -9127,7 +9381,7 @@
       </c>
       <c r="AH25" s="9"/>
       <c r="AI25" s="10" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="AJ25" s="9"/>
       <c r="AK25" t="s">
@@ -9165,35 +9419,35 @@
       <c r="CC25" s="9"/>
       <c r="CD25" s="9"/>
       <c r="CE25" s="9"/>
-      <c r="CS25" s="28"/>
-      <c r="CT25" s="28"/>
-      <c r="CU25" s="28"/>
-      <c r="CV25" s="28"/>
-      <c r="CW25" s="28"/>
-      <c r="CX25" s="28"/>
-      <c r="CY25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="CZ25" s="29"/>
-      <c r="DA25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DB25" s="29"/>
-      <c r="DC25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DD25" s="29"/>
-      <c r="DE25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DF25" s="28"/>
+      <c r="CS25" s="27"/>
+      <c r="CT25" s="27"/>
+      <c r="CU25" s="27"/>
+      <c r="CV25" s="27"/>
+      <c r="CW25" s="27"/>
+      <c r="CX25" s="27"/>
+      <c r="CY25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="CZ25" s="28"/>
+      <c r="DA25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DB25" s="28"/>
+      <c r="DC25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DD25" s="28"/>
+      <c r="DE25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DF25" s="27"/>
     </row>
     <row r="26" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D26" s="12"/>
@@ -9221,7 +9475,7 @@
       </c>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10" t="s">
-        <v>1423</v>
+        <v>748</v>
       </c>
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9" t="s">
@@ -9250,7 +9504,7 @@
       <c r="BU26" s="9"/>
       <c r="BV26" s="9"/>
       <c r="BW26" s="9" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="BX26" s="9"/>
       <c r="BY26" s="9"/>
@@ -9260,28 +9514,28 @@
       <c r="CC26" s="9"/>
       <c r="CD26" s="9"/>
       <c r="CE26" s="9"/>
-      <c r="CS26" s="28"/>
-      <c r="CT26" s="28"/>
-      <c r="CU26" s="29"/>
-      <c r="CV26" s="29"/>
-      <c r="CW26" s="28"/>
-      <c r="CX26" s="28"/>
-      <c r="CY26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="CZ26" s="29"/>
-      <c r="DA26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DB26" s="29"/>
-      <c r="DC26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DD26" s="29"/>
-      <c r="DE26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DF26" s="28"/>
+      <c r="CS26" s="27"/>
+      <c r="CT26" s="27"/>
+      <c r="CU26" s="28"/>
+      <c r="CV26" s="28"/>
+      <c r="CW26" s="27"/>
+      <c r="CX26" s="27"/>
+      <c r="CY26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="CZ26" s="28"/>
+      <c r="DA26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DB26" s="28"/>
+      <c r="DC26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DD26" s="28"/>
+      <c r="DE26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DF26" s="27"/>
     </row>
     <row r="27" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
@@ -9343,7 +9597,7 @@
       <c r="BU27" s="9"/>
       <c r="BV27" s="9"/>
       <c r="BW27" s="9" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="BX27" s="9"/>
       <c r="BY27" s="9"/>
@@ -9353,35 +9607,35 @@
       <c r="CC27" s="9"/>
       <c r="CD27" s="9"/>
       <c r="CE27" s="9"/>
-      <c r="CS27" s="28"/>
-      <c r="CT27" s="28"/>
-      <c r="CU27" s="29"/>
-      <c r="CV27" s="29"/>
-      <c r="CW27" s="28"/>
-      <c r="CX27" s="28"/>
-      <c r="CY27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="CZ27" s="29"/>
-      <c r="DA27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DB27" s="29"/>
-      <c r="DC27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DD27" s="29"/>
-      <c r="DE27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DF27" s="28"/>
+      <c r="CS27" s="27"/>
+      <c r="CT27" s="27"/>
+      <c r="CU27" s="28"/>
+      <c r="CV27" s="28"/>
+      <c r="CW27" s="27"/>
+      <c r="CX27" s="27"/>
+      <c r="CY27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="CZ27" s="28"/>
+      <c r="DA27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DB27" s="28"/>
+      <c r="DC27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DD27" s="28"/>
+      <c r="DE27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DF27" s="27"/>
     </row>
     <row r="28" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B28" s="12"/>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="20" t="s">
         <v>134</v>
       </c>
       <c r="D28" s="12"/>
@@ -9409,7 +9663,7 @@
       </c>
       <c r="AH28" s="9"/>
       <c r="AI28" s="10" t="s">
-        <v>748</v>
+        <v>1425</v>
       </c>
       <c r="AK28" s="9" t="s">
         <v>764</v>
@@ -9436,7 +9690,7 @@
       <c r="BU28" s="9"/>
       <c r="BV28" s="9"/>
       <c r="BW28" s="9" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="BX28" s="9"/>
       <c r="BY28" s="9"/>
@@ -9446,28 +9700,28 @@
       <c r="CC28" s="9"/>
       <c r="CD28" s="9"/>
       <c r="CE28" s="9"/>
-      <c r="CS28" s="28"/>
-      <c r="CT28" s="28"/>
-      <c r="CU28" s="29"/>
-      <c r="CV28" s="29"/>
-      <c r="CW28" s="28"/>
-      <c r="CX28" s="28"/>
-      <c r="CY28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="CZ28" s="29"/>
-      <c r="DA28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DB28" s="29"/>
-      <c r="DC28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DD28" s="29"/>
-      <c r="DE28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DF28" s="28"/>
+      <c r="CS28" s="27"/>
+      <c r="CT28" s="27"/>
+      <c r="CU28" s="28"/>
+      <c r="CV28" s="28"/>
+      <c r="CW28" s="27"/>
+      <c r="CX28" s="27"/>
+      <c r="CY28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="CZ28" s="28"/>
+      <c r="DA28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DB28" s="28"/>
+      <c r="DC28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DD28" s="28"/>
+      <c r="DE28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DF28" s="27"/>
     </row>
     <row r="29" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
@@ -9502,7 +9756,7 @@
       </c>
       <c r="AH29" s="9"/>
       <c r="AI29" s="10" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="AK29" t="s">
         <v>768</v>
@@ -9528,7 +9782,7 @@
       <c r="BU29" s="9"/>
       <c r="BV29" s="9"/>
       <c r="BW29" s="9" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="BX29" s="9"/>
       <c r="BY29" s="9"/>
@@ -9538,35 +9792,35 @@
       <c r="CC29" s="9"/>
       <c r="CD29" s="9"/>
       <c r="CE29" s="9"/>
-      <c r="CS29" s="28"/>
-      <c r="CT29" s="28"/>
-      <c r="CU29" s="28"/>
-      <c r="CV29" s="28"/>
-      <c r="CW29" s="28"/>
-      <c r="CX29" s="28"/>
-      <c r="CY29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="CZ29" s="29"/>
-      <c r="DA29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DB29" s="29"/>
-      <c r="DC29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DD29" s="29"/>
-      <c r="DE29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DF29" s="28"/>
+      <c r="CS29" s="27"/>
+      <c r="CT29" s="27"/>
+      <c r="CU29" s="27"/>
+      <c r="CV29" s="27"/>
+      <c r="CW29" s="27"/>
+      <c r="CX29" s="27"/>
+      <c r="CY29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="CZ29" s="28"/>
+      <c r="DA29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DB29" s="28"/>
+      <c r="DC29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DD29" s="28"/>
+      <c r="DE29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DF29" s="27"/>
     </row>
     <row r="30" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="12"/>
@@ -9593,8 +9847,8 @@
         <v>770</v>
       </c>
       <c r="AH30" s="9"/>
-      <c r="AI30" s="10" t="s">
-        <v>1426</v>
+      <c r="AI30" s="11" t="s">
+        <v>1427</v>
       </c>
       <c r="AK30" s="9" t="s">
         <v>771</v>
@@ -9621,7 +9875,7 @@
       <c r="BU30" s="9"/>
       <c r="BV30" s="9"/>
       <c r="BW30" s="9" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="BX30" s="9"/>
       <c r="BY30" s="9"/>
@@ -9631,28 +9885,28 @@
       <c r="CC30" s="9"/>
       <c r="CD30" s="9"/>
       <c r="CE30" s="9"/>
-      <c r="CS30" s="28"/>
-      <c r="CT30" s="28"/>
-      <c r="CU30" s="28"/>
-      <c r="CV30" s="28"/>
-      <c r="CW30" s="28"/>
-      <c r="CX30" s="28"/>
-      <c r="CY30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="CZ30" s="29"/>
-      <c r="DA30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DB30" s="29"/>
-      <c r="DC30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DD30" s="29"/>
-      <c r="DE30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DF30" s="28"/>
+      <c r="CS30" s="27"/>
+      <c r="CT30" s="27"/>
+      <c r="CU30" s="27"/>
+      <c r="CV30" s="27"/>
+      <c r="CW30" s="27"/>
+      <c r="CX30" s="27"/>
+      <c r="CY30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="CZ30" s="28"/>
+      <c r="DA30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DB30" s="28"/>
+      <c r="DC30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DD30" s="28"/>
+      <c r="DE30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DF30" s="27"/>
     </row>
     <row r="31" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="14" t="s">
@@ -9687,7 +9941,7 @@
       </c>
       <c r="AH31" s="9"/>
       <c r="AI31" s="10" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="AK31" s="9" t="s">
         <v>775</v>
@@ -9715,7 +9969,7 @@
       <c r="BU31" s="9"/>
       <c r="BV31" s="9"/>
       <c r="BW31" s="9" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="BX31" s="9"/>
       <c r="BY31" s="9"/>
@@ -9725,35 +9979,35 @@
       <c r="CC31" s="9"/>
       <c r="CD31" s="9"/>
       <c r="CE31" s="9"/>
-      <c r="CS31" s="28"/>
-      <c r="CT31" s="28"/>
-      <c r="CU31" s="28"/>
-      <c r="CV31" s="28"/>
-      <c r="CW31" s="28"/>
-      <c r="CX31" s="28"/>
-      <c r="CY31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="CZ31" s="29"/>
-      <c r="DA31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DB31" s="29"/>
-      <c r="DC31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DD31" s="29"/>
-      <c r="DE31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DF31" s="28"/>
+      <c r="CS31" s="27"/>
+      <c r="CT31" s="27"/>
+      <c r="CU31" s="27"/>
+      <c r="CV31" s="27"/>
+      <c r="CW31" s="27"/>
+      <c r="CX31" s="27"/>
+      <c r="CY31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="CZ31" s="28"/>
+      <c r="DA31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DB31" s="28"/>
+      <c r="DC31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DD31" s="28"/>
+      <c r="DE31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DF31" s="27"/>
     </row>
     <row r="32" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="20" t="s">
         <v>149</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>150</v>
       </c>
       <c r="D32" s="12"/>
@@ -9780,8 +10034,8 @@
         <v>777</v>
       </c>
       <c r="AH32" s="9"/>
-      <c r="AI32" s="11" t="s">
-        <v>1428</v>
+      <c r="AI32" s="9" t="s">
+        <v>1774</v>
       </c>
       <c r="AK32" t="s">
         <v>778</v>
@@ -9808,7 +10062,7 @@
       <c r="BU32" s="9"/>
       <c r="BV32" s="9"/>
       <c r="BW32" s="9" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="BX32" s="9"/>
       <c r="BY32" s="9"/>
@@ -9818,28 +10072,28 @@
       <c r="CC32" s="9"/>
       <c r="CD32" s="9"/>
       <c r="CE32" s="9"/>
-      <c r="CS32" s="28"/>
-      <c r="CT32" s="28"/>
-      <c r="CU32" s="28"/>
-      <c r="CV32" s="28"/>
-      <c r="CW32" s="28"/>
-      <c r="CX32" s="28"/>
-      <c r="CY32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="CZ32" s="29"/>
-      <c r="DA32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DB32" s="29"/>
-      <c r="DC32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DD32" s="29"/>
-      <c r="DE32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DF32" s="28"/>
+      <c r="CS32" s="27"/>
+      <c r="CT32" s="27"/>
+      <c r="CU32" s="27"/>
+      <c r="CV32" s="27"/>
+      <c r="CW32" s="27"/>
+      <c r="CX32" s="27"/>
+      <c r="CY32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="CZ32" s="28"/>
+      <c r="DA32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DB32" s="28"/>
+      <c r="DC32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DD32" s="28"/>
+      <c r="DE32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DF32" s="27"/>
     </row>
     <row r="33" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
@@ -9873,8 +10127,8 @@
         <v>780</v>
       </c>
       <c r="AH33" s="9"/>
-      <c r="AI33" s="10" t="s">
-        <v>1429</v>
+      <c r="AI33" s="9" t="s">
+        <v>1775</v>
       </c>
       <c r="AK33" s="9" t="s">
         <v>781</v>
@@ -9901,7 +10155,7 @@
       <c r="BU33" s="9"/>
       <c r="BV33" s="9"/>
       <c r="BW33" s="9" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="BX33" s="9"/>
       <c r="BY33" s="9"/>
@@ -9911,35 +10165,35 @@
       <c r="CC33" s="9"/>
       <c r="CD33" s="9"/>
       <c r="CE33" s="9"/>
-      <c r="CS33" s="28"/>
-      <c r="CT33" s="28"/>
-      <c r="CU33" s="28"/>
-      <c r="CV33" s="28"/>
-      <c r="CW33" s="28"/>
-      <c r="CX33" s="28"/>
-      <c r="CY33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="CZ33" s="29"/>
-      <c r="DA33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DB33" s="29"/>
-      <c r="DC33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DD33" s="29"/>
-      <c r="DE33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DF33" s="28"/>
+      <c r="CS33" s="27"/>
+      <c r="CT33" s="27"/>
+      <c r="CU33" s="27"/>
+      <c r="CV33" s="27"/>
+      <c r="CW33" s="27"/>
+      <c r="CX33" s="27"/>
+      <c r="CY33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="CZ33" s="28"/>
+      <c r="DA33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DB33" s="28"/>
+      <c r="DC33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DD33" s="28"/>
+      <c r="DE33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DF33" s="27"/>
     </row>
     <row r="34" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="20" t="s">
         <v>157</v>
       </c>
       <c r="B34" s="12"/>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="20" t="s">
         <v>158</v>
       </c>
       <c r="D34" s="12"/>
@@ -9966,8 +10220,8 @@
         <v>783</v>
       </c>
       <c r="AH34" s="9"/>
-      <c r="AI34" s="10" t="s">
-        <v>1430</v>
+      <c r="AI34" s="9" t="s">
+        <v>1776</v>
       </c>
       <c r="AK34" s="9" t="s">
         <v>784</v>
@@ -9995,7 +10249,7 @@
       <c r="BU34" s="9"/>
       <c r="BV34" s="9"/>
       <c r="BW34" s="9" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="BX34" s="9"/>
       <c r="BY34" s="9"/>
@@ -10005,28 +10259,28 @@
       <c r="CC34" s="9"/>
       <c r="CD34" s="9"/>
       <c r="CE34" s="9"/>
-      <c r="CS34" s="28"/>
-      <c r="CT34" s="28"/>
-      <c r="CU34" s="28"/>
-      <c r="CV34" s="28"/>
-      <c r="CW34" s="28"/>
-      <c r="CX34" s="28"/>
-      <c r="CY34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="CZ34" s="29"/>
-      <c r="DA34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DB34" s="29"/>
-      <c r="DC34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DD34" s="29"/>
-      <c r="DE34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DF34" s="28"/>
+      <c r="CS34" s="27"/>
+      <c r="CT34" s="27"/>
+      <c r="CU34" s="27"/>
+      <c r="CV34" s="27"/>
+      <c r="CW34" s="27"/>
+      <c r="CX34" s="27"/>
+      <c r="CY34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="CZ34" s="28"/>
+      <c r="DA34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DB34" s="28"/>
+      <c r="DC34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DD34" s="28"/>
+      <c r="DE34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DF34" s="27"/>
     </row>
     <row r="35" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="14" t="s">
@@ -10060,6 +10314,9 @@
         <v>786</v>
       </c>
       <c r="AH35" s="9"/>
+      <c r="AI35" s="31" t="s">
+        <v>1777</v>
+      </c>
       <c r="AK35" s="9" t="s">
         <v>787</v>
       </c>
@@ -10086,7 +10343,7 @@
       <c r="BU35" s="9"/>
       <c r="BV35" s="9"/>
       <c r="BW35" s="9" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="BX35" s="9"/>
       <c r="BY35" s="9"/>
@@ -10096,35 +10353,35 @@
       <c r="CC35" s="9"/>
       <c r="CD35" s="9"/>
       <c r="CE35" s="9"/>
-      <c r="CS35" s="28"/>
-      <c r="CT35" s="28"/>
-      <c r="CU35" s="28"/>
-      <c r="CV35" s="28"/>
-      <c r="CW35" s="28"/>
-      <c r="CX35" s="28"/>
-      <c r="CY35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="CZ35" s="29"/>
-      <c r="DA35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DB35" s="29"/>
-      <c r="DC35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DD35" s="29"/>
-      <c r="DE35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DF35" s="28"/>
+      <c r="CS35" s="27"/>
+      <c r="CT35" s="27"/>
+      <c r="CU35" s="27"/>
+      <c r="CV35" s="27"/>
+      <c r="CW35" s="27"/>
+      <c r="CX35" s="27"/>
+      <c r="CY35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="CZ35" s="28"/>
+      <c r="DA35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DB35" s="28"/>
+      <c r="DC35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DD35" s="28"/>
+      <c r="DE35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DF35" s="27"/>
     </row>
     <row r="36" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="20" t="s">
         <v>165</v>
       </c>
       <c r="B36" s="12"/>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="20" t="s">
         <v>166</v>
       </c>
       <c r="D36" s="12"/>
@@ -10147,6 +10404,9 @@
         <v>790</v>
       </c>
       <c r="AH36" s="9"/>
+      <c r="AI36" s="9" t="s">
+        <v>1778</v>
+      </c>
       <c r="AK36" s="9" t="s">
         <v>791</v>
       </c>
@@ -10173,7 +10433,7 @@
       <c r="BU36" s="9"/>
       <c r="BV36" s="9"/>
       <c r="BW36" s="9" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="BX36" s="9"/>
       <c r="BY36" s="9"/>
@@ -10183,28 +10443,28 @@
       <c r="CC36" s="9"/>
       <c r="CD36" s="9"/>
       <c r="CE36" s="9"/>
-      <c r="CS36" s="28"/>
-      <c r="CT36" s="28"/>
-      <c r="CU36" s="28"/>
-      <c r="CV36" s="28"/>
-      <c r="CW36" s="28"/>
-      <c r="CX36" s="28"/>
-      <c r="CY36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="CZ36" s="29"/>
-      <c r="DA36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DB36" s="29"/>
-      <c r="DC36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DD36" s="29"/>
-      <c r="DE36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DF36" s="28"/>
+      <c r="CS36" s="27"/>
+      <c r="CT36" s="27"/>
+      <c r="CU36" s="27"/>
+      <c r="CV36" s="27"/>
+      <c r="CW36" s="27"/>
+      <c r="CX36" s="27"/>
+      <c r="CY36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="CZ36" s="28"/>
+      <c r="DA36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DB36" s="28"/>
+      <c r="DC36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DD36" s="28"/>
+      <c r="DE36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DF36" s="27"/>
     </row>
     <row r="37" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
@@ -10234,6 +10494,9 @@
         <v>793</v>
       </c>
       <c r="AH37" s="9"/>
+      <c r="AI37" s="9" t="s">
+        <v>1779</v>
+      </c>
       <c r="AK37" t="s">
         <v>794</v>
       </c>
@@ -10258,7 +10521,7 @@
       <c r="BU37" s="9"/>
       <c r="BV37" s="9"/>
       <c r="BW37" s="9" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="BX37" s="9"/>
       <c r="BY37" s="9"/>
@@ -10268,35 +10531,35 @@
       <c r="CC37" s="9"/>
       <c r="CD37" s="9"/>
       <c r="CE37" s="9"/>
-      <c r="CS37" s="28"/>
-      <c r="CT37" s="28"/>
-      <c r="CU37" s="28"/>
-      <c r="CV37" s="28"/>
-      <c r="CW37" s="28"/>
-      <c r="CX37" s="28"/>
-      <c r="CY37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="CZ37" s="29"/>
-      <c r="DA37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DB37" s="29"/>
-      <c r="DC37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DD37" s="29"/>
-      <c r="DE37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DF37" s="28"/>
+      <c r="CS37" s="27"/>
+      <c r="CT37" s="27"/>
+      <c r="CU37" s="27"/>
+      <c r="CV37" s="27"/>
+      <c r="CW37" s="27"/>
+      <c r="CX37" s="27"/>
+      <c r="CY37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="CZ37" s="28"/>
+      <c r="DA37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DB37" s="28"/>
+      <c r="DC37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DD37" s="28"/>
+      <c r="DE37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DF37" s="27"/>
     </row>
     <row r="38" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="20" t="s">
         <v>169</v>
       </c>
       <c r="B38" s="12"/>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="20" t="s">
         <v>170</v>
       </c>
       <c r="D38" s="12"/>
@@ -10319,6 +10582,9 @@
         <v>796</v>
       </c>
       <c r="AH38" s="9"/>
+      <c r="AI38" s="9" t="s">
+        <v>1780</v>
+      </c>
       <c r="AK38" s="9" t="s">
         <v>797</v>
       </c>
@@ -10345,7 +10611,7 @@
       <c r="BU38" s="9"/>
       <c r="BV38" s="9"/>
       <c r="BW38" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="BX38" s="9"/>
       <c r="BY38" s="9"/>
@@ -10355,28 +10621,28 @@
       <c r="CC38" s="9"/>
       <c r="CD38" s="9"/>
       <c r="CE38" s="9"/>
-      <c r="CS38" s="28"/>
-      <c r="CT38" s="28"/>
-      <c r="CU38" s="28"/>
-      <c r="CV38" s="28"/>
-      <c r="CW38" s="28"/>
-      <c r="CX38" s="28"/>
-      <c r="CY38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="CZ38" s="29"/>
-      <c r="DA38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DB38" s="29"/>
-      <c r="DC38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DD38" s="29"/>
-      <c r="DE38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DF38" s="28"/>
+      <c r="CS38" s="27"/>
+      <c r="CT38" s="27"/>
+      <c r="CU38" s="27"/>
+      <c r="CV38" s="27"/>
+      <c r="CW38" s="27"/>
+      <c r="CX38" s="27"/>
+      <c r="CY38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="CZ38" s="28"/>
+      <c r="DA38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DB38" s="28"/>
+      <c r="DC38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DD38" s="28"/>
+      <c r="DE38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DF38" s="27"/>
     </row>
     <row r="39" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="14" t="s">
@@ -10406,6 +10672,9 @@
         <v>800</v>
       </c>
       <c r="AH39" s="9"/>
+      <c r="AI39" s="9" t="s">
+        <v>1781</v>
+      </c>
       <c r="AK39" s="9" t="s">
         <v>801</v>
       </c>
@@ -10431,7 +10700,7 @@
       <c r="BU39" s="9"/>
       <c r="BV39" s="9"/>
       <c r="BW39" s="9" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="BX39" s="9"/>
       <c r="BY39" s="9"/>
@@ -10441,35 +10710,35 @@
       <c r="CC39" s="9"/>
       <c r="CD39" s="9"/>
       <c r="CE39" s="9"/>
-      <c r="CS39" s="28"/>
-      <c r="CT39" s="28"/>
-      <c r="CU39" s="28"/>
-      <c r="CV39" s="28"/>
-      <c r="CW39" s="28"/>
-      <c r="CX39" s="28"/>
-      <c r="CY39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="CZ39" s="29"/>
-      <c r="DA39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DB39" s="29"/>
-      <c r="DC39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DD39" s="29"/>
-      <c r="DE39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DF39" s="28"/>
+      <c r="CS39" s="27"/>
+      <c r="CT39" s="27"/>
+      <c r="CU39" s="27"/>
+      <c r="CV39" s="27"/>
+      <c r="CW39" s="27"/>
+      <c r="CX39" s="27"/>
+      <c r="CY39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="CZ39" s="28"/>
+      <c r="DA39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DB39" s="28"/>
+      <c r="DC39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DD39" s="28"/>
+      <c r="DE39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DF39" s="27"/>
     </row>
     <row r="40" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="20" t="s">
         <v>173</v>
       </c>
       <c r="B40" s="12"/>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="20" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="12"/>
@@ -10492,6 +10761,9 @@
         <v>803</v>
       </c>
       <c r="AH40" s="9"/>
+      <c r="AI40" s="9" t="s">
+        <v>1782</v>
+      </c>
       <c r="AM40" s="9" t="s">
         <v>781</v>
       </c>
@@ -10514,7 +10786,7 @@
       <c r="BU40" s="9"/>
       <c r="BV40" s="9"/>
       <c r="BW40" s="9" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="BX40" s="9"/>
       <c r="BY40" s="9"/>
@@ -10524,28 +10796,28 @@
       <c r="CC40" s="9"/>
       <c r="CD40" s="9"/>
       <c r="CE40" s="9"/>
-      <c r="CS40" s="28"/>
-      <c r="CT40" s="28"/>
-      <c r="CU40" s="28"/>
-      <c r="CV40" s="28"/>
-      <c r="CW40" s="28"/>
-      <c r="CX40" s="28"/>
-      <c r="CY40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="CZ40" s="29"/>
-      <c r="DA40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DB40" s="29"/>
-      <c r="DC40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DD40" s="29"/>
-      <c r="DE40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DF40" s="28"/>
+      <c r="CS40" s="27"/>
+      <c r="CT40" s="27"/>
+      <c r="CU40" s="27"/>
+      <c r="CV40" s="27"/>
+      <c r="CW40" s="27"/>
+      <c r="CX40" s="27"/>
+      <c r="CY40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="CZ40" s="28"/>
+      <c r="DA40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DB40" s="28"/>
+      <c r="DC40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DD40" s="28"/>
+      <c r="DE40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DF40" s="27"/>
     </row>
     <row r="41" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A41" s="14" t="s">
@@ -10575,6 +10847,9 @@
         <v>805</v>
       </c>
       <c r="AH41" s="9"/>
+      <c r="AI41" s="9" t="s">
+        <v>1783</v>
+      </c>
       <c r="AM41" s="9" t="s">
         <v>806</v>
       </c>
@@ -10597,7 +10872,7 @@
       <c r="BU41" s="9"/>
       <c r="BV41" s="9"/>
       <c r="BW41" s="9" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="BX41" s="9"/>
       <c r="BY41" s="9"/>
@@ -10607,35 +10882,35 @@
       <c r="CC41" s="9"/>
       <c r="CD41" s="9"/>
       <c r="CE41" s="9"/>
-      <c r="CS41" s="28"/>
-      <c r="CT41" s="28"/>
-      <c r="CU41" s="28"/>
-      <c r="CV41" s="28"/>
-      <c r="CW41" s="28"/>
-      <c r="CX41" s="28"/>
-      <c r="CY41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="CZ41" s="29"/>
-      <c r="DA41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DB41" s="29"/>
-      <c r="DC41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DD41" s="29"/>
-      <c r="DE41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DF41" s="28"/>
+      <c r="CS41" s="27"/>
+      <c r="CT41" s="27"/>
+      <c r="CU41" s="27"/>
+      <c r="CV41" s="27"/>
+      <c r="CW41" s="27"/>
+      <c r="CX41" s="27"/>
+      <c r="CY41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="CZ41" s="28"/>
+      <c r="DA41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DB41" s="28"/>
+      <c r="DC41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DD41" s="28"/>
+      <c r="DE41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DF41" s="27"/>
     </row>
     <row r="42" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="20" t="s">
         <v>177</v>
       </c>
       <c r="B42" s="12"/>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="20" t="s">
         <v>178</v>
       </c>
       <c r="D42" s="12"/>
@@ -10658,6 +10933,9 @@
         <v>808</v>
       </c>
       <c r="AH42" s="9"/>
+      <c r="AI42" s="9" t="s">
+        <v>1784</v>
+      </c>
       <c r="AM42" s="9" t="s">
         <v>784</v>
       </c>
@@ -10680,7 +10958,7 @@
       <c r="BU42" s="9"/>
       <c r="BV42" s="9"/>
       <c r="BW42" s="9" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="BX42" s="9"/>
       <c r="BY42" s="9"/>
@@ -10690,28 +10968,28 @@
       <c r="CC42" s="9"/>
       <c r="CD42" s="9"/>
       <c r="CE42" s="9"/>
-      <c r="CS42" s="28"/>
-      <c r="CT42" s="28"/>
-      <c r="CU42" s="28"/>
-      <c r="CV42" s="28"/>
-      <c r="CW42" s="28"/>
-      <c r="CX42" s="28"/>
-      <c r="CY42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="CZ42" s="29"/>
-      <c r="DA42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DB42" s="29"/>
-      <c r="DC42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DD42" s="29"/>
-      <c r="DE42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DF42" s="28"/>
+      <c r="CS42" s="27"/>
+      <c r="CT42" s="27"/>
+      <c r="CU42" s="27"/>
+      <c r="CV42" s="27"/>
+      <c r="CW42" s="27"/>
+      <c r="CX42" s="27"/>
+      <c r="CY42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="CZ42" s="28"/>
+      <c r="DA42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DB42" s="28"/>
+      <c r="DC42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DD42" s="28"/>
+      <c r="DE42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DF42" s="27"/>
     </row>
     <row r="43" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="14" t="s">
@@ -10741,6 +11019,9 @@
         <v>810</v>
       </c>
       <c r="AH43" s="9"/>
+      <c r="AI43" s="9" t="s">
+        <v>1785</v>
+      </c>
       <c r="AM43" t="s">
         <v>811</v>
       </c>
@@ -10762,7 +11043,7 @@
       <c r="BU43" s="9"/>
       <c r="BV43" s="9"/>
       <c r="BW43" s="9" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="BX43" s="9"/>
       <c r="BY43" s="9"/>
@@ -10772,35 +11053,35 @@
       <c r="CC43" s="9"/>
       <c r="CD43" s="9"/>
       <c r="CE43" s="9"/>
-      <c r="CS43" s="28"/>
-      <c r="CT43" s="28"/>
-      <c r="CU43" s="28"/>
-      <c r="CV43" s="28"/>
-      <c r="CW43" s="28"/>
-      <c r="CX43" s="28"/>
-      <c r="CY43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="CZ43" s="29"/>
-      <c r="DA43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DB43" s="29"/>
-      <c r="DC43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DD43" s="29"/>
-      <c r="DE43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DF43" s="28"/>
+      <c r="CS43" s="27"/>
+      <c r="CT43" s="27"/>
+      <c r="CU43" s="27"/>
+      <c r="CV43" s="27"/>
+      <c r="CW43" s="27"/>
+      <c r="CX43" s="27"/>
+      <c r="CY43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="CZ43" s="28"/>
+      <c r="DA43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DB43" s="28"/>
+      <c r="DC43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DD43" s="28"/>
+      <c r="DE43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DF43" s="27"/>
     </row>
     <row r="44" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="20" t="s">
         <v>181</v>
       </c>
       <c r="B44" s="12"/>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="20" t="s">
         <v>182</v>
       </c>
       <c r="D44" s="12"/>
@@ -10823,6 +11104,9 @@
         <v>813</v>
       </c>
       <c r="AH44" s="9"/>
+      <c r="AI44" s="9" t="s">
+        <v>1786</v>
+      </c>
       <c r="AM44" s="9" t="s">
         <v>787</v>
       </c>
@@ -10845,7 +11129,7 @@
       <c r="BU44" s="9"/>
       <c r="BV44" s="9"/>
       <c r="BW44" s="9" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="BX44" s="9"/>
       <c r="BY44" s="9"/>
@@ -10855,28 +11139,28 @@
       <c r="CC44" s="9"/>
       <c r="CD44" s="9"/>
       <c r="CE44" s="9"/>
-      <c r="CS44" s="28"/>
-      <c r="CT44" s="28"/>
-      <c r="CU44" s="28"/>
-      <c r="CV44" s="28"/>
-      <c r="CW44" s="28"/>
-      <c r="CX44" s="28"/>
-      <c r="CY44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="CZ44" s="29"/>
-      <c r="DA44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DB44" s="29"/>
-      <c r="DC44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DD44" s="29"/>
-      <c r="DE44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DF44" s="28"/>
+      <c r="CS44" s="27"/>
+      <c r="CT44" s="27"/>
+      <c r="CU44" s="27"/>
+      <c r="CV44" s="27"/>
+      <c r="CW44" s="27"/>
+      <c r="CX44" s="27"/>
+      <c r="CY44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="CZ44" s="28"/>
+      <c r="DA44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DB44" s="28"/>
+      <c r="DC44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DD44" s="28"/>
+      <c r="DE44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DF44" s="27"/>
     </row>
     <row r="45" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="14" t="s">
@@ -10906,6 +11190,9 @@
         <v>815</v>
       </c>
       <c r="AH45" s="9"/>
+      <c r="AI45" s="9" t="s">
+        <v>1787</v>
+      </c>
       <c r="AM45" s="9" t="s">
         <v>791</v>
       </c>
@@ -10928,7 +11215,7 @@
       <c r="BU45" s="9"/>
       <c r="BV45" s="9"/>
       <c r="BW45" s="9" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="BX45" s="9"/>
       <c r="BY45" s="9"/>
@@ -10938,35 +11225,35 @@
       <c r="CC45" s="9"/>
       <c r="CD45" s="9"/>
       <c r="CE45" s="9"/>
-      <c r="CS45" s="28"/>
-      <c r="CT45" s="28"/>
-      <c r="CU45" s="28"/>
-      <c r="CV45" s="28"/>
-      <c r="CW45" s="28"/>
-      <c r="CX45" s="28"/>
-      <c r="CY45" s="29" t="s">
+      <c r="CS45" s="27"/>
+      <c r="CT45" s="27"/>
+      <c r="CU45" s="27"/>
+      <c r="CV45" s="27"/>
+      <c r="CW45" s="27"/>
+      <c r="CX45" s="27"/>
+      <c r="CY45" s="28" t="s">
+        <v>1766</v>
+      </c>
+      <c r="CZ45" s="28"/>
+      <c r="DA45" s="28" t="s">
         <v>1767</v>
       </c>
-      <c r="CZ45" s="29"/>
-      <c r="DA45" s="29" t="s">
-        <v>1768</v>
-      </c>
-      <c r="DB45" s="29"/>
-      <c r="DC45" s="29" t="s">
+      <c r="DB45" s="28"/>
+      <c r="DC45" s="28" t="s">
+        <v>1766</v>
+      </c>
+      <c r="DD45" s="28"/>
+      <c r="DE45" s="28" t="s">
         <v>1767</v>
       </c>
-      <c r="DD45" s="29"/>
-      <c r="DE45" s="29" t="s">
-        <v>1768</v>
-      </c>
-      <c r="DF45" s="28"/>
+      <c r="DF45" s="27"/>
     </row>
     <row r="46" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="20" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="12"/>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>186</v>
       </c>
       <c r="D46" s="12"/>
@@ -10989,6 +11276,9 @@
         <v>817</v>
       </c>
       <c r="AH46" s="9"/>
+      <c r="AI46" s="9" t="s">
+        <v>1788</v>
+      </c>
       <c r="AM46" t="s">
         <v>818</v>
       </c>
@@ -11010,7 +11300,7 @@
       <c r="BU46" s="9"/>
       <c r="BV46" s="9"/>
       <c r="BW46" s="9" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="BX46" s="9"/>
       <c r="BY46" s="9"/>
@@ -11020,28 +11310,28 @@
       <c r="CC46" s="9"/>
       <c r="CD46" s="9"/>
       <c r="CE46" s="9"/>
-      <c r="CS46" s="28"/>
-      <c r="CT46" s="28"/>
-      <c r="CU46" s="28"/>
-      <c r="CV46" s="28"/>
-      <c r="CW46" s="28"/>
-      <c r="CX46" s="28"/>
-      <c r="CY46" s="29" t="s">
+      <c r="CS46" s="27"/>
+      <c r="CT46" s="27"/>
+      <c r="CU46" s="27"/>
+      <c r="CV46" s="27"/>
+      <c r="CW46" s="27"/>
+      <c r="CX46" s="27"/>
+      <c r="CY46" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="CZ46" s="28"/>
+      <c r="DA46" s="28" t="s">
         <v>1769</v>
       </c>
-      <c r="CZ46" s="29"/>
-      <c r="DA46" s="29" t="s">
-        <v>1770</v>
-      </c>
-      <c r="DB46" s="29"/>
-      <c r="DC46" s="29" t="s">
+      <c r="DB46" s="28"/>
+      <c r="DC46" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="DD46" s="28"/>
+      <c r="DE46" s="28" t="s">
         <v>1769</v>
       </c>
-      <c r="DD46" s="29"/>
-      <c r="DE46" s="29" t="s">
-        <v>1770</v>
-      </c>
-      <c r="DF46" s="28"/>
+      <c r="DF46" s="27"/>
     </row>
     <row r="47" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="14" t="s">
@@ -11071,6 +11361,9 @@
         <v>820</v>
       </c>
       <c r="AH47" s="9"/>
+      <c r="AI47" s="9" t="s">
+        <v>1789</v>
+      </c>
       <c r="AM47" s="9" t="s">
         <v>801</v>
       </c>
@@ -11093,7 +11386,7 @@
       <c r="BU47" s="9"/>
       <c r="BV47" s="9"/>
       <c r="BW47" s="9" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="BX47" s="9"/>
       <c r="BY47" s="9"/>
@@ -11103,35 +11396,35 @@
       <c r="CC47" s="9"/>
       <c r="CD47" s="9"/>
       <c r="CE47" s="9"/>
-      <c r="CS47" s="28"/>
-      <c r="CT47" s="28"/>
-      <c r="CU47" s="28"/>
-      <c r="CV47" s="28"/>
-      <c r="CW47" s="28"/>
-      <c r="CX47" s="28"/>
-      <c r="CY47" s="29" t="s">
-        <v>1726</v>
-      </c>
-      <c r="CZ47" s="29"/>
-      <c r="DA47" s="29" t="s">
-        <v>1771</v>
-      </c>
-      <c r="DB47" s="29"/>
-      <c r="DC47" s="29" t="s">
-        <v>1726</v>
-      </c>
-      <c r="DD47" s="29"/>
-      <c r="DE47" s="29" t="s">
-        <v>1771</v>
-      </c>
-      <c r="DF47" s="28"/>
+      <c r="CS47" s="27"/>
+      <c r="CT47" s="27"/>
+      <c r="CU47" s="27"/>
+      <c r="CV47" s="27"/>
+      <c r="CW47" s="27"/>
+      <c r="CX47" s="27"/>
+      <c r="CY47" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CZ47" s="28"/>
+      <c r="DA47" s="28" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DB47" s="28"/>
+      <c r="DC47" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DD47" s="28"/>
+      <c r="DE47" s="28" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DF47" s="27"/>
     </row>
     <row r="48" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B48" s="12"/>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="20" t="s">
         <v>190</v>
       </c>
       <c r="D48" s="12"/>
@@ -11154,6 +11447,9 @@
         <v>822</v>
       </c>
       <c r="AH48" s="9"/>
+      <c r="AI48" s="9" t="s">
+        <v>1790</v>
+      </c>
       <c r="AQ48" s="9" t="s">
         <v>823</v>
       </c>
@@ -11172,7 +11468,7 @@
       <c r="BU48" s="9"/>
       <c r="BV48" s="9"/>
       <c r="BW48" s="9" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="BX48" s="9"/>
       <c r="BY48" s="9"/>
@@ -11182,28 +11478,28 @@
       <c r="CC48" s="9"/>
       <c r="CD48" s="9"/>
       <c r="CE48" s="9"/>
-      <c r="CS48" s="28"/>
-      <c r="CT48" s="28"/>
-      <c r="CU48" s="28"/>
-      <c r="CV48" s="28"/>
-      <c r="CW48" s="28"/>
-      <c r="CX48" s="28"/>
-      <c r="CY48" s="29" t="s">
-        <v>1729</v>
-      </c>
-      <c r="CZ48" s="29"/>
-      <c r="DA48" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="DB48" s="29"/>
-      <c r="DC48" s="29" t="s">
-        <v>1729</v>
-      </c>
-      <c r="DD48" s="29"/>
-      <c r="DE48" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="DF48" s="28"/>
+      <c r="CS48" s="27"/>
+      <c r="CT48" s="27"/>
+      <c r="CU48" s="27"/>
+      <c r="CV48" s="27"/>
+      <c r="CW48" s="27"/>
+      <c r="CX48" s="27"/>
+      <c r="CY48" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="CZ48" s="28"/>
+      <c r="DA48" s="28" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DB48" s="28"/>
+      <c r="DC48" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="DD48" s="28"/>
+      <c r="DE48" s="28" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DF48" s="27"/>
     </row>
     <row r="49" spans="1:83" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
@@ -11233,6 +11529,9 @@
         <v>824</v>
       </c>
       <c r="AH49" s="9"/>
+      <c r="AI49" s="9" t="s">
+        <v>1791</v>
+      </c>
       <c r="AQ49" s="9" t="s">
         <v>825</v>
       </c>
@@ -11251,7 +11550,7 @@
       <c r="BU49" s="9"/>
       <c r="BV49" s="9"/>
       <c r="BW49" s="9" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="BX49" s="9"/>
       <c r="BY49" s="9"/>
@@ -11263,11 +11562,11 @@
       <c r="CE49" s="9"/>
     </row>
     <row r="50" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="20" t="s">
         <v>193</v>
       </c>
       <c r="B50" s="12"/>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="20" t="s">
         <v>194</v>
       </c>
       <c r="D50" s="12"/>
@@ -11290,6 +11589,9 @@
         <v>826</v>
       </c>
       <c r="AH50" s="9"/>
+      <c r="AI50" s="9" t="s">
+        <v>1792</v>
+      </c>
       <c r="AQ50" s="9" t="s">
         <v>827</v>
       </c>
@@ -11308,7 +11610,7 @@
       <c r="BU50" s="9"/>
       <c r="BV50" s="9"/>
       <c r="BW50" s="9" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="BX50" s="9"/>
       <c r="BY50" s="9"/>
@@ -11347,6 +11649,9 @@
         <v>828</v>
       </c>
       <c r="AH51" s="9"/>
+      <c r="AI51" s="9" t="s">
+        <v>1793</v>
+      </c>
       <c r="AQ51" s="9" t="s">
         <v>829</v>
       </c>
@@ -11365,7 +11670,7 @@
       <c r="BU51" s="9"/>
       <c r="BV51" s="9"/>
       <c r="BW51" s="9" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="BX51" s="9"/>
       <c r="BY51" s="9"/>
@@ -11377,11 +11682,11 @@
       <c r="CE51" s="9"/>
     </row>
     <row r="52" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="20" t="s">
         <v>197</v>
       </c>
       <c r="B52" s="12"/>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="20" t="s">
         <v>198</v>
       </c>
       <c r="D52" s="12"/>
@@ -11404,6 +11709,9 @@
         <v>830</v>
       </c>
       <c r="AH52" s="9"/>
+      <c r="AI52" s="9" t="s">
+        <v>1794</v>
+      </c>
       <c r="AQ52" s="9" t="s">
         <v>831</v>
       </c>
@@ -11422,7 +11730,7 @@
       <c r="BU52" s="9"/>
       <c r="BV52" s="9"/>
       <c r="BW52" s="9" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="BX52" s="9"/>
       <c r="BY52" s="9"/>
@@ -11461,6 +11769,9 @@
         <v>832</v>
       </c>
       <c r="AH53" s="9"/>
+      <c r="AI53" s="9" t="s">
+        <v>1795</v>
+      </c>
       <c r="AQ53" s="9" t="s">
         <v>833</v>
       </c>
@@ -11479,7 +11790,7 @@
       <c r="BU53" s="9"/>
       <c r="BV53" s="9"/>
       <c r="BW53" s="9" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="BX53" s="9"/>
       <c r="BY53" s="9"/>
@@ -11491,11 +11802,11 @@
       <c r="CE53" s="9"/>
     </row>
     <row r="54" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="20" t="s">
         <v>201</v>
       </c>
       <c r="B54" s="12"/>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="20" t="s">
         <v>202</v>
       </c>
       <c r="D54" s="12"/>
@@ -11518,6 +11829,9 @@
         <v>834</v>
       </c>
       <c r="AH54" s="9"/>
+      <c r="AI54" s="9" t="s">
+        <v>1796</v>
+      </c>
       <c r="AQ54" s="9" t="s">
         <v>835</v>
       </c>
@@ -11536,7 +11850,7 @@
       <c r="BU54" s="9"/>
       <c r="BV54" s="9"/>
       <c r="BW54" s="9" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="BX54" s="9"/>
       <c r="BY54" s="9"/>
@@ -11575,6 +11889,9 @@
         <v>836</v>
       </c>
       <c r="AH55" s="9"/>
+      <c r="AI55" s="9" t="s">
+        <v>1797</v>
+      </c>
       <c r="AQ55" s="9" t="s">
         <v>837</v>
       </c>
@@ -11593,7 +11910,7 @@
       <c r="BU55" s="9"/>
       <c r="BV55" s="9"/>
       <c r="BW55" s="9" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="BX55" s="9"/>
       <c r="BY55" s="9"/>
@@ -11605,11 +11922,11 @@
       <c r="CE55" s="9"/>
     </row>
     <row r="56" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="20" t="s">
         <v>205</v>
       </c>
       <c r="B56" s="12"/>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="20" t="s">
         <v>206</v>
       </c>
       <c r="D56" s="12"/>
@@ -11632,6 +11949,9 @@
         <v>838</v>
       </c>
       <c r="AH56" s="9"/>
+      <c r="AI56" s="9" t="s">
+        <v>1798</v>
+      </c>
       <c r="AQ56" s="9" t="s">
         <v>839</v>
       </c>
@@ -11650,7 +11970,7 @@
       <c r="BU56" s="9"/>
       <c r="BV56" s="9"/>
       <c r="BW56" s="9" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="BX56" s="9"/>
       <c r="BY56" s="9"/>
@@ -11689,6 +12009,9 @@
         <v>840</v>
       </c>
       <c r="AH57" s="9"/>
+      <c r="AI57" s="9" t="s">
+        <v>1799</v>
+      </c>
       <c r="AQ57" s="9" t="s">
         <v>841</v>
       </c>
@@ -11707,7 +12030,7 @@
       <c r="BU57" s="9"/>
       <c r="BV57" s="9"/>
       <c r="BW57" s="9" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="BX57" s="9"/>
       <c r="BY57" s="9"/>
@@ -11719,11 +12042,11 @@
       <c r="CE57" s="9"/>
     </row>
     <row r="58" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B58" s="12"/>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="20" t="s">
         <v>210</v>
       </c>
       <c r="D58" s="12"/>
@@ -11746,6 +12069,9 @@
         <v>842</v>
       </c>
       <c r="AH58" s="9"/>
+      <c r="AI58" s="9" t="s">
+        <v>1800</v>
+      </c>
       <c r="AQ58" s="9" t="s">
         <v>843</v>
       </c>
@@ -11764,7 +12090,7 @@
       <c r="BU58" s="9"/>
       <c r="BV58" s="9"/>
       <c r="BW58" s="9" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="BX58" s="9"/>
       <c r="BY58" s="9"/>
@@ -11803,6 +12129,9 @@
         <v>844</v>
       </c>
       <c r="AH59" s="9"/>
+      <c r="AI59" s="9" t="s">
+        <v>1801</v>
+      </c>
       <c r="AQ59" s="9" t="s">
         <v>845</v>
       </c>
@@ -11821,7 +12150,7 @@
       <c r="BU59" s="9"/>
       <c r="BV59" s="9"/>
       <c r="BW59" s="9" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="BX59" s="9"/>
       <c r="BY59" s="9"/>
@@ -11833,11 +12162,11 @@
       <c r="CE59" s="9"/>
     </row>
     <row r="60" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="20" t="s">
         <v>213</v>
       </c>
       <c r="B60" s="12"/>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="20" t="s">
         <v>214</v>
       </c>
       <c r="D60" s="12"/>
@@ -11860,6 +12189,9 @@
         <v>846</v>
       </c>
       <c r="AH60" s="9"/>
+      <c r="AI60" s="9" t="s">
+        <v>1802</v>
+      </c>
       <c r="AQ60" s="9" t="s">
         <v>847</v>
       </c>
@@ -11878,7 +12210,7 @@
       <c r="BU60" s="9"/>
       <c r="BV60" s="9"/>
       <c r="BW60" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="BX60" s="9"/>
       <c r="BY60" s="9"/>
@@ -11917,6 +12249,9 @@
         <v>848</v>
       </c>
       <c r="AH61" s="9"/>
+      <c r="AI61" s="9" t="s">
+        <v>1803</v>
+      </c>
       <c r="AQ61" s="9" t="s">
         <v>849</v>
       </c>
@@ -11935,7 +12270,7 @@
       <c r="BU61" s="9"/>
       <c r="BV61" s="9"/>
       <c r="BW61" s="9" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="BX61" s="9"/>
       <c r="BY61" s="9"/>
@@ -11947,11 +12282,11 @@
       <c r="CE61" s="9"/>
     </row>
     <row r="62" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="20" t="s">
         <v>217</v>
       </c>
       <c r="B62" s="12"/>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="20" t="s">
         <v>218</v>
       </c>
       <c r="D62" s="12"/>
@@ -11974,6 +12309,9 @@
         <v>850</v>
       </c>
       <c r="AH62" s="9"/>
+      <c r="AI62" s="9" t="s">
+        <v>1804</v>
+      </c>
       <c r="AQ62" s="9" t="s">
         <v>851</v>
       </c>
@@ -11992,7 +12330,7 @@
       <c r="BU62" s="9"/>
       <c r="BV62" s="9"/>
       <c r="BW62" s="9" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="BX62" s="9"/>
       <c r="BY62" s="9"/>
@@ -12031,6 +12369,9 @@
         <v>852</v>
       </c>
       <c r="AH63" s="9"/>
+      <c r="AI63" s="9" t="s">
+        <v>1805</v>
+      </c>
       <c r="AQ63" s="9" t="s">
         <v>853</v>
       </c>
@@ -12049,7 +12390,7 @@
       <c r="BU63" s="9"/>
       <c r="BV63" s="9"/>
       <c r="BW63" s="9" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="BX63" s="9"/>
       <c r="BY63" s="9"/>
@@ -12061,11 +12402,11 @@
       <c r="CE63" s="9"/>
     </row>
     <row r="64" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B64" s="12"/>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="20" t="s">
         <v>222</v>
       </c>
       <c r="D64" s="12"/>
@@ -12088,6 +12429,9 @@
         <v>854</v>
       </c>
       <c r="AH64" s="9"/>
+      <c r="AI64" s="9" t="s">
+        <v>1806</v>
+      </c>
       <c r="AQ64" s="9" t="s">
         <v>855</v>
       </c>
@@ -12106,7 +12450,7 @@
       <c r="BU64" s="9"/>
       <c r="BV64" s="9"/>
       <c r="BW64" s="9" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="BX64" s="9"/>
       <c r="BY64" s="9"/>
@@ -12145,6 +12489,9 @@
         <v>856</v>
       </c>
       <c r="AH65" s="9"/>
+      <c r="AI65" s="9" t="s">
+        <v>1807</v>
+      </c>
       <c r="AQ65" s="9" t="s">
         <v>857</v>
       </c>
@@ -12163,7 +12510,7 @@
       <c r="BU65" s="9"/>
       <c r="BV65" s="9"/>
       <c r="BW65" s="9" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="BX65" s="9"/>
       <c r="BY65" s="9"/>
@@ -12175,11 +12522,11 @@
       <c r="CE65" s="9"/>
     </row>
     <row r="66" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="20" t="s">
         <v>225</v>
       </c>
       <c r="B66" s="12"/>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="20" t="s">
         <v>226</v>
       </c>
       <c r="D66" s="12"/>
@@ -12202,6 +12549,9 @@
         <v>858</v>
       </c>
       <c r="AH66" s="9"/>
+      <c r="AI66" s="9" t="s">
+        <v>1808</v>
+      </c>
       <c r="AQ66" s="9" t="s">
         <v>859</v>
       </c>
@@ -12220,7 +12570,7 @@
       <c r="BU66" s="9"/>
       <c r="BV66" s="9"/>
       <c r="BW66" s="9" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="BX66" s="9"/>
       <c r="BY66" s="9"/>
@@ -12259,6 +12609,9 @@
         <v>860</v>
       </c>
       <c r="AH67" s="9"/>
+      <c r="AI67" s="9" t="s">
+        <v>1809</v>
+      </c>
       <c r="AQ67" s="9" t="s">
         <v>861</v>
       </c>
@@ -12277,7 +12630,7 @@
       <c r="BU67" s="9"/>
       <c r="BV67" s="9"/>
       <c r="BW67" s="9" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="BX67" s="9"/>
       <c r="BY67" s="9"/>
@@ -12289,11 +12642,11 @@
       <c r="CE67" s="9"/>
     </row>
     <row r="68" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="20" t="s">
         <v>229</v>
       </c>
       <c r="B68" s="12"/>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="20" t="s">
         <v>230</v>
       </c>
       <c r="D68" s="12"/>
@@ -12316,6 +12669,9 @@
         <v>862</v>
       </c>
       <c r="AH68" s="9"/>
+      <c r="AI68" s="9" t="s">
+        <v>1810</v>
+      </c>
       <c r="AQ68" s="9" t="s">
         <v>863</v>
       </c>
@@ -12334,7 +12690,7 @@
       <c r="BU68" s="9"/>
       <c r="BV68" s="9"/>
       <c r="BW68" s="9" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="BX68" s="9"/>
       <c r="BY68" s="9"/>
@@ -12373,6 +12729,9 @@
         <v>864</v>
       </c>
       <c r="AH69" s="9"/>
+      <c r="AI69" s="9" t="s">
+        <v>1811</v>
+      </c>
       <c r="AQ69" s="9" t="s">
         <v>865</v>
       </c>
@@ -12391,7 +12750,7 @@
       <c r="BU69" s="9"/>
       <c r="BV69" s="9"/>
       <c r="BW69" s="9" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="BX69" s="9"/>
       <c r="BY69" s="9"/>
@@ -12403,11 +12762,11 @@
       <c r="CE69" s="9"/>
     </row>
     <row r="70" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B70" s="12"/>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>234</v>
       </c>
       <c r="D70" s="12"/>
@@ -12430,6 +12789,9 @@
         <v>866</v>
       </c>
       <c r="AH70" s="9"/>
+      <c r="AI70" s="9" t="s">
+        <v>1812</v>
+      </c>
       <c r="AQ70" s="9" t="s">
         <v>867</v>
       </c>
@@ -12448,7 +12810,7 @@
       <c r="BU70" s="9"/>
       <c r="BV70" s="9"/>
       <c r="BW70" s="9" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="BX70" s="9"/>
       <c r="BY70" s="9"/>
@@ -12487,6 +12849,9 @@
         <v>868</v>
       </c>
       <c r="AH71" s="9"/>
+      <c r="AI71" s="9" t="s">
+        <v>1813</v>
+      </c>
       <c r="AQ71" s="9" t="s">
         <v>869</v>
       </c>
@@ -12505,7 +12870,7 @@
       <c r="BU71" s="9"/>
       <c r="BV71" s="9"/>
       <c r="BW71" s="9" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="BX71" s="9"/>
       <c r="BY71" s="9"/>
@@ -12517,11 +12882,11 @@
       <c r="CE71" s="9"/>
     </row>
     <row r="72" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="20" t="s">
         <v>237</v>
       </c>
       <c r="B72" s="12"/>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="20" t="s">
         <v>238</v>
       </c>
       <c r="D72" s="12"/>
@@ -12544,6 +12909,9 @@
         <v>870</v>
       </c>
       <c r="AH72" s="9"/>
+      <c r="AI72" s="9" t="s">
+        <v>1814</v>
+      </c>
       <c r="AQ72" s="9" t="s">
         <v>871</v>
       </c>
@@ -12562,7 +12930,7 @@
       <c r="BU72" s="9"/>
       <c r="BV72" s="9"/>
       <c r="BW72" s="9" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="BX72" s="9"/>
       <c r="BY72" s="9"/>
@@ -12601,6 +12969,9 @@
         <v>872</v>
       </c>
       <c r="AH73" s="9"/>
+      <c r="AI73" s="9" t="s">
+        <v>1815</v>
+      </c>
       <c r="AQ73" s="9" t="s">
         <v>873</v>
       </c>
@@ -12619,7 +12990,7 @@
       <c r="BU73" s="9"/>
       <c r="BV73" s="9"/>
       <c r="BW73" s="9" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="BX73" s="9"/>
       <c r="BY73" s="9"/>
@@ -12631,11 +13002,11 @@
       <c r="CE73" s="9"/>
     </row>
     <row r="74" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B74" s="12"/>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="20" t="s">
         <v>242</v>
       </c>
       <c r="D74" s="12"/>
@@ -12658,6 +13029,9 @@
         <v>874</v>
       </c>
       <c r="AH74" s="9"/>
+      <c r="AI74" s="9" t="s">
+        <v>1816</v>
+      </c>
       <c r="AQ74" s="9" t="s">
         <v>875</v>
       </c>
@@ -12676,7 +13050,7 @@
       <c r="BU74" s="9"/>
       <c r="BV74" s="9"/>
       <c r="BW74" s="9" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="BX74" s="9"/>
       <c r="BY74" s="9"/>
@@ -12715,6 +13089,9 @@
         <v>876</v>
       </c>
       <c r="AH75" s="9"/>
+      <c r="AI75" s="9" t="s">
+        <v>1817</v>
+      </c>
       <c r="AQ75" s="9" t="s">
         <v>877</v>
       </c>
@@ -12733,7 +13110,7 @@
       <c r="BU75" s="9"/>
       <c r="BV75" s="9"/>
       <c r="BW75" s="9" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="BX75" s="9"/>
       <c r="BY75" s="9"/>
@@ -12745,11 +13122,11 @@
       <c r="CE75" s="9"/>
     </row>
     <row r="76" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B76" s="12"/>
-      <c r="C76" s="21" t="s">
+      <c r="C76" s="20" t="s">
         <v>246</v>
       </c>
       <c r="D76" s="12"/>
@@ -12772,6 +13149,9 @@
         <v>878</v>
       </c>
       <c r="AH76" s="9"/>
+      <c r="AI76" s="9" t="s">
+        <v>1818</v>
+      </c>
       <c r="AQ76" s="9" t="s">
         <v>879</v>
       </c>
@@ -12790,7 +13170,7 @@
       <c r="BU76" s="9"/>
       <c r="BV76" s="9"/>
       <c r="BW76" s="9" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="BX76" s="9"/>
       <c r="BY76" s="9"/>
@@ -12829,6 +13209,9 @@
         <v>880</v>
       </c>
       <c r="AH77" s="9"/>
+      <c r="AI77" s="9" t="s">
+        <v>1819</v>
+      </c>
       <c r="AQ77" s="9" t="s">
         <v>881</v>
       </c>
@@ -12847,7 +13230,7 @@
       <c r="BU77" s="9"/>
       <c r="BV77" s="9"/>
       <c r="BW77" s="9" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="BX77" s="9"/>
       <c r="BY77" s="9"/>
@@ -12859,11 +13242,11 @@
       <c r="CE77" s="9"/>
     </row>
     <row r="78" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="20" t="s">
         <v>249</v>
       </c>
       <c r="B78" s="12"/>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="20" t="s">
         <v>250</v>
       </c>
       <c r="D78" s="12"/>
@@ -12886,6 +13269,9 @@
         <v>882</v>
       </c>
       <c r="AH78" s="9"/>
+      <c r="AI78" s="9" t="s">
+        <v>1820</v>
+      </c>
       <c r="AQ78" s="9" t="s">
         <v>883</v>
       </c>
@@ -12904,7 +13290,7 @@
       <c r="BU78" s="9"/>
       <c r="BV78" s="9"/>
       <c r="BW78" s="9" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="BX78" s="9"/>
       <c r="BY78" s="9"/>
@@ -12943,6 +13329,9 @@
         <v>884</v>
       </c>
       <c r="AH79" s="9"/>
+      <c r="AI79" s="9" t="s">
+        <v>1821</v>
+      </c>
       <c r="AQ79" s="9" t="s">
         <v>885</v>
       </c>
@@ -12961,7 +13350,7 @@
       <c r="BU79" s="9"/>
       <c r="BV79" s="9"/>
       <c r="BW79" s="9" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="BX79" s="9"/>
       <c r="BY79" s="9"/>
@@ -12973,11 +13362,11 @@
       <c r="CE79" s="9"/>
     </row>
     <row r="80" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="20" t="s">
         <v>253</v>
       </c>
       <c r="B80" s="12"/>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="20" t="s">
         <v>254</v>
       </c>
       <c r="D80" s="12"/>
@@ -13000,6 +13389,9 @@
         <v>886</v>
       </c>
       <c r="AH80" s="9"/>
+      <c r="AI80" s="9" t="s">
+        <v>1822</v>
+      </c>
       <c r="AQ80" s="9" t="s">
         <v>887</v>
       </c>
@@ -13018,7 +13410,7 @@
       <c r="BU80" s="9"/>
       <c r="BV80" s="9"/>
       <c r="BW80" s="9" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="BX80" s="9"/>
       <c r="BY80" s="9"/>
@@ -13057,6 +13449,9 @@
         <v>888</v>
       </c>
       <c r="AH81" s="9"/>
+      <c r="AI81" s="9" t="s">
+        <v>1823</v>
+      </c>
       <c r="AQ81" s="9" t="s">
         <v>889</v>
       </c>
@@ -13075,7 +13470,7 @@
       <c r="BU81" s="9"/>
       <c r="BV81" s="9"/>
       <c r="BW81" s="9" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="BX81" s="9"/>
       <c r="BY81" s="9"/>
@@ -13087,11 +13482,11 @@
       <c r="CE81" s="9"/>
     </row>
     <row r="82" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="20" t="s">
         <v>257</v>
       </c>
       <c r="B82" s="12"/>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="20" t="s">
         <v>258</v>
       </c>
       <c r="D82" s="12"/>
@@ -13114,6 +13509,9 @@
         <v>890</v>
       </c>
       <c r="AH82" s="9"/>
+      <c r="AI82" s="9" t="s">
+        <v>1824</v>
+      </c>
       <c r="AQ82" s="9" t="s">
         <v>891</v>
       </c>
@@ -13132,7 +13530,7 @@
       <c r="BU82" s="9"/>
       <c r="BV82" s="9"/>
       <c r="BW82" s="9" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="BX82" s="9"/>
       <c r="BY82" s="9"/>
@@ -13171,6 +13569,9 @@
         <v>892</v>
       </c>
       <c r="AH83" s="9"/>
+      <c r="AI83" s="9" t="s">
+        <v>1825</v>
+      </c>
       <c r="AQ83" s="9" t="s">
         <v>893</v>
       </c>
@@ -13189,7 +13590,7 @@
       <c r="BU83" s="9"/>
       <c r="BV83" s="9"/>
       <c r="BW83" s="9" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="BX83" s="9"/>
       <c r="BY83" s="9"/>
@@ -13201,11 +13602,11 @@
       <c r="CE83" s="9"/>
     </row>
     <row r="84" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A84" s="21" t="s">
+      <c r="A84" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B84" s="12"/>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="20" t="s">
         <v>262</v>
       </c>
       <c r="D84" s="12"/>
@@ -13228,6 +13629,9 @@
         <v>894</v>
       </c>
       <c r="AH84" s="9"/>
+      <c r="AI84" s="9" t="s">
+        <v>1826</v>
+      </c>
       <c r="AQ84" s="9" t="s">
         <v>895</v>
       </c>
@@ -13246,7 +13650,7 @@
       <c r="BU84" s="9"/>
       <c r="BV84" s="9"/>
       <c r="BW84" s="9" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="BX84" s="9"/>
       <c r="BY84" s="9"/>
@@ -13285,6 +13689,9 @@
         <v>896</v>
       </c>
       <c r="AH85" s="9"/>
+      <c r="AI85" s="9" t="s">
+        <v>1827</v>
+      </c>
       <c r="AQ85" s="9" t="s">
         <v>897</v>
       </c>
@@ -13303,7 +13710,7 @@
       <c r="BU85" s="9"/>
       <c r="BV85" s="9"/>
       <c r="BW85" s="9" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="BX85" s="9"/>
       <c r="BY85" s="9"/>
@@ -13315,11 +13722,11 @@
       <c r="CE85" s="9"/>
     </row>
     <row r="86" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A86" s="21" t="s">
+      <c r="A86" s="20" t="s">
         <v>265</v>
       </c>
       <c r="B86" s="12"/>
-      <c r="C86" s="21" t="s">
+      <c r="C86" s="20" t="s">
         <v>266</v>
       </c>
       <c r="D86" s="12"/>
@@ -13342,6 +13749,9 @@
         <v>898</v>
       </c>
       <c r="AH86" s="9"/>
+      <c r="AI86" s="9" t="s">
+        <v>1828</v>
+      </c>
       <c r="AQ86" s="9" t="s">
         <v>899</v>
       </c>
@@ -13360,7 +13770,7 @@
       <c r="BU86" s="9"/>
       <c r="BV86" s="9"/>
       <c r="BW86" s="9" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="BX86" s="9"/>
       <c r="BY86" s="9"/>
@@ -13399,6 +13809,9 @@
         <v>900</v>
       </c>
       <c r="AH87" s="9"/>
+      <c r="AI87" s="9" t="s">
+        <v>1829</v>
+      </c>
       <c r="AQ87" s="9" t="s">
         <v>901</v>
       </c>
@@ -13417,7 +13830,7 @@
       <c r="BU87" s="9"/>
       <c r="BV87" s="9"/>
       <c r="BW87" s="9" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="BX87" s="9"/>
       <c r="BY87" s="9"/>
@@ -13429,11 +13842,11 @@
       <c r="CE87" s="9"/>
     </row>
     <row r="88" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A88" s="21" t="s">
+      <c r="A88" s="20" t="s">
         <v>269</v>
       </c>
       <c r="B88" s="12"/>
-      <c r="C88" s="21" t="s">
+      <c r="C88" s="20" t="s">
         <v>270</v>
       </c>
       <c r="D88" s="12"/>
@@ -13456,6 +13869,9 @@
         <v>902</v>
       </c>
       <c r="AH88" s="9"/>
+      <c r="AI88" s="9" t="s">
+        <v>1830</v>
+      </c>
       <c r="AQ88" s="9" t="s">
         <v>903</v>
       </c>
@@ -13474,7 +13890,7 @@
       <c r="BU88" s="9"/>
       <c r="BV88" s="9"/>
       <c r="BW88" s="9" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="BX88" s="9"/>
       <c r="BY88" s="9"/>
@@ -13513,6 +13929,9 @@
         <v>904</v>
       </c>
       <c r="AH89" s="9"/>
+      <c r="AI89" s="9" t="s">
+        <v>1831</v>
+      </c>
       <c r="AQ89" s="9" t="s">
         <v>905</v>
       </c>
@@ -13531,7 +13950,7 @@
       <c r="BU89" s="9"/>
       <c r="BV89" s="9"/>
       <c r="BW89" s="9" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="BX89" s="9"/>
       <c r="BY89" s="9"/>
@@ -13543,11 +13962,11 @@
       <c r="CE89" s="9"/>
     </row>
     <row r="90" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="20" t="s">
         <v>273</v>
       </c>
       <c r="B90" s="12"/>
-      <c r="C90" s="21" t="s">
+      <c r="C90" s="20" t="s">
         <v>274</v>
       </c>
       <c r="D90" s="12"/>
@@ -13570,6 +13989,9 @@
         <v>906</v>
       </c>
       <c r="AH90" s="9"/>
+      <c r="AI90" s="9" t="s">
+        <v>1832</v>
+      </c>
       <c r="AQ90" s="9" t="s">
         <v>907</v>
       </c>
@@ -13588,7 +14010,7 @@
       <c r="BU90" s="9"/>
       <c r="BV90" s="9"/>
       <c r="BW90" s="9" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="BX90" s="9"/>
       <c r="BY90" s="9"/>
@@ -13627,6 +14049,9 @@
         <v>908</v>
       </c>
       <c r="AH91" s="9"/>
+      <c r="AI91" s="9" t="s">
+        <v>1833</v>
+      </c>
       <c r="AQ91" s="9" t="s">
         <v>909</v>
       </c>
@@ -13645,7 +14070,7 @@
       <c r="BU91" s="9"/>
       <c r="BV91" s="9"/>
       <c r="BW91" s="9" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="BX91" s="9"/>
       <c r="BY91" s="9"/>
@@ -13657,11 +14082,11 @@
       <c r="CE91" s="9"/>
     </row>
     <row r="92" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A92" s="21" t="s">
+      <c r="A92" s="20" t="s">
         <v>277</v>
       </c>
       <c r="B92" s="12"/>
-      <c r="C92" s="21" t="s">
+      <c r="C92" s="20" t="s">
         <v>278</v>
       </c>
       <c r="D92" s="12"/>
@@ -13680,6 +14105,9 @@
       <c r="Q92" s="12"/>
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
+      <c r="AI92" s="9" t="s">
+        <v>1834</v>
+      </c>
       <c r="AQ92" s="9" t="s">
         <v>910</v>
       </c>
@@ -13696,7 +14124,7 @@
       <c r="BU92" s="9"/>
       <c r="BV92" s="9"/>
       <c r="BW92" s="9" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="BX92" s="9"/>
       <c r="BY92" s="9"/>
@@ -13731,6 +14159,9 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="12"/>
       <c r="S93" s="12"/>
+      <c r="AI93" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="AQ93" s="9" t="s">
         <v>911</v>
       </c>
@@ -13747,7 +14178,7 @@
       <c r="BU93" s="9"/>
       <c r="BV93" s="9"/>
       <c r="BW93" s="9" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="BX93" s="9"/>
       <c r="BY93" s="9"/>
@@ -13759,11 +14190,11 @@
       <c r="CE93" s="9"/>
     </row>
     <row r="94" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="20" t="s">
         <v>281</v>
       </c>
       <c r="B94" s="12"/>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="20" t="s">
         <v>282</v>
       </c>
       <c r="D94" s="12"/>
@@ -13782,6 +14213,9 @@
       <c r="Q94" s="12"/>
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
+      <c r="AI94" s="9" t="s">
+        <v>1835</v>
+      </c>
       <c r="AQ94" s="9" t="s">
         <v>912</v>
       </c>
@@ -13798,7 +14232,7 @@
       <c r="BU94" s="9"/>
       <c r="BV94" s="9"/>
       <c r="BW94" s="9" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="BX94" s="9"/>
       <c r="BY94" s="9"/>
@@ -13833,6 +14267,9 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="12"/>
       <c r="S95" s="12"/>
+      <c r="AI95" s="9" t="s">
+        <v>1418</v>
+      </c>
       <c r="AQ95" s="9" t="s">
         <v>913</v>
       </c>
@@ -13849,7 +14286,7 @@
       <c r="BU95" s="9"/>
       <c r="BV95" s="9"/>
       <c r="BW95" s="9" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="BX95" s="9"/>
       <c r="BY95" s="9"/>
@@ -13861,11 +14298,11 @@
       <c r="CE95" s="9"/>
     </row>
     <row r="96" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="20" t="s">
         <v>285</v>
       </c>
       <c r="B96" s="12"/>
-      <c r="C96" s="21" t="s">
+      <c r="C96" s="20" t="s">
         <v>286</v>
       </c>
       <c r="D96" s="12"/>
@@ -13884,6 +14321,9 @@
       <c r="Q96" s="12"/>
       <c r="R96" s="12"/>
       <c r="S96" s="12"/>
+      <c r="AI96" s="9" t="s">
+        <v>1836</v>
+      </c>
       <c r="AQ96" s="9" t="s">
         <v>914</v>
       </c>
@@ -13900,7 +14340,7 @@
       <c r="BU96" s="9"/>
       <c r="BV96" s="9"/>
       <c r="BW96" s="9" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="BX96" s="9"/>
       <c r="BY96" s="9"/>
@@ -13935,6 +14375,9 @@
       <c r="Q97" s="12"/>
       <c r="R97" s="12"/>
       <c r="S97" s="12"/>
+      <c r="AI97" s="9" t="s">
+        <v>1837</v>
+      </c>
       <c r="AQ97" s="9" t="s">
         <v>915</v>
       </c>
@@ -13951,7 +14394,7 @@
       <c r="BU97" s="9"/>
       <c r="BV97" s="9"/>
       <c r="BW97" s="9" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="BX97" s="9"/>
       <c r="BY97" s="9"/>
@@ -13963,11 +14406,11 @@
       <c r="CE97" s="9"/>
     </row>
     <row r="98" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A98" s="21" t="s">
+      <c r="A98" s="20" t="s">
         <v>289</v>
       </c>
       <c r="B98" s="12"/>
-      <c r="C98" s="21" t="s">
+      <c r="C98" s="20" t="s">
         <v>290</v>
       </c>
       <c r="D98" s="12"/>
@@ -13986,6 +14429,9 @@
       <c r="Q98" s="12"/>
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
+      <c r="AI98" s="9" t="s">
+        <v>1838</v>
+      </c>
       <c r="AQ98" s="9" t="s">
         <v>916</v>
       </c>
@@ -14002,7 +14448,7 @@
       <c r="BU98" s="9"/>
       <c r="BV98" s="9"/>
       <c r="BW98" s="9" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="BX98" s="9"/>
       <c r="BY98" s="9"/>
@@ -14037,6 +14483,9 @@
       <c r="Q99" s="12"/>
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
+      <c r="AI99" s="9" t="s">
+        <v>1839</v>
+      </c>
       <c r="AQ99" s="9" t="s">
         <v>917</v>
       </c>
@@ -14053,7 +14502,7 @@
       <c r="BU99" s="9"/>
       <c r="BV99" s="9"/>
       <c r="BW99" s="9" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="BX99" s="9"/>
       <c r="BY99" s="9"/>
@@ -14065,11 +14514,11 @@
       <c r="CE99" s="9"/>
     </row>
     <row r="100" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A100" s="21" t="s">
+      <c r="A100" s="20" t="s">
         <v>293</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="20" t="s">
         <v>294</v>
       </c>
       <c r="D100" s="12"/>
@@ -14088,6 +14537,9 @@
       <c r="Q100" s="12"/>
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
+      <c r="AI100" s="9" t="s">
+        <v>1840</v>
+      </c>
       <c r="AQ100" s="9" t="s">
         <v>918</v>
       </c>
@@ -14104,7 +14556,7 @@
       <c r="BU100" s="9"/>
       <c r="BV100" s="9"/>
       <c r="BW100" s="9" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="BX100" s="9"/>
       <c r="BY100" s="9"/>
@@ -14139,6 +14591,9 @@
       <c r="Q101" s="12"/>
       <c r="R101" s="12"/>
       <c r="S101" s="12"/>
+      <c r="AI101" s="9" t="s">
+        <v>1841</v>
+      </c>
       <c r="AQ101" s="9" t="s">
         <v>919</v>
       </c>
@@ -14155,7 +14610,7 @@
       <c r="BU101" s="9"/>
       <c r="BV101" s="9"/>
       <c r="BW101" s="9" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="BX101" s="9"/>
       <c r="BY101" s="9"/>
@@ -14167,11 +14622,11 @@
       <c r="CE101" s="9"/>
     </row>
     <row r="102" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="20" t="s">
         <v>297</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="21" t="s">
+      <c r="C102" s="20" t="s">
         <v>298</v>
       </c>
       <c r="D102" s="12"/>
@@ -14190,6 +14645,9 @@
       <c r="Q102" s="12"/>
       <c r="R102" s="12"/>
       <c r="S102" s="12"/>
+      <c r="AI102" s="9" t="s">
+        <v>1428</v>
+      </c>
       <c r="AQ102" s="9" t="s">
         <v>920</v>
       </c>
@@ -14206,7 +14664,7 @@
       <c r="BU102" s="9"/>
       <c r="BV102" s="9"/>
       <c r="BW102" s="9" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="BX102" s="9"/>
       <c r="BY102" s="9"/>
@@ -14241,6 +14699,9 @@
       <c r="Q103" s="12"/>
       <c r="R103" s="12"/>
       <c r="S103" s="12"/>
+      <c r="AI103" s="9" t="s">
+        <v>1842</v>
+      </c>
       <c r="AQ103" s="9" t="s">
         <v>921</v>
       </c>
@@ -14257,7 +14718,7 @@
       <c r="BU103" s="9"/>
       <c r="BV103" s="9"/>
       <c r="BW103" s="9" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="BX103" s="9"/>
       <c r="BY103" s="9"/>
@@ -14269,11 +14730,11 @@
       <c r="CE103" s="9"/>
     </row>
     <row r="104" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A104" s="21" t="s">
+      <c r="A104" s="20" t="s">
         <v>301</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="20" t="s">
         <v>302</v>
       </c>
       <c r="D104" s="12"/>
@@ -14292,6 +14753,9 @@
       <c r="Q104" s="12"/>
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
+      <c r="AI104" s="9" t="s">
+        <v>1843</v>
+      </c>
       <c r="AQ104" s="9" t="s">
         <v>922</v>
       </c>
@@ -14308,7 +14772,7 @@
       <c r="BU104" s="9"/>
       <c r="BV104" s="9"/>
       <c r="BW104" s="9" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="BX104" s="9"/>
       <c r="BY104" s="9"/>
@@ -14343,6 +14807,9 @@
       <c r="Q105" s="12"/>
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
+      <c r="AI105" s="9" t="s">
+        <v>1844</v>
+      </c>
       <c r="AQ105" s="9" t="s">
         <v>923</v>
       </c>
@@ -14359,7 +14826,7 @@
       <c r="BU105" s="9"/>
       <c r="BV105" s="9"/>
       <c r="BW105" s="9" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="BX105" s="9"/>
       <c r="BY105" s="9"/>
@@ -14371,11 +14838,11 @@
       <c r="CE105" s="9"/>
     </row>
     <row r="106" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="20" t="s">
         <v>305</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="20" t="s">
         <v>306</v>
       </c>
       <c r="D106" s="12"/>
@@ -14394,6 +14861,9 @@
       <c r="Q106" s="12"/>
       <c r="R106" s="12"/>
       <c r="S106" s="12"/>
+      <c r="AI106" s="9" t="s">
+        <v>1845</v>
+      </c>
       <c r="AQ106" s="9" t="s">
         <v>924</v>
       </c>
@@ -14410,7 +14880,7 @@
       <c r="BU106" s="9"/>
       <c r="BV106" s="9"/>
       <c r="BW106" s="9" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="BX106" s="9"/>
       <c r="BY106" s="9"/>
@@ -14445,6 +14915,9 @@
       <c r="Q107" s="12"/>
       <c r="R107" s="12"/>
       <c r="S107" s="12"/>
+      <c r="AI107" s="9" t="s">
+        <v>1846</v>
+      </c>
       <c r="AQ107" s="9" t="s">
         <v>925</v>
       </c>
@@ -14461,7 +14934,7 @@
       <c r="BU107" s="9"/>
       <c r="BV107" s="9"/>
       <c r="BW107" s="9" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="BX107" s="9"/>
       <c r="BY107" s="9"/>
@@ -14473,11 +14946,11 @@
       <c r="CE107" s="9"/>
     </row>
     <row r="108" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A108" s="21" t="s">
+      <c r="A108" s="20" t="s">
         <v>309</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="21" t="s">
+      <c r="C108" s="20" t="s">
         <v>310</v>
       </c>
       <c r="D108" s="12"/>
@@ -14496,6 +14969,9 @@
       <c r="Q108" s="12"/>
       <c r="R108" s="12"/>
       <c r="S108" s="12"/>
+      <c r="AI108" s="9" t="s">
+        <v>1847</v>
+      </c>
       <c r="AQ108" s="9" t="s">
         <v>926</v>
       </c>
@@ -14512,7 +14988,7 @@
       <c r="BU108" s="9"/>
       <c r="BV108" s="9"/>
       <c r="BW108" s="9" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="BX108" s="9"/>
       <c r="BY108" s="9"/>
@@ -14547,6 +15023,9 @@
       <c r="Q109" s="12"/>
       <c r="R109" s="12"/>
       <c r="S109" s="12"/>
+      <c r="AI109" s="9" t="s">
+        <v>1848</v>
+      </c>
       <c r="AQ109" s="9" t="s">
         <v>927</v>
       </c>
@@ -14563,7 +15042,7 @@
       <c r="BU109" s="9"/>
       <c r="BV109" s="9"/>
       <c r="BW109" s="9" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="BX109" s="9"/>
       <c r="BY109" s="9"/>
@@ -14575,11 +15054,11 @@
       <c r="CE109" s="9"/>
     </row>
     <row r="110" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="20" t="s">
         <v>313</v>
       </c>
       <c r="B110" s="12"/>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="20" t="s">
         <v>314</v>
       </c>
       <c r="D110" s="12"/>
@@ -14598,6 +15077,9 @@
       <c r="Q110" s="12"/>
       <c r="R110" s="12"/>
       <c r="S110" s="12"/>
+      <c r="AI110" s="9" t="s">
+        <v>1849</v>
+      </c>
       <c r="AQ110" s="9" t="s">
         <v>928</v>
       </c>
@@ -14614,7 +15096,7 @@
       <c r="BU110" s="9"/>
       <c r="BV110" s="9"/>
       <c r="BW110" s="9" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="BX110" s="9"/>
       <c r="BY110" s="9"/>
@@ -14649,6 +15131,9 @@
       <c r="Q111" s="12"/>
       <c r="R111" s="12"/>
       <c r="S111" s="12"/>
+      <c r="AI111" s="9" t="s">
+        <v>1850</v>
+      </c>
       <c r="AQ111" s="9" t="s">
         <v>929</v>
       </c>
@@ -14665,7 +15150,7 @@
       <c r="BU111" s="9"/>
       <c r="BV111" s="9"/>
       <c r="BW111" s="9" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="BX111" s="9"/>
       <c r="BY111" s="9"/>
@@ -14677,11 +15162,11 @@
       <c r="CE111" s="9"/>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="20" t="s">
         <v>317</v>
       </c>
       <c r="B112" s="12"/>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="20" t="s">
         <v>318</v>
       </c>
       <c r="D112" s="12"/>
@@ -14700,6 +15185,9 @@
       <c r="Q112" s="12"/>
       <c r="R112" s="12"/>
       <c r="S112" s="12"/>
+      <c r="AI112" s="9" t="s">
+        <v>1851</v>
+      </c>
       <c r="AQ112" s="9" t="s">
         <v>930</v>
       </c>
@@ -14716,7 +15204,7 @@
       <c r="BU112" s="9"/>
       <c r="BV112" s="9"/>
       <c r="BW112" s="9" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="BX112" s="9"/>
       <c r="BY112" s="9"/>
@@ -14751,6 +15239,9 @@
       <c r="Q113" s="12"/>
       <c r="R113" s="12"/>
       <c r="S113" s="12"/>
+      <c r="AI113" s="9" t="s">
+        <v>1852</v>
+      </c>
       <c r="AQ113" s="9" t="s">
         <v>931</v>
       </c>
@@ -14767,7 +15258,7 @@
       <c r="BU113" s="9"/>
       <c r="BV113" s="9"/>
       <c r="BW113" s="9" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="BX113" s="9"/>
       <c r="BY113" s="9"/>
@@ -14779,11 +15270,11 @@
       <c r="CE113" s="9"/>
     </row>
     <row r="114" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="20" t="s">
         <v>321</v>
       </c>
       <c r="B114" s="12"/>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="20" t="s">
         <v>322</v>
       </c>
       <c r="D114" s="12"/>
@@ -14802,6 +15293,9 @@
       <c r="Q114" s="12"/>
       <c r="R114" s="12"/>
       <c r="S114" s="12"/>
+      <c r="AI114" s="9" t="s">
+        <v>1853</v>
+      </c>
       <c r="AQ114" s="9" t="s">
         <v>932</v>
       </c>
@@ -14818,7 +15312,7 @@
       <c r="BU114" s="9"/>
       <c r="BV114" s="9"/>
       <c r="BW114" s="9" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="BX114" s="9"/>
       <c r="BY114" s="9"/>
@@ -14853,6 +15347,9 @@
       <c r="Q115" s="12"/>
       <c r="R115" s="12"/>
       <c r="S115" s="12"/>
+      <c r="AI115" s="9" t="s">
+        <v>1854</v>
+      </c>
       <c r="AQ115" s="9" t="s">
         <v>933</v>
       </c>
@@ -14869,7 +15366,7 @@
       <c r="BU115" s="9"/>
       <c r="BV115" s="9"/>
       <c r="BW115" s="9" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="BX115" s="9"/>
       <c r="BY115" s="9"/>
@@ -14881,11 +15378,11 @@
       <c r="CE115" s="9"/>
     </row>
     <row r="116" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="20" t="s">
         <v>325</v>
       </c>
       <c r="B116" s="12"/>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="20" t="s">
         <v>326</v>
       </c>
       <c r="D116" s="12"/>
@@ -14904,6 +15401,9 @@
       <c r="Q116" s="12"/>
       <c r="R116" s="12"/>
       <c r="S116" s="12"/>
+      <c r="AI116" s="9" t="s">
+        <v>1855</v>
+      </c>
       <c r="AQ116" s="9" t="s">
         <v>934</v>
       </c>
@@ -14920,7 +15420,7 @@
       <c r="BU116" s="9"/>
       <c r="BV116" s="9"/>
       <c r="BW116" s="9" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="BX116" s="9"/>
       <c r="BY116" s="9"/>
@@ -14955,6 +15455,9 @@
       <c r="Q117" s="12"/>
       <c r="R117" s="12"/>
       <c r="S117" s="12"/>
+      <c r="AI117" s="9" t="s">
+        <v>1856</v>
+      </c>
       <c r="AQ117" s="9" t="s">
         <v>935</v>
       </c>
@@ -14971,7 +15474,7 @@
       <c r="BU117" s="9"/>
       <c r="BV117" s="9"/>
       <c r="BW117" s="9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="BX117" s="9"/>
       <c r="BY117" s="9"/>
@@ -14983,11 +15486,11 @@
       <c r="CE117" s="9"/>
     </row>
     <row r="118" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="20" t="s">
         <v>329</v>
       </c>
       <c r="B118" s="12"/>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D118" s="12"/>
@@ -15006,6 +15509,9 @@
       <c r="Q118" s="12"/>
       <c r="R118" s="12"/>
       <c r="S118" s="12"/>
+      <c r="AI118" s="29" t="s">
+        <v>1429</v>
+      </c>
       <c r="AQ118" s="9" t="s">
         <v>936</v>
       </c>
@@ -15022,7 +15528,7 @@
       <c r="BU118" s="9"/>
       <c r="BV118" s="9"/>
       <c r="BW118" s="9" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="BX118" s="9"/>
       <c r="BY118" s="9"/>
@@ -15073,7 +15579,7 @@
       <c r="BU119" s="9"/>
       <c r="BV119" s="9"/>
       <c r="BW119" s="9" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="BX119" s="9"/>
       <c r="BY119" s="9"/>
@@ -15085,11 +15591,11 @@
       <c r="CE119" s="9"/>
     </row>
     <row r="120" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B120" s="12"/>
-      <c r="C120" s="21" t="s">
+      <c r="C120" s="20" t="s">
         <v>334</v>
       </c>
       <c r="D120" s="12"/>
@@ -15124,7 +15630,7 @@
       <c r="BU120" s="9"/>
       <c r="BV120" s="9"/>
       <c r="BW120" s="9" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="BX120" s="9"/>
       <c r="BY120" s="9"/>
@@ -15175,7 +15681,7 @@
       <c r="BU121" s="9"/>
       <c r="BV121" s="9"/>
       <c r="BW121" s="9" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="BX121" s="9"/>
       <c r="BY121" s="9"/>
@@ -15187,11 +15693,11 @@
       <c r="CE121" s="9"/>
     </row>
     <row r="122" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="20" t="s">
         <v>337</v>
       </c>
       <c r="B122" s="12"/>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="20" t="s">
         <v>338</v>
       </c>
       <c r="D122" s="12"/>
@@ -15226,7 +15732,7 @@
       <c r="BU122" s="9"/>
       <c r="BV122" s="9"/>
       <c r="BW122" s="9" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="BX122" s="9"/>
       <c r="BY122" s="9"/>
@@ -15277,7 +15783,7 @@
       <c r="BU123" s="9"/>
       <c r="BV123" s="9"/>
       <c r="BW123" s="9" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="BX123" s="9"/>
       <c r="BY123" s="9"/>
@@ -15289,11 +15795,11 @@
       <c r="CE123" s="9"/>
     </row>
     <row r="124" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="20" t="s">
         <v>341</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="21" t="s">
+      <c r="C124" s="20" t="s">
         <v>342</v>
       </c>
       <c r="D124" s="12"/>
@@ -15328,7 +15834,7 @@
       <c r="BU124" s="9"/>
       <c r="BV124" s="9"/>
       <c r="BW124" s="9" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="BX124" s="9"/>
       <c r="BY124" s="9"/>
@@ -15391,11 +15897,11 @@
       <c r="CE125" s="9"/>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="20" t="s">
         <v>345</v>
       </c>
       <c r="B126" s="12"/>
-      <c r="C126" s="21" t="s">
+      <c r="C126" s="20" t="s">
         <v>346</v>
       </c>
       <c r="D126" s="12"/>
@@ -15430,7 +15936,7 @@
       <c r="BU126" s="9"/>
       <c r="BV126" s="9"/>
       <c r="BW126" s="9" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="BX126" s="9"/>
       <c r="BY126" s="9"/>
@@ -15481,7 +15987,7 @@
       <c r="BU127" s="9"/>
       <c r="BV127" s="9"/>
       <c r="BW127" s="9" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="BX127" s="9"/>
       <c r="BY127" s="9"/>
@@ -15493,11 +15999,11 @@
       <c r="CE127" s="9"/>
     </row>
     <row r="128" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="20" t="s">
         <v>349</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="21" t="s">
+      <c r="C128" s="20" t="s">
         <v>350</v>
       </c>
       <c r="D128" s="12"/>
@@ -15532,7 +16038,7 @@
       <c r="BU128" s="9"/>
       <c r="BV128" s="9"/>
       <c r="BW128" s="9" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="BX128" s="9"/>
       <c r="BY128" s="9"/>
@@ -15583,7 +16089,7 @@
       <c r="BU129" s="9"/>
       <c r="BV129" s="9"/>
       <c r="BW129" s="9" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="BX129" s="9"/>
       <c r="BY129" s="9"/>
@@ -15595,11 +16101,11 @@
       <c r="CE129" s="9"/>
     </row>
     <row r="130" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="20" t="s">
         <v>353</v>
       </c>
       <c r="B130" s="12"/>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="20" t="s">
         <v>354</v>
       </c>
       <c r="D130" s="12"/>
@@ -15634,7 +16140,7 @@
       <c r="BU130" s="9"/>
       <c r="BV130" s="9"/>
       <c r="BW130" s="9" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="BX130" s="9"/>
       <c r="BY130" s="9"/>
@@ -15685,7 +16191,7 @@
       <c r="BU131" s="9"/>
       <c r="BV131" s="9"/>
       <c r="BW131" s="9" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="BX131" s="9"/>
       <c r="BY131" s="9"/>
@@ -15697,11 +16203,11 @@
       <c r="CE131" s="9"/>
     </row>
     <row r="132" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="20" t="s">
         <v>357</v>
       </c>
       <c r="B132" s="12"/>
-      <c r="C132" s="21" t="s">
+      <c r="C132" s="20" t="s">
         <v>358</v>
       </c>
       <c r="D132" s="12"/>
@@ -15736,7 +16242,7 @@
       <c r="BU132" s="9"/>
       <c r="BV132" s="9"/>
       <c r="BW132" s="9" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="BX132" s="9"/>
       <c r="BY132" s="9"/>
@@ -15787,7 +16293,7 @@
       <c r="BU133" s="9"/>
       <c r="BV133" s="9"/>
       <c r="BW133" s="9" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="BX133" s="9"/>
       <c r="BY133" s="9"/>
@@ -15799,11 +16305,11 @@
       <c r="CE133" s="9"/>
     </row>
     <row r="134" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="20" t="s">
         <v>361</v>
       </c>
       <c r="B134" s="12"/>
-      <c r="C134" s="21" t="s">
+      <c r="C134" s="20" t="s">
         <v>362</v>
       </c>
       <c r="D134" s="12"/>
@@ -15838,7 +16344,7 @@
       <c r="BU134" s="9"/>
       <c r="BV134" s="9"/>
       <c r="BW134" s="9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="BX134" s="9"/>
       <c r="BY134" s="9"/>
@@ -15901,11 +16407,11 @@
       <c r="CE135" s="9"/>
     </row>
     <row r="136" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="20" t="s">
         <v>365</v>
       </c>
       <c r="B136" s="12"/>
-      <c r="C136" s="21" t="s">
+      <c r="C136" s="20" t="s">
         <v>366</v>
       </c>
       <c r="D136" s="12"/>
@@ -15940,7 +16446,7 @@
       <c r="BU136" s="9"/>
       <c r="BV136" s="9"/>
       <c r="BW136" s="9" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="BX136" s="9"/>
       <c r="BY136" s="9"/>
@@ -15991,7 +16497,7 @@
       <c r="BU137" s="9"/>
       <c r="BV137" s="9"/>
       <c r="BW137" s="9" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="BX137" s="9"/>
       <c r="BY137" s="9"/>
@@ -16003,11 +16509,11 @@
       <c r="CE137" s="9"/>
     </row>
     <row r="138" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A138" s="21" t="s">
+      <c r="A138" s="20" t="s">
         <v>369</v>
       </c>
       <c r="B138" s="12"/>
-      <c r="C138" s="21" t="s">
+      <c r="C138" s="20" t="s">
         <v>370</v>
       </c>
       <c r="D138" s="12"/>
@@ -16042,7 +16548,7 @@
       <c r="BU138" s="9"/>
       <c r="BV138" s="9"/>
       <c r="BW138" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="BX138" s="9"/>
       <c r="BY138" s="9"/>
@@ -16093,7 +16599,7 @@
       <c r="BU139" s="9"/>
       <c r="BV139" s="9"/>
       <c r="BW139" s="9" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="BX139" s="9"/>
       <c r="BY139" s="9"/>
@@ -16105,11 +16611,11 @@
       <c r="CE139" s="9"/>
     </row>
     <row r="140" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A140" s="21" t="s">
+      <c r="A140" s="20" t="s">
         <v>373</v>
       </c>
       <c r="B140" s="12"/>
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="20" t="s">
         <v>374</v>
       </c>
       <c r="D140" s="12"/>
@@ -16144,7 +16650,7 @@
       <c r="BU140" s="9"/>
       <c r="BV140" s="9"/>
       <c r="BW140" s="9" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="BX140" s="9"/>
       <c r="BY140" s="9"/>
@@ -16195,7 +16701,7 @@
       <c r="BU141" s="9"/>
       <c r="BV141" s="9"/>
       <c r="BW141" s="9" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BX141" s="9"/>
       <c r="BY141" s="9"/>
@@ -16207,11 +16713,11 @@
       <c r="CE141" s="9"/>
     </row>
     <row r="142" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="20" t="s">
         <v>377</v>
       </c>
       <c r="B142" s="12"/>
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="20" t="s">
         <v>378</v>
       </c>
       <c r="D142" s="12"/>
@@ -16246,7 +16752,7 @@
       <c r="BU142" s="9"/>
       <c r="BV142" s="9"/>
       <c r="BW142" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="BX142" s="9"/>
       <c r="BY142" s="9"/>
@@ -16297,7 +16803,7 @@
       <c r="BU143" s="9"/>
       <c r="BV143" s="9"/>
       <c r="BW143" s="9" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="BX143" s="9"/>
       <c r="BY143" s="9"/>
@@ -16309,11 +16815,11 @@
       <c r="CE143" s="9"/>
     </row>
     <row r="144" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="20" t="s">
         <v>381</v>
       </c>
       <c r="B144" s="12"/>
-      <c r="C144" s="21" t="s">
+      <c r="C144" s="20" t="s">
         <v>382</v>
       </c>
       <c r="D144" s="12"/>
@@ -16348,7 +16854,7 @@
       <c r="BU144" s="9"/>
       <c r="BV144" s="9"/>
       <c r="BW144" s="9" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="BX144" s="9"/>
       <c r="BY144" s="9"/>
@@ -16399,7 +16905,7 @@
       <c r="BU145" s="9"/>
       <c r="BV145" s="9"/>
       <c r="BW145" s="9" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="BX145" s="9"/>
       <c r="BY145" s="9"/>
@@ -16411,11 +16917,11 @@
       <c r="CE145" s="9"/>
     </row>
     <row r="146" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="20" t="s">
         <v>385</v>
       </c>
       <c r="B146" s="12"/>
-      <c r="C146" s="21" t="s">
+      <c r="C146" s="20" t="s">
         <v>386</v>
       </c>
       <c r="D146" s="12"/>
@@ -16501,7 +17007,7 @@
       <c r="BU147" s="9"/>
       <c r="BV147" s="9"/>
       <c r="BW147" s="9" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="BX147" s="9"/>
       <c r="BY147" s="9"/>
@@ -16513,11 +17019,11 @@
       <c r="CE147" s="9"/>
     </row>
     <row r="148" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A148" s="21" t="s">
+      <c r="A148" s="20" t="s">
         <v>389</v>
       </c>
       <c r="B148" s="12"/>
-      <c r="C148" s="21" t="s">
+      <c r="C148" s="20" t="s">
         <v>390</v>
       </c>
       <c r="D148" s="12"/>
@@ -16552,7 +17058,7 @@
       <c r="BU148" s="9"/>
       <c r="BV148" s="9"/>
       <c r="BW148" s="9" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="BX148" s="9"/>
       <c r="BY148" s="9"/>
@@ -16603,7 +17109,7 @@
       <c r="BU149" s="9"/>
       <c r="BV149" s="9"/>
       <c r="BW149" s="9" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="BX149" s="9"/>
       <c r="BY149" s="9"/>
@@ -16615,11 +17121,11 @@
       <c r="CE149" s="9"/>
     </row>
     <row r="150" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="20" t="s">
         <v>393</v>
       </c>
       <c r="B150" s="12"/>
-      <c r="C150" s="21" t="s">
+      <c r="C150" s="20" t="s">
         <v>394</v>
       </c>
       <c r="D150" s="12"/>
@@ -16654,7 +17160,7 @@
       <c r="BU150" s="9"/>
       <c r="BV150" s="9"/>
       <c r="BW150" s="9" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="BX150" s="9"/>
       <c r="BY150" s="9"/>
@@ -16705,7 +17211,7 @@
       <c r="BU151" s="9"/>
       <c r="BV151" s="9"/>
       <c r="BW151" s="9" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="BX151" s="9"/>
       <c r="BY151" s="9"/>
@@ -16717,11 +17223,11 @@
       <c r="CE151" s="9"/>
     </row>
     <row r="152" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="20" t="s">
         <v>397</v>
       </c>
       <c r="B152" s="12"/>
-      <c r="C152" s="21" t="s">
+      <c r="C152" s="20" t="s">
         <v>398</v>
       </c>
       <c r="D152" s="12"/>
@@ -16756,7 +17262,7 @@
       <c r="BU152" s="9"/>
       <c r="BV152" s="9"/>
       <c r="BW152" s="9" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="BX152" s="9"/>
       <c r="BY152" s="9"/>
@@ -16807,7 +17313,7 @@
       <c r="BU153" s="9"/>
       <c r="BV153" s="9"/>
       <c r="BW153" s="9" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="BX153" s="9"/>
       <c r="BY153" s="9"/>
@@ -16819,11 +17325,11 @@
       <c r="CE153" s="9"/>
     </row>
     <row r="154" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="20" t="s">
         <v>401</v>
       </c>
       <c r="B154" s="12"/>
-      <c r="C154" s="21" t="s">
+      <c r="C154" s="20" t="s">
         <v>402</v>
       </c>
       <c r="D154" s="12"/>
@@ -16858,7 +17364,7 @@
       <c r="BU154" s="9"/>
       <c r="BV154" s="9"/>
       <c r="BW154" s="9" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="BX154" s="9"/>
       <c r="BY154" s="9"/>
@@ -16909,7 +17415,7 @@
       <c r="BU155" s="9"/>
       <c r="BV155" s="9"/>
       <c r="BW155" s="9" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="BX155" s="9"/>
       <c r="BY155" s="9"/>
@@ -16921,11 +17427,11 @@
       <c r="CE155" s="9"/>
     </row>
     <row r="156" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="20" t="s">
         <v>405</v>
       </c>
       <c r="B156" s="12"/>
-      <c r="C156" s="21" t="s">
+      <c r="C156" s="20" t="s">
         <v>406</v>
       </c>
       <c r="D156" s="12"/>
@@ -16960,7 +17466,7 @@
       <c r="BU156" s="9"/>
       <c r="BV156" s="9"/>
       <c r="BW156" s="9" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="BX156" s="9"/>
       <c r="BY156" s="9"/>
@@ -17011,7 +17517,7 @@
       <c r="BU157" s="9"/>
       <c r="BV157" s="9"/>
       <c r="BW157" s="9" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="BX157" s="9"/>
       <c r="BY157" s="9"/>
@@ -17023,11 +17529,11 @@
       <c r="CE157" s="9"/>
     </row>
     <row r="158" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A158" s="21" t="s">
+      <c r="A158" s="20" t="s">
         <v>409</v>
       </c>
       <c r="B158" s="12"/>
-      <c r="C158" s="21" t="s">
+      <c r="C158" s="20" t="s">
         <v>410</v>
       </c>
       <c r="D158" s="12"/>
@@ -17062,7 +17568,7 @@
       <c r="BU158" s="9"/>
       <c r="BV158" s="9"/>
       <c r="BW158" s="9" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="BX158" s="9"/>
       <c r="BY158" s="9"/>
@@ -17113,7 +17619,7 @@
       <c r="BU159" s="9"/>
       <c r="BV159" s="9"/>
       <c r="BW159" s="9" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="BX159" s="9"/>
       <c r="BY159" s="9"/>
@@ -17125,11 +17631,11 @@
       <c r="CE159" s="9"/>
     </row>
     <row r="160" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A160" s="21" t="s">
+      <c r="A160" s="20" t="s">
         <v>413</v>
       </c>
       <c r="B160" s="12"/>
-      <c r="C160" s="21" t="s">
+      <c r="C160" s="20" t="s">
         <v>414</v>
       </c>
       <c r="D160" s="12"/>
@@ -17164,7 +17670,7 @@
       <c r="BU160" s="9"/>
       <c r="BV160" s="9"/>
       <c r="BW160" s="9" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="BX160" s="9"/>
       <c r="BY160" s="9"/>
@@ -17215,7 +17721,7 @@
       <c r="BU161" s="9"/>
       <c r="BV161" s="9"/>
       <c r="BW161" s="9" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="BX161" s="9"/>
       <c r="BY161" s="9"/>
@@ -17227,11 +17733,11 @@
       <c r="CE161" s="9"/>
     </row>
     <row r="162" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A162" s="21" t="s">
+      <c r="A162" s="20" t="s">
         <v>417</v>
       </c>
       <c r="B162" s="12"/>
-      <c r="C162" s="21" t="s">
+      <c r="C162" s="20" t="s">
         <v>418</v>
       </c>
       <c r="D162" s="12"/>
@@ -17266,7 +17772,7 @@
       <c r="BU162" s="9"/>
       <c r="BV162" s="9"/>
       <c r="BW162" s="9" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="BX162" s="9"/>
       <c r="BY162" s="9"/>
@@ -17317,7 +17823,7 @@
       <c r="BU163" s="9"/>
       <c r="BV163" s="9"/>
       <c r="BW163" s="9" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="BX163" s="9"/>
       <c r="BY163" s="9"/>
@@ -17329,11 +17835,11 @@
       <c r="CE163" s="9"/>
     </row>
     <row r="164" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="20" t="s">
         <v>421</v>
       </c>
       <c r="B164" s="12"/>
-      <c r="C164" s="21" t="s">
+      <c r="C164" s="20" t="s">
         <v>422</v>
       </c>
       <c r="D164" s="12"/>
@@ -17368,7 +17874,7 @@
       <c r="BU164" s="9"/>
       <c r="BV164" s="9"/>
       <c r="BW164" s="9" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="BX164" s="9"/>
       <c r="BY164" s="9"/>
@@ -17419,7 +17925,7 @@
       <c r="BU165" s="9"/>
       <c r="BV165" s="9"/>
       <c r="BW165" s="9" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="BX165" s="9"/>
       <c r="BY165" s="9"/>
@@ -17431,11 +17937,11 @@
       <c r="CE165" s="9"/>
     </row>
     <row r="166" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="20" t="s">
         <v>425</v>
       </c>
       <c r="B166" s="12"/>
-      <c r="C166" s="21" t="s">
+      <c r="C166" s="20" t="s">
         <v>426</v>
       </c>
       <c r="D166" s="12"/>
@@ -17470,7 +17976,7 @@
       <c r="BU166" s="9"/>
       <c r="BV166" s="9"/>
       <c r="BW166" s="9" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="BX166" s="9"/>
       <c r="BY166" s="9"/>
@@ -17521,7 +18027,7 @@
       <c r="BU167" s="9"/>
       <c r="BV167" s="9"/>
       <c r="BW167" s="9" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="BX167" s="9"/>
       <c r="BY167" s="9"/>
@@ -17533,11 +18039,11 @@
       <c r="CE167" s="9"/>
     </row>
     <row r="168" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A168" s="21" t="s">
+      <c r="A168" s="20" t="s">
         <v>429</v>
       </c>
       <c r="B168" s="12"/>
-      <c r="C168" s="21" t="s">
+      <c r="C168" s="20" t="s">
         <v>430</v>
       </c>
       <c r="D168" s="12"/>
@@ -17572,7 +18078,7 @@
       <c r="BU168" s="9"/>
       <c r="BV168" s="9"/>
       <c r="BW168" s="9" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="BX168" s="9"/>
       <c r="BY168" s="9"/>
@@ -17623,7 +18129,7 @@
       <c r="BU169" s="9"/>
       <c r="BV169" s="9"/>
       <c r="BW169" s="9" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="BX169" s="9"/>
       <c r="BY169" s="9"/>
@@ -17635,11 +18141,11 @@
       <c r="CE169" s="9"/>
     </row>
     <row r="170" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A170" s="21" t="s">
+      <c r="A170" s="20" t="s">
         <v>433</v>
       </c>
       <c r="B170" s="12"/>
-      <c r="C170" s="21" t="s">
+      <c r="C170" s="20" t="s">
         <v>434</v>
       </c>
       <c r="D170" s="12"/>
@@ -17674,7 +18180,7 @@
       <c r="BU170" s="9"/>
       <c r="BV170" s="9"/>
       <c r="BW170" s="9" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="BX170" s="9"/>
       <c r="BY170" s="9"/>
@@ -17725,7 +18231,7 @@
       <c r="BU171" s="9"/>
       <c r="BV171" s="9"/>
       <c r="BW171" s="9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="BX171" s="9"/>
       <c r="BY171" s="9"/>
@@ -17737,11 +18243,11 @@
       <c r="CE171" s="9"/>
     </row>
     <row r="172" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A172" s="21" t="s">
+      <c r="A172" s="20" t="s">
         <v>437</v>
       </c>
       <c r="B172" s="12"/>
-      <c r="C172" s="21" t="s">
+      <c r="C172" s="20" t="s">
         <v>438</v>
       </c>
       <c r="D172" s="12"/>
@@ -17793,11 +18299,11 @@
       </c>
     </row>
     <row r="174" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="20" t="s">
         <v>441</v>
       </c>
       <c r="B174" s="12"/>
-      <c r="C174" s="21" t="s">
+      <c r="C174" s="20" t="s">
         <v>442</v>
       </c>
       <c r="D174" s="12"/>
@@ -17849,11 +18355,11 @@
       </c>
     </row>
     <row r="176" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A176" s="21" t="s">
+      <c r="A176" s="20" t="s">
         <v>445</v>
       </c>
       <c r="B176" s="12"/>
-      <c r="C176" s="21" t="s">
+      <c r="C176" s="20" t="s">
         <v>446</v>
       </c>
       <c r="D176" s="12"/>
@@ -17905,11 +18411,11 @@
       </c>
     </row>
     <row r="178" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A178" s="21" t="s">
+      <c r="A178" s="20" t="s">
         <v>449</v>
       </c>
       <c r="B178" s="12"/>
-      <c r="C178" s="21" t="s">
+      <c r="C178" s="20" t="s">
         <v>450</v>
       </c>
       <c r="D178" s="12"/>
@@ -17961,11 +18467,11 @@
       </c>
     </row>
     <row r="180" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A180" s="21" t="s">
+      <c r="A180" s="20" t="s">
         <v>453</v>
       </c>
       <c r="B180" s="12"/>
-      <c r="C180" s="21" t="s">
+      <c r="C180" s="20" t="s">
         <v>454</v>
       </c>
       <c r="D180" s="12"/>
@@ -18017,11 +18523,11 @@
       </c>
     </row>
     <row r="182" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A182" s="21" t="s">
+      <c r="A182" s="20" t="s">
         <v>457</v>
       </c>
       <c r="B182" s="12"/>
-      <c r="C182" s="21" t="s">
+      <c r="C182" s="20" t="s">
         <v>458</v>
       </c>
       <c r="D182" s="12"/>
@@ -18073,11 +18579,11 @@
       </c>
     </row>
     <row r="184" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A184" s="21" t="s">
+      <c r="A184" s="20" t="s">
         <v>461</v>
       </c>
       <c r="B184" s="12"/>
-      <c r="C184" s="21" t="s">
+      <c r="C184" s="20" t="s">
         <v>462</v>
       </c>
       <c r="D184" s="12"/>
@@ -18129,11 +18635,11 @@
       </c>
     </row>
     <row r="186" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A186" s="21" t="s">
+      <c r="A186" s="20" t="s">
         <v>465</v>
       </c>
       <c r="B186" s="12"/>
-      <c r="C186" s="21" t="s">
+      <c r="C186" s="20" t="s">
         <v>466</v>
       </c>
       <c r="D186" s="12"/>
@@ -18185,11 +18691,11 @@
       </c>
     </row>
     <row r="188" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A188" s="21" t="s">
+      <c r="A188" s="20" t="s">
         <v>469</v>
       </c>
       <c r="B188" s="12"/>
-      <c r="C188" s="21" t="s">
+      <c r="C188" s="20" t="s">
         <v>470</v>
       </c>
       <c r="D188" s="12"/>
@@ -18241,11 +18747,11 @@
       </c>
     </row>
     <row r="190" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A190" s="21" t="s">
+      <c r="A190" s="20" t="s">
         <v>473</v>
       </c>
       <c r="B190" s="12"/>
-      <c r="C190" s="21" t="s">
+      <c r="C190" s="20" t="s">
         <v>474</v>
       </c>
       <c r="D190" s="12"/>
@@ -18297,11 +18803,11 @@
       </c>
     </row>
     <row r="192" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A192" s="21" t="s">
+      <c r="A192" s="20" t="s">
         <v>477</v>
       </c>
       <c r="B192" s="12"/>
-      <c r="C192" s="21" t="s">
+      <c r="C192" s="20" t="s">
         <v>478</v>
       </c>
       <c r="D192" s="12"/>
@@ -18353,11 +18859,11 @@
       </c>
     </row>
     <row r="194" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A194" s="21" t="s">
+      <c r="A194" s="20" t="s">
         <v>481</v>
       </c>
       <c r="B194" s="12"/>
-      <c r="C194" s="21" t="s">
+      <c r="C194" s="20" t="s">
         <v>482</v>
       </c>
       <c r="D194" s="12"/>
@@ -18409,11 +18915,11 @@
       </c>
     </row>
     <row r="196" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A196" s="21" t="s">
+      <c r="A196" s="20" t="s">
         <v>485</v>
       </c>
       <c r="B196" s="12"/>
-      <c r="C196" s="21" t="s">
+      <c r="C196" s="20" t="s">
         <v>486</v>
       </c>
       <c r="D196" s="12"/>
@@ -18465,11 +18971,11 @@
       </c>
     </row>
     <row r="198" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A198" s="21" t="s">
+      <c r="A198" s="20" t="s">
         <v>489</v>
       </c>
       <c r="B198" s="12"/>
-      <c r="C198" s="21" t="s">
+      <c r="C198" s="20" t="s">
         <v>490</v>
       </c>
       <c r="D198" s="12"/>
@@ -18521,11 +19027,11 @@
       </c>
     </row>
     <row r="200" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A200" s="21" t="s">
+      <c r="A200" s="20" t="s">
         <v>493</v>
       </c>
       <c r="B200" s="12"/>
-      <c r="C200" s="21" t="s">
+      <c r="C200" s="20" t="s">
         <v>494</v>
       </c>
       <c r="D200" s="12"/>
@@ -18577,11 +19083,11 @@
       </c>
     </row>
     <row r="202" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A202" s="21" t="s">
+      <c r="A202" s="20" t="s">
         <v>497</v>
       </c>
       <c r="B202" s="12"/>
-      <c r="C202" s="21" t="s">
+      <c r="C202" s="20" t="s">
         <v>498</v>
       </c>
       <c r="D202" s="12"/>
@@ -18633,11 +19139,11 @@
       </c>
     </row>
     <row r="204" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A204" s="21" t="s">
+      <c r="A204" s="20" t="s">
         <v>501</v>
       </c>
       <c r="B204" s="12"/>
-      <c r="C204" s="21" t="s">
+      <c r="C204" s="20" t="s">
         <v>502</v>
       </c>
       <c r="D204" s="12"/>
@@ -18689,11 +19195,11 @@
       </c>
     </row>
     <row r="206" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A206" s="21" t="s">
+      <c r="A206" s="20" t="s">
         <v>505</v>
       </c>
       <c r="B206" s="12"/>
-      <c r="C206" s="21" t="s">
+      <c r="C206" s="20" t="s">
         <v>506</v>
       </c>
       <c r="D206" s="12"/>
@@ -18745,11 +19251,11 @@
       </c>
     </row>
     <row r="208" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A208" s="21" t="s">
+      <c r="A208" s="20" t="s">
         <v>509</v>
       </c>
       <c r="B208" s="12"/>
-      <c r="C208" s="21" t="s">
+      <c r="C208" s="20" t="s">
         <v>510</v>
       </c>
       <c r="D208" s="12"/>
@@ -18801,11 +19307,11 @@
       </c>
     </row>
     <row r="210" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A210" s="21" t="s">
+      <c r="A210" s="20" t="s">
         <v>513</v>
       </c>
       <c r="B210" s="12"/>
-      <c r="C210" s="21" t="s">
+      <c r="C210" s="20" t="s">
         <v>514</v>
       </c>
       <c r="D210" s="12"/>
@@ -18857,11 +19363,11 @@
       </c>
     </row>
     <row r="212" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A212" s="21" t="s">
+      <c r="A212" s="20" t="s">
         <v>517</v>
       </c>
       <c r="B212" s="12"/>
-      <c r="C212" s="21" t="s">
+      <c r="C212" s="20" t="s">
         <v>518</v>
       </c>
       <c r="D212" s="12"/>
@@ -18913,11 +19419,11 @@
       </c>
     </row>
     <row r="214" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A214" s="21" t="s">
+      <c r="A214" s="20" t="s">
         <v>521</v>
       </c>
       <c r="B214" s="12"/>
-      <c r="C214" s="21" t="s">
+      <c r="C214" s="20" t="s">
         <v>522</v>
       </c>
       <c r="D214" s="12"/>
@@ -18969,11 +19475,11 @@
       </c>
     </row>
     <row r="216" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A216" s="21" t="s">
+      <c r="A216" s="20" t="s">
         <v>525</v>
       </c>
       <c r="B216" s="12"/>
-      <c r="C216" s="21" t="s">
+      <c r="C216" s="20" t="s">
         <v>526</v>
       </c>
       <c r="D216" s="12"/>
@@ -19025,11 +19531,11 @@
       </c>
     </row>
     <row r="218" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A218" s="21" t="s">
+      <c r="A218" s="20" t="s">
         <v>529</v>
       </c>
       <c r="B218" s="12"/>
-      <c r="C218" s="21" t="s">
+      <c r="C218" s="20" t="s">
         <v>530</v>
       </c>
       <c r="D218" s="12"/>
@@ -19081,11 +19587,11 @@
       </c>
     </row>
     <row r="220" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A220" s="21" t="s">
+      <c r="A220" s="20" t="s">
         <v>533</v>
       </c>
       <c r="B220" s="12"/>
-      <c r="C220" s="21" t="s">
+      <c r="C220" s="20" t="s">
         <v>534</v>
       </c>
       <c r="D220" s="12"/>
@@ -19137,11 +19643,11 @@
       </c>
     </row>
     <row r="222" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A222" s="21" t="s">
+      <c r="A222" s="20" t="s">
         <v>537</v>
       </c>
       <c r="B222" s="12"/>
-      <c r="C222" s="21" t="s">
+      <c r="C222" s="20" t="s">
         <v>538</v>
       </c>
       <c r="D222" s="12"/>
@@ -19193,11 +19699,11 @@
       </c>
     </row>
     <row r="224" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A224" s="21" t="s">
+      <c r="A224" s="20" t="s">
         <v>541</v>
       </c>
       <c r="B224" s="12"/>
-      <c r="C224" s="21" t="s">
+      <c r="C224" s="20" t="s">
         <v>542</v>
       </c>
       <c r="D224" s="12"/>
@@ -19249,11 +19755,11 @@
       </c>
     </row>
     <row r="226" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A226" s="21" t="s">
+      <c r="A226" s="20" t="s">
         <v>545</v>
       </c>
       <c r="B226" s="12"/>
-      <c r="C226" s="21" t="s">
+      <c r="C226" s="20" t="s">
         <v>546</v>
       </c>
       <c r="D226" s="12"/>
@@ -19305,11 +19811,11 @@
       </c>
     </row>
     <row r="228" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A228" s="21" t="s">
+      <c r="A228" s="20" t="s">
         <v>549</v>
       </c>
       <c r="B228" s="12"/>
-      <c r="C228" s="21" t="s">
+      <c r="C228" s="20" t="s">
         <v>550</v>
       </c>
       <c r="D228" s="12"/>
@@ -19361,11 +19867,11 @@
       </c>
     </row>
     <row r="230" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A230" s="21" t="s">
+      <c r="A230" s="20" t="s">
         <v>553</v>
       </c>
       <c r="B230" s="12"/>
-      <c r="C230" s="21" t="s">
+      <c r="C230" s="20" t="s">
         <v>554</v>
       </c>
       <c r="D230" s="12"/>
@@ -19417,11 +19923,11 @@
       </c>
     </row>
     <row r="232" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A232" s="21" t="s">
+      <c r="A232" s="20" t="s">
         <v>557</v>
       </c>
       <c r="B232" s="12"/>
-      <c r="C232" s="21" t="s">
+      <c r="C232" s="20" t="s">
         <v>558</v>
       </c>
       <c r="D232" s="12"/>
@@ -19473,11 +19979,11 @@
       </c>
     </row>
     <row r="234" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A234" s="21" t="s">
+      <c r="A234" s="20" t="s">
         <v>561</v>
       </c>
       <c r="B234" s="12"/>
-      <c r="C234" s="21" t="s">
+      <c r="C234" s="20" t="s">
         <v>562</v>
       </c>
       <c r="D234" s="12"/>
@@ -19529,11 +20035,11 @@
       </c>
     </row>
     <row r="236" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A236" s="21" t="s">
+      <c r="A236" s="20" t="s">
         <v>565</v>
       </c>
       <c r="B236" s="12"/>
-      <c r="C236" s="21" t="s">
+      <c r="C236" s="20" t="s">
         <v>566</v>
       </c>
       <c r="D236" s="12"/>
@@ -19585,11 +20091,11 @@
       </c>
     </row>
     <row r="238" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A238" s="21" t="s">
+      <c r="A238" s="20" t="s">
         <v>569</v>
       </c>
       <c r="B238" s="12"/>
-      <c r="C238" s="21" t="s">
+      <c r="C238" s="20" t="s">
         <v>570</v>
       </c>
       <c r="D238" s="12"/>
@@ -19641,11 +20147,11 @@
       </c>
     </row>
     <row r="240" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A240" s="21" t="s">
+      <c r="A240" s="20" t="s">
         <v>573</v>
       </c>
       <c r="B240" s="12"/>
-      <c r="C240" s="21" t="s">
+      <c r="C240" s="20" t="s">
         <v>574</v>
       </c>
       <c r="D240" s="12"/>
@@ -19697,11 +20203,11 @@
       </c>
     </row>
     <row r="242" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A242" s="21" t="s">
+      <c r="A242" s="20" t="s">
         <v>577</v>
       </c>
       <c r="B242" s="12"/>
-      <c r="C242" s="21" t="s">
+      <c r="C242" s="20" t="s">
         <v>578</v>
       </c>
       <c r="D242" s="12"/>
@@ -19753,11 +20259,11 @@
       </c>
     </row>
     <row r="244" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A244" s="21" t="s">
+      <c r="A244" s="20" t="s">
         <v>581</v>
       </c>
       <c r="B244" s="12"/>
-      <c r="C244" s="21" t="s">
+      <c r="C244" s="20" t="s">
         <v>582</v>
       </c>
       <c r="D244" s="12"/>
@@ -19809,11 +20315,11 @@
       </c>
     </row>
     <row r="246" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A246" s="21" t="s">
+      <c r="A246" s="20" t="s">
         <v>585</v>
       </c>
       <c r="B246" s="12"/>
-      <c r="C246" s="21" t="s">
+      <c r="C246" s="20" t="s">
         <v>586</v>
       </c>
       <c r="D246" s="12"/>
@@ -19865,11 +20371,11 @@
       </c>
     </row>
     <row r="248" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A248" s="21" t="s">
+      <c r="A248" s="20" t="s">
         <v>589</v>
       </c>
       <c r="B248" s="12"/>
-      <c r="C248" s="21" t="s">
+      <c r="C248" s="20" t="s">
         <v>590</v>
       </c>
       <c r="D248" s="12"/>
@@ -19921,11 +20427,11 @@
       </c>
     </row>
     <row r="250" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A250" s="21" t="s">
+      <c r="A250" s="20" t="s">
         <v>593</v>
       </c>
       <c r="B250" s="12"/>
-      <c r="C250" s="21" t="s">
+      <c r="C250" s="20" t="s">
         <v>594</v>
       </c>
       <c r="D250" s="12"/>
@@ -19977,11 +20483,11 @@
       </c>
     </row>
     <row r="252" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A252" s="21" t="s">
+      <c r="A252" s="20" t="s">
         <v>597</v>
       </c>
       <c r="B252" s="12"/>
-      <c r="C252" s="21" t="s">
+      <c r="C252" s="20" t="s">
         <v>598</v>
       </c>
       <c r="D252" s="12"/>
@@ -21271,7 +21777,6 @@
   <hyperlinks>
     <hyperlink ref="I5" r:id="rId1" xr:uid="{CD8C0F40-5433-4BED-8652-01EFA1D6EB1A}"/>
     <hyperlink ref="K5" r:id="rId2" display="Reference the ISO 3166-2 country subdivision code English short name using the respective ISO standard" xr:uid="{53BD7A20-F111-403B-AF54-EC6ED1B2F4D8}"/>
-    <hyperlink ref="AI5" r:id="rId3" xr:uid="{3329A783-2A6D-4802-8F51-CF530039A047}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/7_31_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/R2FT Enumerated Values/Enum List with R2 Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{55F88FD4-860F-4289-8195-ADD9A282EF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F2DD12-B6C9-4BE6-9B5A-7D9A53F3C3F7}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{5B2DF6FD-60F9-42F7-9793-6864D7C82CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D5A4D8-B432-4ABD-9874-5108CB21A4A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-28080" yWindow="1035" windowWidth="27285" windowHeight="14370" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="1775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="1905">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -4136,9 +4136,6 @@
     <t xml:space="preserve">Origination </t>
   </si>
   <si>
-    <t>UNFCCC Article 6.2 common nomenclatures (Activity Type)</t>
-  </si>
-  <si>
     <t>Validation of Project Design Document</t>
   </si>
   <si>
@@ -5361,13 +5358,406 @@
   </si>
   <si>
     <t>project_level_compliance_eligibility &amp; project_level_compliance_potential_ eligibility</t>
+  </si>
+  <si>
+    <t>Bundled Compost Production and Soil Application</t>
+  </si>
+  <si>
+    <t>Carbon Mineralization</t>
+  </si>
+  <si>
+    <t>Enhanced Rock Weathering</t>
+  </si>
+  <si>
+    <t>Feed Additives</t>
+  </si>
+  <si>
+    <t>Improved Irrigation Management</t>
+  </si>
+  <si>
+    <t>Manure Methane Digester</t>
+  </si>
+  <si>
+    <t>Nitrogen Management</t>
+  </si>
+  <si>
+    <t>Rice Emission Reductions</t>
+  </si>
+  <si>
+    <t>Solid Waste Separation</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture</t>
+  </si>
+  <si>
+    <t>Carbon Capture &amp; Enhanced Oil Recovery</t>
+  </si>
+  <si>
+    <t>Carbon Capture in Concrete</t>
+  </si>
+  <si>
+    <t>Carbon Capture in Plastic</t>
+  </si>
+  <si>
+    <t>N2O Destruction in Adipic Acid Production</t>
+  </si>
+  <si>
+    <t>N2O Destruction in Nitric Acid Production</t>
+  </si>
+  <si>
+    <t>Propylene Oxide Production</t>
+  </si>
+  <si>
+    <t>SF6 Replacement</t>
+  </si>
+  <si>
+    <t>Advanced Refrigerants</t>
+  </si>
+  <si>
+    <t>HFC Refrigerants Reclamation</t>
+  </si>
+  <si>
+    <t>HFC Replacement in Foam Production</t>
+  </si>
+  <si>
+    <t>HFC23 Destruction</t>
+  </si>
+  <si>
+    <t>Ozone Depleting Substances Recovery &amp; Destruction</t>
+  </si>
+  <si>
+    <t>Refrigerant Leak Detection</t>
+  </si>
+  <si>
+    <t>BECCS (Bioenergy with Carbon Capture and Storage)</t>
+  </si>
+  <si>
+    <t>Biomass Carbon Removal &amp; Storage (BiCRS)</t>
+  </si>
+  <si>
+    <t>Direct Air Capture</t>
+  </si>
+  <si>
+    <t>Ocean Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>River Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>Wastewater Alkalinity Enhancement</t>
+  </si>
+  <si>
+    <t>Afforestation/Reforestation</t>
+  </si>
+  <si>
+    <t>Avoided Forest Conversion</t>
+  </si>
+  <si>
+    <t>Avoided Grassland Conversion</t>
+  </si>
+  <si>
+    <t>Improved Forest Management</t>
+  </si>
+  <si>
+    <t>REDD+ (Reducing Emissions from Deforestation and Forest Degradation)</t>
+  </si>
+  <si>
+    <t>REDD+ Jurisdictional</t>
+  </si>
+  <si>
+    <t>Sustainable Grassland Management</t>
+  </si>
+  <si>
+    <t>Wetland Restoration</t>
+  </si>
+  <si>
+    <t>Biodigesters</t>
+  </si>
+  <si>
+    <t>Bundled Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Clean Water</t>
+  </si>
+  <si>
+    <t>Community Boreholes</t>
+  </si>
+  <si>
+    <t>Cookstoves</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>Weatherization</t>
+  </si>
+  <si>
+    <t>Aluminum Smelters Emission Reductions</t>
+  </si>
+  <si>
+    <t>Brick Manufacturing Emission Reductions</t>
+  </si>
+  <si>
+    <t>Carbon-Absorbing Concrete</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Fuel Switching</t>
+  </si>
+  <si>
+    <t>Grid Expansion &amp; Mini-Grids</t>
+  </si>
+  <si>
+    <t>Leak Detection &amp; Repair in Gas Systems</t>
+  </si>
+  <si>
+    <t>Lower Carbon Cement &amp; Concrete</t>
+  </si>
+  <si>
+    <t>Mine Methane Capture</t>
+  </si>
+  <si>
+    <t>Natural Gas Electricity Generation</t>
+  </si>
+  <si>
+    <t>Oil Recycling</t>
+  </si>
+  <si>
+    <t>Plugging Oil &amp; Gas Wells</t>
+  </si>
+  <si>
+    <t>Pneumatic Retrofit</t>
+  </si>
+  <si>
+    <t>Road Construction Emission Reductions</t>
+  </si>
+  <si>
+    <t>University Campus Emission Reductions</t>
+  </si>
+  <si>
+    <t>Waste Gas Recovery</t>
+  </si>
+  <si>
+    <t>Waste Heat Recovery</t>
+  </si>
+  <si>
+    <t>Energy Storage</t>
+  </si>
+  <si>
+    <t>Hydropower</t>
+  </si>
+  <si>
+    <t>RE Bundled (Bundled Renewables)</t>
+  </si>
+  <si>
+    <t>Solar - Centralized</t>
+  </si>
+  <si>
+    <t>Solar - Distributed</t>
+  </si>
+  <si>
+    <t>Solar Lighting</t>
+  </si>
+  <si>
+    <t>Solar Water Heaters</t>
+  </si>
+  <si>
+    <t>Bicycles</t>
+  </si>
+  <si>
+    <t>Electric Vehicles &amp; Charging</t>
+  </si>
+  <si>
+    <t>Fleet Efficiency</t>
+  </si>
+  <si>
+    <t>Fuel Transport</t>
+  </si>
+  <si>
+    <t>Mass Transit</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Truck Stop Electrification</t>
+  </si>
+  <si>
+    <t>Biochar</t>
+  </si>
+  <si>
+    <t>Composting</t>
+  </si>
+  <si>
+    <t>Landfill Methane</t>
+  </si>
+  <si>
+    <t>Methane Recovery in Wastewater</t>
+  </si>
+  <si>
+    <t>Waste Diversion</t>
+  </si>
+  <si>
+    <t>Waste Incineration</t>
+  </si>
+  <si>
+    <t>Waste Recycling</t>
+  </si>
+  <si>
+    <t>Waste Reduction</t>
+  </si>
+  <si>
+    <t>current_validation_stage</t>
+  </si>
+  <si>
+    <t>current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_stages</t>
+  </si>
+  <si>
+    <t>Desk review</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>Project validation</t>
+  </si>
+  <si>
+    <t>1. Energy industries (renewable - / non-renewable sources)</t>
+  </si>
+  <si>
+    <t>On-site audits and interviews</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Program validation</t>
+  </si>
+  <si>
+    <t>2. Energy distribution</t>
+  </si>
+  <si>
+    <t>Public comment period</t>
+  </si>
+  <si>
+    <t>3. Energy demand</t>
+  </si>
+  <si>
+    <t>Resolution of findings</t>
+  </si>
+  <si>
+    <t>4. Manufacturing industries</t>
+  </si>
+  <si>
+    <t>Final validation report issued</t>
+  </si>
+  <si>
+    <t>5. Chemical industry</t>
+  </si>
+  <si>
+    <t>6. Construction</t>
+  </si>
+  <si>
+    <t>7. Transport</t>
+  </si>
+  <si>
+    <t>8. Mining/Mineral production</t>
+  </si>
+  <si>
+    <t>9. Metal production</t>
+  </si>
+  <si>
+    <t>10. Fugitive emissions from fuels (solid, oil and gas)</t>
+  </si>
+  <si>
+    <t>11. Fugitive emissions from production and consumption of halocarbons and sulphur hexafluoride</t>
+  </si>
+  <si>
+    <t>12. Solvents use</t>
+  </si>
+  <si>
+    <t>13. Waste handling and disposal</t>
+  </si>
+  <si>
+    <t>14. Afforestation and reforestation</t>
+  </si>
+  <si>
+    <t>15. Agriculture</t>
+  </si>
+  <si>
+    <t>verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>Carbon removal</t>
+  </si>
+  <si>
+    <t>Emission reduction</t>
+  </si>
+  <si>
+    <t>Emission avoidance</t>
+  </si>
+  <si>
+    <t>Biodiversity benefit</t>
+  </si>
+  <si>
+    <t>Water conservation</t>
+  </si>
+  <si>
+    <t>Community benefit</t>
+  </si>
+  <si>
+    <t>tCO2e (Metric tonnes of CO2 equivalent)</t>
+  </si>
+  <si>
+    <t>kgCO2e (Kilograms of CO2 equivalent)</t>
+  </si>
+  <si>
+    <t>MWh (Megawatt-hours)</t>
+  </si>
+  <si>
+    <t>m3_biogas (Cubic meters of biogas)</t>
+  </si>
+  <si>
+    <t>ha (Hectares)</t>
+  </si>
+  <si>
+    <t>kg_plastic (Kilograms of plastic recovered)</t>
+  </si>
+  <si>
+    <t>Pass (Fully compliant with zero reserves)</t>
+  </si>
+  <si>
+    <t>Pass with reservations (Approved, but with Forward Action Requests / FARs)</t>
+  </si>
+  <si>
+    <t>Requires corrective action (On hold pending CAR resolution)</t>
+  </si>
+  <si>
+    <t>Fail (Non-compliant / verification rejected)</t>
+  </si>
+  <si>
+    <t>Pending review (Audit currently in progress)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5455,6 +5845,13 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5500,7 +5897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5532,7 +5929,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5559,6 +5955,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5894,7 +6312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B85F238-80B8-43F8-AABF-7B9427088CCA}">
-  <dimension ref="A1:DQ500"/>
+  <dimension ref="A1:DU500"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="26.08984375" bestFit="1" customWidth="1"/>
@@ -5936,9 +6354,17 @@
     <col min="108" max="108" width="12.90625" customWidth="1"/>
     <col min="109" max="109" width="33.7265625" customWidth="1"/>
     <col min="110" max="110" width="24" customWidth="1"/>
+    <col min="111" max="111" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="33.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5961,7 +6387,7 @@
       <c r="R1" s="12"/>
       <c r="S1" s="12"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:125" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -5982,7 +6408,7 @@
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
     </row>
-    <row r="3" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>1332</v>
       </c>
@@ -6048,10 +6474,10 @@
         <v>1349</v>
       </c>
       <c r="AK3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AM3" t="s">
         <v>1431</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>1432</v>
       </c>
       <c r="AO3" t="s">
         <v>1350</v>
@@ -6087,95 +6513,125 @@
         <v>1358</v>
       </c>
       <c r="BK3" s="9" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="BL3" s="9"/>
       <c r="BM3" s="9" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="BN3" s="9"/>
       <c r="BO3" s="9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="BP3" s="9"/>
       <c r="BQ3" s="9" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="BR3" s="9"/>
       <c r="BS3" s="9" t="s">
+        <v>1436</v>
+      </c>
+      <c r="BT3" s="9"/>
+      <c r="BU3" s="23" t="s">
         <v>1437</v>
       </c>
-      <c r="BT3" s="9"/>
-      <c r="BU3" s="24" t="s">
+      <c r="BV3" s="23"/>
+      <c r="BW3" s="9" t="s">
         <v>1438</v>
-      </c>
-      <c r="BV3" s="24"/>
-      <c r="BW3" s="9" t="s">
-        <v>1439</v>
       </c>
       <c r="BX3" s="9"/>
       <c r="BY3" s="9" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="BZ3" s="9"/>
       <c r="CA3" s="9" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="CB3" s="9"/>
       <c r="CC3" s="9" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="CD3" s="9"/>
       <c r="CE3" s="9" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="CG3" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="CI3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="CK3" s="22" t="s">
+        <v>1683</v>
+      </c>
+      <c r="CM3" t="s">
         <v>1685</v>
       </c>
-      <c r="CK3" s="23" t="s">
-        <v>1684</v>
-      </c>
-      <c r="CM3" t="s">
+      <c r="CO3" t="s">
         <v>1686</v>
       </c>
-      <c r="CO3" t="s">
-        <v>1687</v>
-      </c>
       <c r="CQ3" t="s">
-        <v>1704</v>
-      </c>
-      <c r="CS3" s="28" t="s">
+        <v>1703</v>
+      </c>
+      <c r="CS3" s="27" t="s">
+        <v>1708</v>
+      </c>
+      <c r="CT3" s="27"/>
+      <c r="CU3" s="27" t="s">
         <v>1709</v>
       </c>
-      <c r="CT3" s="28"/>
-      <c r="CU3" s="28" t="s">
+      <c r="CV3" s="27"/>
+      <c r="CW3" s="27" t="s">
         <v>1710</v>
       </c>
-      <c r="CV3" s="28"/>
-      <c r="CW3" s="28" t="s">
+      <c r="CX3" s="27"/>
+      <c r="CY3" s="27" t="s">
         <v>1711</v>
       </c>
-      <c r="CX3" s="28"/>
-      <c r="CY3" s="28" t="s">
-        <v>1712</v>
-      </c>
-      <c r="CZ3" s="28"/>
-      <c r="DA3" s="28" t="s">
+      <c r="CZ3" s="27"/>
+      <c r="DA3" s="27" t="s">
+        <v>1772</v>
+      </c>
+      <c r="DB3" s="27"/>
+      <c r="DC3" s="27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="DD3" s="27"/>
+      <c r="DE3" s="27" t="s">
         <v>1773</v>
       </c>
-      <c r="DB3" s="28"/>
-      <c r="DC3" s="28" t="s">
-        <v>1714</v>
-      </c>
-      <c r="DD3" s="28"/>
-      <c r="DE3" s="28" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="4" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="DG3" s="9" t="s">
+        <v>1857</v>
+      </c>
+      <c r="DH3" s="34"/>
+      <c r="DI3" s="35" t="s">
+        <v>1858</v>
+      </c>
+      <c r="DJ3" s="34"/>
+      <c r="DK3" s="19" t="s">
+        <v>1353</v>
+      </c>
+      <c r="DL3" s="34"/>
+      <c r="DM3" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="DN3" s="34"/>
+      <c r="DO3" s="9" t="s">
+        <v>1860</v>
+      </c>
+      <c r="DQ3" s="34" t="s">
+        <v>1885</v>
+      </c>
+      <c r="DR3" s="34"/>
+      <c r="DS3" s="34" t="s">
+        <v>1886</v>
+      </c>
+      <c r="DT3" s="34"/>
+      <c r="DU3" s="34" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -6291,55 +6747,55 @@
       <c r="BI4" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="BK4" s="25" t="s">
+      <c r="BK4" s="24" t="s">
+        <v>1432</v>
+      </c>
+      <c r="BL4" s="9"/>
+      <c r="BM4" s="24" t="s">
         <v>1433</v>
       </c>
-      <c r="BL4" s="9"/>
-      <c r="BM4" s="25" t="s">
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24" t="s">
         <v>1434</v>
       </c>
-      <c r="BN4" s="25"/>
-      <c r="BO4" s="25" t="s">
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24" t="s">
         <v>1435</v>
       </c>
-      <c r="BP4" s="25"/>
-      <c r="BQ4" s="25" t="s">
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24" t="s">
         <v>1436</v>
       </c>
-      <c r="BR4" s="25"/>
-      <c r="BS4" s="25" t="s">
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="25" t="s">
         <v>1437</v>
       </c>
-      <c r="BT4" s="25"/>
-      <c r="BU4" s="26" t="s">
+      <c r="BV4" s="25"/>
+      <c r="BW4" s="24" t="s">
         <v>1438</v>
       </c>
-      <c r="BV4" s="26"/>
-      <c r="BW4" s="25" t="s">
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24" t="s">
         <v>1439</v>
       </c>
-      <c r="BX4" s="25"/>
-      <c r="BY4" s="25" t="s">
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24" t="s">
         <v>1440</v>
       </c>
-      <c r="BZ4" s="25"/>
-      <c r="CA4" s="25" t="s">
+      <c r="CB4" s="24"/>
+      <c r="CC4" s="24" t="s">
         <v>1441</v>
       </c>
-      <c r="CB4" s="25"/>
-      <c r="CC4" s="25" t="s">
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="24" t="s">
         <v>1442</v>
       </c>
-      <c r="CD4" s="25"/>
-      <c r="CE4" s="25" t="s">
-        <v>1443</v>
-      </c>
       <c r="CG4" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="CH4" s="1"/>
       <c r="CI4" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="CJ4" s="1"/>
       <c r="CK4" s="1" t="s">
@@ -6347,58 +6803,78 @@
       </c>
       <c r="CL4" s="1"/>
       <c r="CM4" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="CN4" s="1"/>
       <c r="CO4" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="CP4" s="1"/>
       <c r="CQ4" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="CR4" s="1"/>
-      <c r="CS4" s="27" t="s">
+      <c r="CS4" s="26" t="s">
+        <v>1708</v>
+      </c>
+      <c r="CT4" s="26"/>
+      <c r="CU4" s="26" t="s">
         <v>1709</v>
       </c>
-      <c r="CT4" s="27"/>
-      <c r="CU4" s="27" t="s">
+      <c r="CV4" s="26"/>
+      <c r="CW4" s="26" t="s">
         <v>1710</v>
       </c>
-      <c r="CV4" s="27"/>
-      <c r="CW4" s="27" t="s">
+      <c r="CX4" s="26"/>
+      <c r="CY4" s="26" t="s">
         <v>1711</v>
       </c>
-      <c r="CX4" s="27"/>
-      <c r="CY4" s="27" t="s">
+      <c r="CZ4" s="26"/>
+      <c r="DA4" s="26" t="s">
         <v>1712</v>
       </c>
-      <c r="CZ4" s="27"/>
-      <c r="DA4" s="27" t="s">
+      <c r="DB4" s="26"/>
+      <c r="DC4" s="26" t="s">
         <v>1713</v>
       </c>
-      <c r="DB4" s="27"/>
-      <c r="DC4" s="27" t="s">
+      <c r="DD4" s="26"/>
+      <c r="DE4" s="26" t="s">
         <v>1714</v>
       </c>
-      <c r="DD4" s="27"/>
-      <c r="DE4" s="27" t="s">
-        <v>1715</v>
-      </c>
-      <c r="DF4" s="27"/>
-      <c r="DG4" s="1"/>
+      <c r="DF4" s="26"/>
+      <c r="DG4" s="24" t="s">
+        <v>1857</v>
+      </c>
       <c r="DH4" s="1"/>
-      <c r="DI4" s="1"/>
+      <c r="DI4" s="31" t="s">
+        <v>1858</v>
+      </c>
       <c r="DJ4" s="1"/>
-      <c r="DK4" s="1"/>
+      <c r="DK4" s="32" t="s">
+        <v>1353</v>
+      </c>
       <c r="DL4" s="1"/>
-      <c r="DM4" s="1"/>
+      <c r="DM4" s="24" t="s">
+        <v>1859</v>
+      </c>
       <c r="DN4" s="1"/>
-      <c r="DO4" s="1"/>
+      <c r="DO4" s="24" t="s">
+        <v>1860</v>
+      </c>
       <c r="DP4" s="1"/>
-      <c r="DQ4" s="1"/>
-    </row>
-    <row r="5" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="DQ4" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="DR4" s="1"/>
+      <c r="DS4" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="DT4" s="1"/>
+      <c r="DU4" s="1" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="5" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -6462,8 +6938,8 @@
         <v>619</v>
       </c>
       <c r="AH5" s="9"/>
-      <c r="AI5" s="17" t="s">
-        <v>1366</v>
+      <c r="AI5" s="10" t="s">
+        <v>1379</v>
       </c>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9" t="s">
@@ -6491,33 +6967,33 @@
         <v>1326</v>
       </c>
       <c r="AY5" s="9" t="s">
+        <v>1366</v>
+      </c>
+      <c r="BA5" s="17" t="s">
         <v>1367</v>
       </c>
-      <c r="BA5" s="18" t="s">
+      <c r="BC5" s="18" t="s">
         <v>1368</v>
       </c>
-      <c r="BC5" s="19" t="s">
+      <c r="BE5" t="s">
         <v>1369</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BG5" s="9" t="s">
         <v>1370</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BI5" t="s">
         <v>1371</v>
       </c>
-      <c r="BI5" t="s">
-        <v>1372</v>
-      </c>
       <c r="BK5" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="BL5" s="9"/>
       <c r="BM5" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="BN5" s="9"/>
       <c r="BO5" s="9" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="BP5" s="9"/>
       <c r="BQ5" s="9" t="s">
@@ -6525,85 +7001,109 @@
       </c>
       <c r="BR5" s="9"/>
       <c r="BS5" s="9" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="BT5" s="9"/>
       <c r="BU5" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BV5" s="9"/>
       <c r="BW5" s="9" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="BX5" s="9"/>
       <c r="BY5" s="9" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="BZ5" s="9"/>
       <c r="CA5" s="9" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="CB5" s="9"/>
       <c r="CC5" s="9" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="CD5" s="9"/>
       <c r="CE5" s="9" t="s">
-        <v>1452</v>
-      </c>
-      <c r="CG5" s="20" t="s">
-        <v>1647</v>
-      </c>
-      <c r="CI5" s="20" t="s">
-        <v>1667</v>
-      </c>
-      <c r="CK5" s="20" t="s">
-        <v>1678</v>
-      </c>
-      <c r="CM5" s="20" t="s">
-        <v>1699</v>
-      </c>
-      <c r="CO5" s="20" t="s">
-        <v>1690</v>
-      </c>
-      <c r="CQ5" s="20" t="s">
-        <v>1706</v>
-      </c>
-      <c r="CS5" s="28" t="s">
+        <v>1451</v>
+      </c>
+      <c r="CG5" s="19" t="s">
+        <v>1646</v>
+      </c>
+      <c r="CI5" s="19" t="s">
+        <v>1666</v>
+      </c>
+      <c r="CK5" s="19" t="s">
+        <v>1677</v>
+      </c>
+      <c r="CM5" s="19" t="s">
+        <v>1698</v>
+      </c>
+      <c r="CO5" s="19" t="s">
+        <v>1689</v>
+      </c>
+      <c r="CQ5" s="19" t="s">
+        <v>1705</v>
+      </c>
+      <c r="CS5" s="27" t="s">
+        <v>1715</v>
+      </c>
+      <c r="CT5" s="27"/>
+      <c r="CU5" s="27" t="s">
         <v>1716</v>
       </c>
-      <c r="CT5" s="28"/>
-      <c r="CU5" s="28" t="s">
+      <c r="CV5" s="27"/>
+      <c r="CW5" s="27" t="s">
         <v>1717</v>
       </c>
-      <c r="CV5" s="28"/>
-      <c r="CW5" s="28" t="s">
+      <c r="CX5" s="27"/>
+      <c r="CY5" s="28" t="s">
         <v>1718</v>
       </c>
-      <c r="CX5" s="28"/>
-      <c r="CY5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="CZ5" s="29"/>
-      <c r="DA5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DB5" s="29"/>
-      <c r="DC5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DD5" s="29"/>
-      <c r="DE5" s="29" t="s">
-        <v>1719</v>
-      </c>
-      <c r="DF5" s="29"/>
-    </row>
-    <row r="6" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="21" t="s">
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28" t="s">
+        <v>1718</v>
+      </c>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="9" t="s">
+        <v>1861</v>
+      </c>
+      <c r="DI5" s="33" t="s">
+        <v>1862</v>
+      </c>
+      <c r="DK5" s="9" t="s">
+        <v>1863</v>
+      </c>
+      <c r="DM5" s="9" t="s">
+        <v>1864</v>
+      </c>
+      <c r="DO5" s="9" t="s">
+        <v>1861</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="DS5" s="36" t="s">
+        <v>1894</v>
+      </c>
+      <c r="DU5" s="36" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="12"/>
@@ -6644,12 +7144,12 @@
         <v>625</v>
       </c>
       <c r="AA6" t="s">
-        <v>1373</v>
-      </c>
-      <c r="AC6" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AC6" s="21" t="s">
         <v>627</v>
       </c>
-      <c r="AD6" s="22"/>
+      <c r="AD6" s="21"/>
       <c r="AE6" s="9" t="s">
         <v>628</v>
       </c>
@@ -6658,7 +7158,9 @@
         <v>629</v>
       </c>
       <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="AI6" s="10" t="s">
+        <v>1385</v>
+      </c>
       <c r="AJ6" s="9"/>
       <c r="AK6" t="s">
         <v>630</v>
@@ -6683,33 +7185,33 @@
         <v>1327</v>
       </c>
       <c r="AY6" s="9" t="s">
+        <v>1373</v>
+      </c>
+      <c r="BA6" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="BC6" s="18" t="s">
         <v>1374</v>
       </c>
-      <c r="BA6" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="BC6" s="19" t="s">
+      <c r="BE6" t="s">
         <v>1375</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BG6" s="9" t="s">
         <v>1376</v>
       </c>
-      <c r="BG6" s="9" t="s">
+      <c r="BI6" t="s">
         <v>1377</v>
       </c>
-      <c r="BI6" t="s">
-        <v>1378</v>
-      </c>
       <c r="BK6" s="9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="BL6" s="9"/>
       <c r="BM6" s="9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="BN6" s="9"/>
       <c r="BO6" s="9" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="BP6" s="9"/>
       <c r="BQ6" s="9" t="s">
@@ -6717,78 +7219,102 @@
       </c>
       <c r="BR6" s="9"/>
       <c r="BS6" s="9" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="BT6" s="9"/>
       <c r="BU6" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="BV6" s="9"/>
       <c r="BW6" s="9" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="BX6" s="9"/>
       <c r="BY6" s="9" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="BZ6" s="9"/>
       <c r="CA6" s="9" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="CB6" s="9"/>
       <c r="CC6" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="CD6" s="9"/>
       <c r="CE6" s="9" t="s">
-        <v>1461</v>
-      </c>
-      <c r="CG6" s="20" t="s">
-        <v>1648</v>
-      </c>
-      <c r="CI6" s="20" t="s">
-        <v>1668</v>
-      </c>
-      <c r="CK6" s="20" t="s">
-        <v>1679</v>
-      </c>
-      <c r="CM6" s="20" t="s">
-        <v>1700</v>
-      </c>
-      <c r="CO6" s="20" t="s">
-        <v>1691</v>
-      </c>
-      <c r="CQ6" s="20" t="s">
-        <v>1707</v>
-      </c>
-      <c r="CS6" s="29" t="s">
+        <v>1460</v>
+      </c>
+      <c r="CG6" s="19" t="s">
+        <v>1647</v>
+      </c>
+      <c r="CI6" s="19" t="s">
+        <v>1667</v>
+      </c>
+      <c r="CK6" s="19" t="s">
+        <v>1678</v>
+      </c>
+      <c r="CM6" s="19" t="s">
+        <v>1699</v>
+      </c>
+      <c r="CO6" s="19" t="s">
+        <v>1690</v>
+      </c>
+      <c r="CQ6" s="19" t="s">
+        <v>1706</v>
+      </c>
+      <c r="CS6" s="28" t="s">
+        <v>1719</v>
+      </c>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="27" t="s">
         <v>1720</v>
       </c>
-      <c r="CT6" s="29"/>
-      <c r="CU6" s="28" t="s">
+      <c r="CV6" s="27"/>
+      <c r="CW6" s="27"/>
+      <c r="CX6" s="27"/>
+      <c r="CY6" s="28" t="s">
         <v>1721</v>
       </c>
-      <c r="CV6" s="28"/>
-      <c r="CW6" s="28"/>
-      <c r="CX6" s="28"/>
-      <c r="CY6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="CZ6" s="29"/>
-      <c r="DA6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DB6" s="29"/>
-      <c r="DC6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DD6" s="29"/>
-      <c r="DE6" s="29" t="s">
-        <v>1722</v>
-      </c>
-      <c r="DF6" s="29"/>
-    </row>
-    <row r="7" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28" t="s">
+        <v>1721</v>
+      </c>
+      <c r="DF6" s="28"/>
+      <c r="DG6" s="9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="DI6" s="33" t="s">
+        <v>1866</v>
+      </c>
+      <c r="DK6" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="DM6" s="9" t="s">
+        <v>1868</v>
+      </c>
+      <c r="DO6" s="9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>1889</v>
+      </c>
+      <c r="DS6" s="36" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DU6" s="36" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>29</v>
       </c>
@@ -6831,10 +7357,10 @@
       <c r="Y7" t="s">
         <v>636</v>
       </c>
-      <c r="AA7" s="23" t="s">
-        <v>1379</v>
-      </c>
-      <c r="AB7" s="23"/>
+      <c r="AA7" s="22" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AB7" s="22"/>
       <c r="AC7" s="9" t="s">
         <v>638</v>
       </c>
@@ -6847,8 +7373,8 @@
         <v>640</v>
       </c>
       <c r="AH7" s="9"/>
-      <c r="AI7" s="10" t="s">
-        <v>1380</v>
+      <c r="AI7" s="11" t="s">
+        <v>1389</v>
       </c>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9" t="s">
@@ -6875,27 +7401,27 @@
         <v>1328</v>
       </c>
       <c r="AY7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="BA7" s="17" t="s">
         <v>1381</v>
       </c>
-      <c r="BA7" s="18" t="s">
+      <c r="BE7" t="s">
         <v>1382</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BG7" s="9" t="s">
         <v>1383</v>
       </c>
-      <c r="BG7" s="9" t="s">
-        <v>1384</v>
-      </c>
       <c r="BK7" s="9" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="BL7" s="9"/>
       <c r="BM7" s="9" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="BN7" s="9"/>
       <c r="BO7" s="9" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="BP7" s="9"/>
       <c r="BQ7" s="9" t="s">
@@ -6903,83 +7429,104 @@
       </c>
       <c r="BR7" s="9"/>
       <c r="BS7" s="9" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="BT7" s="9"/>
       <c r="BU7" s="9" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="BV7" s="9"/>
       <c r="BW7" s="9" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="BX7" s="9"/>
       <c r="BY7" s="9" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="BZ7" s="9"/>
       <c r="CA7" s="9" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="CB7" s="9"/>
       <c r="CC7" s="9" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="CD7" s="9"/>
       <c r="CE7" s="9" t="s">
-        <v>1470</v>
-      </c>
-      <c r="CG7" s="20" t="s">
-        <v>1649</v>
-      </c>
-      <c r="CI7" s="20" t="s">
-        <v>1669</v>
-      </c>
-      <c r="CK7" s="20" t="s">
-        <v>1680</v>
-      </c>
-      <c r="CM7" s="20" t="s">
-        <v>1701</v>
-      </c>
-      <c r="CO7" s="20" t="s">
-        <v>1692</v>
-      </c>
-      <c r="CQ7" s="20" t="s">
-        <v>1708</v>
-      </c>
-      <c r="CS7" s="29" t="s">
+        <v>1469</v>
+      </c>
+      <c r="CG7" s="19" t="s">
+        <v>1648</v>
+      </c>
+      <c r="CI7" s="19" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CK7" s="19" t="s">
+        <v>1679</v>
+      </c>
+      <c r="CM7" s="19" t="s">
+        <v>1700</v>
+      </c>
+      <c r="CO7" s="19" t="s">
+        <v>1691</v>
+      </c>
+      <c r="CQ7" s="19" t="s">
+        <v>1707</v>
+      </c>
+      <c r="CS7" s="28" t="s">
+        <v>1722</v>
+      </c>
+      <c r="CT7" s="28"/>
+      <c r="CU7" s="27" t="s">
         <v>1723</v>
       </c>
-      <c r="CT7" s="29"/>
-      <c r="CU7" s="28" t="s">
+      <c r="CV7" s="27"/>
+      <c r="CW7" s="27"/>
+      <c r="CX7" s="27"/>
+      <c r="CY7" s="28" t="s">
         <v>1724</v>
       </c>
-      <c r="CV7" s="28"/>
-      <c r="CW7" s="28"/>
-      <c r="CX7" s="28"/>
-      <c r="CY7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="CZ7" s="29"/>
-      <c r="DA7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DB7" s="29"/>
-      <c r="DC7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="29" t="s">
-        <v>1725</v>
-      </c>
-      <c r="DF7" s="29"/>
-    </row>
-    <row r="8" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="21" t="s">
+      <c r="CZ7" s="28"/>
+      <c r="DA7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DB7" s="28"/>
+      <c r="DC7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DD7" s="28"/>
+      <c r="DE7" s="28" t="s">
+        <v>1724</v>
+      </c>
+      <c r="DF7" s="28"/>
+      <c r="DG7" s="9" t="s">
+        <v>1869</v>
+      </c>
+      <c r="DI7" s="33" t="s">
+        <v>665</v>
+      </c>
+      <c r="DM7" s="9" t="s">
+        <v>1870</v>
+      </c>
+      <c r="DO7" s="9" t="s">
+        <v>1869</v>
+      </c>
+      <c r="DQ7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="DS7" s="36" t="s">
+        <v>1896</v>
+      </c>
+      <c r="DU7" s="36" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A8" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12"/>
@@ -7016,7 +7563,7 @@
         <v>647</v>
       </c>
       <c r="AA8" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="AE8" s="9" t="s">
         <v>649</v>
@@ -7026,8 +7573,8 @@
         <v>650</v>
       </c>
       <c r="AH8" s="9"/>
-      <c r="AI8" s="10" t="s">
-        <v>1386</v>
+      <c r="AI8" s="11" t="s">
+        <v>1392</v>
       </c>
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9" t="s">
@@ -7057,21 +7604,21 @@
         <v>737</v>
       </c>
       <c r="BE8" t="s">
+        <v>1386</v>
+      </c>
+      <c r="BG8" s="9" t="s">
         <v>1387</v>
       </c>
-      <c r="BG8" s="9" t="s">
-        <v>1388</v>
-      </c>
       <c r="BK8" s="9" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="BL8" s="9"/>
       <c r="BM8" s="9" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="BN8" s="9"/>
       <c r="BO8" s="9" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="BP8" s="9"/>
       <c r="BQ8" s="9" t="s">
@@ -7079,78 +7626,96 @@
       </c>
       <c r="BR8" s="9"/>
       <c r="BS8" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="BT8" s="9"/>
       <c r="BU8" s="9" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="BV8" s="9"/>
       <c r="BW8" s="9" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="BX8" s="9"/>
       <c r="BY8" s="9" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="BZ8" s="9"/>
       <c r="CA8" s="9" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="CB8" s="9"/>
       <c r="CC8" s="9" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="CD8" s="9"/>
       <c r="CE8" s="9" t="s">
-        <v>1478</v>
-      </c>
-      <c r="CG8" s="20" t="s">
-        <v>1650</v>
-      </c>
-      <c r="CI8" s="20" t="s">
-        <v>1670</v>
-      </c>
-      <c r="CK8" s="20" t="s">
-        <v>1681</v>
-      </c>
-      <c r="CM8" s="20" t="s">
-        <v>1372</v>
-      </c>
-      <c r="CO8" s="20" t="s">
-        <v>1693</v>
-      </c>
-      <c r="CQ8" s="20" t="s">
+        <v>1477</v>
+      </c>
+      <c r="CG8" s="19" t="s">
+        <v>1649</v>
+      </c>
+      <c r="CI8" s="19" t="s">
+        <v>1669</v>
+      </c>
+      <c r="CK8" s="19" t="s">
+        <v>1680</v>
+      </c>
+      <c r="CM8" s="19" t="s">
+        <v>1371</v>
+      </c>
+      <c r="CO8" s="19" t="s">
+        <v>1692</v>
+      </c>
+      <c r="CQ8" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="CS8" s="29" t="s">
+      <c r="CS8" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CT8" s="28"/>
+      <c r="CU8" s="27" t="s">
         <v>1726</v>
       </c>
-      <c r="CT8" s="29"/>
-      <c r="CU8" s="28" t="s">
+      <c r="CV8" s="27"/>
+      <c r="CW8" s="27"/>
+      <c r="CX8" s="27"/>
+      <c r="CY8" s="28" t="s">
         <v>1727</v>
       </c>
-      <c r="CV8" s="28"/>
-      <c r="CW8" s="28"/>
-      <c r="CX8" s="28"/>
-      <c r="CY8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="CZ8" s="29"/>
-      <c r="DA8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DB8" s="29"/>
-      <c r="DC8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DD8" s="29"/>
-      <c r="DE8" s="29" t="s">
-        <v>1728</v>
-      </c>
-      <c r="DF8" s="28"/>
-    </row>
-    <row r="9" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="CZ8" s="28"/>
+      <c r="DA8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DB8" s="28"/>
+      <c r="DC8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DD8" s="28"/>
+      <c r="DE8" s="28" t="s">
+        <v>1727</v>
+      </c>
+      <c r="DF8" s="27"/>
+      <c r="DG8" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="DM8" s="9" t="s">
+        <v>1872</v>
+      </c>
+      <c r="DO8" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="DQ8" t="s">
+        <v>1891</v>
+      </c>
+      <c r="DS8" s="36" t="s">
+        <v>1897</v>
+      </c>
+      <c r="DU8" s="36" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>42</v>
       </c>
@@ -7189,7 +7754,7 @@
         <v>656</v>
       </c>
       <c r="AA9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="AE9" s="9" t="s">
         <v>658</v>
@@ -7199,8 +7764,8 @@
         <v>659</v>
       </c>
       <c r="AH9" s="9"/>
-      <c r="AI9" s="11" t="s">
-        <v>1390</v>
+      <c r="AI9" s="10" t="s">
+        <v>1396</v>
       </c>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9" t="s">
@@ -7226,21 +7791,21 @@
         <v>1330</v>
       </c>
       <c r="BE9" t="s">
+        <v>1390</v>
+      </c>
+      <c r="BG9" s="9" t="s">
         <v>1391</v>
       </c>
-      <c r="BG9" s="9" t="s">
-        <v>1392</v>
-      </c>
       <c r="BK9" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BL9" s="9"/>
       <c r="BM9" s="9" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BN9" s="9"/>
       <c r="BO9" s="9" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="BP9" s="9"/>
       <c r="BQ9" s="9" t="s">
@@ -7248,78 +7813,96 @@
       </c>
       <c r="BR9" s="9"/>
       <c r="BS9" s="9" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="BT9" s="9"/>
       <c r="BU9" s="9" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="BV9" s="9"/>
       <c r="BW9" s="9" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="BX9" s="9"/>
       <c r="BY9" s="9"/>
       <c r="BZ9" s="9"/>
       <c r="CA9" s="9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="CB9" s="9"/>
       <c r="CC9" s="9" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="CD9" s="9"/>
       <c r="CE9" s="9" t="s">
-        <v>1484</v>
-      </c>
-      <c r="CG9" s="20" t="s">
-        <v>1651</v>
-      </c>
-      <c r="CI9" s="20" t="s">
-        <v>1671</v>
-      </c>
-      <c r="CK9" s="20" t="s">
-        <v>1682</v>
-      </c>
-      <c r="CM9" s="20" t="s">
-        <v>1475</v>
-      </c>
-      <c r="CO9" s="20" t="s">
-        <v>1694</v>
-      </c>
-      <c r="CS9" s="29" t="s">
+        <v>1483</v>
+      </c>
+      <c r="CG9" s="19" t="s">
+        <v>1650</v>
+      </c>
+      <c r="CI9" s="19" t="s">
+        <v>1670</v>
+      </c>
+      <c r="CK9" s="19" t="s">
+        <v>1681</v>
+      </c>
+      <c r="CM9" s="19" t="s">
+        <v>1474</v>
+      </c>
+      <c r="CO9" s="19" t="s">
+        <v>1693</v>
+      </c>
+      <c r="CS9" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="27" t="s">
         <v>1729</v>
       </c>
-      <c r="CT9" s="29"/>
-      <c r="CU9" s="28" t="s">
+      <c r="CV9" s="27"/>
+      <c r="CW9" s="27"/>
+      <c r="CX9" s="27"/>
+      <c r="CY9" s="28" t="s">
         <v>1730</v>
       </c>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28"/>
-      <c r="CY9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="CZ9" s="29"/>
-      <c r="DA9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DB9" s="29"/>
-      <c r="DC9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DD9" s="29"/>
-      <c r="DE9" s="29" t="s">
-        <v>1731</v>
-      </c>
-      <c r="DF9" s="28"/>
-    </row>
-    <row r="10" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28" t="s">
+        <v>1730</v>
+      </c>
+      <c r="DF9" s="27"/>
+      <c r="DG9" s="9" t="s">
+        <v>1873</v>
+      </c>
+      <c r="DM9" s="9" t="s">
+        <v>1874</v>
+      </c>
+      <c r="DO9" s="9" t="s">
+        <v>1873</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>1892</v>
+      </c>
+      <c r="DS9" s="36" t="s">
+        <v>1898</v>
+      </c>
+      <c r="DU9" s="36" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A10" s="20" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="12"/>
@@ -7366,8 +7949,8 @@
         <v>667</v>
       </c>
       <c r="AH10" s="9"/>
-      <c r="AI10" s="11" t="s">
-        <v>1393</v>
+      <c r="AI10" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="AJ10" s="9"/>
       <c r="AK10" s="9" t="s">
@@ -7393,21 +7976,21 @@
         <v>1331</v>
       </c>
       <c r="BE10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BG10" s="9" t="s">
         <v>1394</v>
       </c>
-      <c r="BG10" s="9" t="s">
-        <v>1395</v>
-      </c>
       <c r="BK10" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BL10" s="9"/>
       <c r="BM10" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BN10" s="9"/>
       <c r="BO10" s="9" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="BP10" s="9"/>
       <c r="BQ10" s="9" t="s">
@@ -7419,7 +8002,7 @@
       <c r="BU10" s="9"/>
       <c r="BV10" s="9"/>
       <c r="BW10" s="9" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="BX10" s="9"/>
       <c r="BY10" s="9"/>
@@ -7435,45 +8018,54 @@
       <c r="CE10" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="CG10" s="20" t="s">
-        <v>1652</v>
-      </c>
-      <c r="CI10" s="20" t="s">
-        <v>1672</v>
-      </c>
-      <c r="CK10" s="20" t="s">
-        <v>1683</v>
-      </c>
-      <c r="CM10" s="20" t="s">
-        <v>1702</v>
-      </c>
-      <c r="CO10" s="20" t="s">
-        <v>1695</v>
-      </c>
-      <c r="CS10" s="28"/>
-      <c r="CT10" s="28"/>
-      <c r="CU10" s="28"/>
-      <c r="CV10" s="28"/>
-      <c r="CW10" s="28"/>
-      <c r="CX10" s="28"/>
-      <c r="CY10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="CZ10" s="29"/>
-      <c r="DA10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DB10" s="29"/>
-      <c r="DC10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DD10" s="29"/>
-      <c r="DE10" s="29" t="s">
-        <v>1732</v>
-      </c>
-      <c r="DF10" s="28"/>
-    </row>
-    <row r="11" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="CG10" s="19" t="s">
+        <v>1651</v>
+      </c>
+      <c r="CI10" s="19" t="s">
+        <v>1671</v>
+      </c>
+      <c r="CK10" s="19" t="s">
+        <v>1682</v>
+      </c>
+      <c r="CM10" s="19" t="s">
+        <v>1701</v>
+      </c>
+      <c r="CO10" s="19" t="s">
+        <v>1694</v>
+      </c>
+      <c r="CS10" s="27"/>
+      <c r="CT10" s="27"/>
+      <c r="CU10" s="27"/>
+      <c r="CV10" s="27"/>
+      <c r="CW10" s="27"/>
+      <c r="CX10" s="27"/>
+      <c r="CY10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="CZ10" s="28"/>
+      <c r="DA10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DB10" s="28"/>
+      <c r="DC10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DD10" s="28"/>
+      <c r="DE10" s="28" t="s">
+        <v>1731</v>
+      </c>
+      <c r="DF10" s="27"/>
+      <c r="DM10" s="9" t="s">
+        <v>1875</v>
+      </c>
+      <c r="DQ10" t="s">
+        <v>1893</v>
+      </c>
+      <c r="DS10" s="36" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="11" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>54</v>
       </c>
@@ -7509,14 +8101,14 @@
         <v>671</v>
       </c>
       <c r="AA11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="AG11" s="9" t="s">
         <v>673</v>
       </c>
       <c r="AH11" s="9"/>
       <c r="AI11" s="10" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="AJ11" s="9"/>
       <c r="AK11" s="9" t="s">
@@ -7538,17 +8130,17 @@
         <v>671</v>
       </c>
       <c r="BE11" t="s">
+        <v>1397</v>
+      </c>
+      <c r="BG11" s="9" t="s">
         <v>1398</v>
       </c>
-      <c r="BG11" s="9" t="s">
-        <v>1399</v>
-      </c>
       <c r="BK11" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="BL11" s="9"/>
       <c r="BM11" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="BN11" s="9"/>
       <c r="BO11" s="9"/>
@@ -7562,61 +8154,64 @@
       <c r="BU11" s="9"/>
       <c r="BV11" s="9"/>
       <c r="BW11" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="BX11" s="9"/>
       <c r="BY11" s="9"/>
       <c r="BZ11" s="9"/>
       <c r="CA11" s="9" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="CB11" s="9"/>
       <c r="CC11" s="9"/>
       <c r="CD11" s="9"/>
       <c r="CE11" s="9" t="s">
-        <v>1490</v>
-      </c>
-      <c r="CG11" s="20" t="s">
-        <v>1653</v>
-      </c>
-      <c r="CI11" s="20" t="s">
-        <v>1673</v>
-      </c>
-      <c r="CM11" s="20" t="s">
-        <v>1703</v>
-      </c>
-      <c r="CO11" s="20" t="s">
-        <v>1696</v>
-      </c>
-      <c r="CS11" s="28"/>
-      <c r="CT11" s="28"/>
-      <c r="CU11" s="28"/>
-      <c r="CV11" s="28"/>
-      <c r="CW11" s="28"/>
-      <c r="CX11" s="28"/>
-      <c r="CY11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="CZ11" s="29"/>
-      <c r="DA11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DB11" s="29"/>
-      <c r="DC11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DD11" s="29"/>
-      <c r="DE11" s="29" t="s">
-        <v>1733</v>
-      </c>
-      <c r="DF11" s="28"/>
-    </row>
-    <row r="12" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="21" t="s">
+        <v>1489</v>
+      </c>
+      <c r="CG11" s="19" t="s">
+        <v>1652</v>
+      </c>
+      <c r="CI11" s="19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="CM11" s="19" t="s">
+        <v>1702</v>
+      </c>
+      <c r="CO11" s="19" t="s">
+        <v>1695</v>
+      </c>
+      <c r="CS11" s="27"/>
+      <c r="CT11" s="27"/>
+      <c r="CU11" s="27"/>
+      <c r="CV11" s="27"/>
+      <c r="CW11" s="27"/>
+      <c r="CX11" s="27"/>
+      <c r="CY11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="CZ11" s="28"/>
+      <c r="DA11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DB11" s="28"/>
+      <c r="DC11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DD11" s="28"/>
+      <c r="DE11" s="28" t="s">
+        <v>1732</v>
+      </c>
+      <c r="DF11" s="27"/>
+      <c r="DM11" s="9" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="12" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A12" s="20" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D12" s="12"/>
@@ -7653,8 +8248,8 @@
         <v>680</v>
       </c>
       <c r="AH12" s="9"/>
-      <c r="AI12" s="10" t="s">
-        <v>1400</v>
+      <c r="AI12" s="11" t="s">
+        <v>1403</v>
       </c>
       <c r="AJ12" s="9"/>
       <c r="AK12" s="9" t="s">
@@ -7677,7 +8272,7 @@
         <v>678</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="BK12" s="9"/>
       <c r="BL12" s="9"/>
@@ -7694,7 +8289,7 @@
       <c r="BU12" s="9"/>
       <c r="BV12" s="9"/>
       <c r="BW12" s="9" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="BX12" s="9"/>
       <c r="BY12" s="9"/>
@@ -7706,39 +8301,42 @@
       <c r="CC12" s="9"/>
       <c r="CD12" s="9"/>
       <c r="CE12" s="9"/>
-      <c r="CG12" s="20" t="s">
-        <v>1654</v>
-      </c>
-      <c r="CI12" s="20" t="s">
-        <v>1674</v>
-      </c>
-      <c r="CO12" s="20" t="s">
-        <v>1697</v>
-      </c>
-      <c r="CS12" s="28"/>
-      <c r="CT12" s="28"/>
-      <c r="CU12" s="28"/>
-      <c r="CV12" s="28"/>
-      <c r="CW12" s="28"/>
-      <c r="CX12" s="28"/>
-      <c r="CY12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="CZ12" s="29"/>
-      <c r="DA12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DB12" s="29"/>
-      <c r="DC12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DD12" s="29"/>
-      <c r="DE12" s="29" t="s">
-        <v>1734</v>
-      </c>
-      <c r="DF12" s="28"/>
-    </row>
-    <row r="13" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="CG12" s="19" t="s">
+        <v>1653</v>
+      </c>
+      <c r="CI12" s="19" t="s">
+        <v>1673</v>
+      </c>
+      <c r="CO12" s="19" t="s">
+        <v>1696</v>
+      </c>
+      <c r="CS12" s="27"/>
+      <c r="CT12" s="27"/>
+      <c r="CU12" s="27"/>
+      <c r="CV12" s="27"/>
+      <c r="CW12" s="27"/>
+      <c r="CX12" s="27"/>
+      <c r="CY12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="CZ12" s="28"/>
+      <c r="DA12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DB12" s="28"/>
+      <c r="DC12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DD12" s="28"/>
+      <c r="DE12" s="28" t="s">
+        <v>1733</v>
+      </c>
+      <c r="DF12" s="27"/>
+      <c r="DM12" s="9" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="13" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>66</v>
       </c>
@@ -7779,7 +8377,7 @@
       </c>
       <c r="AH13" s="9"/>
       <c r="AI13" s="10" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="AJ13" s="9"/>
       <c r="AK13" t="s">
@@ -7800,7 +8398,7 @@
         <v>685</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="BK13" s="9"/>
       <c r="BL13" s="9"/>
@@ -7817,7 +8415,7 @@
       <c r="BU13" s="9"/>
       <c r="BV13" s="9"/>
       <c r="BW13" s="9" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="BX13" s="9"/>
       <c r="BY13" s="9"/>
@@ -7829,44 +8427,47 @@
       <c r="CC13" s="9"/>
       <c r="CD13" s="9"/>
       <c r="CE13" s="9"/>
-      <c r="CG13" s="20" t="s">
-        <v>1655</v>
-      </c>
-      <c r="CI13" s="20" t="s">
-        <v>1675</v>
-      </c>
-      <c r="CO13" s="20" t="s">
-        <v>1698</v>
-      </c>
-      <c r="CS13" s="28"/>
-      <c r="CT13" s="28"/>
-      <c r="CU13" s="28"/>
-      <c r="CV13" s="28"/>
-      <c r="CW13" s="28"/>
-      <c r="CX13" s="28"/>
-      <c r="CY13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="CZ13" s="29"/>
-      <c r="DA13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DB13" s="29"/>
-      <c r="DC13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DD13" s="29"/>
-      <c r="DE13" s="29" t="s">
-        <v>1735</v>
-      </c>
-      <c r="DF13" s="28"/>
-    </row>
-    <row r="14" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="21" t="s">
+      <c r="CG13" s="19" t="s">
+        <v>1654</v>
+      </c>
+      <c r="CI13" s="19" t="s">
+        <v>1674</v>
+      </c>
+      <c r="CO13" s="19" t="s">
+        <v>1697</v>
+      </c>
+      <c r="CS13" s="27"/>
+      <c r="CT13" s="27"/>
+      <c r="CU13" s="27"/>
+      <c r="CV13" s="27"/>
+      <c r="CW13" s="27"/>
+      <c r="CX13" s="27"/>
+      <c r="CY13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="CZ13" s="28"/>
+      <c r="DA13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DB13" s="28"/>
+      <c r="DC13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DD13" s="28"/>
+      <c r="DE13" s="28" t="s">
+        <v>1734</v>
+      </c>
+      <c r="DF13" s="27"/>
+      <c r="DM13" s="9" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="14" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A14" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="20" t="s">
         <v>72</v>
       </c>
       <c r="D14" s="12"/>
@@ -7901,8 +8502,8 @@
         <v>694</v>
       </c>
       <c r="AH14" s="9"/>
-      <c r="AI14" s="11" t="s">
-        <v>1404</v>
+      <c r="AI14" s="10" t="s">
+        <v>1408</v>
       </c>
       <c r="AJ14" s="9"/>
       <c r="AK14" s="9" t="s">
@@ -7925,7 +8526,7 @@
         <v>692</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="BK14" s="9"/>
       <c r="BL14" s="9"/>
@@ -7942,7 +8543,7 @@
       <c r="BU14" s="9"/>
       <c r="BV14" s="9"/>
       <c r="BW14" s="9" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="BX14" s="9"/>
       <c r="BY14" s="9"/>
@@ -7954,39 +8555,42 @@
       <c r="CC14" s="9"/>
       <c r="CD14" s="9"/>
       <c r="CE14" s="9"/>
-      <c r="CG14" s="20" t="s">
-        <v>1656</v>
-      </c>
-      <c r="CI14" s="20" t="s">
-        <v>1676</v>
-      </c>
-      <c r="CO14" s="20" t="s">
+      <c r="CG14" s="19" t="s">
+        <v>1655</v>
+      </c>
+      <c r="CI14" s="19" t="s">
+        <v>1675</v>
+      </c>
+      <c r="CO14" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="CS14" s="28"/>
-      <c r="CT14" s="28"/>
-      <c r="CU14" s="28"/>
-      <c r="CV14" s="28"/>
-      <c r="CW14" s="28"/>
-      <c r="CX14" s="28"/>
-      <c r="CY14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="CZ14" s="29"/>
-      <c r="DA14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DB14" s="29"/>
-      <c r="DC14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DD14" s="29"/>
-      <c r="DE14" s="29" t="s">
-        <v>1736</v>
-      </c>
-      <c r="DF14" s="28"/>
-    </row>
-    <row r="15" spans="1:121" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS14" s="27"/>
+      <c r="CT14" s="27"/>
+      <c r="CU14" s="27"/>
+      <c r="CV14" s="27"/>
+      <c r="CW14" s="27"/>
+      <c r="CX14" s="27"/>
+      <c r="CY14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="CZ14" s="28"/>
+      <c r="DA14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DB14" s="28"/>
+      <c r="DC14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DD14" s="28"/>
+      <c r="DE14" s="28" t="s">
+        <v>1735</v>
+      </c>
+      <c r="DF14" s="27"/>
+      <c r="DM14" s="9" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="15" spans="1:125" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>76</v>
       </c>
@@ -8028,7 +8632,7 @@
       </c>
       <c r="AH15" s="9"/>
       <c r="AI15" s="10" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9" t="s">
@@ -8051,7 +8655,7 @@
         <v>698</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="BK15" s="9"/>
       <c r="BL15" s="9"/>
@@ -8068,7 +8672,7 @@
       <c r="BU15" s="9"/>
       <c r="BV15" s="9"/>
       <c r="BW15" s="9" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="BX15" s="9"/>
       <c r="BY15" s="9"/>
@@ -8080,41 +8684,44 @@
       <c r="CC15" s="9"/>
       <c r="CD15" s="9"/>
       <c r="CE15" s="9"/>
-      <c r="CG15" s="20" t="s">
-        <v>1657</v>
-      </c>
-      <c r="CI15" s="20" t="s">
-        <v>1677</v>
-      </c>
-      <c r="CS15" s="28"/>
-      <c r="CT15" s="28"/>
-      <c r="CU15" s="28"/>
-      <c r="CV15" s="28"/>
-      <c r="CW15" s="28"/>
-      <c r="CX15" s="28"/>
-      <c r="CY15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="CZ15" s="29"/>
-      <c r="DA15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DB15" s="29"/>
-      <c r="DC15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DD15" s="29"/>
-      <c r="DE15" s="29" t="s">
-        <v>1737</v>
-      </c>
-      <c r="DF15" s="28"/>
-    </row>
-    <row r="16" spans="1:121" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="21" t="s">
+      <c r="CG15" s="19" t="s">
+        <v>1656</v>
+      </c>
+      <c r="CI15" s="19" t="s">
+        <v>1676</v>
+      </c>
+      <c r="CS15" s="27"/>
+      <c r="CT15" s="27"/>
+      <c r="CU15" s="27"/>
+      <c r="CV15" s="27"/>
+      <c r="CW15" s="27"/>
+      <c r="CX15" s="27"/>
+      <c r="CY15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="CZ15" s="28"/>
+      <c r="DA15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DB15" s="28"/>
+      <c r="DC15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DD15" s="28"/>
+      <c r="DE15" s="28" t="s">
+        <v>1736</v>
+      </c>
+      <c r="DF15" s="27"/>
+      <c r="DM15" s="9" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="16" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="A16" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="20" t="s">
         <v>82</v>
       </c>
       <c r="D16" s="12"/>
@@ -8143,14 +8750,14 @@
         <v>704</v>
       </c>
       <c r="AA16" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="AG16" s="9" t="s">
         <v>705</v>
       </c>
       <c r="AH16" s="9"/>
       <c r="AI16" s="10" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="AJ16" s="9"/>
       <c r="AK16" t="s">
@@ -8171,7 +8778,7 @@
         <v>704</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="BK16" s="9"/>
       <c r="BL16" s="9"/>
@@ -8188,45 +8795,48 @@
       <c r="BU16" s="9"/>
       <c r="BV16" s="9"/>
       <c r="BW16" s="9" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="BX16" s="9"/>
       <c r="BY16" s="9"/>
       <c r="BZ16" s="9"/>
       <c r="CA16" s="9" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="CB16" s="9"/>
       <c r="CC16" s="9"/>
       <c r="CD16" s="9"/>
       <c r="CE16" s="9"/>
-      <c r="CG16" s="20" t="s">
-        <v>1658</v>
-      </c>
-      <c r="CS16" s="28"/>
-      <c r="CT16" s="28"/>
-      <c r="CU16" s="28"/>
-      <c r="CV16" s="28"/>
-      <c r="CW16" s="28"/>
-      <c r="CX16" s="28"/>
-      <c r="CY16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="CZ16" s="29"/>
-      <c r="DA16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DB16" s="29"/>
-      <c r="DC16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DD16" s="29"/>
-      <c r="DE16" s="29" t="s">
-        <v>1738</v>
-      </c>
-      <c r="DF16" s="28"/>
-    </row>
-    <row r="17" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CG16" s="19" t="s">
+        <v>1657</v>
+      </c>
+      <c r="CS16" s="27"/>
+      <c r="CT16" s="27"/>
+      <c r="CU16" s="27"/>
+      <c r="CV16" s="27"/>
+      <c r="CW16" s="27"/>
+      <c r="CX16" s="27"/>
+      <c r="CY16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="CZ16" s="28"/>
+      <c r="DA16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DB16" s="28"/>
+      <c r="DC16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DD16" s="28"/>
+      <c r="DE16" s="28" t="s">
+        <v>1737</v>
+      </c>
+      <c r="DF16" s="27"/>
+      <c r="DM16" s="9" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="17" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>86</v>
       </c>
@@ -8267,7 +8877,7 @@
       </c>
       <c r="AH17" s="9"/>
       <c r="AI17" s="10" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9" t="s">
@@ -8290,7 +8900,7 @@
         <v>710</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="BK17" s="9"/>
       <c r="BL17" s="9"/>
@@ -8307,7 +8917,7 @@
       <c r="BU17" s="9"/>
       <c r="BV17" s="9"/>
       <c r="BW17" s="9" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="BX17" s="9"/>
       <c r="BY17" s="9"/>
@@ -8317,38 +8927,41 @@
       <c r="CC17" s="9"/>
       <c r="CD17" s="9"/>
       <c r="CE17" s="9"/>
-      <c r="CG17" s="20" t="s">
-        <v>1659</v>
-      </c>
-      <c r="CS17" s="28"/>
-      <c r="CT17" s="28"/>
-      <c r="CU17" s="28"/>
-      <c r="CV17" s="28"/>
-      <c r="CW17" s="28"/>
-      <c r="CX17" s="28"/>
-      <c r="CY17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="CZ17" s="29"/>
-      <c r="DA17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DB17" s="29"/>
-      <c r="DC17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DD17" s="29"/>
-      <c r="DE17" s="29" t="s">
-        <v>1739</v>
-      </c>
-      <c r="DF17" s="28"/>
-    </row>
-    <row r="18" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="21" t="s">
+      <c r="CG17" s="19" t="s">
+        <v>1658</v>
+      </c>
+      <c r="CS17" s="27"/>
+      <c r="CT17" s="27"/>
+      <c r="CU17" s="27"/>
+      <c r="CV17" s="27"/>
+      <c r="CW17" s="27"/>
+      <c r="CX17" s="27"/>
+      <c r="CY17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="CZ17" s="28"/>
+      <c r="DA17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DB17" s="28"/>
+      <c r="DC17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DD17" s="28"/>
+      <c r="DE17" s="28" t="s">
+        <v>1738</v>
+      </c>
+      <c r="DF17" s="27"/>
+      <c r="DM17" s="9" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="18" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>92</v>
       </c>
       <c r="D18" s="12"/>
@@ -8384,7 +8997,7 @@
       </c>
       <c r="AH18" s="9"/>
       <c r="AI18" s="10" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" t="s">
@@ -8406,7 +9019,7 @@
         <v>715</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="BK18" s="9"/>
       <c r="BL18" s="9"/>
@@ -8423,7 +9036,7 @@
       <c r="BU18" s="9"/>
       <c r="BV18" s="9"/>
       <c r="BW18" s="9" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="BX18" s="9"/>
       <c r="BY18" s="9"/>
@@ -8433,33 +9046,36 @@
       <c r="CC18" s="9"/>
       <c r="CD18" s="9"/>
       <c r="CE18" s="9"/>
-      <c r="CG18" s="20" t="s">
-        <v>1660</v>
-      </c>
-      <c r="CS18" s="28"/>
-      <c r="CT18" s="28"/>
-      <c r="CU18" s="28"/>
-      <c r="CV18" s="28"/>
-      <c r="CW18" s="28"/>
-      <c r="CX18" s="28"/>
-      <c r="CY18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="CZ18" s="29"/>
-      <c r="DA18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DB18" s="29"/>
-      <c r="DC18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DD18" s="29"/>
-      <c r="DE18" s="29" t="s">
-        <v>1740</v>
-      </c>
-      <c r="DF18" s="28"/>
-    </row>
-    <row r="19" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CG18" s="19" t="s">
+        <v>1659</v>
+      </c>
+      <c r="CS18" s="27"/>
+      <c r="CT18" s="27"/>
+      <c r="CU18" s="27"/>
+      <c r="CV18" s="27"/>
+      <c r="CW18" s="27"/>
+      <c r="CX18" s="27"/>
+      <c r="CY18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="CZ18" s="28"/>
+      <c r="DA18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DB18" s="28"/>
+      <c r="DC18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DD18" s="28"/>
+      <c r="DE18" s="28" t="s">
+        <v>1739</v>
+      </c>
+      <c r="DF18" s="27"/>
+      <c r="DM18" s="9" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="19" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>96</v>
       </c>
@@ -8500,7 +9116,7 @@
       </c>
       <c r="AH19" s="9"/>
       <c r="AI19" s="10" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="AJ19" s="9"/>
       <c r="AK19" s="9" t="s">
@@ -8522,7 +9138,7 @@
         <v>720</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="BK19" s="9"/>
       <c r="BL19" s="9"/>
@@ -8539,7 +9155,7 @@
       <c r="BU19" s="9"/>
       <c r="BV19" s="9"/>
       <c r="BW19" s="9" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="BX19" s="9"/>
       <c r="BY19" s="9"/>
@@ -8549,38 +9165,41 @@
       <c r="CC19" s="9"/>
       <c r="CD19" s="9"/>
       <c r="CE19" s="9"/>
-      <c r="CG19" s="20" t="s">
-        <v>1661</v>
-      </c>
-      <c r="CS19" s="28"/>
-      <c r="CT19" s="28"/>
-      <c r="CU19" s="28"/>
-      <c r="CV19" s="28"/>
-      <c r="CW19" s="28"/>
-      <c r="CX19" s="28"/>
-      <c r="CY19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="CZ19" s="29"/>
-      <c r="DA19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DB19" s="29"/>
-      <c r="DC19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DD19" s="29"/>
-      <c r="DE19" s="29" t="s">
-        <v>1741</v>
-      </c>
-      <c r="DF19" s="28"/>
-    </row>
-    <row r="20" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="21" t="s">
+      <c r="CG19" s="19" t="s">
+        <v>1660</v>
+      </c>
+      <c r="CS19" s="27"/>
+      <c r="CT19" s="27"/>
+      <c r="CU19" s="27"/>
+      <c r="CV19" s="27"/>
+      <c r="CW19" s="27"/>
+      <c r="CX19" s="27"/>
+      <c r="CY19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="CZ19" s="28"/>
+      <c r="DA19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DB19" s="28"/>
+      <c r="DC19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DD19" s="28"/>
+      <c r="DE19" s="28" t="s">
+        <v>1740</v>
+      </c>
+      <c r="DF19" s="27"/>
+      <c r="DM19" s="9" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="20" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A20" s="20" t="s">
         <v>100</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="20" t="s">
         <v>101</v>
       </c>
       <c r="D20" s="12"/>
@@ -8616,7 +9235,7 @@
       </c>
       <c r="AH20" s="9"/>
       <c r="AI20" s="10" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="AJ20" s="9"/>
       <c r="AK20" t="s">
@@ -8651,7 +9270,7 @@
       <c r="BU20" s="9"/>
       <c r="BV20" s="9"/>
       <c r="BW20" s="9" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="BX20" s="9"/>
       <c r="BY20" s="9"/>
@@ -8661,33 +9280,33 @@
       <c r="CC20" s="9"/>
       <c r="CD20" s="9"/>
       <c r="CE20" s="9"/>
-      <c r="CG20" s="20" t="s">
-        <v>1662</v>
-      </c>
-      <c r="CS20" s="28"/>
-      <c r="CT20" s="28"/>
-      <c r="CU20" s="28"/>
-      <c r="CV20" s="28"/>
-      <c r="CW20" s="28"/>
-      <c r="CX20" s="28"/>
-      <c r="CY20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="CZ20" s="29"/>
-      <c r="DA20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DB20" s="29"/>
-      <c r="DC20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DD20" s="29"/>
-      <c r="DE20" s="29" t="s">
-        <v>1742</v>
-      </c>
-      <c r="DF20" s="28"/>
-    </row>
-    <row r="21" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CG20" s="19" t="s">
+        <v>1661</v>
+      </c>
+      <c r="CS20" s="27"/>
+      <c r="CT20" s="27"/>
+      <c r="CU20" s="27"/>
+      <c r="CV20" s="27"/>
+      <c r="CW20" s="27"/>
+      <c r="CX20" s="27"/>
+      <c r="CY20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="CZ20" s="28"/>
+      <c r="DA20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DB20" s="28"/>
+      <c r="DC20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DD20" s="28"/>
+      <c r="DE20" s="28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="DF20" s="27"/>
+    </row>
+    <row r="21" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>105</v>
       </c>
@@ -8726,7 +9345,7 @@
       </c>
       <c r="AH21" s="9"/>
       <c r="AI21" s="10" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9" t="s">
@@ -8763,7 +9382,7 @@
       <c r="BU21" s="9"/>
       <c r="BV21" s="9"/>
       <c r="BW21" s="9" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="BX21" s="9"/>
       <c r="BY21" s="9"/>
@@ -8773,38 +9392,38 @@
       <c r="CC21" s="9"/>
       <c r="CD21" s="9"/>
       <c r="CE21" s="9"/>
-      <c r="CG21" s="20" t="s">
-        <v>1663</v>
-      </c>
-      <c r="CS21" s="28"/>
-      <c r="CT21" s="28"/>
-      <c r="CU21" s="28"/>
-      <c r="CV21" s="28"/>
-      <c r="CW21" s="28"/>
-      <c r="CX21" s="28"/>
-      <c r="CY21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="CZ21" s="29"/>
-      <c r="DA21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DB21" s="29"/>
-      <c r="DC21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DD21" s="29"/>
-      <c r="DE21" s="29" t="s">
-        <v>1743</v>
-      </c>
-      <c r="DF21" s="28"/>
-    </row>
-    <row r="22" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A22" s="21" t="s">
+      <c r="CG21" s="19" t="s">
+        <v>1662</v>
+      </c>
+      <c r="CS21" s="27"/>
+      <c r="CT21" s="27"/>
+      <c r="CU21" s="27"/>
+      <c r="CV21" s="27"/>
+      <c r="CW21" s="27"/>
+      <c r="CX21" s="27"/>
+      <c r="CY21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CZ21" s="28"/>
+      <c r="DA21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DB21" s="28"/>
+      <c r="DC21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DD21" s="28"/>
+      <c r="DE21" s="28" t="s">
+        <v>1742</v>
+      </c>
+      <c r="DF21" s="27"/>
+    </row>
+    <row r="22" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A22" s="20" t="s">
         <v>109</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="12"/>
@@ -8835,7 +9454,7 @@
       </c>
       <c r="AH22" s="9"/>
       <c r="AI22" s="10" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="AJ22" s="9"/>
       <c r="AK22" s="9" t="s">
@@ -8871,7 +9490,7 @@
       <c r="BU22" s="9"/>
       <c r="BV22" s="9"/>
       <c r="BW22" s="9" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="BX22" s="9"/>
       <c r="BY22" s="9"/>
@@ -8881,30 +9500,30 @@
       <c r="CC22" s="9"/>
       <c r="CD22" s="9"/>
       <c r="CE22" s="9"/>
-      <c r="CS22" s="28"/>
-      <c r="CT22" s="28"/>
-      <c r="CU22" s="28"/>
-      <c r="CV22" s="28"/>
-      <c r="CW22" s="28"/>
-      <c r="CX22" s="28"/>
-      <c r="CY22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="CZ22" s="29"/>
-      <c r="DA22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DB22" s="29"/>
-      <c r="DC22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DD22" s="29"/>
-      <c r="DE22" s="29" t="s">
-        <v>1744</v>
-      </c>
-      <c r="DF22" s="28"/>
-    </row>
-    <row r="23" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS22" s="27"/>
+      <c r="CT22" s="27"/>
+      <c r="CU22" s="27"/>
+      <c r="CV22" s="27"/>
+      <c r="CW22" s="27"/>
+      <c r="CX22" s="27"/>
+      <c r="CY22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="CZ22" s="28"/>
+      <c r="DA22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DB22" s="28"/>
+      <c r="DC22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DD22" s="28"/>
+      <c r="DE22" s="28" t="s">
+        <v>1743</v>
+      </c>
+      <c r="DF22" s="27"/>
+    </row>
+    <row r="23" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>113</v>
       </c>
@@ -8937,7 +9556,7 @@
       </c>
       <c r="AH23" s="9"/>
       <c r="AI23" s="10" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="AJ23" s="9"/>
       <c r="AK23" t="s">
@@ -8968,7 +9587,7 @@
       <c r="BU23" s="9"/>
       <c r="BV23" s="9"/>
       <c r="BW23" s="9" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="BX23" s="9"/>
       <c r="BY23" s="9"/>
@@ -8978,35 +9597,35 @@
       <c r="CC23" s="9"/>
       <c r="CD23" s="9"/>
       <c r="CE23" s="9"/>
-      <c r="CS23" s="28"/>
-      <c r="CT23" s="28"/>
-      <c r="CU23" s="28"/>
-      <c r="CV23" s="28"/>
-      <c r="CW23" s="28"/>
-      <c r="CX23" s="28"/>
-      <c r="CY23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="CZ23" s="29"/>
-      <c r="DA23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DB23" s="29"/>
-      <c r="DC23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DD23" s="29"/>
-      <c r="DE23" s="29" t="s">
-        <v>1745</v>
-      </c>
-      <c r="DF23" s="28"/>
-    </row>
-    <row r="24" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A24" s="21" t="s">
+      <c r="CS23" s="27"/>
+      <c r="CT23" s="27"/>
+      <c r="CU23" s="27"/>
+      <c r="CV23" s="27"/>
+      <c r="CW23" s="27"/>
+      <c r="CX23" s="27"/>
+      <c r="CY23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="CZ23" s="28"/>
+      <c r="DA23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DB23" s="28"/>
+      <c r="DC23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DD23" s="28"/>
+      <c r="DE23" s="28" t="s">
+        <v>1744</v>
+      </c>
+      <c r="DF23" s="27"/>
+    </row>
+    <row r="24" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>118</v>
       </c>
       <c r="D24" s="12"/>
@@ -9034,7 +9653,7 @@
       </c>
       <c r="AH24" s="9"/>
       <c r="AI24" s="10" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="AJ24" s="9"/>
       <c r="AK24" t="s">
@@ -9061,7 +9680,7 @@
       <c r="BU24" s="9"/>
       <c r="BV24" s="9"/>
       <c r="BW24" s="9" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="BX24" s="9"/>
       <c r="BY24" s="9"/>
@@ -9071,30 +9690,30 @@
       <c r="CC24" s="9"/>
       <c r="CD24" s="9"/>
       <c r="CE24" s="9"/>
-      <c r="CS24" s="28"/>
-      <c r="CT24" s="28"/>
-      <c r="CU24" s="28"/>
-      <c r="CV24" s="28"/>
-      <c r="CW24" s="28"/>
-      <c r="CX24" s="28"/>
-      <c r="CY24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="CZ24" s="29"/>
-      <c r="DA24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DB24" s="29"/>
-      <c r="DC24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DD24" s="29"/>
-      <c r="DE24" s="29" t="s">
-        <v>1746</v>
-      </c>
-      <c r="DF24" s="28"/>
-    </row>
-    <row r="25" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS24" s="27"/>
+      <c r="CT24" s="27"/>
+      <c r="CU24" s="27"/>
+      <c r="CV24" s="27"/>
+      <c r="CW24" s="27"/>
+      <c r="CX24" s="27"/>
+      <c r="CY24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="CZ24" s="28"/>
+      <c r="DA24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DB24" s="28"/>
+      <c r="DC24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DD24" s="28"/>
+      <c r="DE24" s="28" t="s">
+        <v>1745</v>
+      </c>
+      <c r="DF24" s="27"/>
+    </row>
+    <row r="25" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>121</v>
       </c>
@@ -9127,7 +9746,7 @@
       </c>
       <c r="AH25" s="9"/>
       <c r="AI25" s="10" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="AJ25" s="9"/>
       <c r="AK25" t="s">
@@ -9165,35 +9784,35 @@
       <c r="CC25" s="9"/>
       <c r="CD25" s="9"/>
       <c r="CE25" s="9"/>
-      <c r="CS25" s="28"/>
-      <c r="CT25" s="28"/>
-      <c r="CU25" s="28"/>
-      <c r="CV25" s="28"/>
-      <c r="CW25" s="28"/>
-      <c r="CX25" s="28"/>
-      <c r="CY25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="CZ25" s="29"/>
-      <c r="DA25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DB25" s="29"/>
-      <c r="DC25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DD25" s="29"/>
-      <c r="DE25" s="29" t="s">
-        <v>1747</v>
-      </c>
-      <c r="DF25" s="28"/>
-    </row>
-    <row r="26" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A26" s="21" t="s">
+      <c r="CS25" s="27"/>
+      <c r="CT25" s="27"/>
+      <c r="CU25" s="27"/>
+      <c r="CV25" s="27"/>
+      <c r="CW25" s="27"/>
+      <c r="CX25" s="27"/>
+      <c r="CY25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="CZ25" s="28"/>
+      <c r="DA25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DB25" s="28"/>
+      <c r="DC25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DD25" s="28"/>
+      <c r="DE25" s="28" t="s">
+        <v>1746</v>
+      </c>
+      <c r="DF25" s="27"/>
+    </row>
+    <row r="26" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A26" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D26" s="12"/>
@@ -9221,7 +9840,7 @@
       </c>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10" t="s">
-        <v>1423</v>
+        <v>748</v>
       </c>
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9" t="s">
@@ -9250,7 +9869,7 @@
       <c r="BU26" s="9"/>
       <c r="BV26" s="9"/>
       <c r="BW26" s="9" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="BX26" s="9"/>
       <c r="BY26" s="9"/>
@@ -9260,30 +9879,30 @@
       <c r="CC26" s="9"/>
       <c r="CD26" s="9"/>
       <c r="CE26" s="9"/>
-      <c r="CS26" s="28"/>
-      <c r="CT26" s="28"/>
-      <c r="CU26" s="29"/>
-      <c r="CV26" s="29"/>
-      <c r="CW26" s="28"/>
-      <c r="CX26" s="28"/>
-      <c r="CY26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="CZ26" s="29"/>
-      <c r="DA26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DB26" s="29"/>
-      <c r="DC26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DD26" s="29"/>
-      <c r="DE26" s="29" t="s">
-        <v>1748</v>
-      </c>
-      <c r="DF26" s="28"/>
-    </row>
-    <row r="27" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS26" s="27"/>
+      <c r="CT26" s="27"/>
+      <c r="CU26" s="28"/>
+      <c r="CV26" s="28"/>
+      <c r="CW26" s="27"/>
+      <c r="CX26" s="27"/>
+      <c r="CY26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="CZ26" s="28"/>
+      <c r="DA26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DB26" s="28"/>
+      <c r="DC26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DD26" s="28"/>
+      <c r="DE26" s="28" t="s">
+        <v>1747</v>
+      </c>
+      <c r="DF26" s="27"/>
+    </row>
+    <row r="27" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
         <v>129</v>
       </c>
@@ -9343,7 +9962,7 @@
       <c r="BU27" s="9"/>
       <c r="BV27" s="9"/>
       <c r="BW27" s="9" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="BX27" s="9"/>
       <c r="BY27" s="9"/>
@@ -9353,35 +9972,35 @@
       <c r="CC27" s="9"/>
       <c r="CD27" s="9"/>
       <c r="CE27" s="9"/>
-      <c r="CS27" s="28"/>
-      <c r="CT27" s="28"/>
-      <c r="CU27" s="29"/>
-      <c r="CV27" s="29"/>
-      <c r="CW27" s="28"/>
-      <c r="CX27" s="28"/>
-      <c r="CY27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="CZ27" s="29"/>
-      <c r="DA27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DB27" s="29"/>
-      <c r="DC27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DD27" s="29"/>
-      <c r="DE27" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="DF27" s="28"/>
-    </row>
-    <row r="28" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A28" s="21" t="s">
+      <c r="CS27" s="27"/>
+      <c r="CT27" s="27"/>
+      <c r="CU27" s="28"/>
+      <c r="CV27" s="28"/>
+      <c r="CW27" s="27"/>
+      <c r="CX27" s="27"/>
+      <c r="CY27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="CZ27" s="28"/>
+      <c r="DA27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DB27" s="28"/>
+      <c r="DC27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DD27" s="28"/>
+      <c r="DE27" s="28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="DF27" s="27"/>
+    </row>
+    <row r="28" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A28" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B28" s="12"/>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="20" t="s">
         <v>134</v>
       </c>
       <c r="D28" s="12"/>
@@ -9409,7 +10028,7 @@
       </c>
       <c r="AH28" s="9"/>
       <c r="AI28" s="10" t="s">
-        <v>748</v>
+        <v>1425</v>
       </c>
       <c r="AK28" s="9" t="s">
         <v>764</v>
@@ -9436,7 +10055,7 @@
       <c r="BU28" s="9"/>
       <c r="BV28" s="9"/>
       <c r="BW28" s="9" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="BX28" s="9"/>
       <c r="BY28" s="9"/>
@@ -9446,30 +10065,30 @@
       <c r="CC28" s="9"/>
       <c r="CD28" s="9"/>
       <c r="CE28" s="9"/>
-      <c r="CS28" s="28"/>
-      <c r="CT28" s="28"/>
-      <c r="CU28" s="29"/>
-      <c r="CV28" s="29"/>
-      <c r="CW28" s="28"/>
-      <c r="CX28" s="28"/>
-      <c r="CY28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="CZ28" s="29"/>
-      <c r="DA28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DB28" s="29"/>
-      <c r="DC28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DD28" s="29"/>
-      <c r="DE28" s="29" t="s">
-        <v>1750</v>
-      </c>
-      <c r="DF28" s="28"/>
-    </row>
-    <row r="29" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS28" s="27"/>
+      <c r="CT28" s="27"/>
+      <c r="CU28" s="28"/>
+      <c r="CV28" s="28"/>
+      <c r="CW28" s="27"/>
+      <c r="CX28" s="27"/>
+      <c r="CY28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="CZ28" s="28"/>
+      <c r="DA28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DB28" s="28"/>
+      <c r="DC28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DD28" s="28"/>
+      <c r="DE28" s="28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="DF28" s="27"/>
+    </row>
+    <row r="29" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
         <v>137</v>
       </c>
@@ -9502,7 +10121,7 @@
       </c>
       <c r="AH29" s="9"/>
       <c r="AI29" s="10" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="AK29" t="s">
         <v>768</v>
@@ -9528,7 +10147,7 @@
       <c r="BU29" s="9"/>
       <c r="BV29" s="9"/>
       <c r="BW29" s="9" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="BX29" s="9"/>
       <c r="BY29" s="9"/>
@@ -9538,35 +10157,35 @@
       <c r="CC29" s="9"/>
       <c r="CD29" s="9"/>
       <c r="CE29" s="9"/>
-      <c r="CS29" s="28"/>
-      <c r="CT29" s="28"/>
-      <c r="CU29" s="28"/>
-      <c r="CV29" s="28"/>
-      <c r="CW29" s="28"/>
-      <c r="CX29" s="28"/>
-      <c r="CY29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="CZ29" s="29"/>
-      <c r="DA29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DB29" s="29"/>
-      <c r="DC29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DD29" s="29"/>
-      <c r="DE29" s="29" t="s">
-        <v>1751</v>
-      </c>
-      <c r="DF29" s="28"/>
-    </row>
-    <row r="30" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A30" s="21" t="s">
+      <c r="CS29" s="27"/>
+      <c r="CT29" s="27"/>
+      <c r="CU29" s="27"/>
+      <c r="CV29" s="27"/>
+      <c r="CW29" s="27"/>
+      <c r="CX29" s="27"/>
+      <c r="CY29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="CZ29" s="28"/>
+      <c r="DA29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DB29" s="28"/>
+      <c r="DC29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DD29" s="28"/>
+      <c r="DE29" s="28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="DF29" s="27"/>
+    </row>
+    <row r="30" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A30" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="12"/>
@@ -9593,8 +10212,8 @@
         <v>770</v>
       </c>
       <c r="AH30" s="9"/>
-      <c r="AI30" s="10" t="s">
-        <v>1426</v>
+      <c r="AI30" s="11" t="s">
+        <v>1427</v>
       </c>
       <c r="AK30" s="9" t="s">
         <v>771</v>
@@ -9621,7 +10240,7 @@
       <c r="BU30" s="9"/>
       <c r="BV30" s="9"/>
       <c r="BW30" s="9" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="BX30" s="9"/>
       <c r="BY30" s="9"/>
@@ -9631,30 +10250,30 @@
       <c r="CC30" s="9"/>
       <c r="CD30" s="9"/>
       <c r="CE30" s="9"/>
-      <c r="CS30" s="28"/>
-      <c r="CT30" s="28"/>
-      <c r="CU30" s="28"/>
-      <c r="CV30" s="28"/>
-      <c r="CW30" s="28"/>
-      <c r="CX30" s="28"/>
-      <c r="CY30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="CZ30" s="29"/>
-      <c r="DA30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DB30" s="29"/>
-      <c r="DC30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DD30" s="29"/>
-      <c r="DE30" s="29" t="s">
-        <v>1752</v>
-      </c>
-      <c r="DF30" s="28"/>
-    </row>
-    <row r="31" spans="1:110" ht="16" x14ac:dyDescent="0.4">
+      <c r="CS30" s="27"/>
+      <c r="CT30" s="27"/>
+      <c r="CU30" s="27"/>
+      <c r="CV30" s="27"/>
+      <c r="CW30" s="27"/>
+      <c r="CX30" s="27"/>
+      <c r="CY30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="CZ30" s="28"/>
+      <c r="DA30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DB30" s="28"/>
+      <c r="DC30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DD30" s="28"/>
+      <c r="DE30" s="28" t="s">
+        <v>1751</v>
+      </c>
+      <c r="DF30" s="27"/>
+    </row>
+    <row r="31" spans="1:117" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="14" t="s">
         <v>145</v>
       </c>
@@ -9687,7 +10306,7 @@
       </c>
       <c r="AH31" s="9"/>
       <c r="AI31" s="10" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="AK31" s="9" t="s">
         <v>775</v>
@@ -9715,7 +10334,7 @@
       <c r="BU31" s="9"/>
       <c r="BV31" s="9"/>
       <c r="BW31" s="9" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="BX31" s="9"/>
       <c r="BY31" s="9"/>
@@ -9725,35 +10344,35 @@
       <c r="CC31" s="9"/>
       <c r="CD31" s="9"/>
       <c r="CE31" s="9"/>
-      <c r="CS31" s="28"/>
-      <c r="CT31" s="28"/>
-      <c r="CU31" s="28"/>
-      <c r="CV31" s="28"/>
-      <c r="CW31" s="28"/>
-      <c r="CX31" s="28"/>
-      <c r="CY31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="CZ31" s="29"/>
-      <c r="DA31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DB31" s="29"/>
-      <c r="DC31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DD31" s="29"/>
-      <c r="DE31" s="29" t="s">
-        <v>1753</v>
-      </c>
-      <c r="DF31" s="28"/>
-    </row>
-    <row r="32" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A32" s="21" t="s">
+      <c r="CS31" s="27"/>
+      <c r="CT31" s="27"/>
+      <c r="CU31" s="27"/>
+      <c r="CV31" s="27"/>
+      <c r="CW31" s="27"/>
+      <c r="CX31" s="27"/>
+      <c r="CY31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="CZ31" s="28"/>
+      <c r="DA31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DB31" s="28"/>
+      <c r="DC31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DD31" s="28"/>
+      <c r="DE31" s="28" t="s">
+        <v>1752</v>
+      </c>
+      <c r="DF31" s="27"/>
+    </row>
+    <row r="32" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="A32" s="20" t="s">
         <v>149</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>150</v>
       </c>
       <c r="D32" s="12"/>
@@ -9780,8 +10399,8 @@
         <v>777</v>
       </c>
       <c r="AH32" s="9"/>
-      <c r="AI32" s="11" t="s">
-        <v>1428</v>
+      <c r="AI32" s="9" t="s">
+        <v>1774</v>
       </c>
       <c r="AK32" t="s">
         <v>778</v>
@@ -9808,7 +10427,7 @@
       <c r="BU32" s="9"/>
       <c r="BV32" s="9"/>
       <c r="BW32" s="9" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="BX32" s="9"/>
       <c r="BY32" s="9"/>
@@ -9818,28 +10437,28 @@
       <c r="CC32" s="9"/>
       <c r="CD32" s="9"/>
       <c r="CE32" s="9"/>
-      <c r="CS32" s="28"/>
-      <c r="CT32" s="28"/>
-      <c r="CU32" s="28"/>
-      <c r="CV32" s="28"/>
-      <c r="CW32" s="28"/>
-      <c r="CX32" s="28"/>
-      <c r="CY32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="CZ32" s="29"/>
-      <c r="DA32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DB32" s="29"/>
-      <c r="DC32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DD32" s="29"/>
-      <c r="DE32" s="29" t="s">
-        <v>1754</v>
-      </c>
-      <c r="DF32" s="28"/>
+      <c r="CS32" s="27"/>
+      <c r="CT32" s="27"/>
+      <c r="CU32" s="27"/>
+      <c r="CV32" s="27"/>
+      <c r="CW32" s="27"/>
+      <c r="CX32" s="27"/>
+      <c r="CY32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="CZ32" s="28"/>
+      <c r="DA32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DB32" s="28"/>
+      <c r="DC32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DD32" s="28"/>
+      <c r="DE32" s="28" t="s">
+        <v>1753</v>
+      </c>
+      <c r="DF32" s="27"/>
     </row>
     <row r="33" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="14" t="s">
@@ -9873,8 +10492,8 @@
         <v>780</v>
       </c>
       <c r="AH33" s="9"/>
-      <c r="AI33" s="10" t="s">
-        <v>1429</v>
+      <c r="AI33" s="9" t="s">
+        <v>1775</v>
       </c>
       <c r="AK33" s="9" t="s">
         <v>781</v>
@@ -9901,7 +10520,7 @@
       <c r="BU33" s="9"/>
       <c r="BV33" s="9"/>
       <c r="BW33" s="9" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="BX33" s="9"/>
       <c r="BY33" s="9"/>
@@ -9911,35 +10530,35 @@
       <c r="CC33" s="9"/>
       <c r="CD33" s="9"/>
       <c r="CE33" s="9"/>
-      <c r="CS33" s="28"/>
-      <c r="CT33" s="28"/>
-      <c r="CU33" s="28"/>
-      <c r="CV33" s="28"/>
-      <c r="CW33" s="28"/>
-      <c r="CX33" s="28"/>
-      <c r="CY33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="CZ33" s="29"/>
-      <c r="DA33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DB33" s="29"/>
-      <c r="DC33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DD33" s="29"/>
-      <c r="DE33" s="29" t="s">
-        <v>1755</v>
-      </c>
-      <c r="DF33" s="28"/>
+      <c r="CS33" s="27"/>
+      <c r="CT33" s="27"/>
+      <c r="CU33" s="27"/>
+      <c r="CV33" s="27"/>
+      <c r="CW33" s="27"/>
+      <c r="CX33" s="27"/>
+      <c r="CY33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="CZ33" s="28"/>
+      <c r="DA33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DB33" s="28"/>
+      <c r="DC33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DD33" s="28"/>
+      <c r="DE33" s="28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="DF33" s="27"/>
     </row>
     <row r="34" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="20" t="s">
         <v>157</v>
       </c>
       <c r="B34" s="12"/>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="20" t="s">
         <v>158</v>
       </c>
       <c r="D34" s="12"/>
@@ -9966,8 +10585,8 @@
         <v>783</v>
       </c>
       <c r="AH34" s="9"/>
-      <c r="AI34" s="10" t="s">
-        <v>1430</v>
+      <c r="AI34" s="9" t="s">
+        <v>1776</v>
       </c>
       <c r="AK34" s="9" t="s">
         <v>784</v>
@@ -9995,7 +10614,7 @@
       <c r="BU34" s="9"/>
       <c r="BV34" s="9"/>
       <c r="BW34" s="9" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="BX34" s="9"/>
       <c r="BY34" s="9"/>
@@ -10005,28 +10624,28 @@
       <c r="CC34" s="9"/>
       <c r="CD34" s="9"/>
       <c r="CE34" s="9"/>
-      <c r="CS34" s="28"/>
-      <c r="CT34" s="28"/>
-      <c r="CU34" s="28"/>
-      <c r="CV34" s="28"/>
-      <c r="CW34" s="28"/>
-      <c r="CX34" s="28"/>
-      <c r="CY34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="CZ34" s="29"/>
-      <c r="DA34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DB34" s="29"/>
-      <c r="DC34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DD34" s="29"/>
-      <c r="DE34" s="29" t="s">
-        <v>1756</v>
-      </c>
-      <c r="DF34" s="28"/>
+      <c r="CS34" s="27"/>
+      <c r="CT34" s="27"/>
+      <c r="CU34" s="27"/>
+      <c r="CV34" s="27"/>
+      <c r="CW34" s="27"/>
+      <c r="CX34" s="27"/>
+      <c r="CY34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="CZ34" s="28"/>
+      <c r="DA34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DB34" s="28"/>
+      <c r="DC34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DD34" s="28"/>
+      <c r="DE34" s="28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="DF34" s="27"/>
     </row>
     <row r="35" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="14" t="s">
@@ -10060,6 +10679,9 @@
         <v>786</v>
       </c>
       <c r="AH35" s="9"/>
+      <c r="AI35" s="30" t="s">
+        <v>1777</v>
+      </c>
       <c r="AK35" s="9" t="s">
         <v>787</v>
       </c>
@@ -10086,7 +10708,7 @@
       <c r="BU35" s="9"/>
       <c r="BV35" s="9"/>
       <c r="BW35" s="9" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="BX35" s="9"/>
       <c r="BY35" s="9"/>
@@ -10096,35 +10718,35 @@
       <c r="CC35" s="9"/>
       <c r="CD35" s="9"/>
       <c r="CE35" s="9"/>
-      <c r="CS35" s="28"/>
-      <c r="CT35" s="28"/>
-      <c r="CU35" s="28"/>
-      <c r="CV35" s="28"/>
-      <c r="CW35" s="28"/>
-      <c r="CX35" s="28"/>
-      <c r="CY35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="CZ35" s="29"/>
-      <c r="DA35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DB35" s="29"/>
-      <c r="DC35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DD35" s="29"/>
-      <c r="DE35" s="29" t="s">
-        <v>1757</v>
-      </c>
-      <c r="DF35" s="28"/>
+      <c r="CS35" s="27"/>
+      <c r="CT35" s="27"/>
+      <c r="CU35" s="27"/>
+      <c r="CV35" s="27"/>
+      <c r="CW35" s="27"/>
+      <c r="CX35" s="27"/>
+      <c r="CY35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="CZ35" s="28"/>
+      <c r="DA35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DB35" s="28"/>
+      <c r="DC35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DD35" s="28"/>
+      <c r="DE35" s="28" t="s">
+        <v>1756</v>
+      </c>
+      <c r="DF35" s="27"/>
     </row>
     <row r="36" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="20" t="s">
         <v>165</v>
       </c>
       <c r="B36" s="12"/>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="20" t="s">
         <v>166</v>
       </c>
       <c r="D36" s="12"/>
@@ -10147,6 +10769,9 @@
         <v>790</v>
       </c>
       <c r="AH36" s="9"/>
+      <c r="AI36" s="9" t="s">
+        <v>1778</v>
+      </c>
       <c r="AK36" s="9" t="s">
         <v>791</v>
       </c>
@@ -10173,7 +10798,7 @@
       <c r="BU36" s="9"/>
       <c r="BV36" s="9"/>
       <c r="BW36" s="9" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="BX36" s="9"/>
       <c r="BY36" s="9"/>
@@ -10183,28 +10808,28 @@
       <c r="CC36" s="9"/>
       <c r="CD36" s="9"/>
       <c r="CE36" s="9"/>
-      <c r="CS36" s="28"/>
-      <c r="CT36" s="28"/>
-      <c r="CU36" s="28"/>
-      <c r="CV36" s="28"/>
-      <c r="CW36" s="28"/>
-      <c r="CX36" s="28"/>
-      <c r="CY36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="CZ36" s="29"/>
-      <c r="DA36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DB36" s="29"/>
-      <c r="DC36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DD36" s="29"/>
-      <c r="DE36" s="29" t="s">
-        <v>1758</v>
-      </c>
-      <c r="DF36" s="28"/>
+      <c r="CS36" s="27"/>
+      <c r="CT36" s="27"/>
+      <c r="CU36" s="27"/>
+      <c r="CV36" s="27"/>
+      <c r="CW36" s="27"/>
+      <c r="CX36" s="27"/>
+      <c r="CY36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="CZ36" s="28"/>
+      <c r="DA36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DB36" s="28"/>
+      <c r="DC36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DD36" s="28"/>
+      <c r="DE36" s="28" t="s">
+        <v>1757</v>
+      </c>
+      <c r="DF36" s="27"/>
     </row>
     <row r="37" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="14" t="s">
@@ -10234,6 +10859,9 @@
         <v>793</v>
       </c>
       <c r="AH37" s="9"/>
+      <c r="AI37" s="9" t="s">
+        <v>1779</v>
+      </c>
       <c r="AK37" t="s">
         <v>794</v>
       </c>
@@ -10258,7 +10886,7 @@
       <c r="BU37" s="9"/>
       <c r="BV37" s="9"/>
       <c r="BW37" s="9" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="BX37" s="9"/>
       <c r="BY37" s="9"/>
@@ -10268,35 +10896,35 @@
       <c r="CC37" s="9"/>
       <c r="CD37" s="9"/>
       <c r="CE37" s="9"/>
-      <c r="CS37" s="28"/>
-      <c r="CT37" s="28"/>
-      <c r="CU37" s="28"/>
-      <c r="CV37" s="28"/>
-      <c r="CW37" s="28"/>
-      <c r="CX37" s="28"/>
-      <c r="CY37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="CZ37" s="29"/>
-      <c r="DA37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DB37" s="29"/>
-      <c r="DC37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DD37" s="29"/>
-      <c r="DE37" s="29" t="s">
-        <v>1759</v>
-      </c>
-      <c r="DF37" s="28"/>
+      <c r="CS37" s="27"/>
+      <c r="CT37" s="27"/>
+      <c r="CU37" s="27"/>
+      <c r="CV37" s="27"/>
+      <c r="CW37" s="27"/>
+      <c r="CX37" s="27"/>
+      <c r="CY37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="CZ37" s="28"/>
+      <c r="DA37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DB37" s="28"/>
+      <c r="DC37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DD37" s="28"/>
+      <c r="DE37" s="28" t="s">
+        <v>1758</v>
+      </c>
+      <c r="DF37" s="27"/>
     </row>
     <row r="38" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="20" t="s">
         <v>169</v>
       </c>
       <c r="B38" s="12"/>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="20" t="s">
         <v>170</v>
       </c>
       <c r="D38" s="12"/>
@@ -10319,6 +10947,9 @@
         <v>796</v>
       </c>
       <c r="AH38" s="9"/>
+      <c r="AI38" s="9" t="s">
+        <v>1780</v>
+      </c>
       <c r="AK38" s="9" t="s">
         <v>797</v>
       </c>
@@ -10345,7 +10976,7 @@
       <c r="BU38" s="9"/>
       <c r="BV38" s="9"/>
       <c r="BW38" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="BX38" s="9"/>
       <c r="BY38" s="9"/>
@@ -10355,28 +10986,28 @@
       <c r="CC38" s="9"/>
       <c r="CD38" s="9"/>
       <c r="CE38" s="9"/>
-      <c r="CS38" s="28"/>
-      <c r="CT38" s="28"/>
-      <c r="CU38" s="28"/>
-      <c r="CV38" s="28"/>
-      <c r="CW38" s="28"/>
-      <c r="CX38" s="28"/>
-      <c r="CY38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="CZ38" s="29"/>
-      <c r="DA38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DB38" s="29"/>
-      <c r="DC38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DD38" s="29"/>
-      <c r="DE38" s="29" t="s">
-        <v>1760</v>
-      </c>
-      <c r="DF38" s="28"/>
+      <c r="CS38" s="27"/>
+      <c r="CT38" s="27"/>
+      <c r="CU38" s="27"/>
+      <c r="CV38" s="27"/>
+      <c r="CW38" s="27"/>
+      <c r="CX38" s="27"/>
+      <c r="CY38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="CZ38" s="28"/>
+      <c r="DA38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DB38" s="28"/>
+      <c r="DC38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DD38" s="28"/>
+      <c r="DE38" s="28" t="s">
+        <v>1759</v>
+      </c>
+      <c r="DF38" s="27"/>
     </row>
     <row r="39" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="14" t="s">
@@ -10406,6 +11037,9 @@
         <v>800</v>
       </c>
       <c r="AH39" s="9"/>
+      <c r="AI39" s="9" t="s">
+        <v>1781</v>
+      </c>
       <c r="AK39" s="9" t="s">
         <v>801</v>
       </c>
@@ -10431,7 +11065,7 @@
       <c r="BU39" s="9"/>
       <c r="BV39" s="9"/>
       <c r="BW39" s="9" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="BX39" s="9"/>
       <c r="BY39" s="9"/>
@@ -10441,35 +11075,35 @@
       <c r="CC39" s="9"/>
       <c r="CD39" s="9"/>
       <c r="CE39" s="9"/>
-      <c r="CS39" s="28"/>
-      <c r="CT39" s="28"/>
-      <c r="CU39" s="28"/>
-      <c r="CV39" s="28"/>
-      <c r="CW39" s="28"/>
-      <c r="CX39" s="28"/>
-      <c r="CY39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="CZ39" s="29"/>
-      <c r="DA39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DB39" s="29"/>
-      <c r="DC39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DD39" s="29"/>
-      <c r="DE39" s="29" t="s">
-        <v>1761</v>
-      </c>
-      <c r="DF39" s="28"/>
+      <c r="CS39" s="27"/>
+      <c r="CT39" s="27"/>
+      <c r="CU39" s="27"/>
+      <c r="CV39" s="27"/>
+      <c r="CW39" s="27"/>
+      <c r="CX39" s="27"/>
+      <c r="CY39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="CZ39" s="28"/>
+      <c r="DA39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DB39" s="28"/>
+      <c r="DC39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DD39" s="28"/>
+      <c r="DE39" s="28" t="s">
+        <v>1760</v>
+      </c>
+      <c r="DF39" s="27"/>
     </row>
     <row r="40" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="20" t="s">
         <v>173</v>
       </c>
       <c r="B40" s="12"/>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="20" t="s">
         <v>174</v>
       </c>
       <c r="D40" s="12"/>
@@ -10492,6 +11126,9 @@
         <v>803</v>
       </c>
       <c r="AH40" s="9"/>
+      <c r="AI40" s="9" t="s">
+        <v>1782</v>
+      </c>
       <c r="AM40" s="9" t="s">
         <v>781</v>
       </c>
@@ -10514,7 +11151,7 @@
       <c r="BU40" s="9"/>
       <c r="BV40" s="9"/>
       <c r="BW40" s="9" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="BX40" s="9"/>
       <c r="BY40" s="9"/>
@@ -10524,28 +11161,28 @@
       <c r="CC40" s="9"/>
       <c r="CD40" s="9"/>
       <c r="CE40" s="9"/>
-      <c r="CS40" s="28"/>
-      <c r="CT40" s="28"/>
-      <c r="CU40" s="28"/>
-      <c r="CV40" s="28"/>
-      <c r="CW40" s="28"/>
-      <c r="CX40" s="28"/>
-      <c r="CY40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="CZ40" s="29"/>
-      <c r="DA40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DB40" s="29"/>
-      <c r="DC40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DD40" s="29"/>
-      <c r="DE40" s="29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="DF40" s="28"/>
+      <c r="CS40" s="27"/>
+      <c r="CT40" s="27"/>
+      <c r="CU40" s="27"/>
+      <c r="CV40" s="27"/>
+      <c r="CW40" s="27"/>
+      <c r="CX40" s="27"/>
+      <c r="CY40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="CZ40" s="28"/>
+      <c r="DA40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DB40" s="28"/>
+      <c r="DC40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DD40" s="28"/>
+      <c r="DE40" s="28" t="s">
+        <v>1761</v>
+      </c>
+      <c r="DF40" s="27"/>
     </row>
     <row r="41" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A41" s="14" t="s">
@@ -10575,6 +11212,9 @@
         <v>805</v>
       </c>
       <c r="AH41" s="9"/>
+      <c r="AI41" s="9" t="s">
+        <v>1783</v>
+      </c>
       <c r="AM41" s="9" t="s">
         <v>806</v>
       </c>
@@ -10597,7 +11237,7 @@
       <c r="BU41" s="9"/>
       <c r="BV41" s="9"/>
       <c r="BW41" s="9" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="BX41" s="9"/>
       <c r="BY41" s="9"/>
@@ -10607,35 +11247,35 @@
       <c r="CC41" s="9"/>
       <c r="CD41" s="9"/>
       <c r="CE41" s="9"/>
-      <c r="CS41" s="28"/>
-      <c r="CT41" s="28"/>
-      <c r="CU41" s="28"/>
-      <c r="CV41" s="28"/>
-      <c r="CW41" s="28"/>
-      <c r="CX41" s="28"/>
-      <c r="CY41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="CZ41" s="29"/>
-      <c r="DA41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DB41" s="29"/>
-      <c r="DC41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DD41" s="29"/>
-      <c r="DE41" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="DF41" s="28"/>
+      <c r="CS41" s="27"/>
+      <c r="CT41" s="27"/>
+      <c r="CU41" s="27"/>
+      <c r="CV41" s="27"/>
+      <c r="CW41" s="27"/>
+      <c r="CX41" s="27"/>
+      <c r="CY41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="CZ41" s="28"/>
+      <c r="DA41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DB41" s="28"/>
+      <c r="DC41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DD41" s="28"/>
+      <c r="DE41" s="28" t="s">
+        <v>1762</v>
+      </c>
+      <c r="DF41" s="27"/>
     </row>
     <row r="42" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="20" t="s">
         <v>177</v>
       </c>
       <c r="B42" s="12"/>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="20" t="s">
         <v>178</v>
       </c>
       <c r="D42" s="12"/>
@@ -10658,6 +11298,9 @@
         <v>808</v>
       </c>
       <c r="AH42" s="9"/>
+      <c r="AI42" s="9" t="s">
+        <v>1784</v>
+      </c>
       <c r="AM42" s="9" t="s">
         <v>784</v>
       </c>
@@ -10680,7 +11323,7 @@
       <c r="BU42" s="9"/>
       <c r="BV42" s="9"/>
       <c r="BW42" s="9" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="BX42" s="9"/>
       <c r="BY42" s="9"/>
@@ -10690,28 +11333,28 @@
       <c r="CC42" s="9"/>
       <c r="CD42" s="9"/>
       <c r="CE42" s="9"/>
-      <c r="CS42" s="28"/>
-      <c r="CT42" s="28"/>
-      <c r="CU42" s="28"/>
-      <c r="CV42" s="28"/>
-      <c r="CW42" s="28"/>
-      <c r="CX42" s="28"/>
-      <c r="CY42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="CZ42" s="29"/>
-      <c r="DA42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DB42" s="29"/>
-      <c r="DC42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DD42" s="29"/>
-      <c r="DE42" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="DF42" s="28"/>
+      <c r="CS42" s="27"/>
+      <c r="CT42" s="27"/>
+      <c r="CU42" s="27"/>
+      <c r="CV42" s="27"/>
+      <c r="CW42" s="27"/>
+      <c r="CX42" s="27"/>
+      <c r="CY42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="CZ42" s="28"/>
+      <c r="DA42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DB42" s="28"/>
+      <c r="DC42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DD42" s="28"/>
+      <c r="DE42" s="28" t="s">
+        <v>1763</v>
+      </c>
+      <c r="DF42" s="27"/>
     </row>
     <row r="43" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A43" s="14" t="s">
@@ -10741,6 +11384,9 @@
         <v>810</v>
       </c>
       <c r="AH43" s="9"/>
+      <c r="AI43" s="9" t="s">
+        <v>1785</v>
+      </c>
       <c r="AM43" t="s">
         <v>811</v>
       </c>
@@ -10762,7 +11408,7 @@
       <c r="BU43" s="9"/>
       <c r="BV43" s="9"/>
       <c r="BW43" s="9" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="BX43" s="9"/>
       <c r="BY43" s="9"/>
@@ -10772,35 +11418,35 @@
       <c r="CC43" s="9"/>
       <c r="CD43" s="9"/>
       <c r="CE43" s="9"/>
-      <c r="CS43" s="28"/>
-      <c r="CT43" s="28"/>
-      <c r="CU43" s="28"/>
-      <c r="CV43" s="28"/>
-      <c r="CW43" s="28"/>
-      <c r="CX43" s="28"/>
-      <c r="CY43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="CZ43" s="29"/>
-      <c r="DA43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DB43" s="29"/>
-      <c r="DC43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DD43" s="29"/>
-      <c r="DE43" s="29" t="s">
-        <v>1765</v>
-      </c>
-      <c r="DF43" s="28"/>
+      <c r="CS43" s="27"/>
+      <c r="CT43" s="27"/>
+      <c r="CU43" s="27"/>
+      <c r="CV43" s="27"/>
+      <c r="CW43" s="27"/>
+      <c r="CX43" s="27"/>
+      <c r="CY43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="CZ43" s="28"/>
+      <c r="DA43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DB43" s="28"/>
+      <c r="DC43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DD43" s="28"/>
+      <c r="DE43" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="DF43" s="27"/>
     </row>
     <row r="44" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="20" t="s">
         <v>181</v>
       </c>
       <c r="B44" s="12"/>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="20" t="s">
         <v>182</v>
       </c>
       <c r="D44" s="12"/>
@@ -10823,6 +11469,9 @@
         <v>813</v>
       </c>
       <c r="AH44" s="9"/>
+      <c r="AI44" s="9" t="s">
+        <v>1786</v>
+      </c>
       <c r="AM44" s="9" t="s">
         <v>787</v>
       </c>
@@ -10845,7 +11494,7 @@
       <c r="BU44" s="9"/>
       <c r="BV44" s="9"/>
       <c r="BW44" s="9" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="BX44" s="9"/>
       <c r="BY44" s="9"/>
@@ -10855,28 +11504,28 @@
       <c r="CC44" s="9"/>
       <c r="CD44" s="9"/>
       <c r="CE44" s="9"/>
-      <c r="CS44" s="28"/>
-      <c r="CT44" s="28"/>
-      <c r="CU44" s="28"/>
-      <c r="CV44" s="28"/>
-      <c r="CW44" s="28"/>
-      <c r="CX44" s="28"/>
-      <c r="CY44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="CZ44" s="29"/>
-      <c r="DA44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DB44" s="29"/>
-      <c r="DC44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DD44" s="29"/>
-      <c r="DE44" s="29" t="s">
-        <v>1766</v>
-      </c>
-      <c r="DF44" s="28"/>
+      <c r="CS44" s="27"/>
+      <c r="CT44" s="27"/>
+      <c r="CU44" s="27"/>
+      <c r="CV44" s="27"/>
+      <c r="CW44" s="27"/>
+      <c r="CX44" s="27"/>
+      <c r="CY44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="CZ44" s="28"/>
+      <c r="DA44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DB44" s="28"/>
+      <c r="DC44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DD44" s="28"/>
+      <c r="DE44" s="28" t="s">
+        <v>1765</v>
+      </c>
+      <c r="DF44" s="27"/>
     </row>
     <row r="45" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A45" s="14" t="s">
@@ -10906,6 +11555,9 @@
         <v>815</v>
       </c>
       <c r="AH45" s="9"/>
+      <c r="AI45" s="9" t="s">
+        <v>1787</v>
+      </c>
       <c r="AM45" s="9" t="s">
         <v>791</v>
       </c>
@@ -10928,7 +11580,7 @@
       <c r="BU45" s="9"/>
       <c r="BV45" s="9"/>
       <c r="BW45" s="9" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="BX45" s="9"/>
       <c r="BY45" s="9"/>
@@ -10938,35 +11590,35 @@
       <c r="CC45" s="9"/>
       <c r="CD45" s="9"/>
       <c r="CE45" s="9"/>
-      <c r="CS45" s="28"/>
-      <c r="CT45" s="28"/>
-      <c r="CU45" s="28"/>
-      <c r="CV45" s="28"/>
-      <c r="CW45" s="28"/>
-      <c r="CX45" s="28"/>
-      <c r="CY45" s="29" t="s">
+      <c r="CS45" s="27"/>
+      <c r="CT45" s="27"/>
+      <c r="CU45" s="27"/>
+      <c r="CV45" s="27"/>
+      <c r="CW45" s="27"/>
+      <c r="CX45" s="27"/>
+      <c r="CY45" s="28" t="s">
+        <v>1766</v>
+      </c>
+      <c r="CZ45" s="28"/>
+      <c r="DA45" s="28" t="s">
         <v>1767</v>
       </c>
-      <c r="CZ45" s="29"/>
-      <c r="DA45" s="29" t="s">
-        <v>1768</v>
-      </c>
-      <c r="DB45" s="29"/>
-      <c r="DC45" s="29" t="s">
+      <c r="DB45" s="28"/>
+      <c r="DC45" s="28" t="s">
+        <v>1766</v>
+      </c>
+      <c r="DD45" s="28"/>
+      <c r="DE45" s="28" t="s">
         <v>1767</v>
       </c>
-      <c r="DD45" s="29"/>
-      <c r="DE45" s="29" t="s">
-        <v>1768</v>
-      </c>
-      <c r="DF45" s="28"/>
+      <c r="DF45" s="27"/>
     </row>
     <row r="46" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="20" t="s">
         <v>185</v>
       </c>
       <c r="B46" s="12"/>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>186</v>
       </c>
       <c r="D46" s="12"/>
@@ -10989,6 +11641,9 @@
         <v>817</v>
       </c>
       <c r="AH46" s="9"/>
+      <c r="AI46" s="9" t="s">
+        <v>1788</v>
+      </c>
       <c r="AM46" t="s">
         <v>818</v>
       </c>
@@ -11010,7 +11665,7 @@
       <c r="BU46" s="9"/>
       <c r="BV46" s="9"/>
       <c r="BW46" s="9" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="BX46" s="9"/>
       <c r="BY46" s="9"/>
@@ -11020,28 +11675,28 @@
       <c r="CC46" s="9"/>
       <c r="CD46" s="9"/>
       <c r="CE46" s="9"/>
-      <c r="CS46" s="28"/>
-      <c r="CT46" s="28"/>
-      <c r="CU46" s="28"/>
-      <c r="CV46" s="28"/>
-      <c r="CW46" s="28"/>
-      <c r="CX46" s="28"/>
-      <c r="CY46" s="29" t="s">
+      <c r="CS46" s="27"/>
+      <c r="CT46" s="27"/>
+      <c r="CU46" s="27"/>
+      <c r="CV46" s="27"/>
+      <c r="CW46" s="27"/>
+      <c r="CX46" s="27"/>
+      <c r="CY46" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="CZ46" s="28"/>
+      <c r="DA46" s="28" t="s">
         <v>1769</v>
       </c>
-      <c r="CZ46" s="29"/>
-      <c r="DA46" s="29" t="s">
-        <v>1770</v>
-      </c>
-      <c r="DB46" s="29"/>
-      <c r="DC46" s="29" t="s">
+      <c r="DB46" s="28"/>
+      <c r="DC46" s="28" t="s">
+        <v>1768</v>
+      </c>
+      <c r="DD46" s="28"/>
+      <c r="DE46" s="28" t="s">
         <v>1769</v>
       </c>
-      <c r="DD46" s="29"/>
-      <c r="DE46" s="29" t="s">
-        <v>1770</v>
-      </c>
-      <c r="DF46" s="28"/>
+      <c r="DF46" s="27"/>
     </row>
     <row r="47" spans="1:110" ht="16" x14ac:dyDescent="0.4">
       <c r="A47" s="14" t="s">
@@ -11071,6 +11726,9 @@
         <v>820</v>
       </c>
       <c r="AH47" s="9"/>
+      <c r="AI47" s="9" t="s">
+        <v>1789</v>
+      </c>
       <c r="AM47" s="9" t="s">
         <v>801</v>
       </c>
@@ -11093,7 +11751,7 @@
       <c r="BU47" s="9"/>
       <c r="BV47" s="9"/>
       <c r="BW47" s="9" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="BX47" s="9"/>
       <c r="BY47" s="9"/>
@@ -11103,35 +11761,35 @@
       <c r="CC47" s="9"/>
       <c r="CD47" s="9"/>
       <c r="CE47" s="9"/>
-      <c r="CS47" s="28"/>
-      <c r="CT47" s="28"/>
-      <c r="CU47" s="28"/>
-      <c r="CV47" s="28"/>
-      <c r="CW47" s="28"/>
-      <c r="CX47" s="28"/>
-      <c r="CY47" s="29" t="s">
-        <v>1726</v>
-      </c>
-      <c r="CZ47" s="29"/>
-      <c r="DA47" s="29" t="s">
-        <v>1771</v>
-      </c>
-      <c r="DB47" s="29"/>
-      <c r="DC47" s="29" t="s">
-        <v>1726</v>
-      </c>
-      <c r="DD47" s="29"/>
-      <c r="DE47" s="29" t="s">
-        <v>1771</v>
-      </c>
-      <c r="DF47" s="28"/>
+      <c r="CS47" s="27"/>
+      <c r="CT47" s="27"/>
+      <c r="CU47" s="27"/>
+      <c r="CV47" s="27"/>
+      <c r="CW47" s="27"/>
+      <c r="CX47" s="27"/>
+      <c r="CY47" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CZ47" s="28"/>
+      <c r="DA47" s="28" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DB47" s="28"/>
+      <c r="DC47" s="28" t="s">
+        <v>1725</v>
+      </c>
+      <c r="DD47" s="28"/>
+      <c r="DE47" s="28" t="s">
+        <v>1770</v>
+      </c>
+      <c r="DF47" s="27"/>
     </row>
     <row r="48" spans="1:110" ht="16" x14ac:dyDescent="0.4">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B48" s="12"/>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="20" t="s">
         <v>190</v>
       </c>
       <c r="D48" s="12"/>
@@ -11154,6 +11812,9 @@
         <v>822</v>
       </c>
       <c r="AH48" s="9"/>
+      <c r="AI48" s="9" t="s">
+        <v>1790</v>
+      </c>
       <c r="AQ48" s="9" t="s">
         <v>823</v>
       </c>
@@ -11172,7 +11833,7 @@
       <c r="BU48" s="9"/>
       <c r="BV48" s="9"/>
       <c r="BW48" s="9" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="BX48" s="9"/>
       <c r="BY48" s="9"/>
@@ -11182,28 +11843,28 @@
       <c r="CC48" s="9"/>
       <c r="CD48" s="9"/>
       <c r="CE48" s="9"/>
-      <c r="CS48" s="28"/>
-      <c r="CT48" s="28"/>
-      <c r="CU48" s="28"/>
-      <c r="CV48" s="28"/>
-      <c r="CW48" s="28"/>
-      <c r="CX48" s="28"/>
-      <c r="CY48" s="29" t="s">
-        <v>1729</v>
-      </c>
-      <c r="CZ48" s="29"/>
-      <c r="DA48" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="DB48" s="29"/>
-      <c r="DC48" s="29" t="s">
-        <v>1729</v>
-      </c>
-      <c r="DD48" s="29"/>
-      <c r="DE48" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="DF48" s="28"/>
+      <c r="CS48" s="27"/>
+      <c r="CT48" s="27"/>
+      <c r="CU48" s="27"/>
+      <c r="CV48" s="27"/>
+      <c r="CW48" s="27"/>
+      <c r="CX48" s="27"/>
+      <c r="CY48" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="CZ48" s="28"/>
+      <c r="DA48" s="28" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DB48" s="28"/>
+      <c r="DC48" s="28" t="s">
+        <v>1728</v>
+      </c>
+      <c r="DD48" s="28"/>
+      <c r="DE48" s="28" t="s">
+        <v>1771</v>
+      </c>
+      <c r="DF48" s="27"/>
     </row>
     <row r="49" spans="1:83" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
@@ -11233,6 +11894,9 @@
         <v>824</v>
       </c>
       <c r="AH49" s="9"/>
+      <c r="AI49" s="9" t="s">
+        <v>1791</v>
+      </c>
       <c r="AQ49" s="9" t="s">
         <v>825</v>
       </c>
@@ -11251,7 +11915,7 @@
       <c r="BU49" s="9"/>
       <c r="BV49" s="9"/>
       <c r="BW49" s="9" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="BX49" s="9"/>
       <c r="BY49" s="9"/>
@@ -11263,11 +11927,11 @@
       <c r="CE49" s="9"/>
     </row>
     <row r="50" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="20" t="s">
         <v>193</v>
       </c>
       <c r="B50" s="12"/>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="20" t="s">
         <v>194</v>
       </c>
       <c r="D50" s="12"/>
@@ -11290,6 +11954,9 @@
         <v>826</v>
       </c>
       <c r="AH50" s="9"/>
+      <c r="AI50" s="9" t="s">
+        <v>1792</v>
+      </c>
       <c r="AQ50" s="9" t="s">
         <v>827</v>
       </c>
@@ -11308,7 +11975,7 @@
       <c r="BU50" s="9"/>
       <c r="BV50" s="9"/>
       <c r="BW50" s="9" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="BX50" s="9"/>
       <c r="BY50" s="9"/>
@@ -11347,6 +12014,9 @@
         <v>828</v>
       </c>
       <c r="AH51" s="9"/>
+      <c r="AI51" s="9" t="s">
+        <v>1793</v>
+      </c>
       <c r="AQ51" s="9" t="s">
         <v>829</v>
       </c>
@@ -11365,7 +12035,7 @@
       <c r="BU51" s="9"/>
       <c r="BV51" s="9"/>
       <c r="BW51" s="9" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="BX51" s="9"/>
       <c r="BY51" s="9"/>
@@ -11377,11 +12047,11 @@
       <c r="CE51" s="9"/>
     </row>
     <row r="52" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="20" t="s">
         <v>197</v>
       </c>
       <c r="B52" s="12"/>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="20" t="s">
         <v>198</v>
       </c>
       <c r="D52" s="12"/>
@@ -11404,6 +12074,9 @@
         <v>830</v>
       </c>
       <c r="AH52" s="9"/>
+      <c r="AI52" s="9" t="s">
+        <v>1794</v>
+      </c>
       <c r="AQ52" s="9" t="s">
         <v>831</v>
       </c>
@@ -11422,7 +12095,7 @@
       <c r="BU52" s="9"/>
       <c r="BV52" s="9"/>
       <c r="BW52" s="9" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="BX52" s="9"/>
       <c r="BY52" s="9"/>
@@ -11461,6 +12134,9 @@
         <v>832</v>
       </c>
       <c r="AH53" s="9"/>
+      <c r="AI53" s="9" t="s">
+        <v>1795</v>
+      </c>
       <c r="AQ53" s="9" t="s">
         <v>833</v>
       </c>
@@ -11479,7 +12155,7 @@
       <c r="BU53" s="9"/>
       <c r="BV53" s="9"/>
       <c r="BW53" s="9" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="BX53" s="9"/>
       <c r="BY53" s="9"/>
@@ -11491,11 +12167,11 @@
       <c r="CE53" s="9"/>
     </row>
     <row r="54" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="20" t="s">
         <v>201</v>
       </c>
       <c r="B54" s="12"/>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="20" t="s">
         <v>202</v>
       </c>
       <c r="D54" s="12"/>
@@ -11518,6 +12194,9 @@
         <v>834</v>
       </c>
       <c r="AH54" s="9"/>
+      <c r="AI54" s="9" t="s">
+        <v>1796</v>
+      </c>
       <c r="AQ54" s="9" t="s">
         <v>835</v>
       </c>
@@ -11536,7 +12215,7 @@
       <c r="BU54" s="9"/>
       <c r="BV54" s="9"/>
       <c r="BW54" s="9" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="BX54" s="9"/>
       <c r="BY54" s="9"/>
@@ -11575,6 +12254,9 @@
         <v>836</v>
       </c>
       <c r="AH55" s="9"/>
+      <c r="AI55" s="9" t="s">
+        <v>1797</v>
+      </c>
       <c r="AQ55" s="9" t="s">
         <v>837</v>
       </c>
@@ -11593,7 +12275,7 @@
       <c r="BU55" s="9"/>
       <c r="BV55" s="9"/>
       <c r="BW55" s="9" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="BX55" s="9"/>
       <c r="BY55" s="9"/>
@@ -11605,11 +12287,11 @@
       <c r="CE55" s="9"/>
     </row>
     <row r="56" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="20" t="s">
         <v>205</v>
       </c>
       <c r="B56" s="12"/>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="20" t="s">
         <v>206</v>
       </c>
       <c r="D56" s="12"/>
@@ -11632,6 +12314,9 @@
         <v>838</v>
       </c>
       <c r="AH56" s="9"/>
+      <c r="AI56" s="9" t="s">
+        <v>1798</v>
+      </c>
       <c r="AQ56" s="9" t="s">
         <v>839</v>
       </c>
@@ -11650,7 +12335,7 @@
       <c r="BU56" s="9"/>
       <c r="BV56" s="9"/>
       <c r="BW56" s="9" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="BX56" s="9"/>
       <c r="BY56" s="9"/>
@@ -11689,6 +12374,9 @@
         <v>840</v>
       </c>
       <c r="AH57" s="9"/>
+      <c r="AI57" s="9" t="s">
+        <v>1799</v>
+      </c>
       <c r="AQ57" s="9" t="s">
         <v>841</v>
       </c>
@@ -11707,7 +12395,7 @@
       <c r="BU57" s="9"/>
       <c r="BV57" s="9"/>
       <c r="BW57" s="9" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="BX57" s="9"/>
       <c r="BY57" s="9"/>
@@ -11719,11 +12407,11 @@
       <c r="CE57" s="9"/>
     </row>
     <row r="58" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B58" s="12"/>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="20" t="s">
         <v>210</v>
       </c>
       <c r="D58" s="12"/>
@@ -11746,6 +12434,9 @@
         <v>842</v>
       </c>
       <c r="AH58" s="9"/>
+      <c r="AI58" s="9" t="s">
+        <v>1800</v>
+      </c>
       <c r="AQ58" s="9" t="s">
         <v>843</v>
       </c>
@@ -11764,7 +12455,7 @@
       <c r="BU58" s="9"/>
       <c r="BV58" s="9"/>
       <c r="BW58" s="9" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="BX58" s="9"/>
       <c r="BY58" s="9"/>
@@ -11803,6 +12494,9 @@
         <v>844</v>
       </c>
       <c r="AH59" s="9"/>
+      <c r="AI59" s="9" t="s">
+        <v>1801</v>
+      </c>
       <c r="AQ59" s="9" t="s">
         <v>845</v>
       </c>
@@ -11821,7 +12515,7 @@
       <c r="BU59" s="9"/>
       <c r="BV59" s="9"/>
       <c r="BW59" s="9" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="BX59" s="9"/>
       <c r="BY59" s="9"/>
@@ -11833,11 +12527,11 @@
       <c r="CE59" s="9"/>
     </row>
     <row r="60" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="20" t="s">
         <v>213</v>
       </c>
       <c r="B60" s="12"/>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="20" t="s">
         <v>214</v>
       </c>
       <c r="D60" s="12"/>
@@ -11860,6 +12554,9 @@
         <v>846</v>
       </c>
       <c r="AH60" s="9"/>
+      <c r="AI60" s="9" t="s">
+        <v>1802</v>
+      </c>
       <c r="AQ60" s="9" t="s">
         <v>847</v>
       </c>
@@ -11878,7 +12575,7 @@
       <c r="BU60" s="9"/>
       <c r="BV60" s="9"/>
       <c r="BW60" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="BX60" s="9"/>
       <c r="BY60" s="9"/>
@@ -11917,6 +12614,9 @@
         <v>848</v>
       </c>
       <c r="AH61" s="9"/>
+      <c r="AI61" s="9" t="s">
+        <v>1803</v>
+      </c>
       <c r="AQ61" s="9" t="s">
         <v>849</v>
       </c>
@@ -11935,7 +12635,7 @@
       <c r="BU61" s="9"/>
       <c r="BV61" s="9"/>
       <c r="BW61" s="9" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="BX61" s="9"/>
       <c r="BY61" s="9"/>
@@ -11947,11 +12647,11 @@
       <c r="CE61" s="9"/>
     </row>
     <row r="62" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="20" t="s">
         <v>217</v>
       </c>
       <c r="B62" s="12"/>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="20" t="s">
         <v>218</v>
       </c>
       <c r="D62" s="12"/>
@@ -11974,6 +12674,9 @@
         <v>850</v>
       </c>
       <c r="AH62" s="9"/>
+      <c r="AI62" s="9" t="s">
+        <v>1804</v>
+      </c>
       <c r="AQ62" s="9" t="s">
         <v>851</v>
       </c>
@@ -11992,7 +12695,7 @@
       <c r="BU62" s="9"/>
       <c r="BV62" s="9"/>
       <c r="BW62" s="9" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="BX62" s="9"/>
       <c r="BY62" s="9"/>
@@ -12031,6 +12734,9 @@
         <v>852</v>
       </c>
       <c r="AH63" s="9"/>
+      <c r="AI63" s="9" t="s">
+        <v>1805</v>
+      </c>
       <c r="AQ63" s="9" t="s">
         <v>853</v>
       </c>
@@ -12049,7 +12755,7 @@
       <c r="BU63" s="9"/>
       <c r="BV63" s="9"/>
       <c r="BW63" s="9" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="BX63" s="9"/>
       <c r="BY63" s="9"/>
@@ -12061,11 +12767,11 @@
       <c r="CE63" s="9"/>
     </row>
     <row r="64" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B64" s="12"/>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="20" t="s">
         <v>222</v>
       </c>
       <c r="D64" s="12"/>
@@ -12088,6 +12794,9 @@
         <v>854</v>
       </c>
       <c r="AH64" s="9"/>
+      <c r="AI64" s="9" t="s">
+        <v>1806</v>
+      </c>
       <c r="AQ64" s="9" t="s">
         <v>855</v>
       </c>
@@ -12106,7 +12815,7 @@
       <c r="BU64" s="9"/>
       <c r="BV64" s="9"/>
       <c r="BW64" s="9" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="BX64" s="9"/>
       <c r="BY64" s="9"/>
@@ -12145,6 +12854,9 @@
         <v>856</v>
       </c>
       <c r="AH65" s="9"/>
+      <c r="AI65" s="9" t="s">
+        <v>1807</v>
+      </c>
       <c r="AQ65" s="9" t="s">
         <v>857</v>
       </c>
@@ -12163,7 +12875,7 @@
       <c r="BU65" s="9"/>
       <c r="BV65" s="9"/>
       <c r="BW65" s="9" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="BX65" s="9"/>
       <c r="BY65" s="9"/>
@@ -12175,11 +12887,11 @@
       <c r="CE65" s="9"/>
     </row>
     <row r="66" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="20" t="s">
         <v>225</v>
       </c>
       <c r="B66" s="12"/>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="20" t="s">
         <v>226</v>
       </c>
       <c r="D66" s="12"/>
@@ -12202,6 +12914,9 @@
         <v>858</v>
       </c>
       <c r="AH66" s="9"/>
+      <c r="AI66" s="9" t="s">
+        <v>1808</v>
+      </c>
       <c r="AQ66" s="9" t="s">
         <v>859</v>
       </c>
@@ -12220,7 +12935,7 @@
       <c r="BU66" s="9"/>
       <c r="BV66" s="9"/>
       <c r="BW66" s="9" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="BX66" s="9"/>
       <c r="BY66" s="9"/>
@@ -12259,6 +12974,9 @@
         <v>860</v>
       </c>
       <c r="AH67" s="9"/>
+      <c r="AI67" s="9" t="s">
+        <v>1809</v>
+      </c>
       <c r="AQ67" s="9" t="s">
         <v>861</v>
       </c>
@@ -12277,7 +12995,7 @@
       <c r="BU67" s="9"/>
       <c r="BV67" s="9"/>
       <c r="BW67" s="9" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="BX67" s="9"/>
       <c r="BY67" s="9"/>
@@ -12289,11 +13007,11 @@
       <c r="CE67" s="9"/>
     </row>
     <row r="68" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="20" t="s">
         <v>229</v>
       </c>
       <c r="B68" s="12"/>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="20" t="s">
         <v>230</v>
       </c>
       <c r="D68" s="12"/>
@@ -12316,6 +13034,9 @@
         <v>862</v>
       </c>
       <c r="AH68" s="9"/>
+      <c r="AI68" s="9" t="s">
+        <v>1810</v>
+      </c>
       <c r="AQ68" s="9" t="s">
         <v>863</v>
       </c>
@@ -12334,7 +13055,7 @@
       <c r="BU68" s="9"/>
       <c r="BV68" s="9"/>
       <c r="BW68" s="9" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="BX68" s="9"/>
       <c r="BY68" s="9"/>
@@ -12373,6 +13094,9 @@
         <v>864</v>
       </c>
       <c r="AH69" s="9"/>
+      <c r="AI69" s="9" t="s">
+        <v>1811</v>
+      </c>
       <c r="AQ69" s="9" t="s">
         <v>865</v>
       </c>
@@ -12391,7 +13115,7 @@
       <c r="BU69" s="9"/>
       <c r="BV69" s="9"/>
       <c r="BW69" s="9" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="BX69" s="9"/>
       <c r="BY69" s="9"/>
@@ -12403,11 +13127,11 @@
       <c r="CE69" s="9"/>
     </row>
     <row r="70" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B70" s="12"/>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>234</v>
       </c>
       <c r="D70" s="12"/>
@@ -12430,6 +13154,9 @@
         <v>866</v>
       </c>
       <c r="AH70" s="9"/>
+      <c r="AI70" s="9" t="s">
+        <v>1812</v>
+      </c>
       <c r="AQ70" s="9" t="s">
         <v>867</v>
       </c>
@@ -12448,7 +13175,7 @@
       <c r="BU70" s="9"/>
       <c r="BV70" s="9"/>
       <c r="BW70" s="9" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="BX70" s="9"/>
       <c r="BY70" s="9"/>
@@ -12487,6 +13214,9 @@
         <v>868</v>
       </c>
       <c r="AH71" s="9"/>
+      <c r="AI71" s="9" t="s">
+        <v>1813</v>
+      </c>
       <c r="AQ71" s="9" t="s">
         <v>869</v>
       </c>
@@ -12505,7 +13235,7 @@
       <c r="BU71" s="9"/>
       <c r="BV71" s="9"/>
       <c r="BW71" s="9" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="BX71" s="9"/>
       <c r="BY71" s="9"/>
@@ -12517,11 +13247,11 @@
       <c r="CE71" s="9"/>
     </row>
     <row r="72" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="20" t="s">
         <v>237</v>
       </c>
       <c r="B72" s="12"/>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="20" t="s">
         <v>238</v>
       </c>
       <c r="D72" s="12"/>
@@ -12544,6 +13274,9 @@
         <v>870</v>
       </c>
       <c r="AH72" s="9"/>
+      <c r="AI72" s="9" t="s">
+        <v>1814</v>
+      </c>
       <c r="AQ72" s="9" t="s">
         <v>871</v>
       </c>
@@ -12562,7 +13295,7 @@
       <c r="BU72" s="9"/>
       <c r="BV72" s="9"/>
       <c r="BW72" s="9" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="BX72" s="9"/>
       <c r="BY72" s="9"/>
@@ -12601,6 +13334,9 @@
         <v>872</v>
       </c>
       <c r="AH73" s="9"/>
+      <c r="AI73" s="9" t="s">
+        <v>1815</v>
+      </c>
       <c r="AQ73" s="9" t="s">
         <v>873</v>
       </c>
@@ -12619,7 +13355,7 @@
       <c r="BU73" s="9"/>
       <c r="BV73" s="9"/>
       <c r="BW73" s="9" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="BX73" s="9"/>
       <c r="BY73" s="9"/>
@@ -12631,11 +13367,11 @@
       <c r="CE73" s="9"/>
     </row>
     <row r="74" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B74" s="12"/>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="20" t="s">
         <v>242</v>
       </c>
       <c r="D74" s="12"/>
@@ -12658,6 +13394,9 @@
         <v>874</v>
       </c>
       <c r="AH74" s="9"/>
+      <c r="AI74" s="9" t="s">
+        <v>1816</v>
+      </c>
       <c r="AQ74" s="9" t="s">
         <v>875</v>
       </c>
@@ -12676,7 +13415,7 @@
       <c r="BU74" s="9"/>
       <c r="BV74" s="9"/>
       <c r="BW74" s="9" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="BX74" s="9"/>
       <c r="BY74" s="9"/>
@@ -12715,6 +13454,9 @@
         <v>876</v>
       </c>
       <c r="AH75" s="9"/>
+      <c r="AI75" s="9" t="s">
+        <v>1817</v>
+      </c>
       <c r="AQ75" s="9" t="s">
         <v>877</v>
       </c>
@@ -12733,7 +13475,7 @@
       <c r="BU75" s="9"/>
       <c r="BV75" s="9"/>
       <c r="BW75" s="9" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="BX75" s="9"/>
       <c r="BY75" s="9"/>
@@ -12745,11 +13487,11 @@
       <c r="CE75" s="9"/>
     </row>
     <row r="76" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B76" s="12"/>
-      <c r="C76" s="21" t="s">
+      <c r="C76" s="20" t="s">
         <v>246</v>
       </c>
       <c r="D76" s="12"/>
@@ -12772,6 +13514,9 @@
         <v>878</v>
       </c>
       <c r="AH76" s="9"/>
+      <c r="AI76" s="9" t="s">
+        <v>1818</v>
+      </c>
       <c r="AQ76" s="9" t="s">
         <v>879</v>
       </c>
@@ -12790,7 +13535,7 @@
       <c r="BU76" s="9"/>
       <c r="BV76" s="9"/>
       <c r="BW76" s="9" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="BX76" s="9"/>
       <c r="BY76" s="9"/>
@@ -12829,6 +13574,9 @@
         <v>880</v>
       </c>
       <c r="AH77" s="9"/>
+      <c r="AI77" s="9" t="s">
+        <v>1819</v>
+      </c>
       <c r="AQ77" s="9" t="s">
         <v>881</v>
       </c>
@@ -12847,7 +13595,7 @@
       <c r="BU77" s="9"/>
       <c r="BV77" s="9"/>
       <c r="BW77" s="9" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="BX77" s="9"/>
       <c r="BY77" s="9"/>
@@ -12859,11 +13607,11 @@
       <c r="CE77" s="9"/>
     </row>
     <row r="78" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="20" t="s">
         <v>249</v>
       </c>
       <c r="B78" s="12"/>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="20" t="s">
         <v>250</v>
       </c>
       <c r="D78" s="12"/>
@@ -12886,6 +13634,9 @@
         <v>882</v>
       </c>
       <c r="AH78" s="9"/>
+      <c r="AI78" s="9" t="s">
+        <v>1820</v>
+      </c>
       <c r="AQ78" s="9" t="s">
         <v>883</v>
       </c>
@@ -12904,7 +13655,7 @@
       <c r="BU78" s="9"/>
       <c r="BV78" s="9"/>
       <c r="BW78" s="9" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="BX78" s="9"/>
       <c r="BY78" s="9"/>
@@ -12943,6 +13694,9 @@
         <v>884</v>
       </c>
       <c r="AH79" s="9"/>
+      <c r="AI79" s="9" t="s">
+        <v>1821</v>
+      </c>
       <c r="AQ79" s="9" t="s">
         <v>885</v>
       </c>
@@ -12961,7 +13715,7 @@
       <c r="BU79" s="9"/>
       <c r="BV79" s="9"/>
       <c r="BW79" s="9" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="BX79" s="9"/>
       <c r="BY79" s="9"/>
@@ -12973,11 +13727,11 @@
       <c r="CE79" s="9"/>
     </row>
     <row r="80" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="20" t="s">
         <v>253</v>
       </c>
       <c r="B80" s="12"/>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="20" t="s">
         <v>254</v>
       </c>
       <c r="D80" s="12"/>
@@ -13000,6 +13754,9 @@
         <v>886</v>
       </c>
       <c r="AH80" s="9"/>
+      <c r="AI80" s="9" t="s">
+        <v>1822</v>
+      </c>
       <c r="AQ80" s="9" t="s">
         <v>887</v>
       </c>
@@ -13018,7 +13775,7 @@
       <c r="BU80" s="9"/>
       <c r="BV80" s="9"/>
       <c r="BW80" s="9" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="BX80" s="9"/>
       <c r="BY80" s="9"/>
@@ -13057,6 +13814,9 @@
         <v>888</v>
       </c>
       <c r="AH81" s="9"/>
+      <c r="AI81" s="9" t="s">
+        <v>1823</v>
+      </c>
       <c r="AQ81" s="9" t="s">
         <v>889</v>
       </c>
@@ -13075,7 +13835,7 @@
       <c r="BU81" s="9"/>
       <c r="BV81" s="9"/>
       <c r="BW81" s="9" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="BX81" s="9"/>
       <c r="BY81" s="9"/>
@@ -13087,11 +13847,11 @@
       <c r="CE81" s="9"/>
     </row>
     <row r="82" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="20" t="s">
         <v>257</v>
       </c>
       <c r="B82" s="12"/>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="20" t="s">
         <v>258</v>
       </c>
       <c r="D82" s="12"/>
@@ -13114,6 +13874,9 @@
         <v>890</v>
       </c>
       <c r="AH82" s="9"/>
+      <c r="AI82" s="9" t="s">
+        <v>1824</v>
+      </c>
       <c r="AQ82" s="9" t="s">
         <v>891</v>
       </c>
@@ -13132,7 +13895,7 @@
       <c r="BU82" s="9"/>
       <c r="BV82" s="9"/>
       <c r="BW82" s="9" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="BX82" s="9"/>
       <c r="BY82" s="9"/>
@@ -13171,6 +13934,9 @@
         <v>892</v>
       </c>
       <c r="AH83" s="9"/>
+      <c r="AI83" s="9" t="s">
+        <v>1825</v>
+      </c>
       <c r="AQ83" s="9" t="s">
         <v>893</v>
       </c>
@@ -13189,7 +13955,7 @@
       <c r="BU83" s="9"/>
       <c r="BV83" s="9"/>
       <c r="BW83" s="9" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="BX83" s="9"/>
       <c r="BY83" s="9"/>
@@ -13201,11 +13967,11 @@
       <c r="CE83" s="9"/>
     </row>
     <row r="84" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A84" s="21" t="s">
+      <c r="A84" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B84" s="12"/>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="20" t="s">
         <v>262</v>
       </c>
       <c r="D84" s="12"/>
@@ -13228,6 +13994,9 @@
         <v>894</v>
       </c>
       <c r="AH84" s="9"/>
+      <c r="AI84" s="9" t="s">
+        <v>1826</v>
+      </c>
       <c r="AQ84" s="9" t="s">
         <v>895</v>
       </c>
@@ -13246,7 +14015,7 @@
       <c r="BU84" s="9"/>
       <c r="BV84" s="9"/>
       <c r="BW84" s="9" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="BX84" s="9"/>
       <c r="BY84" s="9"/>
@@ -13285,6 +14054,9 @@
         <v>896</v>
       </c>
       <c r="AH85" s="9"/>
+      <c r="AI85" s="9" t="s">
+        <v>1827</v>
+      </c>
       <c r="AQ85" s="9" t="s">
         <v>897</v>
       </c>
@@ -13303,7 +14075,7 @@
       <c r="BU85" s="9"/>
       <c r="BV85" s="9"/>
       <c r="BW85" s="9" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="BX85" s="9"/>
       <c r="BY85" s="9"/>
@@ -13315,11 +14087,11 @@
       <c r="CE85" s="9"/>
     </row>
     <row r="86" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A86" s="21" t="s">
+      <c r="A86" s="20" t="s">
         <v>265</v>
       </c>
       <c r="B86" s="12"/>
-      <c r="C86" s="21" t="s">
+      <c r="C86" s="20" t="s">
         <v>266</v>
       </c>
       <c r="D86" s="12"/>
@@ -13342,6 +14114,9 @@
         <v>898</v>
       </c>
       <c r="AH86" s="9"/>
+      <c r="AI86" s="9" t="s">
+        <v>1828</v>
+      </c>
       <c r="AQ86" s="9" t="s">
         <v>899</v>
       </c>
@@ -13360,7 +14135,7 @@
       <c r="BU86" s="9"/>
       <c r="BV86" s="9"/>
       <c r="BW86" s="9" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="BX86" s="9"/>
       <c r="BY86" s="9"/>
@@ -13399,6 +14174,9 @@
         <v>900</v>
       </c>
       <c r="AH87" s="9"/>
+      <c r="AI87" s="9" t="s">
+        <v>1829</v>
+      </c>
       <c r="AQ87" s="9" t="s">
         <v>901</v>
       </c>
@@ -13417,7 +14195,7 @@
       <c r="BU87" s="9"/>
       <c r="BV87" s="9"/>
       <c r="BW87" s="9" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="BX87" s="9"/>
       <c r="BY87" s="9"/>
@@ -13429,11 +14207,11 @@
       <c r="CE87" s="9"/>
     </row>
     <row r="88" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A88" s="21" t="s">
+      <c r="A88" s="20" t="s">
         <v>269</v>
       </c>
       <c r="B88" s="12"/>
-      <c r="C88" s="21" t="s">
+      <c r="C88" s="20" t="s">
         <v>270</v>
       </c>
       <c r="D88" s="12"/>
@@ -13456,6 +14234,9 @@
         <v>902</v>
       </c>
       <c r="AH88" s="9"/>
+      <c r="AI88" s="9" t="s">
+        <v>1830</v>
+      </c>
       <c r="AQ88" s="9" t="s">
         <v>903</v>
       </c>
@@ -13474,7 +14255,7 @@
       <c r="BU88" s="9"/>
       <c r="BV88" s="9"/>
       <c r="BW88" s="9" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="BX88" s="9"/>
       <c r="BY88" s="9"/>
@@ -13513,6 +14294,9 @@
         <v>904</v>
       </c>
       <c r="AH89" s="9"/>
+      <c r="AI89" s="9" t="s">
+        <v>1831</v>
+      </c>
       <c r="AQ89" s="9" t="s">
         <v>905</v>
       </c>
@@ -13531,7 +14315,7 @@
       <c r="BU89" s="9"/>
       <c r="BV89" s="9"/>
       <c r="BW89" s="9" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="BX89" s="9"/>
       <c r="BY89" s="9"/>
@@ -13543,11 +14327,11 @@
       <c r="CE89" s="9"/>
     </row>
     <row r="90" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="20" t="s">
         <v>273</v>
       </c>
       <c r="B90" s="12"/>
-      <c r="C90" s="21" t="s">
+      <c r="C90" s="20" t="s">
         <v>274</v>
       </c>
       <c r="D90" s="12"/>
@@ -13570,6 +14354,9 @@
         <v>906</v>
       </c>
       <c r="AH90" s="9"/>
+      <c r="AI90" s="9" t="s">
+        <v>1832</v>
+      </c>
       <c r="AQ90" s="9" t="s">
         <v>907</v>
       </c>
@@ -13588,7 +14375,7 @@
       <c r="BU90" s="9"/>
       <c r="BV90" s="9"/>
       <c r="BW90" s="9" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="BX90" s="9"/>
       <c r="BY90" s="9"/>
@@ -13627,6 +14414,9 @@
         <v>908</v>
       </c>
       <c r="AH91" s="9"/>
+      <c r="AI91" s="9" t="s">
+        <v>1833</v>
+      </c>
       <c r="AQ91" s="9" t="s">
         <v>909</v>
       </c>
@@ -13645,7 +14435,7 @@
       <c r="BU91" s="9"/>
       <c r="BV91" s="9"/>
       <c r="BW91" s="9" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="BX91" s="9"/>
       <c r="BY91" s="9"/>
@@ -13657,11 +14447,11 @@
       <c r="CE91" s="9"/>
     </row>
     <row r="92" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A92" s="21" t="s">
+      <c r="A92" s="20" t="s">
         <v>277</v>
       </c>
       <c r="B92" s="12"/>
-      <c r="C92" s="21" t="s">
+      <c r="C92" s="20" t="s">
         <v>278</v>
       </c>
       <c r="D92" s="12"/>
@@ -13680,6 +14470,9 @@
       <c r="Q92" s="12"/>
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
+      <c r="AI92" s="9" t="s">
+        <v>1834</v>
+      </c>
       <c r="AQ92" s="9" t="s">
         <v>910</v>
       </c>
@@ -13696,7 +14489,7 @@
       <c r="BU92" s="9"/>
       <c r="BV92" s="9"/>
       <c r="BW92" s="9" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="BX92" s="9"/>
       <c r="BY92" s="9"/>
@@ -13731,6 +14524,9 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="12"/>
       <c r="S93" s="12"/>
+      <c r="AI93" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="AQ93" s="9" t="s">
         <v>911</v>
       </c>
@@ -13747,7 +14543,7 @@
       <c r="BU93" s="9"/>
       <c r="BV93" s="9"/>
       <c r="BW93" s="9" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="BX93" s="9"/>
       <c r="BY93" s="9"/>
@@ -13759,11 +14555,11 @@
       <c r="CE93" s="9"/>
     </row>
     <row r="94" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="20" t="s">
         <v>281</v>
       </c>
       <c r="B94" s="12"/>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="20" t="s">
         <v>282</v>
       </c>
       <c r="D94" s="12"/>
@@ -13782,6 +14578,9 @@
       <c r="Q94" s="12"/>
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
+      <c r="AI94" s="9" t="s">
+        <v>1835</v>
+      </c>
       <c r="AQ94" s="9" t="s">
         <v>912</v>
       </c>
@@ -13798,7 +14597,7 @@
       <c r="BU94" s="9"/>
       <c r="BV94" s="9"/>
       <c r="BW94" s="9" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="BX94" s="9"/>
       <c r="BY94" s="9"/>
@@ -13833,6 +14632,9 @@
       <c r="Q95" s="12"/>
       <c r="R95" s="12"/>
       <c r="S95" s="12"/>
+      <c r="AI95" s="9" t="s">
+        <v>1418</v>
+      </c>
       <c r="AQ95" s="9" t="s">
         <v>913</v>
       </c>
@@ -13849,7 +14651,7 @@
       <c r="BU95" s="9"/>
       <c r="BV95" s="9"/>
       <c r="BW95" s="9" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="BX95" s="9"/>
       <c r="BY95" s="9"/>
@@ -13861,11 +14663,11 @@
       <c r="CE95" s="9"/>
     </row>
     <row r="96" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A96" s="21" t="s">
+      <c r="A96" s="20" t="s">
         <v>285</v>
       </c>
       <c r="B96" s="12"/>
-      <c r="C96" s="21" t="s">
+      <c r="C96" s="20" t="s">
         <v>286</v>
       </c>
       <c r="D96" s="12"/>
@@ -13884,6 +14686,9 @@
       <c r="Q96" s="12"/>
       <c r="R96" s="12"/>
       <c r="S96" s="12"/>
+      <c r="AI96" s="9" t="s">
+        <v>1836</v>
+      </c>
       <c r="AQ96" s="9" t="s">
         <v>914</v>
       </c>
@@ -13900,7 +14705,7 @@
       <c r="BU96" s="9"/>
       <c r="BV96" s="9"/>
       <c r="BW96" s="9" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="BX96" s="9"/>
       <c r="BY96" s="9"/>
@@ -13935,6 +14740,9 @@
       <c r="Q97" s="12"/>
       <c r="R97" s="12"/>
       <c r="S97" s="12"/>
+      <c r="AI97" s="9" t="s">
+        <v>1837</v>
+      </c>
       <c r="AQ97" s="9" t="s">
         <v>915</v>
       </c>
@@ -13951,7 +14759,7 @@
       <c r="BU97" s="9"/>
       <c r="BV97" s="9"/>
       <c r="BW97" s="9" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="BX97" s="9"/>
       <c r="BY97" s="9"/>
@@ -13963,11 +14771,11 @@
       <c r="CE97" s="9"/>
     </row>
     <row r="98" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A98" s="21" t="s">
+      <c r="A98" s="20" t="s">
         <v>289</v>
       </c>
       <c r="B98" s="12"/>
-      <c r="C98" s="21" t="s">
+      <c r="C98" s="20" t="s">
         <v>290</v>
       </c>
       <c r="D98" s="12"/>
@@ -13986,6 +14794,9 @@
       <c r="Q98" s="12"/>
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
+      <c r="AI98" s="9" t="s">
+        <v>1838</v>
+      </c>
       <c r="AQ98" s="9" t="s">
         <v>916</v>
       </c>
@@ -14002,7 +14813,7 @@
       <c r="BU98" s="9"/>
       <c r="BV98" s="9"/>
       <c r="BW98" s="9" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="BX98" s="9"/>
       <c r="BY98" s="9"/>
@@ -14037,6 +14848,9 @@
       <c r="Q99" s="12"/>
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
+      <c r="AI99" s="9" t="s">
+        <v>1839</v>
+      </c>
       <c r="AQ99" s="9" t="s">
         <v>917</v>
       </c>
@@ -14053,7 +14867,7 @@
       <c r="BU99" s="9"/>
       <c r="BV99" s="9"/>
       <c r="BW99" s="9" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="BX99" s="9"/>
       <c r="BY99" s="9"/>
@@ -14065,11 +14879,11 @@
       <c r="CE99" s="9"/>
     </row>
     <row r="100" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A100" s="21" t="s">
+      <c r="A100" s="20" t="s">
         <v>293</v>
       </c>
       <c r="B100" s="12"/>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="20" t="s">
         <v>294</v>
       </c>
       <c r="D100" s="12"/>
@@ -14088,6 +14902,9 @@
       <c r="Q100" s="12"/>
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
+      <c r="AI100" s="9" t="s">
+        <v>1840</v>
+      </c>
       <c r="AQ100" s="9" t="s">
         <v>918</v>
       </c>
@@ -14104,7 +14921,7 @@
       <c r="BU100" s="9"/>
       <c r="BV100" s="9"/>
       <c r="BW100" s="9" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="BX100" s="9"/>
       <c r="BY100" s="9"/>
@@ -14139,6 +14956,9 @@
       <c r="Q101" s="12"/>
       <c r="R101" s="12"/>
       <c r="S101" s="12"/>
+      <c r="AI101" s="9" t="s">
+        <v>1841</v>
+      </c>
       <c r="AQ101" s="9" t="s">
         <v>919</v>
       </c>
@@ -14155,7 +14975,7 @@
       <c r="BU101" s="9"/>
       <c r="BV101" s="9"/>
       <c r="BW101" s="9" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="BX101" s="9"/>
       <c r="BY101" s="9"/>
@@ -14167,11 +14987,11 @@
       <c r="CE101" s="9"/>
     </row>
     <row r="102" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="20" t="s">
         <v>297</v>
       </c>
       <c r="B102" s="12"/>
-      <c r="C102" s="21" t="s">
+      <c r="C102" s="20" t="s">
         <v>298</v>
       </c>
       <c r="D102" s="12"/>
@@ -14190,6 +15010,9 @@
       <c r="Q102" s="12"/>
       <c r="R102" s="12"/>
       <c r="S102" s="12"/>
+      <c r="AI102" s="9" t="s">
+        <v>1428</v>
+      </c>
       <c r="AQ102" s="9" t="s">
         <v>920</v>
       </c>
@@ -14206,7 +15029,7 @@
       <c r="BU102" s="9"/>
       <c r="BV102" s="9"/>
       <c r="BW102" s="9" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="BX102" s="9"/>
       <c r="BY102" s="9"/>
@@ -14241,6 +15064,9 @@
       <c r="Q103" s="12"/>
       <c r="R103" s="12"/>
       <c r="S103" s="12"/>
+      <c r="AI103" s="9" t="s">
+        <v>1842</v>
+      </c>
       <c r="AQ103" s="9" t="s">
         <v>921</v>
       </c>
@@ -14257,7 +15083,7 @@
       <c r="BU103" s="9"/>
       <c r="BV103" s="9"/>
       <c r="BW103" s="9" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="BX103" s="9"/>
       <c r="BY103" s="9"/>
@@ -14269,11 +15095,11 @@
       <c r="CE103" s="9"/>
     </row>
     <row r="104" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A104" s="21" t="s">
+      <c r="A104" s="20" t="s">
         <v>301</v>
       </c>
       <c r="B104" s="12"/>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="20" t="s">
         <v>302</v>
       </c>
       <c r="D104" s="12"/>
@@ -14292,6 +15118,9 @@
       <c r="Q104" s="12"/>
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
+      <c r="AI104" s="9" t="s">
+        <v>1843</v>
+      </c>
       <c r="AQ104" s="9" t="s">
         <v>922</v>
       </c>
@@ -14308,7 +15137,7 @@
       <c r="BU104" s="9"/>
       <c r="BV104" s="9"/>
       <c r="BW104" s="9" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="BX104" s="9"/>
       <c r="BY104" s="9"/>
@@ -14343,6 +15172,9 @@
       <c r="Q105" s="12"/>
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
+      <c r="AI105" s="9" t="s">
+        <v>1844</v>
+      </c>
       <c r="AQ105" s="9" t="s">
         <v>923</v>
       </c>
@@ -14359,7 +15191,7 @@
       <c r="BU105" s="9"/>
       <c r="BV105" s="9"/>
       <c r="BW105" s="9" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="BX105" s="9"/>
       <c r="BY105" s="9"/>
@@ -14371,11 +15203,11 @@
       <c r="CE105" s="9"/>
     </row>
     <row r="106" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="20" t="s">
         <v>305</v>
       </c>
       <c r="B106" s="12"/>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="20" t="s">
         <v>306</v>
       </c>
       <c r="D106" s="12"/>
@@ -14394,6 +15226,9 @@
       <c r="Q106" s="12"/>
       <c r="R106" s="12"/>
       <c r="S106" s="12"/>
+      <c r="AI106" s="9" t="s">
+        <v>1845</v>
+      </c>
       <c r="AQ106" s="9" t="s">
         <v>924</v>
       </c>
@@ -14410,7 +15245,7 @@
       <c r="BU106" s="9"/>
       <c r="BV106" s="9"/>
       <c r="BW106" s="9" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="BX106" s="9"/>
       <c r="BY106" s="9"/>
@@ -14445,6 +15280,9 @@
       <c r="Q107" s="12"/>
       <c r="R107" s="12"/>
       <c r="S107" s="12"/>
+      <c r="AI107" s="9" t="s">
+        <v>1846</v>
+      </c>
       <c r="AQ107" s="9" t="s">
         <v>925</v>
       </c>
@@ -14461,7 +15299,7 @@
       <c r="BU107" s="9"/>
       <c r="BV107" s="9"/>
       <c r="BW107" s="9" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="BX107" s="9"/>
       <c r="BY107" s="9"/>
@@ -14473,11 +15311,11 @@
       <c r="CE107" s="9"/>
     </row>
     <row r="108" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A108" s="21" t="s">
+      <c r="A108" s="20" t="s">
         <v>309</v>
       </c>
       <c r="B108" s="12"/>
-      <c r="C108" s="21" t="s">
+      <c r="C108" s="20" t="s">
         <v>310</v>
       </c>
       <c r="D108" s="12"/>
@@ -14496,6 +15334,9 @@
       <c r="Q108" s="12"/>
       <c r="R108" s="12"/>
       <c r="S108" s="12"/>
+      <c r="AI108" s="9" t="s">
+        <v>1847</v>
+      </c>
       <c r="AQ108" s="9" t="s">
         <v>926</v>
       </c>
@@ -14512,7 +15353,7 @@
       <c r="BU108" s="9"/>
       <c r="BV108" s="9"/>
       <c r="BW108" s="9" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="BX108" s="9"/>
       <c r="BY108" s="9"/>
@@ -14547,6 +15388,9 @@
       <c r="Q109" s="12"/>
       <c r="R109" s="12"/>
       <c r="S109" s="12"/>
+      <c r="AI109" s="9" t="s">
+        <v>1848</v>
+      </c>
       <c r="AQ109" s="9" t="s">
         <v>927</v>
       </c>
@@ -14563,7 +15407,7 @@
       <c r="BU109" s="9"/>
       <c r="BV109" s="9"/>
       <c r="BW109" s="9" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="BX109" s="9"/>
       <c r="BY109" s="9"/>
@@ -14575,11 +15419,11 @@
       <c r="CE109" s="9"/>
     </row>
     <row r="110" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="20" t="s">
         <v>313</v>
       </c>
       <c r="B110" s="12"/>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="20" t="s">
         <v>314</v>
       </c>
       <c r="D110" s="12"/>
@@ -14598,6 +15442,9 @@
       <c r="Q110" s="12"/>
       <c r="R110" s="12"/>
       <c r="S110" s="12"/>
+      <c r="AI110" s="9" t="s">
+        <v>1849</v>
+      </c>
       <c r="AQ110" s="9" t="s">
         <v>928</v>
       </c>
@@ -14614,7 +15461,7 @@
       <c r="BU110" s="9"/>
       <c r="BV110" s="9"/>
       <c r="BW110" s="9" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="BX110" s="9"/>
       <c r="BY110" s="9"/>
@@ -14649,6 +15496,9 @@
       <c r="Q111" s="12"/>
       <c r="R111" s="12"/>
       <c r="S111" s="12"/>
+      <c r="AI111" s="9" t="s">
+        <v>1850</v>
+      </c>
       <c r="AQ111" s="9" t="s">
         <v>929</v>
       </c>
@@ -14665,7 +15515,7 @@
       <c r="BU111" s="9"/>
       <c r="BV111" s="9"/>
       <c r="BW111" s="9" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="BX111" s="9"/>
       <c r="BY111" s="9"/>
@@ -14677,11 +15527,11 @@
       <c r="CE111" s="9"/>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="20" t="s">
         <v>317</v>
       </c>
       <c r="B112" s="12"/>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="20" t="s">
         <v>318</v>
       </c>
       <c r="D112" s="12"/>
@@ -14700,6 +15550,9 @@
       <c r="Q112" s="12"/>
       <c r="R112" s="12"/>
       <c r="S112" s="12"/>
+      <c r="AI112" s="9" t="s">
+        <v>1851</v>
+      </c>
       <c r="AQ112" s="9" t="s">
         <v>930</v>
       </c>
@@ -14716,7 +15569,7 @@
       <c r="BU112" s="9"/>
       <c r="BV112" s="9"/>
       <c r="BW112" s="9" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="BX112" s="9"/>
       <c r="BY112" s="9"/>
@@ -14751,6 +15604,9 @@
       <c r="Q113" s="12"/>
       <c r="R113" s="12"/>
       <c r="S113" s="12"/>
+      <c r="AI113" s="9" t="s">
+        <v>1852</v>
+      </c>
       <c r="AQ113" s="9" t="s">
         <v>931</v>
       </c>
@@ -14767,7 +15623,7 @@
       <c r="BU113" s="9"/>
       <c r="BV113" s="9"/>
       <c r="BW113" s="9" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="BX113" s="9"/>
       <c r="BY113" s="9"/>
@@ -14779,11 +15635,11 @@
       <c r="CE113" s="9"/>
     </row>
     <row r="114" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="20" t="s">
         <v>321</v>
       </c>
       <c r="B114" s="12"/>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="20" t="s">
         <v>322</v>
       </c>
       <c r="D114" s="12"/>
@@ -14802,6 +15658,9 @@
       <c r="Q114" s="12"/>
       <c r="R114" s="12"/>
       <c r="S114" s="12"/>
+      <c r="AI114" s="9" t="s">
+        <v>1853</v>
+      </c>
       <c r="AQ114" s="9" t="s">
         <v>932</v>
       </c>
@@ -14818,7 +15677,7 @@
       <c r="BU114" s="9"/>
       <c r="BV114" s="9"/>
       <c r="BW114" s="9" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="BX114" s="9"/>
       <c r="BY114" s="9"/>
@@ -14853,6 +15712,9 @@
       <c r="Q115" s="12"/>
       <c r="R115" s="12"/>
       <c r="S115" s="12"/>
+      <c r="AI115" s="9" t="s">
+        <v>1854</v>
+      </c>
       <c r="AQ115" s="9" t="s">
         <v>933</v>
       </c>
@@ -14869,7 +15731,7 @@
       <c r="BU115" s="9"/>
       <c r="BV115" s="9"/>
       <c r="BW115" s="9" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="BX115" s="9"/>
       <c r="BY115" s="9"/>
@@ -14881,11 +15743,11 @@
       <c r="CE115" s="9"/>
     </row>
     <row r="116" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="20" t="s">
         <v>325</v>
       </c>
       <c r="B116" s="12"/>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="20" t="s">
         <v>326</v>
       </c>
       <c r="D116" s="12"/>
@@ -14904,6 +15766,9 @@
       <c r="Q116" s="12"/>
       <c r="R116" s="12"/>
       <c r="S116" s="12"/>
+      <c r="AI116" s="9" t="s">
+        <v>1855</v>
+      </c>
       <c r="AQ116" s="9" t="s">
         <v>934</v>
       </c>
@@ -14920,7 +15785,7 @@
       <c r="BU116" s="9"/>
       <c r="BV116" s="9"/>
       <c r="BW116" s="9" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="BX116" s="9"/>
       <c r="BY116" s="9"/>
@@ -14955,6 +15820,9 @@
       <c r="Q117" s="12"/>
       <c r="R117" s="12"/>
       <c r="S117" s="12"/>
+      <c r="AI117" s="9" t="s">
+        <v>1856</v>
+      </c>
       <c r="AQ117" s="9" t="s">
         <v>935</v>
       </c>
@@ -14971,7 +15839,7 @@
       <c r="BU117" s="9"/>
       <c r="BV117" s="9"/>
       <c r="BW117" s="9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="BX117" s="9"/>
       <c r="BY117" s="9"/>
@@ -14983,11 +15851,11 @@
       <c r="CE117" s="9"/>
     </row>
     <row r="118" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="20" t="s">
         <v>329</v>
       </c>
       <c r="B118" s="12"/>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D118" s="12"/>
@@ -15006,6 +15874,9 @@
       <c r="Q118" s="12"/>
       <c r="R118" s="12"/>
       <c r="S118" s="12"/>
+      <c r="AI118" s="29" t="s">
+        <v>1429</v>
+      </c>
       <c r="AQ118" s="9" t="s">
         <v>936</v>
       </c>
@@ -15022,7 +15893,7 @@
       <c r="BU118" s="9"/>
       <c r="BV118" s="9"/>
       <c r="BW118" s="9" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="BX118" s="9"/>
       <c r="BY118" s="9"/>
@@ -15073,7 +15944,7 @@
       <c r="BU119" s="9"/>
       <c r="BV119" s="9"/>
       <c r="BW119" s="9" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="BX119" s="9"/>
       <c r="BY119" s="9"/>
@@ -15085,11 +15956,11 @@
       <c r="CE119" s="9"/>
     </row>
     <row r="120" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B120" s="12"/>
-      <c r="C120" s="21" t="s">
+      <c r="C120" s="20" t="s">
         <v>334</v>
       </c>
       <c r="D120" s="12"/>
@@ -15124,7 +15995,7 @@
       <c r="BU120" s="9"/>
       <c r="BV120" s="9"/>
       <c r="BW120" s="9" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="BX120" s="9"/>
       <c r="BY120" s="9"/>
@@ -15175,7 +16046,7 @@
       <c r="BU121" s="9"/>
       <c r="BV121" s="9"/>
       <c r="BW121" s="9" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="BX121" s="9"/>
       <c r="BY121" s="9"/>
@@ -15187,11 +16058,11 @@
       <c r="CE121" s="9"/>
     </row>
     <row r="122" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="20" t="s">
         <v>337</v>
       </c>
       <c r="B122" s="12"/>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="20" t="s">
         <v>338</v>
       </c>
       <c r="D122" s="12"/>
@@ -15226,7 +16097,7 @@
       <c r="BU122" s="9"/>
       <c r="BV122" s="9"/>
       <c r="BW122" s="9" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="BX122" s="9"/>
       <c r="BY122" s="9"/>
@@ -15277,7 +16148,7 @@
       <c r="BU123" s="9"/>
       <c r="BV123" s="9"/>
       <c r="BW123" s="9" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="BX123" s="9"/>
       <c r="BY123" s="9"/>
@@ -15289,11 +16160,11 @@
       <c r="CE123" s="9"/>
     </row>
     <row r="124" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="20" t="s">
         <v>341</v>
       </c>
       <c r="B124" s="12"/>
-      <c r="C124" s="21" t="s">
+      <c r="C124" s="20" t="s">
         <v>342</v>
       </c>
       <c r="D124" s="12"/>
@@ -15328,7 +16199,7 @@
       <c r="BU124" s="9"/>
       <c r="BV124" s="9"/>
       <c r="BW124" s="9" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="BX124" s="9"/>
       <c r="BY124" s="9"/>
@@ -15391,11 +16262,11 @@
       <c r="CE125" s="9"/>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="20" t="s">
         <v>345</v>
       </c>
       <c r="B126" s="12"/>
-      <c r="C126" s="21" t="s">
+      <c r="C126" s="20" t="s">
         <v>346</v>
       </c>
       <c r="D126" s="12"/>
@@ -15430,7 +16301,7 @@
       <c r="BU126" s="9"/>
       <c r="BV126" s="9"/>
       <c r="BW126" s="9" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="BX126" s="9"/>
       <c r="BY126" s="9"/>
@@ -15481,7 +16352,7 @@
       <c r="BU127" s="9"/>
       <c r="BV127" s="9"/>
       <c r="BW127" s="9" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="BX127" s="9"/>
       <c r="BY127" s="9"/>
@@ -15493,11 +16364,11 @@
       <c r="CE127" s="9"/>
     </row>
     <row r="128" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="20" t="s">
         <v>349</v>
       </c>
       <c r="B128" s="12"/>
-      <c r="C128" s="21" t="s">
+      <c r="C128" s="20" t="s">
         <v>350</v>
       </c>
       <c r="D128" s="12"/>
@@ -15532,7 +16403,7 @@
       <c r="BU128" s="9"/>
       <c r="BV128" s="9"/>
       <c r="BW128" s="9" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="BX128" s="9"/>
       <c r="BY128" s="9"/>
@@ -15583,7 +16454,7 @@
       <c r="BU129" s="9"/>
       <c r="BV129" s="9"/>
       <c r="BW129" s="9" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="BX129" s="9"/>
       <c r="BY129" s="9"/>
@@ -15595,11 +16466,11 @@
       <c r="CE129" s="9"/>
     </row>
     <row r="130" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="20" t="s">
         <v>353</v>
       </c>
       <c r="B130" s="12"/>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="20" t="s">
         <v>354</v>
       </c>
       <c r="D130" s="12"/>
@@ -15634,7 +16505,7 @@
       <c r="BU130" s="9"/>
       <c r="BV130" s="9"/>
       <c r="BW130" s="9" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="BX130" s="9"/>
       <c r="BY130" s="9"/>
@@ -15685,7 +16556,7 @@
       <c r="BU131" s="9"/>
       <c r="BV131" s="9"/>
       <c r="BW131" s="9" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="BX131" s="9"/>
       <c r="BY131" s="9"/>
@@ -15697,11 +16568,11 @@
       <c r="CE131" s="9"/>
     </row>
     <row r="132" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="20" t="s">
         <v>357</v>
       </c>
       <c r="B132" s="12"/>
-      <c r="C132" s="21" t="s">
+      <c r="C132" s="20" t="s">
         <v>358</v>
       </c>
       <c r="D132" s="12"/>
@@ -15736,7 +16607,7 @@
       <c r="BU132" s="9"/>
       <c r="BV132" s="9"/>
       <c r="BW132" s="9" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="BX132" s="9"/>
       <c r="BY132" s="9"/>
@@ -15787,7 +16658,7 @@
       <c r="BU133" s="9"/>
       <c r="BV133" s="9"/>
       <c r="BW133" s="9" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="BX133" s="9"/>
       <c r="BY133" s="9"/>
@@ -15799,11 +16670,11 @@
       <c r="CE133" s="9"/>
     </row>
     <row r="134" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="20" t="s">
         <v>361</v>
       </c>
       <c r="B134" s="12"/>
-      <c r="C134" s="21" t="s">
+      <c r="C134" s="20" t="s">
         <v>362</v>
       </c>
       <c r="D134" s="12"/>
@@ -15838,7 +16709,7 @@
       <c r="BU134" s="9"/>
       <c r="BV134" s="9"/>
       <c r="BW134" s="9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="BX134" s="9"/>
       <c r="BY134" s="9"/>
@@ -15901,11 +16772,11 @@
       <c r="CE135" s="9"/>
     </row>
     <row r="136" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="20" t="s">
         <v>365</v>
       </c>
       <c r="B136" s="12"/>
-      <c r="C136" s="21" t="s">
+      <c r="C136" s="20" t="s">
         <v>366</v>
       </c>
       <c r="D136" s="12"/>
@@ -15940,7 +16811,7 @@
       <c r="BU136" s="9"/>
       <c r="BV136" s="9"/>
       <c r="BW136" s="9" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="BX136" s="9"/>
       <c r="BY136" s="9"/>
@@ -15991,7 +16862,7 @@
       <c r="BU137" s="9"/>
       <c r="BV137" s="9"/>
       <c r="BW137" s="9" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="BX137" s="9"/>
       <c r="BY137" s="9"/>
@@ -16003,11 +16874,11 @@
       <c r="CE137" s="9"/>
     </row>
     <row r="138" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A138" s="21" t="s">
+      <c r="A138" s="20" t="s">
         <v>369</v>
       </c>
       <c r="B138" s="12"/>
-      <c r="C138" s="21" t="s">
+      <c r="C138" s="20" t="s">
         <v>370</v>
       </c>
       <c r="D138" s="12"/>
@@ -16042,7 +16913,7 @@
       <c r="BU138" s="9"/>
       <c r="BV138" s="9"/>
       <c r="BW138" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="BX138" s="9"/>
       <c r="BY138" s="9"/>
@@ -16093,7 +16964,7 @@
       <c r="BU139" s="9"/>
       <c r="BV139" s="9"/>
       <c r="BW139" s="9" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="BX139" s="9"/>
       <c r="BY139" s="9"/>
@@ -16105,11 +16976,11 @@
       <c r="CE139" s="9"/>
     </row>
     <row r="140" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A140" s="21" t="s">
+      <c r="A140" s="20" t="s">
         <v>373</v>
       </c>
       <c r="B140" s="12"/>
-      <c r="C140" s="21" t="s">
+      <c r="C140" s="20" t="s">
         <v>374</v>
       </c>
       <c r="D140" s="12"/>
@@ -16144,7 +17015,7 @@
       <c r="BU140" s="9"/>
       <c r="BV140" s="9"/>
       <c r="BW140" s="9" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="BX140" s="9"/>
       <c r="BY140" s="9"/>
@@ -16195,7 +17066,7 @@
       <c r="BU141" s="9"/>
       <c r="BV141" s="9"/>
       <c r="BW141" s="9" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BX141" s="9"/>
       <c r="BY141" s="9"/>
@@ -16207,11 +17078,11 @@
       <c r="CE141" s="9"/>
     </row>
     <row r="142" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="20" t="s">
         <v>377</v>
       </c>
       <c r="B142" s="12"/>
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="20" t="s">
         <v>378</v>
       </c>
       <c r="D142" s="12"/>
@@ -16246,7 +17117,7 @@
       <c r="BU142" s="9"/>
       <c r="BV142" s="9"/>
       <c r="BW142" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="BX142" s="9"/>
       <c r="BY142" s="9"/>
@@ -16297,7 +17168,7 @@
       <c r="BU143" s="9"/>
       <c r="BV143" s="9"/>
       <c r="BW143" s="9" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="BX143" s="9"/>
       <c r="BY143" s="9"/>
@@ -16309,11 +17180,11 @@
       <c r="CE143" s="9"/>
     </row>
     <row r="144" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="20" t="s">
         <v>381</v>
       </c>
       <c r="B144" s="12"/>
-      <c r="C144" s="21" t="s">
+      <c r="C144" s="20" t="s">
         <v>382</v>
       </c>
       <c r="D144" s="12"/>
@@ -16348,7 +17219,7 @@
       <c r="BU144" s="9"/>
       <c r="BV144" s="9"/>
       <c r="BW144" s="9" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="BX144" s="9"/>
       <c r="BY144" s="9"/>
@@ -16399,7 +17270,7 @@
       <c r="BU145" s="9"/>
       <c r="BV145" s="9"/>
       <c r="BW145" s="9" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="BX145" s="9"/>
       <c r="BY145" s="9"/>
@@ -16411,11 +17282,11 @@
       <c r="CE145" s="9"/>
     </row>
     <row r="146" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="20" t="s">
         <v>385</v>
       </c>
       <c r="B146" s="12"/>
-      <c r="C146" s="21" t="s">
+      <c r="C146" s="20" t="s">
         <v>386</v>
       </c>
       <c r="D146" s="12"/>
@@ -16501,7 +17372,7 @@
       <c r="BU147" s="9"/>
       <c r="BV147" s="9"/>
       <c r="BW147" s="9" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="BX147" s="9"/>
       <c r="BY147" s="9"/>
@@ -16513,11 +17384,11 @@
       <c r="CE147" s="9"/>
     </row>
     <row r="148" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A148" s="21" t="s">
+      <c r="A148" s="20" t="s">
         <v>389</v>
       </c>
       <c r="B148" s="12"/>
-      <c r="C148" s="21" t="s">
+      <c r="C148" s="20" t="s">
         <v>390</v>
       </c>
       <c r="D148" s="12"/>
@@ -16552,7 +17423,7 @@
       <c r="BU148" s="9"/>
       <c r="BV148" s="9"/>
       <c r="BW148" s="9" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="BX148" s="9"/>
       <c r="BY148" s="9"/>
@@ -16603,7 +17474,7 @@
       <c r="BU149" s="9"/>
       <c r="BV149" s="9"/>
       <c r="BW149" s="9" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="BX149" s="9"/>
       <c r="BY149" s="9"/>
@@ -16615,11 +17486,11 @@
       <c r="CE149" s="9"/>
     </row>
     <row r="150" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="20" t="s">
         <v>393</v>
       </c>
       <c r="B150" s="12"/>
-      <c r="C150" s="21" t="s">
+      <c r="C150" s="20" t="s">
         <v>394</v>
       </c>
       <c r="D150" s="12"/>
@@ -16654,7 +17525,7 @@
       <c r="BU150" s="9"/>
       <c r="BV150" s="9"/>
       <c r="BW150" s="9" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="BX150" s="9"/>
       <c r="BY150" s="9"/>
@@ -16705,7 +17576,7 @@
       <c r="BU151" s="9"/>
       <c r="BV151" s="9"/>
       <c r="BW151" s="9" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="BX151" s="9"/>
       <c r="BY151" s="9"/>
@@ -16717,11 +17588,11 @@
       <c r="CE151" s="9"/>
     </row>
     <row r="152" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="20" t="s">
         <v>397</v>
       </c>
       <c r="B152" s="12"/>
-      <c r="C152" s="21" t="s">
+      <c r="C152" s="20" t="s">
         <v>398</v>
       </c>
       <c r="D152" s="12"/>
@@ -16756,7 +17627,7 @@
       <c r="BU152" s="9"/>
       <c r="BV152" s="9"/>
       <c r="BW152" s="9" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="BX152" s="9"/>
       <c r="BY152" s="9"/>
@@ -16807,7 +17678,7 @@
       <c r="BU153" s="9"/>
       <c r="BV153" s="9"/>
       <c r="BW153" s="9" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="BX153" s="9"/>
       <c r="BY153" s="9"/>
@@ -16819,11 +17690,11 @@
       <c r="CE153" s="9"/>
     </row>
     <row r="154" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="20" t="s">
         <v>401</v>
       </c>
       <c r="B154" s="12"/>
-      <c r="C154" s="21" t="s">
+      <c r="C154" s="20" t="s">
         <v>402</v>
       </c>
       <c r="D154" s="12"/>
@@ -16858,7 +17729,7 @@
       <c r="BU154" s="9"/>
       <c r="BV154" s="9"/>
       <c r="BW154" s="9" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="BX154" s="9"/>
       <c r="BY154" s="9"/>
@@ -16909,7 +17780,7 @@
       <c r="BU155" s="9"/>
       <c r="BV155" s="9"/>
       <c r="BW155" s="9" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="BX155" s="9"/>
       <c r="BY155" s="9"/>
@@ -16921,11 +17792,11 @@
       <c r="CE155" s="9"/>
     </row>
     <row r="156" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="20" t="s">
         <v>405</v>
       </c>
       <c r="B156" s="12"/>
-      <c r="C156" s="21" t="s">
+      <c r="C156" s="20" t="s">
         <v>406</v>
       </c>
       <c r="D156" s="12"/>
@@ -16960,7 +17831,7 @@
       <c r="BU156" s="9"/>
       <c r="BV156" s="9"/>
       <c r="BW156" s="9" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="BX156" s="9"/>
       <c r="BY156" s="9"/>
@@ -17011,7 +17882,7 @@
       <c r="BU157" s="9"/>
       <c r="BV157" s="9"/>
       <c r="BW157" s="9" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="BX157" s="9"/>
       <c r="BY157" s="9"/>
@@ -17023,11 +17894,11 @@
       <c r="CE157" s="9"/>
     </row>
     <row r="158" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A158" s="21" t="s">
+      <c r="A158" s="20" t="s">
         <v>409</v>
       </c>
       <c r="B158" s="12"/>
-      <c r="C158" s="21" t="s">
+      <c r="C158" s="20" t="s">
         <v>410</v>
       </c>
       <c r="D158" s="12"/>
@@ -17062,7 +17933,7 @@
       <c r="BU158" s="9"/>
       <c r="BV158" s="9"/>
       <c r="BW158" s="9" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="BX158" s="9"/>
       <c r="BY158" s="9"/>
@@ -17113,7 +17984,7 @@
       <c r="BU159" s="9"/>
       <c r="BV159" s="9"/>
       <c r="BW159" s="9" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="BX159" s="9"/>
       <c r="BY159" s="9"/>
@@ -17125,11 +17996,11 @@
       <c r="CE159" s="9"/>
     </row>
     <row r="160" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A160" s="21" t="s">
+      <c r="A160" s="20" t="s">
         <v>413</v>
       </c>
       <c r="B160" s="12"/>
-      <c r="C160" s="21" t="s">
+      <c r="C160" s="20" t="s">
         <v>414</v>
       </c>
       <c r="D160" s="12"/>
@@ -17164,7 +18035,7 @@
       <c r="BU160" s="9"/>
       <c r="BV160" s="9"/>
       <c r="BW160" s="9" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="BX160" s="9"/>
       <c r="BY160" s="9"/>
@@ -17215,7 +18086,7 @@
       <c r="BU161" s="9"/>
       <c r="BV161" s="9"/>
       <c r="BW161" s="9" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="BX161" s="9"/>
       <c r="BY161" s="9"/>
@@ -17227,11 +18098,11 @@
       <c r="CE161" s="9"/>
     </row>
     <row r="162" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A162" s="21" t="s">
+      <c r="A162" s="20" t="s">
         <v>417</v>
       </c>
       <c r="B162" s="12"/>
-      <c r="C162" s="21" t="s">
+      <c r="C162" s="20" t="s">
         <v>418</v>
       </c>
       <c r="D162" s="12"/>
@@ -17266,7 +18137,7 @@
       <c r="BU162" s="9"/>
       <c r="BV162" s="9"/>
       <c r="BW162" s="9" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="BX162" s="9"/>
       <c r="BY162" s="9"/>
@@ -17317,7 +18188,7 @@
       <c r="BU163" s="9"/>
       <c r="BV163" s="9"/>
       <c r="BW163" s="9" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="BX163" s="9"/>
       <c r="BY163" s="9"/>
@@ -17329,11 +18200,11 @@
       <c r="CE163" s="9"/>
     </row>
     <row r="164" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="20" t="s">
         <v>421</v>
       </c>
       <c r="B164" s="12"/>
-      <c r="C164" s="21" t="s">
+      <c r="C164" s="20" t="s">
         <v>422</v>
       </c>
       <c r="D164" s="12"/>
@@ -17368,7 +18239,7 @@
       <c r="BU164" s="9"/>
       <c r="BV164" s="9"/>
       <c r="BW164" s="9" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="BX164" s="9"/>
       <c r="BY164" s="9"/>
@@ -17419,7 +18290,7 @@
       <c r="BU165" s="9"/>
       <c r="BV165" s="9"/>
       <c r="BW165" s="9" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="BX165" s="9"/>
       <c r="BY165" s="9"/>
@@ -17431,11 +18302,11 @@
       <c r="CE165" s="9"/>
     </row>
     <row r="166" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="20" t="s">
         <v>425</v>
       </c>
       <c r="B166" s="12"/>
-      <c r="C166" s="21" t="s">
+      <c r="C166" s="20" t="s">
         <v>426</v>
       </c>
       <c r="D166" s="12"/>
@@ -17470,7 +18341,7 @@
       <c r="BU166" s="9"/>
       <c r="BV166" s="9"/>
       <c r="BW166" s="9" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="BX166" s="9"/>
       <c r="BY166" s="9"/>
@@ -17521,7 +18392,7 @@
       <c r="BU167" s="9"/>
       <c r="BV167" s="9"/>
       <c r="BW167" s="9" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="BX167" s="9"/>
       <c r="BY167" s="9"/>
@@ -17533,11 +18404,11 @@
       <c r="CE167" s="9"/>
     </row>
     <row r="168" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A168" s="21" t="s">
+      <c r="A168" s="20" t="s">
         <v>429</v>
       </c>
       <c r="B168" s="12"/>
-      <c r="C168" s="21" t="s">
+      <c r="C168" s="20" t="s">
         <v>430</v>
       </c>
       <c r="D168" s="12"/>
@@ -17572,7 +18443,7 @@
       <c r="BU168" s="9"/>
       <c r="BV168" s="9"/>
       <c r="BW168" s="9" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="BX168" s="9"/>
       <c r="BY168" s="9"/>
@@ -17623,7 +18494,7 @@
       <c r="BU169" s="9"/>
       <c r="BV169" s="9"/>
       <c r="BW169" s="9" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="BX169" s="9"/>
       <c r="BY169" s="9"/>
@@ -17635,11 +18506,11 @@
       <c r="CE169" s="9"/>
     </row>
     <row r="170" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A170" s="21" t="s">
+      <c r="A170" s="20" t="s">
         <v>433</v>
       </c>
       <c r="B170" s="12"/>
-      <c r="C170" s="21" t="s">
+      <c r="C170" s="20" t="s">
         <v>434</v>
       </c>
       <c r="D170" s="12"/>
@@ -17674,7 +18545,7 @@
       <c r="BU170" s="9"/>
       <c r="BV170" s="9"/>
       <c r="BW170" s="9" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="BX170" s="9"/>
       <c r="BY170" s="9"/>
@@ -17725,7 +18596,7 @@
       <c r="BU171" s="9"/>
       <c r="BV171" s="9"/>
       <c r="BW171" s="9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="BX171" s="9"/>
       <c r="BY171" s="9"/>
@@ -17737,11 +18608,11 @@
       <c r="CE171" s="9"/>
     </row>
     <row r="172" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A172" s="21" t="s">
+      <c r="A172" s="20" t="s">
         <v>437</v>
       </c>
       <c r="B172" s="12"/>
-      <c r="C172" s="21" t="s">
+      <c r="C172" s="20" t="s">
         <v>438</v>
       </c>
       <c r="D172" s="12"/>
@@ -17793,11 +18664,11 @@
       </c>
     </row>
     <row r="174" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="20" t="s">
         <v>441</v>
       </c>
       <c r="B174" s="12"/>
-      <c r="C174" s="21" t="s">
+      <c r="C174" s="20" t="s">
         <v>442</v>
       </c>
       <c r="D174" s="12"/>
@@ -17849,11 +18720,11 @@
       </c>
     </row>
     <row r="176" spans="1:83" x14ac:dyDescent="0.35">
-      <c r="A176" s="21" t="s">
+      <c r="A176" s="20" t="s">
         <v>445</v>
       </c>
       <c r="B176" s="12"/>
-      <c r="C176" s="21" t="s">
+      <c r="C176" s="20" t="s">
         <v>446</v>
       </c>
       <c r="D176" s="12"/>
@@ -17905,11 +18776,11 @@
       </c>
     </row>
     <row r="178" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A178" s="21" t="s">
+      <c r="A178" s="20" t="s">
         <v>449</v>
       </c>
       <c r="B178" s="12"/>
-      <c r="C178" s="21" t="s">
+      <c r="C178" s="20" t="s">
         <v>450</v>
       </c>
       <c r="D178" s="12"/>
@@ -17961,11 +18832,11 @@
       </c>
     </row>
     <row r="180" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A180" s="21" t="s">
+      <c r="A180" s="20" t="s">
         <v>453</v>
       </c>
       <c r="B180" s="12"/>
-      <c r="C180" s="21" t="s">
+      <c r="C180" s="20" t="s">
         <v>454</v>
       </c>
       <c r="D180" s="12"/>
@@ -18017,11 +18888,11 @@
       </c>
     </row>
     <row r="182" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A182" s="21" t="s">
+      <c r="A182" s="20" t="s">
         <v>457</v>
       </c>
       <c r="B182" s="12"/>
-      <c r="C182" s="21" t="s">
+      <c r="C182" s="20" t="s">
         <v>458</v>
       </c>
       <c r="D182" s="12"/>
@@ -18073,11 +18944,11 @@
       </c>
     </row>
     <row r="184" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A184" s="21" t="s">
+      <c r="A184" s="20" t="s">
         <v>461</v>
       </c>
       <c r="B184" s="12"/>
-      <c r="C184" s="21" t="s">
+      <c r="C184" s="20" t="s">
         <v>462</v>
       </c>
       <c r="D184" s="12"/>
@@ -18129,11 +19000,11 @@
       </c>
     </row>
     <row r="186" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A186" s="21" t="s">
+      <c r="A186" s="20" t="s">
         <v>465</v>
       </c>
       <c r="B186" s="12"/>
-      <c r="C186" s="21" t="s">
+      <c r="C186" s="20" t="s">
         <v>466</v>
       </c>
       <c r="D186" s="12"/>
@@ -18185,11 +19056,11 @@
       </c>
     </row>
     <row r="188" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A188" s="21" t="s">
+      <c r="A188" s="20" t="s">
         <v>469</v>
       </c>
       <c r="B188" s="12"/>
-      <c r="C188" s="21" t="s">
+      <c r="C188" s="20" t="s">
         <v>470</v>
       </c>
       <c r="D188" s="12"/>
@@ -18241,11 +19112,11 @@
       </c>
     </row>
     <row r="190" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A190" s="21" t="s">
+      <c r="A190" s="20" t="s">
         <v>473</v>
       </c>
       <c r="B190" s="12"/>
-      <c r="C190" s="21" t="s">
+      <c r="C190" s="20" t="s">
         <v>474</v>
       </c>
       <c r="D190" s="12"/>
@@ -18297,11 +19168,11 @@
       </c>
     </row>
     <row r="192" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A192" s="21" t="s">
+      <c r="A192" s="20" t="s">
         <v>477</v>
       </c>
       <c r="B192" s="12"/>
-      <c r="C192" s="21" t="s">
+      <c r="C192" s="20" t="s">
         <v>478</v>
       </c>
       <c r="D192" s="12"/>
@@ -18353,11 +19224,11 @@
       </c>
     </row>
     <row r="194" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A194" s="21" t="s">
+      <c r="A194" s="20" t="s">
         <v>481</v>
       </c>
       <c r="B194" s="12"/>
-      <c r="C194" s="21" t="s">
+      <c r="C194" s="20" t="s">
         <v>482</v>
       </c>
       <c r="D194" s="12"/>
@@ -18409,11 +19280,11 @@
       </c>
     </row>
     <row r="196" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A196" s="21" t="s">
+      <c r="A196" s="20" t="s">
         <v>485</v>
       </c>
       <c r="B196" s="12"/>
-      <c r="C196" s="21" t="s">
+      <c r="C196" s="20" t="s">
         <v>486</v>
       </c>
       <c r="D196" s="12"/>
@@ -18465,11 +19336,11 @@
       </c>
     </row>
     <row r="198" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A198" s="21" t="s">
+      <c r="A198" s="20" t="s">
         <v>489</v>
       </c>
       <c r="B198" s="12"/>
-      <c r="C198" s="21" t="s">
+      <c r="C198" s="20" t="s">
         <v>490</v>
       </c>
       <c r="D198" s="12"/>
@@ -18521,11 +19392,11 @@
       </c>
     </row>
     <row r="200" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A200" s="21" t="s">
+      <c r="A200" s="20" t="s">
         <v>493</v>
       </c>
       <c r="B200" s="12"/>
-      <c r="C200" s="21" t="s">
+      <c r="C200" s="20" t="s">
         <v>494</v>
       </c>
       <c r="D200" s="12"/>
@@ -18577,11 +19448,11 @@
       </c>
     </row>
     <row r="202" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A202" s="21" t="s">
+      <c r="A202" s="20" t="s">
         <v>497</v>
       </c>
       <c r="B202" s="12"/>
-      <c r="C202" s="21" t="s">
+      <c r="C202" s="20" t="s">
         <v>498</v>
       </c>
       <c r="D202" s="12"/>
@@ -18633,11 +19504,11 @@
       </c>
     </row>
     <row r="204" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A204" s="21" t="s">
+      <c r="A204" s="20" t="s">
         <v>501</v>
       </c>
       <c r="B204" s="12"/>
-      <c r="C204" s="21" t="s">
+      <c r="C204" s="20" t="s">
         <v>502</v>
       </c>
       <c r="D204" s="12"/>
@@ -18689,11 +19560,11 @@
       </c>
     </row>
     <row r="206" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A206" s="21" t="s">
+      <c r="A206" s="20" t="s">
         <v>505</v>
       </c>
       <c r="B206" s="12"/>
-      <c r="C206" s="21" t="s">
+      <c r="C206" s="20" t="s">
         <v>506</v>
       </c>
       <c r="D206" s="12"/>
@@ -18745,11 +19616,11 @@
       </c>
     </row>
     <row r="208" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A208" s="21" t="s">
+      <c r="A208" s="20" t="s">
         <v>509</v>
       </c>
       <c r="B208" s="12"/>
-      <c r="C208" s="21" t="s">
+      <c r="C208" s="20" t="s">
         <v>510</v>
       </c>
       <c r="D208" s="12"/>
@@ -18801,11 +19672,11 @@
       </c>
     </row>
     <row r="210" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A210" s="21" t="s">
+      <c r="A210" s="20" t="s">
         <v>513</v>
       </c>
       <c r="B210" s="12"/>
-      <c r="C210" s="21" t="s">
+      <c r="C210" s="20" t="s">
         <v>514</v>
       </c>
       <c r="D210" s="12"/>
@@ -18857,11 +19728,11 @@
       </c>
     </row>
     <row r="212" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A212" s="21" t="s">
+      <c r="A212" s="20" t="s">
         <v>517</v>
       </c>
       <c r="B212" s="12"/>
-      <c r="C212" s="21" t="s">
+      <c r="C212" s="20" t="s">
         <v>518</v>
       </c>
       <c r="D212" s="12"/>
@@ -18913,11 +19784,11 @@
       </c>
     </row>
     <row r="214" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A214" s="21" t="s">
+      <c r="A214" s="20" t="s">
         <v>521</v>
       </c>
       <c r="B214" s="12"/>
-      <c r="C214" s="21" t="s">
+      <c r="C214" s="20" t="s">
         <v>522</v>
       </c>
       <c r="D214" s="12"/>
@@ -18969,11 +19840,11 @@
       </c>
     </row>
     <row r="216" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A216" s="21" t="s">
+      <c r="A216" s="20" t="s">
         <v>525</v>
       </c>
       <c r="B216" s="12"/>
-      <c r="C216" s="21" t="s">
+      <c r="C216" s="20" t="s">
         <v>526</v>
       </c>
       <c r="D216" s="12"/>
@@ -19025,11 +19896,11 @@
       </c>
     </row>
     <row r="218" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A218" s="21" t="s">
+      <c r="A218" s="20" t="s">
         <v>529</v>
       </c>
       <c r="B218" s="12"/>
-      <c r="C218" s="21" t="s">
+      <c r="C218" s="20" t="s">
         <v>530</v>
       </c>
       <c r="D218" s="12"/>
@@ -19081,11 +19952,11 @@
       </c>
     </row>
     <row r="220" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A220" s="21" t="s">
+      <c r="A220" s="20" t="s">
         <v>533</v>
       </c>
       <c r="B220" s="12"/>
-      <c r="C220" s="21" t="s">
+      <c r="C220" s="20" t="s">
         <v>534</v>
       </c>
       <c r="D220" s="12"/>
@@ -19137,11 +20008,11 @@
       </c>
     </row>
     <row r="222" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A222" s="21" t="s">
+      <c r="A222" s="20" t="s">
         <v>537</v>
       </c>
       <c r="B222" s="12"/>
-      <c r="C222" s="21" t="s">
+      <c r="C222" s="20" t="s">
         <v>538</v>
       </c>
       <c r="D222" s="12"/>
@@ -19193,11 +20064,11 @@
       </c>
     </row>
     <row r="224" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A224" s="21" t="s">
+      <c r="A224" s="20" t="s">
         <v>541</v>
       </c>
       <c r="B224" s="12"/>
-      <c r="C224" s="21" t="s">
+      <c r="C224" s="20" t="s">
         <v>542</v>
       </c>
       <c r="D224" s="12"/>
@@ -19249,11 +20120,11 @@
       </c>
     </row>
     <row r="226" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A226" s="21" t="s">
+      <c r="A226" s="20" t="s">
         <v>545</v>
       </c>
       <c r="B226" s="12"/>
-      <c r="C226" s="21" t="s">
+      <c r="C226" s="20" t="s">
         <v>546</v>
       </c>
       <c r="D226" s="12"/>
@@ -19305,11 +20176,11 @@
       </c>
     </row>
     <row r="228" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A228" s="21" t="s">
+      <c r="A228" s="20" t="s">
         <v>549</v>
       </c>
       <c r="B228" s="12"/>
-      <c r="C228" s="21" t="s">
+      <c r="C228" s="20" t="s">
         <v>550</v>
       </c>
       <c r="D228" s="12"/>
@@ -19361,11 +20232,11 @@
       </c>
     </row>
     <row r="230" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A230" s="21" t="s">
+      <c r="A230" s="20" t="s">
         <v>553</v>
       </c>
       <c r="B230" s="12"/>
-      <c r="C230" s="21" t="s">
+      <c r="C230" s="20" t="s">
         <v>554</v>
       </c>
       <c r="D230" s="12"/>
@@ -19417,11 +20288,11 @@
       </c>
     </row>
     <row r="232" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A232" s="21" t="s">
+      <c r="A232" s="20" t="s">
         <v>557</v>
       </c>
       <c r="B232" s="12"/>
-      <c r="C232" s="21" t="s">
+      <c r="C232" s="20" t="s">
         <v>558</v>
       </c>
       <c r="D232" s="12"/>
@@ -19473,11 +20344,11 @@
       </c>
     </row>
     <row r="234" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A234" s="21" t="s">
+      <c r="A234" s="20" t="s">
         <v>561</v>
       </c>
       <c r="B234" s="12"/>
-      <c r="C234" s="21" t="s">
+      <c r="C234" s="20" t="s">
         <v>562</v>
       </c>
       <c r="D234" s="12"/>
@@ -19529,11 +20400,11 @@
       </c>
     </row>
     <row r="236" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A236" s="21" t="s">
+      <c r="A236" s="20" t="s">
         <v>565</v>
       </c>
       <c r="B236" s="12"/>
-      <c r="C236" s="21" t="s">
+      <c r="C236" s="20" t="s">
         <v>566</v>
       </c>
       <c r="D236" s="12"/>
@@ -19585,11 +20456,11 @@
       </c>
     </row>
     <row r="238" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A238" s="21" t="s">
+      <c r="A238" s="20" t="s">
         <v>569</v>
       </c>
       <c r="B238" s="12"/>
-      <c r="C238" s="21" t="s">
+      <c r="C238" s="20" t="s">
         <v>570</v>
       </c>
       <c r="D238" s="12"/>
@@ -19641,11 +20512,11 @@
       </c>
     </row>
     <row r="240" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A240" s="21" t="s">
+      <c r="A240" s="20" t="s">
         <v>573</v>
       </c>
       <c r="B240" s="12"/>
-      <c r="C240" s="21" t="s">
+      <c r="C240" s="20" t="s">
         <v>574</v>
       </c>
       <c r="D240" s="12"/>
@@ -19697,11 +20568,11 @@
       </c>
     </row>
     <row r="242" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A242" s="21" t="s">
+      <c r="A242" s="20" t="s">
         <v>577</v>
       </c>
       <c r="B242" s="12"/>
-      <c r="C242" s="21" t="s">
+      <c r="C242" s="20" t="s">
         <v>578</v>
       </c>
       <c r="D242" s="12"/>
@@ -19753,11 +20624,11 @@
       </c>
     </row>
     <row r="244" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A244" s="21" t="s">
+      <c r="A244" s="20" t="s">
         <v>581</v>
       </c>
       <c r="B244" s="12"/>
-      <c r="C244" s="21" t="s">
+      <c r="C244" s="20" t="s">
         <v>582</v>
       </c>
       <c r="D244" s="12"/>
@@ -19809,11 +20680,11 @@
       </c>
     </row>
     <row r="246" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A246" s="21" t="s">
+      <c r="A246" s="20" t="s">
         <v>585</v>
       </c>
       <c r="B246" s="12"/>
-      <c r="C246" s="21" t="s">
+      <c r="C246" s="20" t="s">
         <v>586</v>
       </c>
       <c r="D246" s="12"/>
@@ -19865,11 +20736,11 @@
       </c>
     </row>
     <row r="248" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A248" s="21" t="s">
+      <c r="A248" s="20" t="s">
         <v>589</v>
       </c>
       <c r="B248" s="12"/>
-      <c r="C248" s="21" t="s">
+      <c r="C248" s="20" t="s">
         <v>590</v>
       </c>
       <c r="D248" s="12"/>
@@ -19921,11 +20792,11 @@
       </c>
     </row>
     <row r="250" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A250" s="21" t="s">
+      <c r="A250" s="20" t="s">
         <v>593</v>
       </c>
       <c r="B250" s="12"/>
-      <c r="C250" s="21" t="s">
+      <c r="C250" s="20" t="s">
         <v>594</v>
       </c>
       <c r="D250" s="12"/>
@@ -19977,11 +20848,11 @@
       </c>
     </row>
     <row r="252" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A252" s="21" t="s">
+      <c r="A252" s="20" t="s">
         <v>597</v>
       </c>
       <c r="B252" s="12"/>
-      <c r="C252" s="21" t="s">
+      <c r="C252" s="20" t="s">
         <v>598</v>
       </c>
       <c r="D252" s="12"/>
@@ -21271,7 +22142,6 @@
   <hyperlinks>
     <hyperlink ref="I5" r:id="rId1" xr:uid="{CD8C0F40-5433-4BED-8652-01EFA1D6EB1A}"/>
     <hyperlink ref="K5" r:id="rId2" display="Reference the ISO 3166-2 country subdivision code English short name using the respective ISO standard" xr:uid="{53BD7A20-F111-403B-AF54-EC6ED1B2F4D8}"/>
-    <hyperlink ref="AI5" r:id="rId3" xr:uid="{3329A783-2A6D-4802-8F51-CF530039A047}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
